--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>Elimination Round 1</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>Player Dojo</t>
+  </si>
+  <si>
+    <t>Metadata</t>
   </si>
   <si>
     <t>Pool A</t>
@@ -514,7 +517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
@@ -570,44 +573,8 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
@@ -641,21 +608,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -876,8 +828,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="true"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="15"/>
-    <col customWidth="true" max="4" min="2" width="30"/>
-    <col customWidth="true" max="26" min="5" width="10.6640625"/>
+    <col customWidth="true" max="26" min="2" width="30"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="12.75" customHeight="true">
@@ -890,115 +841,118 @@
       <c r="C1" t="s">
         <v>13</v>
       </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="2" spans="1:2" ht="12.75" customHeight="true">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="12.75" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="12.75" customHeight="true">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="12.75" customHeight="true">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="12.75" customHeight="true">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="12.75" customHeight="true">
       <c r="A7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
         <v>23</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="12.75" customHeight="true">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="12.75" customHeight="true">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="12.75" customHeight="true">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="12.75" customHeight="true">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="12.75" customHeight="true">
@@ -2089,138 +2043,137 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
-      <c r="A2" s="40" t="str">
+      <c r="A2" s="28" t="str">
         <f>data!$A$5</f>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="41" t="str">
+      <c r="A3" s="29" t="str">
         <f>"1. " &amp; data!$B$2</f>
       </c>
-      <c r="E3" s="39" t="str">
+      <c r="E3" s="27" t="str">
         <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G81)</f>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="42" t="str">
+      <c r="A4" s="30" t="str">
         <f>"2. " &amp; data!$B$3</f>
       </c>
-      <c r="F4" s="38"/>
-      <c r="G4" s="36"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="24"/>
     </row>
     <row r="5">
-      <c r="A5" s="42" t="str">
+      <c r="A5" s="30" t="str">
         <f>"3. " &amp; data!$B$4</f>
       </c>
-      <c r="G5" s="37">
+      <c r="G5" s="25">
         <v>3</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="43" t="str">
+      <c r="A6" s="31" t="str">
         <f>"4. " &amp; data!$B$5</f>
       </c>
-      <c r="C6" s="39" t="str">
+      <c r="C6" s="27" t="str">
         <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G125)</f>
       </c>
-      <c r="G6" s="36"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="36"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="24"/>
     </row>
     <row r="7">
-      <c r="A7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="37">
+      <c r="A7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="25">
         <v>1</v>
       </c>
-      <c r="F7" s="29"/>
-      <c r="G7" s="36"/>
-      <c r="I7" s="36"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="24"/>
+      <c r="I7" s="24"/>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="str">
+      <c r="A8" s="28" t="str">
         <f>data!$A$8</f>
       </c>
-      <c r="C8" s="39" t="str">
+      <c r="C8" s="27" t="str">
         <f>CONCATENATE("Pool B.2 ",'Pool Matches'!O43)</f>
       </c>
-      <c r="D8" s="29"/>
-      <c r="E8" s="36"/>
-      <c r="I8" s="36"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="24"/>
+      <c r="I8" s="24"/>
     </row>
     <row r="9">
-      <c r="A9" s="41" t="str">
+      <c r="A9" s="29" t="str">
         <f>"1. " &amp; data!$B$6</f>
       </c>
-      <c r="I9" s="37">
+      <c r="I9" s="25">
         <v>5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="42" t="str">
+      <c r="A10" s="30" t="str">
         <f>"2. " &amp; data!$B$7</f>
       </c>
-      <c r="I10" s="36"/>
+      <c r="I10" s="24"/>
     </row>
     <row r="11">
-      <c r="A11" s="43" t="str">
+      <c r="A11" s="31" t="str">
         <f>"3. " &amp; data!$B$8</f>
       </c>
-      <c r="E11" s="39" t="str">
+      <c r="E11" s="27" t="str">
         <f>CONCATENATE("Pool B.1 ",'Pool Matches'!O42)</f>
       </c>
-      <c r="I11" s="36"/>
+      <c r="I11" s="24"/>
     </row>
     <row r="12">
-      <c r="A12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="36"/>
-      <c r="I12" s="36"/>
+      <c r="A12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="24"/>
+      <c r="I12" s="24"/>
     </row>
     <row r="13">
-      <c r="A13" s="40" t="str">
+      <c r="A13" s="28" t="str">
         <f>data!$A$11</f>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="25">
         <v>4</v>
       </c>
-      <c r="H13" s="29"/>
-      <c r="I13" s="36"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="24"/>
     </row>
     <row r="14">
-      <c r="A14" s="41" t="str">
+      <c r="A14" s="29" t="str">
         <f>"1. " &amp; data!$B$9</f>
       </c>
-      <c r="C14" s="39" t="str">
+      <c r="C14" s="27" t="str">
         <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G82)</f>
       </c>
-      <c r="G14" s="36"/>
+      <c r="G14" s="24"/>
     </row>
     <row r="15">
-      <c r="A15" s="42" t="str">
+      <c r="A15" s="30" t="str">
         <f>"2. " &amp; data!$B$10</f>
       </c>
-      <c r="D15" s="38"/>
-      <c r="E15" s="37">
+      <c r="D15" s="26"/>
+      <c r="E15" s="25">
         <v>2</v>
       </c>
-      <c r="F15" s="29"/>
-      <c r="G15" s="36"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="24"/>
     </row>
     <row r="16">
-      <c r="A16" s="43" t="str">
+      <c r="A16" s="31" t="str">
         <f>"3. " &amp; data!$B$11</f>
       </c>
-      <c r="C16" s="39" t="str">
+      <c r="C16" s="27" t="str">
         <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G126)</f>
       </c>
-      <c r="D16" s="29"/>
-      <c r="E16" s="36"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="24"/>
     </row>
     <row r="17">
-      <c r="A17" s="38"/>
+      <c r="A17" s="26"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
@@ -2234,53 +2187,53 @@
   <dimension ref="A1"/>
   <sheetData>
     <row r="1" ht="400" customHeight="true">
-      <c r="A1" s="46" t="s">
-        <v>42</v>
+      <c r="A1" s="34" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="2" ht="400" customHeight="true">
-      <c r="A2" s="46" t="s">
-        <v>43</v>
+      <c r="A2" s="34" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="3" ht="400" customHeight="true">
-      <c r="A3" s="46" t="s">
-        <v>44</v>
+      <c r="A3" s="34" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="4" ht="400" customHeight="true">
-      <c r="A4" s="46" t="s">
-        <v>45</v>
+      <c r="A4" s="34" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="5" ht="400" customHeight="true">
-      <c r="A5" s="46" t="s">
-        <v>46</v>
+      <c r="A5" s="34" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" ht="400" customHeight="true">
-      <c r="A6" s="46" t="s">
-        <v>47</v>
+      <c r="A6" s="34" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="7" ht="400" customHeight="true">
-      <c r="A7" s="46" t="s">
-        <v>48</v>
+      <c r="A7" s="34" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="8" ht="400" customHeight="true">
-      <c r="A8" s="46" t="s">
-        <v>49</v>
+      <c r="A8" s="34" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="9" ht="400" customHeight="true">
-      <c r="A9" s="46" t="s">
-        <v>50</v>
+      <c r="A9" s="34" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="10" ht="400" customHeight="true">
-      <c r="A10" s="46" t="s">
-        <v>51</v>
+      <c r="A10" s="34" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -2529,7 +2482,6 @@
     <col customWidth="true" max="26" min="11" width="8.83203125"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" spans="1:8" ht="20">
       <c r="A2" s="2"/>
       <c r="B2" s="15" t="s">
@@ -2641,9 +2593,6 @@
     <col max="16384" min="16" style="7" width="10.83203125"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="20" t="str">
         <f>data!$A$5</f>
@@ -2666,30 +2615,30 @@
     </row>
     <row r="5">
       <c r="A5" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="21"/>
       <c r="D5" s="21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
-      <c r="G5" s="23" t="s">
-        <v>34</v>
+      <c r="G5" t="s">
+        <v>35</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J5" s="21"/>
       <c r="K5" s="21"/>
       <c r="L5" s="21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M5" s="21"/>
       <c r="N5" s="21"/>
-      <c r="O5" s="30" t="s">
-        <v>34</v>
+      <c r="O5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -2836,23 +2785,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="21" t="str">
         <f>data!$B$2</f>
       </c>
       <c r="B13" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" s="21"/>
       <c r="E13" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="21" t="s">
         <v>36</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>35</v>
       </c>
       <c r="G13" s="21" t="str">
         <f>data!$B$3</f>
@@ -2861,17 +2809,17 @@
         <f>data!$B$6</f>
       </c>
       <c r="J13" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K13" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L13" s="21"/>
       <c r="M13" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="N13" s="21" t="s">
         <v>36</v>
-      </c>
-      <c r="N13" s="21" t="s">
-        <v>35</v>
       </c>
       <c r="O13" s="21" t="str">
         <f>data!$B$7</f>
@@ -2879,7 +2827,7 @@
     </row>
     <row r="14">
       <c r="A14" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
@@ -2887,10 +2835,10 @@
       <c r="E14" s="21"/>
       <c r="F14" s="21"/>
       <c r="G14" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21"/>
@@ -2898,38 +2846,35 @@
       <c r="M14" s="21"/>
       <c r="N14" s="21"/>
       <c r="O14" s="21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
+        <v>38</v>
+      </c>
+    </row>
     <row r="18">
       <c r="A18" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B18" s="21"/>
       <c r="C18" s="21"/>
       <c r="D18" s="21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E18" s="21"/>
       <c r="F18" s="21"/>
-      <c r="G18" s="24" t="s">
-        <v>34</v>
+      <c r="G18" t="s">
+        <v>35</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J18" s="21"/>
       <c r="K18" s="21"/>
       <c r="L18" s="21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M18" s="21"/>
       <c r="N18" s="21"/>
-      <c r="O18" s="31" t="s">
-        <v>34</v>
+      <c r="O18" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="19">
@@ -3076,23 +3021,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="21" t="str">
         <f>data!$B$4</f>
       </c>
       <c r="B26" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D26" s="21"/>
       <c r="E26" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F26" s="21" t="s">
         <v>36</v>
-      </c>
-      <c r="F26" s="21" t="s">
-        <v>35</v>
       </c>
       <c r="G26" s="21" t="str">
         <f>data!$B$3</f>
@@ -3101,17 +3045,17 @@
         <f>data!$B$8</f>
       </c>
       <c r="J26" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K26" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L26" s="21"/>
       <c r="M26" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="N26" s="21" t="s">
         <v>36</v>
-      </c>
-      <c r="N26" s="21" t="s">
-        <v>35</v>
       </c>
       <c r="O26" s="21" t="str">
         <f>data!$B$7</f>
@@ -3119,7 +3063,7 @@
     </row>
     <row r="27">
       <c r="A27" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
@@ -3127,10 +3071,10 @@
       <c r="E27" s="21"/>
       <c r="F27" s="21"/>
       <c r="G27" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J27" s="21"/>
       <c r="K27" s="21"/>
@@ -3138,38 +3082,35 @@
       <c r="M27" s="21"/>
       <c r="N27" s="21"/>
       <c r="O27" s="21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
+        <v>38</v>
+      </c>
+    </row>
     <row r="31">
       <c r="A31" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31" s="21"/>
       <c r="C31" s="21"/>
       <c r="D31" s="21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E31" s="21"/>
       <c r="F31" s="21"/>
-      <c r="G31" s="25" t="s">
-        <v>34</v>
+      <c r="G31" t="s">
+        <v>35</v>
       </c>
       <c r="I31" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J31" s="21"/>
       <c r="K31" s="21"/>
       <c r="L31" s="21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M31" s="21"/>
       <c r="N31" s="21"/>
-      <c r="O31" s="32" t="s">
-        <v>34</v>
+      <c r="O31" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="32">
@@ -3316,23 +3257,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="21" t="str">
         <f>data!$B$4</f>
       </c>
       <c r="B39" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D39" s="21"/>
       <c r="E39" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F39" s="21" t="s">
         <v>36</v>
-      </c>
-      <c r="F39" s="21" t="s">
-        <v>35</v>
       </c>
       <c r="G39" s="21" t="str">
         <f>data!$B$5</f>
@@ -3341,17 +3281,17 @@
         <f>data!$B$8</f>
       </c>
       <c r="J39" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K39" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L39" s="21"/>
       <c r="M39" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="N39" s="21" t="s">
         <v>36</v>
-      </c>
-      <c r="N39" s="21" t="s">
-        <v>35</v>
       </c>
       <c r="O39" s="21" t="str">
         <f>data!$B$6</f>
@@ -3359,7 +3299,7 @@
     </row>
     <row r="40">
       <c r="A40" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B40" s="21"/>
       <c r="C40" s="21"/>
@@ -3367,10 +3307,10 @@
       <c r="E40" s="21"/>
       <c r="F40" s="21"/>
       <c r="G40" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I40" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J40" s="21"/>
       <c r="K40" s="21"/>
@@ -3378,40 +3318,39 @@
       <c r="M40" s="21"/>
       <c r="N40" s="21"/>
       <c r="O40" s="21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="41"/>
+        <v>38</v>
+      </c>
+    </row>
     <row r="42">
       <c r="N42" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="O42" s="29"/>
+        <v>39</v>
+      </c>
+      <c r="O42" s="23"/>
     </row>
     <row r="43">
       <c r="N43" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="O43" s="29"/>
+        <v>40</v>
+      </c>
+      <c r="O43" s="23"/>
     </row>
     <row r="44">
       <c r="A44" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
       <c r="D44" s="21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E44" s="21"/>
       <c r="F44" s="21"/>
-      <c r="G44" s="26" t="s">
-        <v>34</v>
+      <c r="G44" t="s">
+        <v>35</v>
       </c>
       <c r="N44" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="O44" s="29"/>
+        <v>41</v>
+      </c>
+      <c r="O44" s="23"/>
     </row>
     <row r="45">
       <c r="A45" s="21" t="str">
@@ -3491,23 +3430,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51"/>
     <row r="52">
       <c r="A52" s="21" t="str">
         <f>data!$B$3</f>
       </c>
       <c r="B52" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D52" s="21"/>
       <c r="E52" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F52" s="21" t="s">
         <v>36</v>
-      </c>
-      <c r="F52" s="21" t="s">
-        <v>35</v>
       </c>
       <c r="G52" s="21" t="str">
         <f>data!$B$5</f>
@@ -3515,7 +3453,7 @@
     </row>
     <row r="53">
       <c r="A53" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B53" s="21"/>
       <c r="C53" s="21"/>
@@ -3523,25 +3461,22 @@
       <c r="E53" s="21"/>
       <c r="F53" s="21"/>
       <c r="G53" s="21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
+        <v>38</v>
+      </c>
+    </row>
     <row r="57">
       <c r="A57" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B57" s="21"/>
       <c r="C57" s="21"/>
       <c r="D57" s="21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E57" s="21"/>
       <c r="F57" s="21"/>
-      <c r="G57" s="27" t="s">
-        <v>34</v>
+      <c r="G57" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="58">
@@ -3622,23 +3557,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="21" t="str">
         <f>data!$B$2</f>
       </c>
       <c r="B65" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D65" s="21"/>
       <c r="E65" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F65" s="21" t="s">
         <v>36</v>
-      </c>
-      <c r="F65" s="21" t="s">
-        <v>35</v>
       </c>
       <c r="G65" s="21" t="str">
         <f>data!$B$4</f>
@@ -3646,7 +3580,7 @@
     </row>
     <row r="66">
       <c r="A66" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B66" s="21"/>
       <c r="C66" s="21"/>
@@ -3654,25 +3588,22 @@
       <c r="E66" s="21"/>
       <c r="F66" s="21"/>
       <c r="G66" s="21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
+        <v>38</v>
+      </c>
+    </row>
     <row r="70">
       <c r="A70" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B70" s="21"/>
       <c r="C70" s="21"/>
       <c r="D70" s="21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E70" s="21"/>
       <c r="F70" s="21"/>
-      <c r="G70" s="28" t="s">
-        <v>34</v>
+      <c r="G70" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="71">
@@ -3753,23 +3684,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77"/>
     <row r="78">
       <c r="A78" s="21" t="str">
         <f>data!$B$2</f>
       </c>
       <c r="B78" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D78" s="21"/>
       <c r="E78" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F78" s="21" t="s">
         <v>36</v>
-      </c>
-      <c r="F78" s="21" t="s">
-        <v>35</v>
       </c>
       <c r="G78" s="21" t="str">
         <f>data!$B$5</f>
@@ -3777,7 +3707,7 @@
     </row>
     <row r="79">
       <c r="A79" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B79" s="21"/>
       <c r="C79" s="21"/>
@@ -3785,36 +3715,33 @@
       <c r="E79" s="21"/>
       <c r="F79" s="21"/>
       <c r="G79" s="21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="80"/>
+        <v>38</v>
+      </c>
+    </row>
     <row r="81">
       <c r="F81" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G81" s="29"/>
+        <v>39</v>
+      </c>
+      <c r="G81" s="23"/>
     </row>
     <row r="82">
       <c r="F82" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G82" s="29"/>
+        <v>40</v>
+      </c>
+      <c r="G82" s="23"/>
     </row>
     <row r="83">
       <c r="F83" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G83" s="29"/>
+        <v>41</v>
+      </c>
+      <c r="G83" s="23"/>
     </row>
     <row r="84">
       <c r="F84" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G84" s="29"/>
-    </row>
-    <row r="85"/>
-    <row r="86"/>
+        <v>42</v>
+      </c>
+      <c r="G84" s="23"/>
+    </row>
     <row r="87">
       <c r="A87" s="20" t="str">
         <f>data!$A$11</f>
@@ -3828,17 +3755,17 @@
     </row>
     <row r="88">
       <c r="A88" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B88" s="21"/>
       <c r="C88" s="21"/>
       <c r="D88" s="21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E88" s="21"/>
       <c r="F88" s="21"/>
-      <c r="G88" s="33" t="s">
-        <v>34</v>
+      <c r="G88" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="89">
@@ -3919,23 +3846,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95"/>
     <row r="96">
       <c r="A96" s="21" t="str">
         <f>data!$B$9</f>
       </c>
       <c r="B96" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D96" s="21"/>
       <c r="E96" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F96" s="21" t="s">
         <v>36</v>
-      </c>
-      <c r="F96" s="21" t="s">
-        <v>35</v>
       </c>
       <c r="G96" s="21" t="str">
         <f>data!$B$10</f>
@@ -3943,7 +3869,7 @@
     </row>
     <row r="97">
       <c r="A97" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B97" s="21"/>
       <c r="C97" s="21"/>
@@ -3951,25 +3877,22 @@
       <c r="E97" s="21"/>
       <c r="F97" s="21"/>
       <c r="G97" s="21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
+        <v>38</v>
+      </c>
+    </row>
     <row r="101">
       <c r="A101" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B101" s="21"/>
       <c r="C101" s="21"/>
       <c r="D101" s="21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E101" s="21"/>
       <c r="F101" s="21"/>
-      <c r="G101" s="34" t="s">
-        <v>34</v>
+      <c r="G101" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="102">
@@ -4050,23 +3973,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108"/>
     <row r="109">
       <c r="A109" s="21" t="str">
         <f>data!$B$11</f>
       </c>
       <c r="B109" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C109" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D109" s="21"/>
       <c r="E109" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F109" s="21" t="s">
         <v>36</v>
-      </c>
-      <c r="F109" s="21" t="s">
-        <v>35</v>
       </c>
       <c r="G109" s="21" t="str">
         <f>data!$B$10</f>
@@ -4074,7 +3996,7 @@
     </row>
     <row r="110">
       <c r="A110" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B110" s="21"/>
       <c r="C110" s="21"/>
@@ -4082,25 +4004,22 @@
       <c r="E110" s="21"/>
       <c r="F110" s="21"/>
       <c r="G110" s="21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
+        <v>38</v>
+      </c>
+    </row>
     <row r="114">
       <c r="A114" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B114" s="21"/>
       <c r="C114" s="21"/>
       <c r="D114" s="21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E114" s="21"/>
       <c r="F114" s="21"/>
-      <c r="G114" s="35" t="s">
-        <v>34</v>
+      <c r="G114" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="115">
@@ -4181,23 +4100,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121"/>
     <row r="122">
       <c r="A122" s="21" t="str">
         <f>data!$B$11</f>
       </c>
       <c r="B122" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C122" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D122" s="21"/>
       <c r="E122" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F122" s="21" t="s">
         <v>36</v>
-      </c>
-      <c r="F122" s="21" t="s">
-        <v>35</v>
       </c>
       <c r="G122" s="21" t="str">
         <f>data!$B$9</f>
@@ -4205,7 +4123,7 @@
     </row>
     <row r="123">
       <c r="A123" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B123" s="21"/>
       <c r="C123" s="21"/>
@@ -4213,27 +4131,26 @@
       <c r="E123" s="21"/>
       <c r="F123" s="21"/>
       <c r="G123" s="21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="124"/>
+        <v>38</v>
+      </c>
+    </row>
     <row r="125">
       <c r="F125" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G125" s="29"/>
+        <v>39</v>
+      </c>
+      <c r="G125" s="23"/>
     </row>
     <row r="126">
       <c r="F126" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G126" s="29"/>
+        <v>40</v>
+      </c>
+      <c r="G126" s="23"/>
     </row>
     <row r="127">
       <c r="F127" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G127" s="29"/>
+        <v>41</v>
+      </c>
+      <c r="G127" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4283,10 +4200,9 @@
       <c r="N1" s="20"/>
       <c r="O1" s="20"/>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3" s="20"/>
       <c r="C3" s="20"/>
@@ -4295,7 +4211,7 @@
       <c r="F3" s="20"/>
       <c r="G3" s="20"/>
       <c r="I3" s="20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J3" s="20"/>
       <c r="K3" s="20"/>
@@ -4306,22 +4222,22 @@
     </row>
     <row r="4">
       <c r="A4" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="47" t="s">
+      <c r="L4" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="L4" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="O4" s="48" t="s">
-        <v>34</v>
+      <c r="O4" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="5">
@@ -4468,23 +4384,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="21" t="str">
         <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G125)</f>
       </c>
       <c r="B12" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D12" s="21"/>
       <c r="E12" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="21" t="s">
         <v>36</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>35</v>
       </c>
       <c r="G12" s="21" t="str">
         <f>CONCATENATE("Pool B.2 ",'Pool Matches'!O43)</f>
@@ -4493,17 +4408,17 @@
         <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G82)</f>
       </c>
       <c r="J12" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K12" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L12" s="21"/>
       <c r="M12" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="N12" s="21" t="s">
         <v>36</v>
-      </c>
-      <c r="N12" s="21" t="s">
-        <v>35</v>
       </c>
       <c r="O12" s="21" t="str">
         <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G126)</f>
@@ -4511,7 +4426,7 @@
     </row>
     <row r="13">
       <c r="A13" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
@@ -4519,10 +4434,10 @@
       <c r="E13" s="21"/>
       <c r="F13" s="21"/>
       <c r="G13" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I13" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21"/>
@@ -4530,40 +4445,32 @@
       <c r="M13" s="21"/>
       <c r="N13" s="21"/>
       <c r="O13" s="21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14"/>
+        <v>38</v>
+      </c>
+    </row>
     <row r="15">
       <c r="F15" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="29"/>
+        <v>54</v>
+      </c>
+      <c r="G15" s="23"/>
       <c r="N15" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="O15" s="29"/>
+        <v>54</v>
+      </c>
+      <c r="O15" s="23"/>
     </row>
     <row r="16">
       <c r="F16" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16" s="29"/>
+        <v>55</v>
+      </c>
+      <c r="G16" s="23"/>
       <c r="N16" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="O16" s="29"/>
-    </row>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
+        <v>55</v>
+      </c>
+      <c r="O16" s="23"/>
+    </row>
     <row r="24">
       <c r="A24" s="20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B24" s="20"/>
       <c r="C24" s="20"/>
@@ -4580,10 +4487,9 @@
       <c r="N24" s="20"/>
       <c r="O24" s="20"/>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -4592,7 +4498,7 @@
       <c r="F26" s="20"/>
       <c r="G26" s="20"/>
       <c r="I26" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J26" s="20"/>
       <c r="K26" s="20"/>
@@ -4603,22 +4509,22 @@
     </row>
     <row r="27">
       <c r="A27" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D27" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="G27" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="G27" s="49" t="s">
+      <c r="L27" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="I27" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="L27" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="O27" s="50" t="s">
-        <v>34</v>
+      <c r="O27" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="28">
@@ -4765,23 +4671,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="21" t="str">
         <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G81)</f>
       </c>
       <c r="B35" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D35" s="21"/>
       <c r="E35" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F35" s="21" t="s">
         <v>36</v>
-      </c>
-      <c r="F35" s="21" t="s">
-        <v>35</v>
       </c>
       <c r="G35" s="21" t="str">
         <f>CONCATENATE("M 1 ",'Elimination Matches'!G15)</f>
@@ -4790,17 +4695,17 @@
         <f>CONCATENATE("Pool B.1 ",'Pool Matches'!O42)</f>
       </c>
       <c r="J35" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K35" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L35" s="21"/>
       <c r="M35" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="N35" s="21" t="s">
         <v>36</v>
-      </c>
-      <c r="N35" s="21" t="s">
-        <v>35</v>
       </c>
       <c r="O35" s="21" t="str">
         <f>CONCATENATE("M 2 ",'Elimination Matches'!O15)</f>
@@ -4808,7 +4713,7 @@
     </row>
     <row r="36">
       <c r="A36" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36" s="21"/>
       <c r="C36" s="21"/>
@@ -4816,10 +4721,10 @@
       <c r="E36" s="21"/>
       <c r="F36" s="21"/>
       <c r="G36" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I36" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J36" s="21"/>
       <c r="K36" s="21"/>
@@ -4827,40 +4732,32 @@
       <c r="M36" s="21"/>
       <c r="N36" s="21"/>
       <c r="O36" s="21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37"/>
+        <v>38</v>
+      </c>
+    </row>
     <row r="38">
       <c r="F38" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G38" s="29"/>
+        <v>54</v>
+      </c>
+      <c r="G38" s="23"/>
       <c r="N38" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="O38" s="29"/>
+        <v>54</v>
+      </c>
+      <c r="O38" s="23"/>
     </row>
     <row r="39">
       <c r="F39" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G39" s="29"/>
+        <v>55</v>
+      </c>
+      <c r="G39" s="23"/>
       <c r="N39" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="O39" s="29"/>
-    </row>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
+        <v>55</v>
+      </c>
+      <c r="O39" s="23"/>
+    </row>
     <row r="47">
       <c r="A47" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B47" s="20"/>
       <c r="C47" s="20"/>
@@ -4877,10 +4774,9 @@
       <c r="N47" s="20"/>
       <c r="O47" s="20"/>
     </row>
-    <row r="48"/>
     <row r="49">
       <c r="A49" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B49" s="20"/>
       <c r="C49" s="20"/>
@@ -4891,13 +4787,13 @@
     </row>
     <row r="50">
       <c r="A50" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="G50" s="51" t="s">
         <v>34</v>
+      </c>
+      <c r="G50" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="51">
@@ -4978,23 +4874,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57"/>
     <row r="58">
       <c r="A58" s="21" t="str">
         <f>CONCATENATE("M 3 ",'Elimination Matches'!G38)</f>
       </c>
       <c r="B58" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D58" s="21"/>
       <c r="E58" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F58" s="21" t="s">
         <v>36</v>
-      </c>
-      <c r="F58" s="21" t="s">
-        <v>35</v>
       </c>
       <c r="G58" s="21" t="str">
         <f>CONCATENATE("M 4 ",'Elimination Matches'!O38)</f>
@@ -5002,7 +4897,7 @@
     </row>
     <row r="59">
       <c r="A59" s="21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B59" s="21"/>
       <c r="C59" s="21"/>
@@ -5010,21 +4905,20 @@
       <c r="E59" s="21"/>
       <c r="F59" s="21"/>
       <c r="G59" s="21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="60"/>
+        <v>38</v>
+      </c>
+    </row>
     <row r="61">
       <c r="F61" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G61" s="29"/>
+        <v>54</v>
+      </c>
+      <c r="G61" s="23"/>
     </row>
     <row r="62">
       <c r="F62" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G62" s="29"/>
+        <v>55</v>
+      </c>
+      <c r="G62" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -5055,144 +4949,144 @@
   </cols>
   <sheetData>
     <row r="1" ht="110" customHeight="true">
-      <c r="A1" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="45" t="str">
+      <c r="A1" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="33" t="str">
         <f>data!$B$2</f>
       </c>
     </row>
     <row r="2" ht="115" customHeight="true">
-      <c r="A2" s="44">
+      <c r="A2" s="32">
         <v>1</v>
       </c>
-      <c r="B2" s="45"/>
+      <c r="B2" s="33"/>
     </row>
     <row r="3" ht="110" customHeight="true">
-      <c r="A3" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="45" t="str">
+      <c r="A3" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="33" t="str">
         <f>data!$B$3</f>
       </c>
     </row>
     <row r="4" ht="115" customHeight="true">
-      <c r="A4" s="44">
+      <c r="A4" s="32">
         <v>2</v>
       </c>
-      <c r="B4" s="45"/>
+      <c r="B4" s="33"/>
     </row>
     <row r="5" ht="110" customHeight="true">
-      <c r="A5" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="45" t="str">
+      <c r="A5" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="33" t="str">
         <f>data!$B$4</f>
       </c>
     </row>
     <row r="6" ht="115" customHeight="true">
-      <c r="A6" s="44">
+      <c r="A6" s="32">
         <v>3</v>
       </c>
-      <c r="B6" s="45"/>
+      <c r="B6" s="33"/>
     </row>
     <row r="7" ht="110" customHeight="true">
-      <c r="A7" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="45" t="str">
+      <c r="A7" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="33" t="str">
         <f>data!$B$5</f>
       </c>
     </row>
     <row r="8" ht="115" customHeight="true">
-      <c r="A8" s="44">
+      <c r="A8" s="32">
         <v>4</v>
       </c>
-      <c r="B8" s="45"/>
+      <c r="B8" s="33"/>
     </row>
     <row r="9" ht="110" customHeight="true">
-      <c r="A9" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="45" t="str">
+      <c r="A9" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="33" t="str">
         <f>data!$B$6</f>
       </c>
     </row>
     <row r="10" ht="115" customHeight="true">
-      <c r="A10" s="44">
+      <c r="A10" s="32">
         <v>1</v>
       </c>
-      <c r="B10" s="45"/>
+      <c r="B10" s="33"/>
     </row>
     <row r="11" ht="110" customHeight="true">
-      <c r="A11" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="45" t="str">
+      <c r="A11" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="33" t="str">
         <f>data!$B$7</f>
       </c>
     </row>
     <row r="12" ht="115" customHeight="true">
-      <c r="A12" s="44">
+      <c r="A12" s="32">
         <v>2</v>
       </c>
-      <c r="B12" s="45"/>
+      <c r="B12" s="33"/>
     </row>
     <row r="13" ht="110" customHeight="true">
-      <c r="A13" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="45" t="str">
+      <c r="A13" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="33" t="str">
         <f>data!$B$8</f>
       </c>
     </row>
     <row r="14" ht="115" customHeight="true">
-      <c r="A14" s="44">
+      <c r="A14" s="32">
         <v>3</v>
       </c>
-      <c r="B14" s="45"/>
+      <c r="B14" s="33"/>
     </row>
     <row r="15" ht="110" customHeight="true">
-      <c r="A15" s="44" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="45" t="str">
+      <c r="A15" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="33" t="str">
         <f>data!$B$9</f>
       </c>
     </row>
     <row r="16" ht="115" customHeight="true">
-      <c r="A16" s="44">
+      <c r="A16" s="32">
         <v>1</v>
       </c>
-      <c r="B16" s="45"/>
+      <c r="B16" s="33"/>
     </row>
     <row r="17" ht="110" customHeight="true">
-      <c r="A17" s="44" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="45" t="str">
+      <c r="A17" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="33" t="str">
         <f>data!$B$10</f>
       </c>
     </row>
     <row r="18" ht="115" customHeight="true">
-      <c r="A18" s="44">
+      <c r="A18" s="32">
         <v>2</v>
       </c>
-      <c r="B18" s="45"/>
+      <c r="B18" s="33"/>
     </row>
     <row r="19" ht="110" customHeight="true">
-      <c r="A19" s="44" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="45" t="str">
+      <c r="A19" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="33" t="str">
         <f>data!$B$11</f>
       </c>
     </row>
     <row r="20" ht="115" customHeight="true">
-      <c r="A20" s="44">
+      <c r="A20" s="32">
         <v>3</v>
       </c>
-      <c r="B20" s="45"/>
+      <c r="B20" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -2890,7 +2890,7 @@
         <f>data!$B$3</f>
       </c>
       <c r="I19" s="21" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$6</f>
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21"/>
@@ -2898,7 +2898,7 @@
       <c r="M19" s="21"/>
       <c r="N19" s="21"/>
       <c r="O19" s="21" t="str">
-        <f>data!$B$7</f>
+        <f>data!$B$8</f>
       </c>
     </row>
     <row r="20">
@@ -3042,7 +3042,7 @@
         <f>data!$B$3</f>
       </c>
       <c r="I26" s="21" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$6</f>
       </c>
       <c r="J26" s="21" t="s">
         <v>36</v>
@@ -3058,7 +3058,7 @@
         <v>36</v>
       </c>
       <c r="O26" s="21" t="str">
-        <f>data!$B$7</f>
+        <f>data!$B$8</f>
       </c>
     </row>
     <row r="27">
@@ -3126,7 +3126,7 @@
         <f>data!$B$5</f>
       </c>
       <c r="I32" s="21" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$7</f>
       </c>
       <c r="J32" s="21"/>
       <c r="K32" s="21"/>
@@ -3134,7 +3134,7 @@
       <c r="M32" s="21"/>
       <c r="N32" s="21"/>
       <c r="O32" s="21" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$8</f>
       </c>
     </row>
     <row r="33">
@@ -3278,7 +3278,7 @@
         <f>data!$B$5</f>
       </c>
       <c r="I39" s="21" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$7</f>
       </c>
       <c r="J39" s="21" t="s">
         <v>36</v>
@@ -3294,7 +3294,7 @@
         <v>36</v>
       </c>
       <c r="O39" s="21" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$8</f>
       </c>
     </row>
     <row r="40">
@@ -3354,7 +3354,7 @@
     </row>
     <row r="45">
       <c r="A45" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$2</f>
       </c>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="52">
       <c r="A52" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$2</f>
       </c>
       <c r="B52" s="21" t="s">
         <v>36</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="71">
       <c r="A71" s="21" t="str">
-        <f>data!$B$2</f>
+        <f>data!$B$3</f>
       </c>
       <c r="B71" s="21"/>
       <c r="C71" s="21"/>
@@ -3686,7 +3686,7 @@
     </row>
     <row r="78">
       <c r="A78" s="21" t="str">
-        <f>data!$B$2</f>
+        <f>data!$B$3</f>
       </c>
       <c r="B78" s="21" t="s">
         <v>36</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="102">
       <c r="A102" s="21" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$9</f>
       </c>
       <c r="B102" s="21"/>
       <c r="C102" s="21"/>
@@ -3905,7 +3905,7 @@
       <c r="E102" s="21"/>
       <c r="F102" s="21"/>
       <c r="G102" s="21" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$11</f>
       </c>
     </row>
     <row r="103">
@@ -3975,7 +3975,7 @@
     </row>
     <row r="109">
       <c r="A109" s="21" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$9</f>
       </c>
       <c r="B109" s="21" t="s">
         <v>36</v>
@@ -3991,7 +3991,7 @@
         <v>36</v>
       </c>
       <c r="G109" s="21" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$11</f>
       </c>
     </row>
     <row r="110">
@@ -4024,7 +4024,7 @@
     </row>
     <row r="115">
       <c r="A115" s="21" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$10</f>
       </c>
       <c r="B115" s="21"/>
       <c r="C115" s="21"/>
@@ -4032,7 +4032,7 @@
       <c r="E115" s="21"/>
       <c r="F115" s="21"/>
       <c r="G115" s="21" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$11</f>
       </c>
     </row>
     <row r="116">
@@ -4102,7 +4102,7 @@
     </row>
     <row r="122">
       <c r="A122" s="21" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$10</f>
       </c>
       <c r="B122" s="21" t="s">
         <v>36</v>
@@ -4118,7 +4118,7 @@
         <v>36</v>
       </c>
       <c r="G122" s="21" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$11</f>
       </c>
     </row>
     <row r="123">

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -21,7 +21,9 @@
     <sheet name="Tree 1" sheetId="10" r:id="rId13"/>
     <sheet name="Tags" sheetId="11" r:id="rId14"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName localSheetId="5" name="_xlnm.Print_Area">'Names to Print'!$A$1:$B$20</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -99,46 +101,46 @@
     <t>Team Alpha</t>
   </si>
   <si>
+    <t>Nathan Lee</t>
+  </si>
+  <si>
+    <t>Team Delta</t>
+  </si>
+  <si>
+    <t>Quentin Allen</t>
+  </si>
+  <si>
+    <t>Team Beta</t>
+  </si>
+  <si>
+    <t>Thomas King</t>
+  </si>
+  <si>
+    <t>Team Epsilon</t>
+  </si>
+  <si>
+    <t>Pool B</t>
+  </si>
+  <si>
     <t>Luke Rodriguez</t>
   </si>
   <si>
-    <t>Team Beta</t>
+    <t>Oliver Walker</t>
+  </si>
+  <si>
+    <t>Robert Young</t>
+  </si>
+  <si>
+    <t>Team Gamma</t>
+  </si>
+  <si>
+    <t>Pool C</t>
   </si>
   <si>
     <t>Michael Lewis</t>
   </si>
   <si>
-    <t>Team Gamma</t>
-  </si>
-  <si>
-    <t>Thomas King</t>
-  </si>
-  <si>
-    <t>Team Epsilon</t>
-  </si>
-  <si>
-    <t>Pool B</t>
-  </si>
-  <si>
-    <t>Nathan Lee</t>
-  </si>
-  <si>
-    <t>Team Delta</t>
-  </si>
-  <si>
-    <t>Oliver Walker</t>
-  </si>
-  <si>
     <t>Paul Hall</t>
-  </si>
-  <si>
-    <t>Pool C</t>
-  </si>
-  <si>
-    <t>Quentin Allen</t>
-  </si>
-  <si>
-    <t>Robert Young</t>
   </si>
   <si>
     <t>Steven Hernandez</t>
@@ -353,7 +355,7 @@
       <sz val="150"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -369,6 +371,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -517,7 +524,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
@@ -570,11 +577,14 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="true" applyAlignment="false">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="true" applyAlignment="false">
-      <alignment/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
@@ -897,7 +907,7 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="12.75" customHeight="true">
@@ -905,7 +915,7 @@
         <v>24</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
@@ -916,10 +926,10 @@
         <v>24</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
         <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="12.75" customHeight="true">
@@ -930,7 +940,7 @@
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="12.75" customHeight="true">
@@ -941,7 +951,7 @@
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="12.75" customHeight="true">
@@ -952,7 +962,7 @@
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="12.75" customHeight="true">
@@ -2043,212 +2053,211 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="A2" s="28" t="str">
+    <row r="4">
+      <c r="A4" s="29" t="str">
         <f>data!$A$5</f>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="29" t="str">
-        <f>"1. " &amp; data!$B$2</f>
-      </c>
-      <c r="E3" s="27" t="str">
-        <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G81)</f>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="30" t="str">
-        <f>"2. " &amp; data!$B$3</f>
-      </c>
-      <c r="F4" s="26"/>
-      <c r="G4" s="24"/>
     </row>
     <row r="5">
       <c r="A5" s="30" t="str">
-        <f>"3. " &amp; data!$B$4</f>
-      </c>
-      <c r="G5" s="25">
-        <v>3</v>
+        <f>"1. " &amp; data!$B$2</f>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="31" t="str">
+        <f>"2. " &amp; data!$B$3</f>
+      </c>
+      <c r="E6" s="28" t="str">
+        <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G81)</f>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="str">
+        <f>"3. " &amp; data!$B$4</f>
+      </c>
+      <c r="F7" s="27"/>
+      <c r="G7" s="25"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="32" t="str">
         <f>"4. " &amp; data!$B$5</f>
       </c>
-      <c r="C6" s="27" t="str">
+      <c r="G8" s="26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="27"/>
+      <c r="C9" s="28" t="str">
         <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G125)</f>
       </c>
-      <c r="G6" s="24"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="24"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="25">
+      <c r="G9" s="25"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="25"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="str">
+        <f>data!$A$8</f>
+      </c>
+      <c r="D10" s="27"/>
+      <c r="E10" s="26">
         <v>1</v>
       </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="24"/>
-      <c r="I7" s="24"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="28" t="str">
-        <f>data!$A$8</f>
-      </c>
-      <c r="C8" s="27" t="str">
+      <c r="F10" s="22"/>
+      <c r="G10" s="25"/>
+      <c r="I10" s="25"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="30" t="str">
+        <f>"1. " &amp; data!$B$6</f>
+      </c>
+      <c r="C11" s="28" t="str">
         <f>CONCATENATE("Pool B.2 ",'Pool Matches'!O43)</f>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="24"/>
-      <c r="I8" s="24"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="29" t="str">
-        <f>"1. " &amp; data!$B$6</f>
-      </c>
-      <c r="I9" s="25">
+      <c r="D11" s="22"/>
+      <c r="E11" s="25"/>
+      <c r="I11" s="25"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="str">
+        <f>"2. " &amp; data!$B$7</f>
+      </c>
+      <c r="I12" s="26">
         <v>5</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="30" t="str">
-        <f>"2. " &amp; data!$B$7</f>
-      </c>
-      <c r="I10" s="24"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="31" t="str">
+    <row r="13">
+      <c r="A13" s="32" t="str">
         <f>"3. " &amp; data!$B$8</f>
       </c>
-      <c r="E11" s="27" t="str">
+      <c r="I13" s="25"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="27"/>
+      <c r="E14" s="28" t="str">
         <f>CONCATENATE("Pool B.1 ",'Pool Matches'!O42)</f>
       </c>
-      <c r="I11" s="24"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="24"/>
-      <c r="I12" s="24"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="28" t="str">
+      <c r="I14" s="25"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="str">
         <f>data!$A$11</f>
       </c>
-      <c r="G13" s="25">
+      <c r="F15" s="27"/>
+      <c r="G15" s="25"/>
+      <c r="I15" s="25"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="str">
+        <f>"1. " &amp; data!$B$9</f>
+      </c>
+      <c r="G16" s="26">
         <v>4</v>
       </c>
-      <c r="H13" s="23"/>
-      <c r="I13" s="24"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="29" t="str">
-        <f>"1. " &amp; data!$B$9</f>
-      </c>
-      <c r="C14" s="27" t="str">
+      <c r="H16" s="22"/>
+      <c r="I16" s="25"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="str">
+        <f>"2. " &amp; data!$B$10</f>
+      </c>
+      <c r="C17" s="28" t="str">
         <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G82)</f>
       </c>
-      <c r="G14" s="24"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="30" t="str">
-        <f>"2. " &amp; data!$B$10</f>
-      </c>
-      <c r="D15" s="26"/>
-      <c r="E15" s="25">
+      <c r="G17" s="25"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="32" t="str">
+        <f>"3. " &amp; data!$B$11</f>
+      </c>
+      <c r="D18" s="27"/>
+      <c r="E18" s="26">
         <v>2</v>
       </c>
-      <c r="F15" s="23"/>
-      <c r="G15" s="24"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="31" t="str">
-        <f>"3. " &amp; data!$B$11</f>
-      </c>
-      <c r="C16" s="27" t="str">
+      <c r="F18" s="22"/>
+      <c r="G18" s="25"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="27"/>
+      <c r="C19" s="28" t="str">
         <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G126)</f>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="24"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="26"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="25"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageMargins left="0.25" right="0.25" top="0" bottom="0" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="90"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="400" customHeight="true">
-      <c r="A1" s="34" t="s">
+    <row r="1" ht="390" customHeight="true">
+      <c r="A1" s="35" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" ht="400" customHeight="true">
-      <c r="A2" s="34" t="s">
+    <row r="2" ht="390" customHeight="true">
+      <c r="A2" s="35" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" ht="400" customHeight="true">
-      <c r="A3" s="34" t="s">
+    <row r="3" ht="390" customHeight="true">
+      <c r="A3" s="35" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" ht="400" customHeight="true">
-      <c r="A4" s="34" t="s">
+    <row r="4" ht="390" customHeight="true">
+      <c r="A4" s="35" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="5" ht="400" customHeight="true">
-      <c r="A5" s="34" t="s">
+    <row r="5" ht="390" customHeight="true">
+      <c r="A5" s="35" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6" ht="400" customHeight="true">
-      <c r="A6" s="34" t="s">
+    <row r="6" ht="390" customHeight="true">
+      <c r="A6" s="35" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="7" ht="400" customHeight="true">
-      <c r="A7" s="34" t="s">
+    <row r="7" ht="390" customHeight="true">
+      <c r="A7" s="35" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="8" ht="400" customHeight="true">
-      <c r="A8" s="34" t="s">
+    <row r="8" ht="390" customHeight="true">
+      <c r="A8" s="35" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="9" ht="400" customHeight="true">
-      <c r="A9" s="34" t="s">
+    <row r="9" ht="390" customHeight="true">
+      <c r="A9" s="35" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="10" ht="400" customHeight="true">
-      <c r="A10" s="34" t="s">
+    <row r="10" ht="390" customHeight="true">
+      <c r="A10" s="35" t="s">
         <v>52</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
-  <pageSetup paperSize="11"/>
-  <rowBreaks count="9" manualBreakCount="9">
-    <brk id="1" max="16383" man="true"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+  <rowBreaks count="5" manualBreakCount="5">
     <brk id="2" max="16383" man="true"/>
-    <brk id="3" max="16383" man="true"/>
     <brk id="4" max="16383" man="true"/>
-    <brk id="5" max="16383" man="true"/>
     <brk id="6" max="16383" man="true"/>
-    <brk id="7" max="16383" man="true"/>
     <brk id="8" max="16383" man="true"/>
-    <brk id="9" max="16383" man="true"/>
+    <brk id="10" max="16383" man="true"/>
   </rowBreaks>
   <colBreaks/>
 </worksheet>
@@ -2614,7 +2623,7 @@
       <c r="O4" s="20"/>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="23" t="s">
         <v>33</v>
       </c>
       <c r="B5" s="21"/>
@@ -2624,10 +2633,10 @@
       </c>
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
-      <c r="G5" t="s">
+      <c r="G5" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="23" t="s">
         <v>33</v>
       </c>
       <c r="J5" s="21"/>
@@ -2637,7 +2646,7 @@
       </c>
       <c r="M5" s="21"/>
       <c r="N5" s="21"/>
-      <c r="O5" t="s">
+      <c r="O5" s="24" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2850,7 +2859,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="23" t="s">
         <v>33</v>
       </c>
       <c r="B18" s="21"/>
@@ -2860,10 +2869,10 @@
       </c>
       <c r="E18" s="21"/>
       <c r="F18" s="21"/>
-      <c r="G18" t="s">
+      <c r="G18" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="I18" s="22" t="s">
+      <c r="I18" s="23" t="s">
         <v>33</v>
       </c>
       <c r="J18" s="21"/>
@@ -2873,7 +2882,7 @@
       </c>
       <c r="M18" s="21"/>
       <c r="N18" s="21"/>
-      <c r="O18" t="s">
+      <c r="O18" s="24" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3086,7 +3095,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="23" t="s">
         <v>33</v>
       </c>
       <c r="B31" s="21"/>
@@ -3096,10 +3105,10 @@
       </c>
       <c r="E31" s="21"/>
       <c r="F31" s="21"/>
-      <c r="G31" t="s">
+      <c r="G31" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="I31" s="22" t="s">
+      <c r="I31" s="23" t="s">
         <v>33</v>
       </c>
       <c r="J31" s="21"/>
@@ -3109,7 +3118,7 @@
       </c>
       <c r="M31" s="21"/>
       <c r="N31" s="21"/>
-      <c r="O31" t="s">
+      <c r="O31" s="24" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3325,16 +3334,16 @@
       <c r="N42" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="O42" s="23"/>
+      <c r="O42" s="22"/>
     </row>
     <row r="43">
       <c r="N43" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="O43" s="23"/>
+      <c r="O43" s="22"/>
     </row>
     <row r="44">
-      <c r="A44" s="22" t="s">
+      <c r="A44" s="23" t="s">
         <v>33</v>
       </c>
       <c r="B44" s="21"/>
@@ -3344,13 +3353,13 @@
       </c>
       <c r="E44" s="21"/>
       <c r="F44" s="21"/>
-      <c r="G44" t="s">
+      <c r="G44" s="24" t="s">
         <v>35</v>
       </c>
       <c r="N44" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="O44" s="23"/>
+      <c r="O44" s="22"/>
     </row>
     <row r="45">
       <c r="A45" s="21" t="str">
@@ -3465,7 +3474,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="22" t="s">
+      <c r="A57" s="23" t="s">
         <v>33</v>
       </c>
       <c r="B57" s="21"/>
@@ -3475,7 +3484,7 @@
       </c>
       <c r="E57" s="21"/>
       <c r="F57" s="21"/>
-      <c r="G57" t="s">
+      <c r="G57" s="24" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3592,7 +3601,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="22" t="s">
+      <c r="A70" s="23" t="s">
         <v>33</v>
       </c>
       <c r="B70" s="21"/>
@@ -3602,7 +3611,7 @@
       </c>
       <c r="E70" s="21"/>
       <c r="F70" s="21"/>
-      <c r="G70" t="s">
+      <c r="G70" s="24" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3722,25 +3731,25 @@
       <c r="F81" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G81" s="23"/>
+      <c r="G81" s="22"/>
     </row>
     <row r="82">
       <c r="F82" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G82" s="23"/>
+      <c r="G82" s="22"/>
     </row>
     <row r="83">
       <c r="F83" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G83" s="23"/>
+      <c r="G83" s="22"/>
     </row>
     <row r="84">
       <c r="F84" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="G84" s="23"/>
+      <c r="G84" s="22"/>
     </row>
     <row r="87">
       <c r="A87" s="20" t="str">
@@ -3754,7 +3763,7 @@
       <c r="G87" s="20"/>
     </row>
     <row r="88">
-      <c r="A88" s="22" t="s">
+      <c r="A88" s="23" t="s">
         <v>33</v>
       </c>
       <c r="B88" s="21"/>
@@ -3764,7 +3773,7 @@
       </c>
       <c r="E88" s="21"/>
       <c r="F88" s="21"/>
-      <c r="G88" t="s">
+      <c r="G88" s="24" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3881,7 +3890,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="22" t="s">
+      <c r="A101" s="23" t="s">
         <v>33</v>
       </c>
       <c r="B101" s="21"/>
@@ -3891,7 +3900,7 @@
       </c>
       <c r="E101" s="21"/>
       <c r="F101" s="21"/>
-      <c r="G101" t="s">
+      <c r="G101" s="24" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4008,7 +4017,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="22" t="s">
+      <c r="A114" s="23" t="s">
         <v>33</v>
       </c>
       <c r="B114" s="21"/>
@@ -4018,7 +4027,7 @@
       </c>
       <c r="E114" s="21"/>
       <c r="F114" s="21"/>
-      <c r="G114" t="s">
+      <c r="G114" s="24" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4138,19 +4147,19 @@
       <c r="F125" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G125" s="23"/>
+      <c r="G125" s="22"/>
     </row>
     <row r="126">
       <c r="F126" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G126" s="23"/>
+      <c r="G126" s="22"/>
     </row>
     <row r="127">
       <c r="F127" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G127" s="23"/>
+      <c r="G127" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4221,22 +4230,22 @@
       <c r="O3" s="20"/>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="23" t="s">
         <v>33</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="22" t="s">
+      <c r="I4" s="23" t="s">
         <v>33</v>
       </c>
       <c r="L4" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="O4" t="s">
+      <c r="O4" s="24" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4452,21 +4461,21 @@
       <c r="F15" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G15" s="23"/>
+      <c r="G15" s="22"/>
       <c r="N15" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="O15" s="23"/>
+      <c r="O15" s="22"/>
     </row>
     <row r="16">
       <c r="F16" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G16" s="23"/>
+      <c r="G16" s="22"/>
       <c r="N16" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="O16" s="23"/>
+      <c r="O16" s="22"/>
     </row>
     <row r="24">
       <c r="A24" s="20" t="s">
@@ -4508,22 +4517,22 @@
       <c r="O26" s="20"/>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="23" t="s">
         <v>33</v>
       </c>
       <c r="D27" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="I27" s="22" t="s">
+      <c r="I27" s="23" t="s">
         <v>33</v>
       </c>
       <c r="L27" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="O27" t="s">
+      <c r="O27" s="24" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4739,21 +4748,21 @@
       <c r="F38" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G38" s="23"/>
+      <c r="G38" s="22"/>
       <c r="N38" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="O38" s="23"/>
+      <c r="O38" s="22"/>
     </row>
     <row r="39">
       <c r="F39" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G39" s="23"/>
+      <c r="G39" s="22"/>
       <c r="N39" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="O39" s="23"/>
+      <c r="O39" s="22"/>
     </row>
     <row r="47">
       <c r="A47" s="20" t="s">
@@ -4786,13 +4795,13 @@
       <c r="G49" s="20"/>
     </row>
     <row r="50">
-      <c r="A50" s="22" t="s">
+      <c r="A50" s="23" t="s">
         <v>33</v>
       </c>
       <c r="D50" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="G50" t="s">
+      <c r="G50" s="24" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4912,13 +4921,13 @@
       <c r="F61" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G61" s="23"/>
+      <c r="G61" s="22"/>
     </row>
     <row r="62">
       <c r="F62" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G62" s="23"/>
+      <c r="G62" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4943,150 +4952,150 @@
   <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="115" customHeight="true"/>
   <cols>
-    <col customWidth="true" max="1" min="1" style="10" width="21.6640625"/>
-    <col customWidth="true" max="2" min="2" style="9" width="170.6640625"/>
+    <col customWidth="true" max="1" min="1" style="10" width="20"/>
+    <col customWidth="true" max="2" min="2" style="9" width="170"/>
     <col max="16384" min="3" style="8" width="10.83203125"/>
   </cols>
   <sheetData>
     <row r="1" ht="110" customHeight="true">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="33" t="str">
+      <c r="B1" s="34" t="str">
         <f>data!$B$2</f>
       </c>
     </row>
     <row r="2" ht="115" customHeight="true">
-      <c r="A2" s="32">
+      <c r="A2" s="33">
         <v>1</v>
       </c>
-      <c r="B2" s="33"/>
+      <c r="B2" s="34"/>
     </row>
     <row r="3" ht="110" customHeight="true">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="33" t="str">
+      <c r="B3" s="34" t="str">
         <f>data!$B$3</f>
       </c>
     </row>
     <row r="4" ht="115" customHeight="true">
-      <c r="A4" s="32">
+      <c r="A4" s="33">
         <v>2</v>
       </c>
-      <c r="B4" s="33"/>
+      <c r="B4" s="34"/>
     </row>
     <row r="5" ht="110" customHeight="true">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="33" t="str">
+      <c r="B5" s="34" t="str">
         <f>data!$B$4</f>
       </c>
     </row>
     <row r="6" ht="115" customHeight="true">
-      <c r="A6" s="32">
+      <c r="A6" s="33">
         <v>3</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="34"/>
     </row>
     <row r="7" ht="110" customHeight="true">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="33" t="str">
+      <c r="B7" s="34" t="str">
         <f>data!$B$5</f>
       </c>
     </row>
     <row r="8" ht="115" customHeight="true">
-      <c r="A8" s="32">
+      <c r="A8" s="33">
         <v>4</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="34"/>
     </row>
     <row r="9" ht="110" customHeight="true">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="33" t="str">
+      <c r="B9" s="34" t="str">
         <f>data!$B$6</f>
       </c>
     </row>
     <row r="10" ht="115" customHeight="true">
-      <c r="A10" s="32">
+      <c r="A10" s="33">
         <v>1</v>
       </c>
-      <c r="B10" s="33"/>
+      <c r="B10" s="34"/>
     </row>
     <row r="11" ht="110" customHeight="true">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="33" t="str">
+      <c r="B11" s="34" t="str">
         <f>data!$B$7</f>
       </c>
     </row>
     <row r="12" ht="115" customHeight="true">
-      <c r="A12" s="32">
+      <c r="A12" s="33">
         <v>2</v>
       </c>
-      <c r="B12" s="33"/>
+      <c r="B12" s="34"/>
     </row>
     <row r="13" ht="110" customHeight="true">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="33" t="str">
+      <c r="B13" s="34" t="str">
         <f>data!$B$8</f>
       </c>
     </row>
     <row r="14" ht="115" customHeight="true">
-      <c r="A14" s="32">
+      <c r="A14" s="33">
         <v>3</v>
       </c>
-      <c r="B14" s="33"/>
+      <c r="B14" s="34"/>
     </row>
     <row r="15" ht="110" customHeight="true">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="33" t="str">
+      <c r="B15" s="34" t="str">
         <f>data!$B$9</f>
       </c>
     </row>
     <row r="16" ht="115" customHeight="true">
-      <c r="A16" s="32">
+      <c r="A16" s="33">
         <v>1</v>
       </c>
-      <c r="B16" s="33"/>
+      <c r="B16" s="34"/>
     </row>
     <row r="17" ht="110" customHeight="true">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="33" t="str">
+      <c r="B17" s="34" t="str">
         <f>data!$B$10</f>
       </c>
     </row>
     <row r="18" ht="115" customHeight="true">
-      <c r="A18" s="32">
+      <c r="A18" s="33">
         <v>2</v>
       </c>
-      <c r="B18" s="33"/>
+      <c r="B18" s="34"/>
     </row>
     <row r="19" ht="110" customHeight="true">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="33" t="str">
+      <c r="B19" s="34" t="str">
         <f>data!$B$11</f>
       </c>
     </row>
     <row r="20" ht="115" customHeight="true">
-      <c r="A20" s="32">
+      <c r="A20" s="33">
         <v>3</v>
       </c>
-      <c r="B20" s="33"/>
+      <c r="B20" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -5103,7 +5112,7 @@
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="0" horizontalDpi="0" orientation="landscape" paperSize="8" verticalDpi="0"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" horizontalDpi="0" orientation="landscape" paperSize="8" verticalDpi="0"/>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="6" max="16383" man="true"/>
     <brk id="12" max="16383" man="true"/>

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="26060" windowHeight="21580" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="26060" windowHeight="21580" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="Elimination Matches" sheetId="7" r:id="rId5"/>
     <sheet name="Names to Print" sheetId="8" r:id="rId6"/>
     <sheet name="Tree 1" sheetId="10" r:id="rId13"/>
-    <sheet name="Tags" sheetId="11" r:id="rId14"/>
+    <sheet name="Tree 2" sheetId="11" r:id="rId14"/>
+    <sheet name="Tags" sheetId="12" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName localSheetId="5" name="_xlnm.Print_Area">'Names to Print'!$A$1:$B$20</definedName>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>Elimination Round 1</t>
   </si>
@@ -80,6 +81,9 @@
     <t>Number of Elimination Matches</t>
   </si>
   <si>
+    <t>Title prefix:</t>
+  </si>
+  <si>
     <t>Pool</t>
   </si>
   <si>
@@ -122,6 +126,21 @@
     <t>Pool B</t>
   </si>
   <si>
+    <t>Michael Lewis</t>
+  </si>
+  <si>
+    <t>Team Gamma</t>
+  </si>
+  <si>
+    <t>Paul Hall</t>
+  </si>
+  <si>
+    <t>Steven Hernandez</t>
+  </si>
+  <si>
+    <t>Pool C</t>
+  </si>
+  <si>
     <t>Luke Rodriguez</t>
   </si>
   <si>
@@ -131,19 +150,10 @@
     <t>Robert Young</t>
   </si>
   <si>
-    <t>Team Gamma</t>
-  </si>
-  <si>
-    <t>Pool C</t>
-  </si>
-  <si>
-    <t>Michael Lewis</t>
-  </si>
-  <si>
-    <t>Paul Hall</t>
-  </si>
-  <si>
-    <t>Steven Hernandez</t>
+    <t>Shiaijo A</t>
+  </si>
+  <si>
+    <t>Shiaijo B</t>
   </si>
   <si>
     <t>Red</t>
@@ -230,7 +240,7 @@
     <t>Elimination Round 3</t>
   </si>
   <si>
-    <t>Match 5</t>
+    <t>Match 0</t>
   </si>
 </sst>
 </file>
@@ -845,129 +855,131 @@
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" t="s">
-        <v>14</v>
-      </c>
+      <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:2" ht="12.75" customHeight="true">
       <c r="A2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
         <v>15</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="12.75" customHeight="true">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
         <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="12.75" customHeight="true">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
         <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="12.75" customHeight="true">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
         <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="12.75" customHeight="true">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
         <v>24</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="12.75" customHeight="true">
       <c r="A7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="12.75" customHeight="true">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="12.75" customHeight="true">
       <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
         <v>29</v>
       </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="12.75" customHeight="true">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="12.75" customHeight="true">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="12.75" customHeight="true">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
+      <c r="A12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="13" spans="1:2" ht="12.75" customHeight="true"/>
     <row r="14" spans="1:2" ht="12.75" customHeight="true">
@@ -2053,19 +2065,39 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="str">
+        <f>IF(data!$B$1="","Shiaijo A",data!$B$1&amp;" - Shiaijo A")</f>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+    </row>
     <row r="4">
       <c r="A4" s="29" t="str">
-        <f>data!$A$5</f>
+        <f>data!$A$6</f>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="30" t="str">
-        <f>"1. " &amp; data!$B$2</f>
+        <f>"1. " &amp; data!$B$3</f>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="31" t="str">
-        <f>"2. " &amp; data!$B$3</f>
+        <f>"2. " &amp; data!$B$4</f>
       </c>
       <c r="E6" s="28" t="str">
         <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G81)</f>
@@ -2073,14 +2105,14 @@
     </row>
     <row r="7">
       <c r="A7" s="31" t="str">
-        <f>"3. " &amp; data!$B$4</f>
+        <f>"3. " &amp; data!$B$5</f>
       </c>
       <c r="F7" s="27"/>
       <c r="G7" s="25"/>
     </row>
     <row r="8">
       <c r="A8" s="32" t="str">
-        <f>"4. " &amp; data!$B$5</f>
+        <f>"4. " &amp; data!$B$6</f>
       </c>
       <c r="G8" s="26">
         <v>3</v>
@@ -2089,15 +2121,13 @@
     <row r="9">
       <c r="A9" s="27"/>
       <c r="C9" s="28" t="str">
-        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G125)</f>
+        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!O42)</f>
       </c>
       <c r="G9" s="25"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="25"/>
     </row>
     <row r="10">
       <c r="A10" s="29" t="str">
-        <f>data!$A$8</f>
+        <f>data!$A$9</f>
       </c>
       <c r="D10" s="27"/>
       <c r="E10" s="26">
@@ -2105,87 +2135,34 @@
       </c>
       <c r="F10" s="22"/>
       <c r="G10" s="25"/>
-      <c r="I10" s="25"/>
     </row>
     <row r="11">
       <c r="A11" s="30" t="str">
-        <f>"1. " &amp; data!$B$6</f>
+        <f>"1. " &amp; data!$B$7</f>
       </c>
       <c r="C11" s="28" t="str">
-        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!O43)</f>
+        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!G126)</f>
       </c>
       <c r="D11" s="22"/>
       <c r="E11" s="25"/>
-      <c r="I11" s="25"/>
     </row>
     <row r="12">
       <c r="A12" s="31" t="str">
-        <f>"2. " &amp; data!$B$7</f>
-      </c>
-      <c r="I12" s="26">
-        <v>5</v>
+        <f>"2. " &amp; data!$B$8</f>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="32" t="str">
-        <f>"3. " &amp; data!$B$8</f>
-      </c>
-      <c r="I13" s="25"/>
+        <f>"3. " &amp; data!$B$9</f>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="27"/>
-      <c r="E14" s="28" t="str">
-        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!O42)</f>
-      </c>
-      <c r="I14" s="25"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="29" t="str">
-        <f>data!$A$11</f>
-      </c>
-      <c r="F15" s="27"/>
-      <c r="G15" s="25"/>
-      <c r="I15" s="25"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="30" t="str">
-        <f>"1. " &amp; data!$B$9</f>
-      </c>
-      <c r="G16" s="26">
-        <v>4</v>
-      </c>
-      <c r="H16" s="22"/>
-      <c r="I16" s="25"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="31" t="str">
-        <f>"2. " &amp; data!$B$10</f>
-      </c>
-      <c r="C17" s="28" t="str">
-        <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G82)</f>
-      </c>
-      <c r="G17" s="25"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="32" t="str">
-        <f>"3. " &amp; data!$B$11</f>
-      </c>
-      <c r="D18" s="27"/>
-      <c r="E18" s="26">
-        <v>2</v>
-      </c>
-      <c r="F18" s="22"/>
-      <c r="G18" s="25"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="27"/>
-      <c r="C19" s="28" t="str">
-        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G126)</f>
-      </c>
-      <c r="D19" s="22"/>
-      <c r="E19" s="25"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:P1"/>
+  </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageMargins left="0.25" right="0.25" top="0" bottom="0" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -2193,6 +2170,100 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4065E12-1BC4-BF48-9DCD-AFB9407081DC}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="3.5" defaultRowHeight="13"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="20.83203125"/>
+    <col customWidth="true" max="2" min="2" width="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="str">
+        <f>IF(data!$B$1="","Shiaijo B",data!$B$1&amp;" - Shiaijo B")</f>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="29" t="str">
+        <f>data!$A$12</f>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="30" t="str">
+        <f>"1. " &amp; data!$B$10</f>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="str">
+        <f>"2. " &amp; data!$B$11</f>
+      </c>
+      <c r="E6" s="28" t="str">
+        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!G125)</f>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="32" t="str">
+        <f>"3. " &amp; data!$B$12</f>
+      </c>
+      <c r="F7" s="27"/>
+      <c r="G7" s="25"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="27"/>
+      <c r="G8" s="26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" s="28" t="str">
+        <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G82)</f>
+      </c>
+      <c r="G9" s="25"/>
+    </row>
+    <row r="10">
+      <c r="D10" s="27"/>
+      <c r="E10" s="26">
+        <v>2</v>
+      </c>
+      <c r="F10" s="22"/>
+      <c r="G10" s="25"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="28" t="str">
+        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!O43)</f>
+      </c>
+      <c r="D11" s="22"/>
+      <c r="E11" s="25"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:P1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageMargins left="0.25" right="0.25" top="0" bottom="0" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
@@ -2201,52 +2272,52 @@
   <sheetData>
     <row r="1" ht="390" customHeight="true">
       <c r="A1" s="35" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" ht="390" customHeight="true">
       <c r="A2" s="35" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" ht="390" customHeight="true">
       <c r="A3" s="35" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" ht="390" customHeight="true">
       <c r="A4" s="35" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" ht="390" customHeight="true">
       <c r="A5" s="35" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" ht="390" customHeight="true">
       <c r="A6" s="35" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" ht="390" customHeight="true">
       <c r="A7" s="35" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" ht="390" customHeight="true">
       <c r="A8" s="35" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" ht="390" customHeight="true">
       <c r="A9" s="35" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" ht="390" customHeight="true">
       <c r="A10" s="35" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -2493,7 +2564,8 @@
   <sheetData>
     <row r="2" spans="1:8" ht="20">
       <c r="A2" s="2"/>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="15" t="str">
+        <f>IF(data!$B$1="","Tournament Pools",data!$B$1&amp;" - Tournament Pools")</f>
         <v>1</v>
       </c>
       <c r="C2" s="16"/>
@@ -2522,55 +2594,55 @@
     </row>
     <row r="5" spans="1:8" ht="17" customHeight="true" thickBot="true">
       <c r="B5" s="6" t="str">
-        <f>data!$A$5</f>
+        <f>data!$A$6</f>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="6" t="str">
-        <f>data!$A$8</f>
+        <f>data!$A$9</f>
       </c>
       <c r="F5" s="6" t="str">
-        <f>data!$A$11</f>
+        <f>data!$A$12</f>
       </c>
     </row>
     <row r="6" spans="1:8" ht="17" customHeight="true" thickBot="true">
       <c r="B6" s="5" t="str">
-        <f>"1. " &amp; data!$B$2</f>
+        <f>"1. " &amp; data!$B$3</f>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="5" t="str">
-        <f>"1. " &amp; data!$B$6</f>
+        <f>"1. " &amp; data!$B$7</f>
       </c>
       <c r="F6" s="5" t="str">
-        <f>"1. " &amp; data!$B$9</f>
+        <f>"1. " &amp; data!$B$10</f>
       </c>
     </row>
     <row r="7" spans="1:8" ht="17" customHeight="true" thickBot="true">
       <c r="B7" s="5" t="str">
-        <f>"2. " &amp; data!$B$3</f>
+        <f>"2. " &amp; data!$B$4</f>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="5" t="str">
-        <f>"2. " &amp; data!$B$7</f>
+        <f>"2. " &amp; data!$B$8</f>
       </c>
       <c r="F7" s="5" t="str">
-        <f>"2. " &amp; data!$B$10</f>
+        <f>"2. " &amp; data!$B$11</f>
       </c>
     </row>
     <row r="8" spans="1:8" ht="17" customHeight="true" thickBot="true">
       <c r="B8" s="5" t="str">
-        <f>"3. " &amp; data!$B$4</f>
+        <f>"3. " &amp; data!$B$5</f>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="5" t="str">
-        <f>"3. " &amp; data!$B$8</f>
+        <f>"3. " &amp; data!$B$9</f>
       </c>
       <c r="F8" s="5" t="str">
-        <f>"3. " &amp; data!$B$11</f>
+        <f>"3. " &amp; data!$B$12</f>
       </c>
     </row>
     <row r="9" ht="17" customHeight="true">
       <c r="B9" s="5" t="str">
-        <f>"4. " &amp; data!$B$5</f>
+        <f>"4. " &amp; data!$B$6</f>
       </c>
     </row>
   </sheetData>
@@ -2602,9 +2674,29 @@
     <col max="16384" min="16" style="7" width="10.83203125"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="I1" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+    </row>
     <row r="4">
       <c r="A4" s="20" t="str">
-        <f>data!$A$5</f>
+        <f>data!$A$6</f>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -2613,7 +2705,7 @@
       <c r="F4" s="20"/>
       <c r="G4" s="20"/>
       <c r="I4" s="20" t="str">
-        <f>data!$A$8</f>
+        <f>data!$A$12</f>
       </c>
       <c r="J4" s="20"/>
       <c r="K4" s="20"/>
@@ -2624,35 +2716,35 @@
     </row>
     <row r="5">
       <c r="A5" s="23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="21"/>
       <c r="D5" s="21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
       <c r="G5" s="24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J5" s="21"/>
       <c r="K5" s="21"/>
       <c r="L5" s="21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M5" s="21"/>
       <c r="N5" s="21"/>
       <c r="O5" s="24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="21" t="str">
-        <f>data!$B$2</f>
+        <f>data!$B$3</f>
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="21"/>
@@ -2660,10 +2752,10 @@
       <c r="E6" s="21"/>
       <c r="F6" s="21"/>
       <c r="G6" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$4</f>
       </c>
       <c r="I6" s="21" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$10</f>
       </c>
       <c r="J6" s="21"/>
       <c r="K6" s="21"/>
@@ -2671,7 +2763,7 @@
       <c r="M6" s="21"/>
       <c r="N6" s="21"/>
       <c r="O6" s="21" t="str">
-        <f>data!$B$7</f>
+        <f>data!$B$11</f>
       </c>
     </row>
     <row r="7">
@@ -2796,47 +2888,47 @@
     </row>
     <row r="13">
       <c r="A13" s="21" t="str">
-        <f>data!$B$2</f>
+        <f>data!$B$3</f>
       </c>
       <c r="B13" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D13" s="21"/>
       <c r="E13" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G13" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$4</f>
       </c>
       <c r="I13" s="21" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$10</f>
       </c>
       <c r="J13" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K13" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L13" s="21"/>
       <c r="M13" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N13" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="O13" s="21" t="str">
-        <f>data!$B$7</f>
+        <f>data!$B$11</f>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
@@ -2844,10 +2936,10 @@
       <c r="E14" s="21"/>
       <c r="F14" s="21"/>
       <c r="G14" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J14" s="21"/>
       <c r="K14" s="21"/>
@@ -2855,40 +2947,40 @@
       <c r="M14" s="21"/>
       <c r="N14" s="21"/>
       <c r="O14" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B18" s="21"/>
       <c r="C18" s="21"/>
       <c r="D18" s="21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E18" s="21"/>
       <c r="F18" s="21"/>
       <c r="G18" s="24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I18" s="23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J18" s="21"/>
       <c r="K18" s="21"/>
       <c r="L18" s="21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M18" s="21"/>
       <c r="N18" s="21"/>
       <c r="O18" s="24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="21" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$5</f>
       </c>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
@@ -2896,10 +2988,10 @@
       <c r="E19" s="21"/>
       <c r="F19" s="21"/>
       <c r="G19" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$4</f>
       </c>
       <c r="I19" s="21" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$10</f>
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21"/>
@@ -2907,7 +2999,7 @@
       <c r="M19" s="21"/>
       <c r="N19" s="21"/>
       <c r="O19" s="21" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$12</f>
       </c>
     </row>
     <row r="20">
@@ -3032,47 +3124,47 @@
     </row>
     <row r="26">
       <c r="A26" s="21" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$5</f>
       </c>
       <c r="B26" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D26" s="21"/>
       <c r="E26" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G26" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$4</f>
       </c>
       <c r="I26" s="21" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$10</f>
       </c>
       <c r="J26" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K26" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L26" s="21"/>
       <c r="M26" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N26" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="O26" s="21" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$12</f>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
@@ -3080,10 +3172,10 @@
       <c r="E27" s="21"/>
       <c r="F27" s="21"/>
       <c r="G27" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J27" s="21"/>
       <c r="K27" s="21"/>
@@ -3091,40 +3183,40 @@
       <c r="M27" s="21"/>
       <c r="N27" s="21"/>
       <c r="O27" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B31" s="21"/>
       <c r="C31" s="21"/>
       <c r="D31" s="21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E31" s="21"/>
       <c r="F31" s="21"/>
       <c r="G31" s="24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I31" s="23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J31" s="21"/>
       <c r="K31" s="21"/>
       <c r="L31" s="21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M31" s="21"/>
       <c r="N31" s="21"/>
       <c r="O31" s="24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="21" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$5</f>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="21"/>
@@ -3132,10 +3224,10 @@
       <c r="E32" s="21"/>
       <c r="F32" s="21"/>
       <c r="G32" s="21" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$6</f>
       </c>
       <c r="I32" s="21" t="str">
-        <f>data!$B$7</f>
+        <f>data!$B$11</f>
       </c>
       <c r="J32" s="21"/>
       <c r="K32" s="21"/>
@@ -3143,7 +3235,7 @@
       <c r="M32" s="21"/>
       <c r="N32" s="21"/>
       <c r="O32" s="21" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$12</f>
       </c>
     </row>
     <row r="33">
@@ -3268,47 +3360,47 @@
     </row>
     <row r="39">
       <c r="A39" s="21" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$5</f>
       </c>
       <c r="B39" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D39" s="21"/>
       <c r="E39" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F39" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G39" s="21" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$6</f>
       </c>
       <c r="I39" s="21" t="str">
-        <f>data!$B$7</f>
+        <f>data!$B$11</f>
       </c>
       <c r="J39" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K39" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L39" s="21"/>
       <c r="M39" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N39" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="O39" s="21" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$12</f>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B40" s="21"/>
       <c r="C40" s="21"/>
@@ -3316,10 +3408,10 @@
       <c r="E40" s="21"/>
       <c r="F40" s="21"/>
       <c r="G40" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I40" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J40" s="21"/>
       <c r="K40" s="21"/>
@@ -3327,43 +3419,43 @@
       <c r="M40" s="21"/>
       <c r="N40" s="21"/>
       <c r="O40" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42">
       <c r="N42" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O42" s="22"/>
     </row>
     <row r="43">
       <c r="N43" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="O43" s="22"/>
     </row>
     <row r="44">
       <c r="A44" s="23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
       <c r="D44" s="21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E44" s="21"/>
       <c r="F44" s="21"/>
       <c r="G44" s="24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N44" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="O44" s="22"/>
     </row>
     <row r="45">
       <c r="A45" s="21" t="str">
-        <f>data!$B$2</f>
+        <f>data!$B$3</f>
       </c>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
@@ -3371,7 +3463,7 @@
       <c r="E45" s="21"/>
       <c r="F45" s="21"/>
       <c r="G45" s="21" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$6</f>
       </c>
     </row>
     <row r="46">
@@ -3441,28 +3533,28 @@
     </row>
     <row r="52">
       <c r="A52" s="21" t="str">
-        <f>data!$B$2</f>
+        <f>data!$B$3</f>
       </c>
       <c r="B52" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D52" s="21"/>
       <c r="E52" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F52" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G52" s="21" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$6</f>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B53" s="21"/>
       <c r="C53" s="21"/>
@@ -3470,27 +3562,27 @@
       <c r="E53" s="21"/>
       <c r="F53" s="21"/>
       <c r="G53" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B57" s="21"/>
       <c r="C57" s="21"/>
       <c r="D57" s="21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E57" s="21"/>
       <c r="F57" s="21"/>
       <c r="G57" s="24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="21" t="str">
-        <f>data!$B$2</f>
+        <f>data!$B$3</f>
       </c>
       <c r="B58" s="21"/>
       <c r="C58" s="21"/>
@@ -3498,7 +3590,7 @@
       <c r="E58" s="21"/>
       <c r="F58" s="21"/>
       <c r="G58" s="21" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$5</f>
       </c>
     </row>
     <row r="59">
@@ -3568,28 +3660,28 @@
     </row>
     <row r="65">
       <c r="A65" s="21" t="str">
-        <f>data!$B$2</f>
+        <f>data!$B$3</f>
       </c>
       <c r="B65" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D65" s="21"/>
       <c r="E65" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F65" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G65" s="21" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$5</f>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B66" s="21"/>
       <c r="C66" s="21"/>
@@ -3597,27 +3689,27 @@
       <c r="E66" s="21"/>
       <c r="F66" s="21"/>
       <c r="G66" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B70" s="21"/>
       <c r="C70" s="21"/>
       <c r="D70" s="21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E70" s="21"/>
       <c r="F70" s="21"/>
       <c r="G70" s="24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$4</f>
       </c>
       <c r="B71" s="21"/>
       <c r="C71" s="21"/>
@@ -3625,7 +3717,7 @@
       <c r="E71" s="21"/>
       <c r="F71" s="21"/>
       <c r="G71" s="21" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$6</f>
       </c>
     </row>
     <row r="72">
@@ -3695,28 +3787,28 @@
     </row>
     <row r="78">
       <c r="A78" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$4</f>
       </c>
       <c r="B78" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D78" s="21"/>
       <c r="E78" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F78" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G78" s="21" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$6</f>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B79" s="21"/>
       <c r="C79" s="21"/>
@@ -3724,36 +3816,36 @@
       <c r="E79" s="21"/>
       <c r="F79" s="21"/>
       <c r="G79" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="81">
       <c r="F81" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G81" s="22"/>
     </row>
     <row r="82">
       <c r="F82" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G82" s="22"/>
     </row>
     <row r="83">
       <c r="F83" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G83" s="22"/>
     </row>
     <row r="84">
       <c r="F84" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G84" s="22"/>
     </row>
     <row r="87">
       <c r="A87" s="20" t="str">
-        <f>data!$A$11</f>
+        <f>data!$A$9</f>
       </c>
       <c r="B87" s="20"/>
       <c r="C87" s="20"/>
@@ -3764,22 +3856,22 @@
     </row>
     <row r="88">
       <c r="A88" s="23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B88" s="21"/>
       <c r="C88" s="21"/>
       <c r="D88" s="21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E88" s="21"/>
       <c r="F88" s="21"/>
       <c r="G88" s="24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="21" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$7</f>
       </c>
       <c r="B89" s="21"/>
       <c r="C89" s="21"/>
@@ -3787,7 +3879,7 @@
       <c r="E89" s="21"/>
       <c r="F89" s="21"/>
       <c r="G89" s="21" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$8</f>
       </c>
     </row>
     <row r="90">
@@ -3857,28 +3949,28 @@
     </row>
     <row r="96">
       <c r="A96" s="21" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$7</f>
       </c>
       <c r="B96" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D96" s="21"/>
       <c r="E96" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F96" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G96" s="21" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$8</f>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B97" s="21"/>
       <c r="C97" s="21"/>
@@ -3886,27 +3978,27 @@
       <c r="E97" s="21"/>
       <c r="F97" s="21"/>
       <c r="G97" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B101" s="21"/>
       <c r="C101" s="21"/>
       <c r="D101" s="21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E101" s="21"/>
       <c r="F101" s="21"/>
       <c r="G101" s="24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="21" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$7</f>
       </c>
       <c r="B102" s="21"/>
       <c r="C102" s="21"/>
@@ -3914,7 +4006,7 @@
       <c r="E102" s="21"/>
       <c r="F102" s="21"/>
       <c r="G102" s="21" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$9</f>
       </c>
     </row>
     <row r="103">
@@ -3984,28 +4076,28 @@
     </row>
     <row r="109">
       <c r="A109" s="21" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$7</f>
       </c>
       <c r="B109" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C109" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D109" s="21"/>
       <c r="E109" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F109" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G109" s="21" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$9</f>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B110" s="21"/>
       <c r="C110" s="21"/>
@@ -4013,27 +4105,27 @@
       <c r="E110" s="21"/>
       <c r="F110" s="21"/>
       <c r="G110" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B114" s="21"/>
       <c r="C114" s="21"/>
       <c r="D114" s="21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E114" s="21"/>
       <c r="F114" s="21"/>
       <c r="G114" s="24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="21" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$8</f>
       </c>
       <c r="B115" s="21"/>
       <c r="C115" s="21"/>
@@ -4041,7 +4133,7 @@
       <c r="E115" s="21"/>
       <c r="F115" s="21"/>
       <c r="G115" s="21" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$9</f>
       </c>
     </row>
     <row r="116">
@@ -4111,28 +4203,28 @@
     </row>
     <row r="122">
       <c r="A122" s="21" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$8</f>
       </c>
       <c r="B122" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C122" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D122" s="21"/>
       <c r="E122" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F122" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G122" s="21" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$9</f>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B123" s="21"/>
       <c r="C123" s="21"/>
@@ -4140,32 +4232,34 @@
       <c r="E123" s="21"/>
       <c r="F123" s="21"/>
       <c r="G123" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="125">
       <c r="F125" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G125" s="22"/>
     </row>
     <row r="126">
       <c r="F126" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G126" s="22"/>
     </row>
     <row r="127">
       <c r="F127" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G127" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="I1:O1"/>
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A87:G87"/>
     <mergeCell ref="I4:O4"/>
-    <mergeCell ref="A87:G87"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4211,7 +4305,7 @@
     </row>
     <row r="3">
       <c r="A3" s="20" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B3" s="20"/>
       <c r="C3" s="20"/>
@@ -4220,7 +4314,7 @@
       <c r="F3" s="20"/>
       <c r="G3" s="20"/>
       <c r="I3" s="20" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J3" s="20"/>
       <c r="K3" s="20"/>
@@ -4231,27 +4325,27 @@
     </row>
     <row r="4">
       <c r="A4" s="23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O4" s="24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="21" t="str">
-        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G125)</f>
+        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!O42)</f>
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="21"/>
@@ -4259,7 +4353,7 @@
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
       <c r="G5" s="21" t="str">
-        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!O43)</f>
+        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!G126)</f>
       </c>
       <c r="I5" s="21" t="str">
         <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G82)</f>
@@ -4270,7 +4364,7 @@
       <c r="M5" s="21"/>
       <c r="N5" s="21"/>
       <c r="O5" s="21" t="str">
-        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G126)</f>
+        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!O43)</f>
       </c>
     </row>
     <row r="6">
@@ -4395,47 +4489,47 @@
     </row>
     <row r="12">
       <c r="A12" s="21" t="str">
-        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!G125)</f>
+        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!O42)</f>
       </c>
       <c r="B12" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D12" s="21"/>
       <c r="E12" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G12" s="21" t="str">
-        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!O43)</f>
+        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!G126)</f>
       </c>
       <c r="I12" s="21" t="str">
         <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G82)</f>
       </c>
       <c r="J12" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K12" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L12" s="21"/>
       <c r="M12" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N12" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="O12" s="21" t="str">
-        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!G126)</f>
+        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!O43)</f>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
@@ -4443,10 +4537,10 @@
       <c r="E13" s="21"/>
       <c r="F13" s="21"/>
       <c r="G13" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I13" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21"/>
@@ -4454,32 +4548,32 @@
       <c r="M13" s="21"/>
       <c r="N13" s="21"/>
       <c r="O13" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15">
       <c r="F15" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G15" s="22"/>
       <c r="N15" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O15" s="22"/>
     </row>
     <row r="16">
       <c r="F16" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G16" s="22"/>
       <c r="N16" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="O16" s="22"/>
     </row>
     <row r="24">
       <c r="A24" s="20" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B24" s="20"/>
       <c r="C24" s="20"/>
@@ -4498,7 +4592,7 @@
     </row>
     <row r="26">
       <c r="A26" s="20" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -4507,7 +4601,7 @@
       <c r="F26" s="20"/>
       <c r="G26" s="20"/>
       <c r="I26" s="20" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J26" s="20"/>
       <c r="K26" s="20"/>
@@ -4518,22 +4612,22 @@
     </row>
     <row r="27">
       <c r="A27" s="23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G27" s="24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I27" s="23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L27" s="21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O27" s="24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28">
@@ -4549,7 +4643,7 @@
         <f>CONCATENATE("M 1 ",'Elimination Matches'!G15)</f>
       </c>
       <c r="I28" s="21" t="str">
-        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!O42)</f>
+        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!G125)</f>
       </c>
       <c r="J28" s="21"/>
       <c r="K28" s="21"/>
@@ -4685,36 +4779,36 @@
         <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G81)</f>
       </c>
       <c r="B35" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D35" s="21"/>
       <c r="E35" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F35" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G35" s="21" t="str">
         <f>CONCATENATE("M 1 ",'Elimination Matches'!G15)</f>
       </c>
       <c r="I35" s="21" t="str">
-        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!O42)</f>
+        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!G125)</f>
       </c>
       <c r="J35" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K35" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L35" s="21"/>
       <c r="M35" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N35" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="O35" s="21" t="str">
         <f>CONCATENATE("M 2 ",'Elimination Matches'!O15)</f>
@@ -4722,7 +4816,7 @@
     </row>
     <row r="36">
       <c r="A36" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B36" s="21"/>
       <c r="C36" s="21"/>
@@ -4730,10 +4824,10 @@
       <c r="E36" s="21"/>
       <c r="F36" s="21"/>
       <c r="G36" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I36" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J36" s="21"/>
       <c r="K36" s="21"/>
@@ -4741,32 +4835,32 @@
       <c r="M36" s="21"/>
       <c r="N36" s="21"/>
       <c r="O36" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38">
       <c r="F38" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G38" s="22"/>
       <c r="N38" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O38" s="22"/>
     </row>
     <row r="39">
       <c r="F39" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G39" s="22"/>
       <c r="N39" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="O39" s="22"/>
     </row>
     <row r="47">
       <c r="A47" s="20" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B47" s="20"/>
       <c r="C47" s="20"/>
@@ -4785,7 +4879,7 @@
     </row>
     <row r="49">
       <c r="A49" s="20" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B49" s="20"/>
       <c r="C49" s="20"/>
@@ -4796,13 +4890,13 @@
     </row>
     <row r="50">
       <c r="A50" s="23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G50" s="24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51">
@@ -4888,17 +4982,17 @@
         <f>CONCATENATE("M 3 ",'Elimination Matches'!G38)</f>
       </c>
       <c r="B58" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D58" s="21"/>
       <c r="E58" s="21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F58" s="21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G58" s="21" t="str">
         <f>CONCATENATE("M 4 ",'Elimination Matches'!O38)</f>
@@ -4906,7 +5000,7 @@
     </row>
     <row r="59">
       <c r="A59" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B59" s="21"/>
       <c r="C59" s="21"/>
@@ -4914,18 +5008,18 @@
       <c r="E59" s="21"/>
       <c r="F59" s="21"/>
       <c r="G59" s="21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61">
       <c r="F61" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G61" s="22"/>
     </row>
     <row r="62">
       <c r="F62" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G62" s="22"/>
     </row>
@@ -4959,10 +5053,10 @@
   <sheetData>
     <row r="1" ht="110" customHeight="true">
       <c r="A1" s="33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="34" t="str">
-        <f>data!$B$2</f>
+        <f>data!$B$3</f>
       </c>
     </row>
     <row r="2" ht="115" customHeight="true">
@@ -4973,10 +5067,10 @@
     </row>
     <row r="3" ht="110" customHeight="true">
       <c r="A3" s="33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="34" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$4</f>
       </c>
     </row>
     <row r="4" ht="115" customHeight="true">
@@ -4987,10 +5081,10 @@
     </row>
     <row r="5" ht="110" customHeight="true">
       <c r="A5" s="33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="34" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$5</f>
       </c>
     </row>
     <row r="6" ht="115" customHeight="true">
@@ -5001,10 +5095,10 @@
     </row>
     <row r="7" ht="110" customHeight="true">
       <c r="A7" s="33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="34" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$6</f>
       </c>
     </row>
     <row r="8" ht="115" customHeight="true">
@@ -5015,10 +5109,10 @@
     </row>
     <row r="9" ht="110" customHeight="true">
       <c r="A9" s="33" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="34" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$7</f>
       </c>
     </row>
     <row r="10" ht="115" customHeight="true">
@@ -5029,10 +5123,10 @@
     </row>
     <row r="11" ht="110" customHeight="true">
       <c r="A11" s="33" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" s="34" t="str">
-        <f>data!$B$7</f>
+        <f>data!$B$8</f>
       </c>
     </row>
     <row r="12" ht="115" customHeight="true">
@@ -5043,10 +5137,10 @@
     </row>
     <row r="13" ht="110" customHeight="true">
       <c r="A13" s="33" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13" s="34" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$9</f>
       </c>
     </row>
     <row r="14" ht="115" customHeight="true">
@@ -5057,10 +5151,10 @@
     </row>
     <row r="15" ht="110" customHeight="true">
       <c r="A15" s="33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15" s="34" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$10</f>
       </c>
     </row>
     <row r="16" ht="115" customHeight="true">
@@ -5071,10 +5165,10 @@
     </row>
     <row r="17" ht="110" customHeight="true">
       <c r="A17" s="33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" s="34" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$11</f>
       </c>
     </row>
     <row r="18" ht="115" customHeight="true">
@@ -5085,10 +5179,10 @@
     </row>
     <row r="19" ht="110" customHeight="true">
       <c r="A19" s="33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19" s="34" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$12</f>
       </c>
     </row>
     <row r="20" ht="115" customHeight="true">

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -23,6 +23,8 @@
     <sheet name="Tags" sheetId="12" r:id="rId15"/>
   </sheets>
   <definedNames>
+    <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$10</definedName>
+    <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$O$129</definedName>
     <definedName localSheetId="5" name="_xlnm.Print_Area">'Names to Print'!$A$1:$B$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -2121,7 +2123,7 @@
     <row r="9">
       <c r="A9" s="27"/>
       <c r="C9" s="28" t="str">
-        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!O42)</f>
+        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!O81)</f>
       </c>
       <c r="G9" s="25"/>
     </row>
@@ -2248,7 +2250,7 @@
     </row>
     <row r="11">
       <c r="C11" s="28" t="str">
-        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!O43)</f>
+        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!O82)</f>
       </c>
       <c r="D11" s="22"/>
       <c r="E11" s="25"/>
@@ -2657,21 +2659,25 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02F663BF-AB57-994A-845A-DBCD1B560412}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col customWidth="true" max="1" min="1" style="7" width="34"/>
-    <col customWidth="true" max="3" min="2" style="7" width="3.83203125"/>
+    <col customWidth="true" max="1" min="1" style="7" width="30"/>
+    <col customWidth="true" max="3" min="2" style="7" width="5"/>
     <col customWidth="true" max="4" min="4" style="7" width="3"/>
-    <col customWidth="true" max="6" min="5" style="7" width="3.83203125"/>
-    <col customWidth="true" max="7" min="7" style="7" width="34"/>
-    <col customWidth="true" max="8" min="8" style="7" width="3.83203125"/>
-    <col customWidth="true" max="9" min="9" style="7" width="34"/>
-    <col customWidth="true" max="11" min="10" style="7" width="3.83203125"/>
+    <col customWidth="true" max="6" min="5" style="7" width="5"/>
+    <col customWidth="true" max="7" min="7" style="7" width="30"/>
+    <col customWidth="true" max="8" min="8" style="7" width="2"/>
+    <col customWidth="true" max="9" min="9" style="7" width="30"/>
+    <col customWidth="true" max="11" min="10" style="7" width="5"/>
     <col customWidth="true" max="12" min="12" style="7" width="3"/>
-    <col customWidth="true" max="14" min="13" style="7" width="3.83203125"/>
-    <col customWidth="true" max="15" min="15" style="7" width="34"/>
-    <col max="16384" min="16" style="7" width="10.83203125"/>
+    <col customWidth="true" max="14" min="13" style="7" width="5"/>
+    <col customWidth="true" max="15" min="15" style="7" width="30"/>
+    <col customWidth="true" max="16" min="16" style="7" width="2"/>
+    <col max="16384" min="17" style="7" width="10.83203125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3422,18 +3428,6 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42">
-      <c r="N42" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="O42" s="22"/>
-    </row>
-    <row r="43">
-      <c r="N43" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="O43" s="22"/>
-    </row>
     <row r="44">
       <c r="A44" s="23" t="s">
         <v>36</v>
@@ -3448,10 +3442,6 @@
       <c r="G44" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="N44" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="O44" s="22"/>
     </row>
     <row r="45">
       <c r="A45" s="21" t="str">
@@ -3824,18 +3814,30 @@
         <v>42</v>
       </c>
       <c r="G81" s="22"/>
+      <c r="N81" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="O81" s="22"/>
     </row>
     <row r="82">
       <c r="F82" s="7" t="s">
         <v>43</v>
       </c>
       <c r="G82" s="22"/>
+      <c r="N82" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="O82" s="22"/>
     </row>
     <row r="83">
       <c r="F83" s="7" t="s">
         <v>44</v>
       </c>
       <c r="G83" s="22"/>
+      <c r="N83" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="O83" s="22"/>
     </row>
     <row r="84">
       <c r="F84" s="7" t="s">
@@ -4258,10 +4260,20 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I1:O1"/>
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="I4:O4"/>
     <mergeCell ref="A87:G87"/>
-    <mergeCell ref="I4:O4"/>
   </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup fitToHeight="0" fitToWidth="2" orientation="portrait" pageOrder="downThenOver" paperSize="9"/>
+  <rowBreaks count="3" manualBreakCount="3">
+    <brk id="30" max="16383" man="true"/>
+    <brk id="69" max="16383" man="true"/>
+    <brk id="100" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="8" max="1048575" man="true"/>
+  </colBreaks>
 </worksheet>
 </file>
 
@@ -4270,18 +4282,19 @@
   <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col customWidth="true" max="1" min="1" style="7" width="34"/>
-    <col customWidth="true" max="3" min="2" style="7" width="3.83203125"/>
+    <col customWidth="true" max="1" min="1" style="7" width="30"/>
+    <col customWidth="true" max="3" min="2" style="7" width="5"/>
     <col customWidth="true" max="4" min="4" style="7" width="3"/>
-    <col customWidth="true" max="6" min="5" style="7" width="3.83203125"/>
-    <col customWidth="true" max="7" min="7" style="7" width="34"/>
-    <col customWidth="true" max="8" min="8" style="7" width="3.83203125"/>
-    <col customWidth="true" max="9" min="9" style="7" width="34"/>
-    <col customWidth="true" max="11" min="10" style="7" width="3.83203125"/>
+    <col customWidth="true" max="6" min="5" style="7" width="5"/>
+    <col customWidth="true" max="7" min="7" style="7" width="30"/>
+    <col customWidth="true" max="8" min="8" style="7" width="2"/>
+    <col customWidth="true" max="9" min="9" style="7" width="30"/>
+    <col customWidth="true" max="11" min="10" style="7" width="5"/>
     <col customWidth="true" max="12" min="12" style="7" width="3"/>
-    <col customWidth="true" max="14" min="13" style="7" width="3.83203125"/>
-    <col customWidth="true" max="15" min="15" style="7" width="34"/>
-    <col max="16384" min="16" style="7" width="10.83203125"/>
+    <col customWidth="true" max="14" min="13" style="7" width="5"/>
+    <col customWidth="true" max="15" min="15" style="7" width="30"/>
+    <col customWidth="true" max="16" min="16" style="7" width="2"/>
+    <col max="16384" min="17" style="7" width="10.83203125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17" thickBot="true">
@@ -4345,7 +4358,7 @@
     </row>
     <row r="5">
       <c r="A5" s="21" t="str">
-        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!O42)</f>
+        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!O81)</f>
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="21"/>
@@ -4364,7 +4377,7 @@
       <c r="M5" s="21"/>
       <c r="N5" s="21"/>
       <c r="O5" s="21" t="str">
-        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!O43)</f>
+        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!O82)</f>
       </c>
     </row>
     <row r="6">
@@ -4489,7 +4502,7 @@
     </row>
     <row r="12">
       <c r="A12" s="21" t="str">
-        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!O42)</f>
+        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!O81)</f>
       </c>
       <c r="B12" s="21" t="s">
         <v>39</v>
@@ -4524,7 +4537,7 @@
         <v>39</v>
       </c>
       <c r="O12" s="21" t="str">
-        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!O43)</f>
+        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!O82)</f>
       </c>
     </row>
     <row r="13">

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -158,13 +158,13 @@
     <t>Shiaijo B</t>
   </si>
   <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>vs</t>
+  </si>
+  <si>
     <t>Red</t>
-  </si>
-  <si>
-    <t>vs</t>
-  </si>
-  <si>
-    <t>White</t>
   </si>
   <si>
     <t>V</t>
@@ -2721,7 +2721,7 @@
       <c r="O4" s="20"/>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="24" t="s">
         <v>36</v>
       </c>
       <c r="B5" s="21"/>
@@ -2731,10 +2731,10 @@
       </c>
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
-      <c r="G5" s="24" t="s">
+      <c r="G5" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="24" t="s">
         <v>36</v>
       </c>
       <c r="J5" s="21"/>
@@ -2744,13 +2744,13 @@
       </c>
       <c r="M5" s="21"/>
       <c r="N5" s="21"/>
-      <c r="O5" s="24" t="s">
+      <c r="O5" s="23" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$4</f>
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="21"/>
@@ -2758,10 +2758,10 @@
       <c r="E6" s="21"/>
       <c r="F6" s="21"/>
       <c r="G6" s="21" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$3</f>
       </c>
       <c r="I6" s="21" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$11</f>
       </c>
       <c r="J6" s="21"/>
       <c r="K6" s="21"/>
@@ -2769,7 +2769,7 @@
       <c r="M6" s="21"/>
       <c r="N6" s="21"/>
       <c r="O6" s="21" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$10</f>
       </c>
     </row>
     <row r="7">
@@ -2894,7 +2894,7 @@
     </row>
     <row r="13">
       <c r="A13" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$4</f>
       </c>
       <c r="B13" s="21" t="s">
         <v>39</v>
@@ -2910,10 +2910,10 @@
         <v>39</v>
       </c>
       <c r="G13" s="21" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$3</f>
       </c>
       <c r="I13" s="21" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$11</f>
       </c>
       <c r="J13" s="21" t="s">
         <v>39</v>
@@ -2929,7 +2929,7 @@
         <v>39</v>
       </c>
       <c r="O13" s="21" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$10</f>
       </c>
     </row>
     <row r="14">
@@ -2957,7 +2957,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="24" t="s">
         <v>36</v>
       </c>
       <c r="B18" s="21"/>
@@ -2967,10 +2967,10 @@
       </c>
       <c r="E18" s="21"/>
       <c r="F18" s="21"/>
-      <c r="G18" s="24" t="s">
+      <c r="G18" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="I18" s="23" t="s">
+      <c r="I18" s="24" t="s">
         <v>36</v>
       </c>
       <c r="J18" s="21"/>
@@ -2980,13 +2980,13 @@
       </c>
       <c r="M18" s="21"/>
       <c r="N18" s="21"/>
-      <c r="O18" s="24" t="s">
+      <c r="O18" s="23" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="21" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$4</f>
       </c>
       <c r="B19" s="21"/>
       <c r="C19" s="21"/>
@@ -2994,10 +2994,10 @@
       <c r="E19" s="21"/>
       <c r="F19" s="21"/>
       <c r="G19" s="21" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$5</f>
       </c>
       <c r="I19" s="21" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$12</f>
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21"/>
@@ -3005,7 +3005,7 @@
       <c r="M19" s="21"/>
       <c r="N19" s="21"/>
       <c r="O19" s="21" t="str">
-        <f>data!$B$12</f>
+        <f>data!$B$10</f>
       </c>
     </row>
     <row r="20">
@@ -3130,7 +3130,7 @@
     </row>
     <row r="26">
       <c r="A26" s="21" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$4</f>
       </c>
       <c r="B26" s="21" t="s">
         <v>39</v>
@@ -3146,10 +3146,10 @@
         <v>39</v>
       </c>
       <c r="G26" s="21" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$5</f>
       </c>
       <c r="I26" s="21" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$12</f>
       </c>
       <c r="J26" s="21" t="s">
         <v>39</v>
@@ -3165,7 +3165,7 @@
         <v>39</v>
       </c>
       <c r="O26" s="21" t="str">
-        <f>data!$B$12</f>
+        <f>data!$B$10</f>
       </c>
     </row>
     <row r="27">
@@ -3193,7 +3193,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="24" t="s">
         <v>36</v>
       </c>
       <c r="B31" s="21"/>
@@ -3203,10 +3203,10 @@
       </c>
       <c r="E31" s="21"/>
       <c r="F31" s="21"/>
-      <c r="G31" s="24" t="s">
+      <c r="G31" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="I31" s="23" t="s">
+      <c r="I31" s="24" t="s">
         <v>36</v>
       </c>
       <c r="J31" s="21"/>
@@ -3216,13 +3216,13 @@
       </c>
       <c r="M31" s="21"/>
       <c r="N31" s="21"/>
-      <c r="O31" s="24" t="s">
+      <c r="O31" s="23" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="21" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$6</f>
       </c>
       <c r="B32" s="21"/>
       <c r="C32" s="21"/>
@@ -3230,10 +3230,10 @@
       <c r="E32" s="21"/>
       <c r="F32" s="21"/>
       <c r="G32" s="21" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$5</f>
       </c>
       <c r="I32" s="21" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$12</f>
       </c>
       <c r="J32" s="21"/>
       <c r="K32" s="21"/>
@@ -3241,7 +3241,7 @@
       <c r="M32" s="21"/>
       <c r="N32" s="21"/>
       <c r="O32" s="21" t="str">
-        <f>data!$B$12</f>
+        <f>data!$B$11</f>
       </c>
     </row>
     <row r="33">
@@ -3366,7 +3366,7 @@
     </row>
     <row r="39">
       <c r="A39" s="21" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$6</f>
       </c>
       <c r="B39" s="21" t="s">
         <v>39</v>
@@ -3382,10 +3382,10 @@
         <v>39</v>
       </c>
       <c r="G39" s="21" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$5</f>
       </c>
       <c r="I39" s="21" t="str">
-        <f>data!$B$11</f>
+        <f>data!$B$12</f>
       </c>
       <c r="J39" s="21" t="s">
         <v>39</v>
@@ -3401,7 +3401,7 @@
         <v>39</v>
       </c>
       <c r="O39" s="21" t="str">
-        <f>data!$B$12</f>
+        <f>data!$B$11</f>
       </c>
     </row>
     <row r="40">
@@ -3429,7 +3429,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="23" t="s">
+      <c r="A44" s="24" t="s">
         <v>36</v>
       </c>
       <c r="B44" s="21"/>
@@ -3439,13 +3439,13 @@
       </c>
       <c r="E44" s="21"/>
       <c r="F44" s="21"/>
-      <c r="G44" s="24" t="s">
+      <c r="G44" s="23" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$6</f>
       </c>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
@@ -3453,7 +3453,7 @@
       <c r="E45" s="21"/>
       <c r="F45" s="21"/>
       <c r="G45" s="21" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$3</f>
       </c>
     </row>
     <row r="46">
@@ -3523,7 +3523,7 @@
     </row>
     <row r="52">
       <c r="A52" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$6</f>
       </c>
       <c r="B52" s="21" t="s">
         <v>39</v>
@@ -3539,7 +3539,7 @@
         <v>39</v>
       </c>
       <c r="G52" s="21" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$3</f>
       </c>
     </row>
     <row r="53">
@@ -3556,7 +3556,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="23" t="s">
+      <c r="A57" s="24" t="s">
         <v>36</v>
       </c>
       <c r="B57" s="21"/>
@@ -3566,13 +3566,13 @@
       </c>
       <c r="E57" s="21"/>
       <c r="F57" s="21"/>
-      <c r="G57" s="24" t="s">
+      <c r="G57" s="23" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$5</f>
       </c>
       <c r="B58" s="21"/>
       <c r="C58" s="21"/>
@@ -3580,7 +3580,7 @@
       <c r="E58" s="21"/>
       <c r="F58" s="21"/>
       <c r="G58" s="21" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$3</f>
       </c>
     </row>
     <row r="59">
@@ -3650,7 +3650,7 @@
     </row>
     <row r="65">
       <c r="A65" s="21" t="str">
-        <f>data!$B$3</f>
+        <f>data!$B$5</f>
       </c>
       <c r="B65" s="21" t="s">
         <v>39</v>
@@ -3666,7 +3666,7 @@
         <v>39</v>
       </c>
       <c r="G65" s="21" t="str">
-        <f>data!$B$5</f>
+        <f>data!$B$3</f>
       </c>
     </row>
     <row r="66">
@@ -3683,7 +3683,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="23" t="s">
+      <c r="A70" s="24" t="s">
         <v>36</v>
       </c>
       <c r="B70" s="21"/>
@@ -3693,13 +3693,13 @@
       </c>
       <c r="E70" s="21"/>
       <c r="F70" s="21"/>
-      <c r="G70" s="24" t="s">
+      <c r="G70" s="23" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="21" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$6</f>
       </c>
       <c r="B71" s="21"/>
       <c r="C71" s="21"/>
@@ -3707,7 +3707,7 @@
       <c r="E71" s="21"/>
       <c r="F71" s="21"/>
       <c r="G71" s="21" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$4</f>
       </c>
     </row>
     <row r="72">
@@ -3777,7 +3777,7 @@
     </row>
     <row r="78">
       <c r="A78" s="21" t="str">
-        <f>data!$B$4</f>
+        <f>data!$B$6</f>
       </c>
       <c r="B78" s="21" t="s">
         <v>39</v>
@@ -3793,7 +3793,7 @@
         <v>39</v>
       </c>
       <c r="G78" s="21" t="str">
-        <f>data!$B$6</f>
+        <f>data!$B$4</f>
       </c>
     </row>
     <row r="79">
@@ -3857,7 +3857,7 @@
       <c r="G87" s="20"/>
     </row>
     <row r="88">
-      <c r="A88" s="23" t="s">
+      <c r="A88" s="24" t="s">
         <v>36</v>
       </c>
       <c r="B88" s="21"/>
@@ -3867,13 +3867,13 @@
       </c>
       <c r="E88" s="21"/>
       <c r="F88" s="21"/>
-      <c r="G88" s="24" t="s">
+      <c r="G88" s="23" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="21" t="str">
-        <f>data!$B$7</f>
+        <f>data!$B$8</f>
       </c>
       <c r="B89" s="21"/>
       <c r="C89" s="21"/>
@@ -3881,7 +3881,7 @@
       <c r="E89" s="21"/>
       <c r="F89" s="21"/>
       <c r="G89" s="21" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$7</f>
       </c>
     </row>
     <row r="90">
@@ -3951,7 +3951,7 @@
     </row>
     <row r="96">
       <c r="A96" s="21" t="str">
-        <f>data!$B$7</f>
+        <f>data!$B$8</f>
       </c>
       <c r="B96" s="21" t="s">
         <v>39</v>
@@ -3967,7 +3967,7 @@
         <v>39</v>
       </c>
       <c r="G96" s="21" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$7</f>
       </c>
     </row>
     <row r="97">
@@ -3984,7 +3984,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="23" t="s">
+      <c r="A101" s="24" t="s">
         <v>36</v>
       </c>
       <c r="B101" s="21"/>
@@ -3994,13 +3994,13 @@
       </c>
       <c r="E101" s="21"/>
       <c r="F101" s="21"/>
-      <c r="G101" s="24" t="s">
+      <c r="G101" s="23" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="21" t="str">
-        <f>data!$B$7</f>
+        <f>data!$B$9</f>
       </c>
       <c r="B102" s="21"/>
       <c r="C102" s="21"/>
@@ -4008,7 +4008,7 @@
       <c r="E102" s="21"/>
       <c r="F102" s="21"/>
       <c r="G102" s="21" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$7</f>
       </c>
     </row>
     <row r="103">
@@ -4078,7 +4078,7 @@
     </row>
     <row r="109">
       <c r="A109" s="21" t="str">
-        <f>data!$B$7</f>
+        <f>data!$B$9</f>
       </c>
       <c r="B109" s="21" t="s">
         <v>39</v>
@@ -4094,7 +4094,7 @@
         <v>39</v>
       </c>
       <c r="G109" s="21" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$7</f>
       </c>
     </row>
     <row r="110">
@@ -4111,7 +4111,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="23" t="s">
+      <c r="A114" s="24" t="s">
         <v>36</v>
       </c>
       <c r="B114" s="21"/>
@@ -4121,13 +4121,13 @@
       </c>
       <c r="E114" s="21"/>
       <c r="F114" s="21"/>
-      <c r="G114" s="24" t="s">
+      <c r="G114" s="23" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="21" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$9</f>
       </c>
       <c r="B115" s="21"/>
       <c r="C115" s="21"/>
@@ -4135,7 +4135,7 @@
       <c r="E115" s="21"/>
       <c r="F115" s="21"/>
       <c r="G115" s="21" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$8</f>
       </c>
     </row>
     <row r="116">
@@ -4205,7 +4205,7 @@
     </row>
     <row r="122">
       <c r="A122" s="21" t="str">
-        <f>data!$B$8</f>
+        <f>data!$B$9</f>
       </c>
       <c r="B122" s="21" t="s">
         <v>39</v>
@@ -4221,7 +4221,7 @@
         <v>39</v>
       </c>
       <c r="G122" s="21" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$8</f>
       </c>
     </row>
     <row r="123">
@@ -4337,28 +4337,28 @@
       <c r="O3" s="20"/>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="24" t="s">
         <v>36</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="24" t="s">
         <v>36</v>
       </c>
       <c r="L4" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="O4" s="24" t="s">
+      <c r="O4" s="23" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="21" t="str">
-        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!O81)</f>
+        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!G126)</f>
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="21"/>
@@ -4366,10 +4366,10 @@
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
       <c r="G5" s="21" t="str">
-        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!G126)</f>
+        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!O81)</f>
       </c>
       <c r="I5" s="21" t="str">
-        <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G82)</f>
+        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!O82)</f>
       </c>
       <c r="J5" s="21"/>
       <c r="K5" s="21"/>
@@ -4377,7 +4377,7 @@
       <c r="M5" s="21"/>
       <c r="N5" s="21"/>
       <c r="O5" s="21" t="str">
-        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!O82)</f>
+        <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G82)</f>
       </c>
     </row>
     <row r="6">
@@ -4502,7 +4502,7 @@
     </row>
     <row r="12">
       <c r="A12" s="21" t="str">
-        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!O81)</f>
+        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!G126)</f>
       </c>
       <c r="B12" s="21" t="s">
         <v>39</v>
@@ -4518,10 +4518,10 @@
         <v>39</v>
       </c>
       <c r="G12" s="21" t="str">
-        <f>CONCATENATE("Pool B.2 ",'Pool Matches'!G126)</f>
+        <f>CONCATENATE("Pool C.1 ",'Pool Matches'!O81)</f>
       </c>
       <c r="I12" s="21" t="str">
-        <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G82)</f>
+        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!O82)</f>
       </c>
       <c r="J12" s="21" t="s">
         <v>39</v>
@@ -4537,7 +4537,7 @@
         <v>39</v>
       </c>
       <c r="O12" s="21" t="str">
-        <f>CONCATENATE("Pool C.2 ",'Pool Matches'!O82)</f>
+        <f>CONCATENATE("Pool A.2 ",'Pool Matches'!G82)</f>
       </c>
     </row>
     <row r="13">
@@ -4624,28 +4624,28 @@
       <c r="O26" s="20"/>
     </row>
     <row r="27">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="24" t="s">
         <v>36</v>
       </c>
       <c r="D27" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="G27" s="24" t="s">
+      <c r="G27" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="I27" s="23" t="s">
+      <c r="I27" s="24" t="s">
         <v>36</v>
       </c>
       <c r="L27" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="O27" s="24" t="s">
+      <c r="O27" s="23" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="21" t="str">
-        <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G81)</f>
+        <f>CONCATENATE("M 1 ",'Elimination Matches'!G15)</f>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
@@ -4653,10 +4653,10 @@
       <c r="E28" s="21"/>
       <c r="F28" s="21"/>
       <c r="G28" s="21" t="str">
-        <f>CONCATENATE("M 1 ",'Elimination Matches'!G15)</f>
+        <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G81)</f>
       </c>
       <c r="I28" s="21" t="str">
-        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!G125)</f>
+        <f>CONCATENATE("M 2 ",'Elimination Matches'!O15)</f>
       </c>
       <c r="J28" s="21"/>
       <c r="K28" s="21"/>
@@ -4664,7 +4664,7 @@
       <c r="M28" s="21"/>
       <c r="N28" s="21"/>
       <c r="O28" s="21" t="str">
-        <f>CONCATENATE("M 2 ",'Elimination Matches'!O15)</f>
+        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!G125)</f>
       </c>
     </row>
     <row r="29">
@@ -4789,7 +4789,7 @@
     </row>
     <row r="35">
       <c r="A35" s="21" t="str">
-        <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G81)</f>
+        <f>CONCATENATE("M 1 ",'Elimination Matches'!G15)</f>
       </c>
       <c r="B35" s="21" t="s">
         <v>39</v>
@@ -4805,10 +4805,10 @@
         <v>39</v>
       </c>
       <c r="G35" s="21" t="str">
-        <f>CONCATENATE("M 1 ",'Elimination Matches'!G15)</f>
+        <f>CONCATENATE("Pool A.1 ",'Pool Matches'!G81)</f>
       </c>
       <c r="I35" s="21" t="str">
-        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!G125)</f>
+        <f>CONCATENATE("M 2 ",'Elimination Matches'!O15)</f>
       </c>
       <c r="J35" s="21" t="s">
         <v>39</v>
@@ -4824,7 +4824,7 @@
         <v>39</v>
       </c>
       <c r="O35" s="21" t="str">
-        <f>CONCATENATE("M 2 ",'Elimination Matches'!O15)</f>
+        <f>CONCATENATE("Pool B.1 ",'Pool Matches'!G125)</f>
       </c>
     </row>
     <row r="36">
@@ -4902,19 +4902,19 @@
       <c r="G49" s="20"/>
     </row>
     <row r="50">
-      <c r="A50" s="23" t="s">
+      <c r="A50" s="24" t="s">
         <v>36</v>
       </c>
       <c r="D50" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="G50" s="24" t="s">
+      <c r="G50" s="23" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="21" t="str">
-        <f>CONCATENATE("M 3 ",'Elimination Matches'!G38)</f>
+        <f>CONCATENATE("M 4 ",'Elimination Matches'!O38)</f>
       </c>
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
@@ -4922,7 +4922,7 @@
       <c r="E51" s="21"/>
       <c r="F51" s="21"/>
       <c r="G51" s="21" t="str">
-        <f>CONCATENATE("M 4 ",'Elimination Matches'!O38)</f>
+        <f>CONCATENATE("M 3 ",'Elimination Matches'!G38)</f>
       </c>
     </row>
     <row r="52">
@@ -4992,7 +4992,7 @@
     </row>
     <row r="58">
       <c r="A58" s="21" t="str">
-        <f>CONCATENATE("M 3 ",'Elimination Matches'!G38)</f>
+        <f>CONCATENATE("M 4 ",'Elimination Matches'!O38)</f>
       </c>
       <c r="B58" s="21" t="s">
         <v>39</v>
@@ -5008,7 +5008,7 @@
         <v>39</v>
       </c>
       <c r="G58" s="21" t="str">
-        <f>CONCATENATE("M 4 ",'Elimination Matches'!O38)</f>
+        <f>CONCATENATE("M 3 ",'Elimination Matches'!G38)</f>
       </c>
     </row>
     <row r="59">

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -812,11 +812,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="15"/>
-    <col customWidth="true" max="26" min="2" width="30"/>
+    <col customWidth="true" max="1" min="1" width="9"/>
+    <col customWidth="true" max="3" min="2" width="20"/>
+    <col customWidth="true" max="26" min="4" width="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -952,7 +956,8 @@
       </c>
     </row>
   </sheetData>
-  <pageSetup orientation="landscape"/>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -3930,7 +3935,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -4042,7 +4047,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -12,15 +12,17 @@
     <sheet name="Pool Draw" sheetId="3" r:id="rId5"/>
     <sheet name="Pool Matches" sheetId="4" r:id="rId6"/>
     <sheet name="Elimination Matches" sheetId="5" r:id="rId7"/>
-    <sheet name="Names to Print" sheetId="6" r:id="rId8"/>
     <sheet name="Tree 1" sheetId="8" r:id="rId11"/>
     <sheet name="Tree 2" sheetId="9" r:id="rId12"/>
-    <sheet name="Tags" sheetId="10" r:id="rId13"/>
+    <sheet name="Names to Print A" sheetId="10" r:id="rId13"/>
+    <sheet name="Names to Print B" sheetId="11" r:id="rId14"/>
+    <sheet name="Tags" sheetId="12" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$12</definedName>
     <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$O$118</definedName>
-    <definedName localSheetId="5" name="_xlnm.Print_Area">'Names to Print'!$A$1:$B$10</definedName>
+    <definedName localSheetId="7" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$7</definedName>
+    <definedName localSheetId="8" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$3</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$O$64</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
@@ -213,7 +215,7 @@
     <t>Round 2 - Match 4</t>
   </si>
   <si>
-    <t>Round 3 - Match 0</t>
+    <t>Round 3 - Match 5</t>
   </si>
   <si>
     <t>Tournament Summary</t>
@@ -965,6 +967,123 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
+    <col customWidth="true" max="1" min="1" width="30"/>
+    <col customWidth="true" max="2" min="2" width="160"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="270" customHeight="true">
+      <c r="A1" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="27" t="str">
+        <f>data!$B$3</f>
+      </c>
+    </row>
+    <row r="2" ht="270" customHeight="true">
+      <c r="A2" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="27" t="str">
+        <f>data!$B$4</f>
+      </c>
+    </row>
+    <row r="3" ht="270" customHeight="true">
+      <c r="A3" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="27" t="str">
+        <f>data!$B$5</f>
+      </c>
+    </row>
+    <row r="4" ht="270" customHeight="true">
+      <c r="A4" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="27" t="str">
+        <f>data!$B$6</f>
+      </c>
+    </row>
+    <row r="5" ht="270" customHeight="true">
+      <c r="A5" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="27" t="str">
+        <f>data!$B$7</f>
+      </c>
+    </row>
+    <row r="6" ht="270" customHeight="true">
+      <c r="A6" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="27" t="str">
+        <f>data!$B$8</f>
+      </c>
+    </row>
+    <row r="7" ht="270" customHeight="true">
+      <c r="A7" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="27" t="str">
+        <f>data!$B$9</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="8"/>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="3" max="16383" man="true"/>
+    <brk id="6" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="30"/>
+    <col customWidth="true" max="2" min="2" width="160"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="270" customHeight="true">
+      <c r="A1" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="27" t="str">
+        <f>data!$B$10</f>
+      </c>
+    </row>
+    <row r="2" ht="270" customHeight="true">
+      <c r="A2" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="27" t="str">
+        <f>data!$B$11</f>
+      </c>
+    </row>
+    <row r="3" ht="270" customHeight="true">
+      <c r="A3" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="27" t="str">
+        <f>data!$B$12</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="8"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="3" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
     <col customWidth="true" max="1" min="1" width="90"/>
   </cols>
   <sheetData>
@@ -3831,106 +3950,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <cols>
-    <col customWidth="true" max="1" min="1" style="9" width="30"/>
-    <col customWidth="true" max="2" min="2" style="10" width="160"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="27" t="str">
-        <f>data!$B$3</f>
-      </c>
-    </row>
-    <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="27" t="str">
-        <f>data!$B$4</f>
-      </c>
-    </row>
-    <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3" s="27" t="str">
-        <f>data!$B$5</f>
-      </c>
-    </row>
-    <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="27" t="str">
-        <f>data!$B$6</f>
-      </c>
-    </row>
-    <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="27" t="str">
-        <f>data!$B$7</f>
-      </c>
-    </row>
-    <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="27" t="str">
-        <f>data!$B$8</f>
-      </c>
-    </row>
-    <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="27" t="str">
-        <f>data!$B$9</f>
-      </c>
-    </row>
-    <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="27" t="str">
-        <f>data!$B$10</f>
-      </c>
-    </row>
-    <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="27" t="str">
-        <f>data!$B$11</f>
-      </c>
-    </row>
-    <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10" s="27" t="str">
-        <f>data!$B$12</f>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="8"/>
-  <rowBreaks count="3" manualBreakCount="3">
-    <brk id="3" max="16383" man="true"/>
-    <brk id="6" max="16383" man="true"/>
-    <brk id="9" max="16383" man="true"/>
-  </rowBreaks>
-  <colBreaks/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$12</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$O$118</definedName>
+    <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$O$109</definedName>
     <definedName localSheetId="7" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$7</definedName>
     <definedName localSheetId="8" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$3</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$O$64</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
   <si>
     <t>Number of pools</t>
   </si>
@@ -146,58 +146,79 @@
     <t>Red</t>
   </si>
   <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>P</t>
+    <t>W</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>IV</t>
+  </si>
+  <si>
+    <t>IL</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>PW</t>
+  </si>
+  <si>
+    <t>PL</t>
+  </si>
+  <si>
+    <t>Ranking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. </t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 1</t>
   </si>
   <si>
     <t>Victories / Points</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. </t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>A2</t>
-  </si>
-  <si>
-    <t>A3</t>
-  </si>
-  <si>
-    <t>A4</t>
-  </si>
-  <si>
-    <t>B1</t>
-  </si>
-  <si>
-    <t>B2</t>
-  </si>
-  <si>
-    <t>B3</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 1</t>
   </si>
   <si>
     <t>1.</t>
@@ -339,7 +360,7 @@
       <sz val="150"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -349,6 +370,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFEFEF"/>
       </patternFill>
     </fill>
     <fill>
@@ -455,7 +481,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -496,17 +522,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center"/>
+      <protection hidden="false" locked="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment/>
+      <protection hidden="false" locked="false"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
@@ -517,10 +551,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
@@ -542,6 +576,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
@@ -972,62 +1009,63 @@
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="27" t="str">
+      <c r="A1" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="29" t="str">
         <f>data!$B$3</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="27" t="str">
+      <c r="A2" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="29" t="str">
         <f>data!$B$4</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3" s="27" t="str">
+      <c r="A3" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="29" t="str">
         <f>data!$B$5</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="27" t="str">
+      <c r="A4" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="29" t="str">
         <f>data!$B$6</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="27" t="str">
+      <c r="A5" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="29" t="str">
         <f>data!$B$7</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="27" t="str">
+      <c r="A6" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="29" t="str">
         <f>data!$B$8</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="27" t="str">
+      <c r="A7" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="29" t="str">
         <f>data!$B$9</f>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="8"/>
   <rowBreaks count="2" manualBreakCount="2">
@@ -1047,30 +1085,31 @@
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="27" t="str">
+      <c r="A1" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="29" t="str">
         <f>data!$B$10</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="27" t="str">
+      <c r="A2" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="29" t="str">
         <f>data!$B$11</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="27" t="str">
+      <c r="A3" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="29" t="str">
         <f>data!$B$12</f>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="8"/>
   <rowBreaks count="1" manualBreakCount="1">
@@ -1088,106 +1127,107 @@
   </cols>
   <sheetData>
     <row r="1" ht="390" customHeight="true">
-      <c r="A1" s="28" t="s">
-        <v>45</v>
+      <c r="A1" s="30" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="2" ht="390" customHeight="true">
-      <c r="A2" s="28" t="s">
-        <v>45</v>
+      <c r="A2" s="30" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="3" ht="390" customHeight="true">
-      <c r="A3" s="28" t="s">
-        <v>46</v>
+      <c r="A3" s="30" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="4" ht="390" customHeight="true">
-      <c r="A4" s="28" t="s">
-        <v>46</v>
+      <c r="A4" s="30" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="5" ht="390" customHeight="true">
-      <c r="A5" s="28" t="s">
-        <v>47</v>
+      <c r="A5" s="30" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="6" ht="390" customHeight="true">
-      <c r="A6" s="28" t="s">
-        <v>47</v>
+      <c r="A6" s="30" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="7" ht="390" customHeight="true">
-      <c r="A7" s="28" t="s">
-        <v>48</v>
+      <c r="A7" s="30" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="8" ht="390" customHeight="true">
-      <c r="A8" s="28" t="s">
-        <v>48</v>
+      <c r="A8" s="30" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="9" ht="390" customHeight="true">
-      <c r="A9" s="28" t="s">
-        <v>49</v>
+      <c r="A9" s="30" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="10" ht="390" customHeight="true">
-      <c r="A10" s="28" t="s">
-        <v>49</v>
+      <c r="A10" s="30" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="11" ht="390" customHeight="true">
-      <c r="A11" s="28" t="s">
-        <v>50</v>
+      <c r="A11" s="30" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="12" ht="390" customHeight="true">
-      <c r="A12" s="28" t="s">
-        <v>50</v>
+      <c r="A12" s="30" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="390" customHeight="true">
-      <c r="A13" s="28" t="s">
-        <v>51</v>
+      <c r="A13" s="30" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="14" ht="390" customHeight="true">
-      <c r="A14" s="28" t="s">
-        <v>51</v>
+      <c r="A14" s="30" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="15" ht="390" customHeight="true">
-      <c r="A15" s="28" t="s">
-        <v>52</v>
+      <c r="A15" s="30" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="16" ht="390" customHeight="true">
-      <c r="A16" s="28" t="s">
-        <v>52</v>
+      <c r="A16" s="30" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="17" ht="390" customHeight="true">
-      <c r="A17" s="28" t="s">
-        <v>53</v>
+      <c r="A17" s="30" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="18" ht="390" customHeight="true">
-      <c r="A18" s="28" t="s">
-        <v>53</v>
+      <c r="A18" s="30" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="19" ht="390" customHeight="true">
-      <c r="A19" s="28" t="s">
-        <v>54</v>
+      <c r="A19" s="30" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="20" ht="390" customHeight="true">
-      <c r="A20" s="28" t="s">
-        <v>54</v>
+      <c r="A20" s="30" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9"/>
   <rowBreaks count="10" manualBreakCount="10">
@@ -1266,7 +1306,7 @@
       <c r="G2" s="3">
         <v>0.020833333333333332</v>
       </c>
-      <c r="H2" s="29" t="str">
+      <c r="H2" s="31" t="str">
         <f>C2*I2+J2</f>
       </c>
     </row>
@@ -1370,7 +1410,7 @@
       <c r="G8" s="3">
         <v>0.020833333333333332</v>
       </c>
-      <c r="H8" s="29" t="str">
+      <c r="H8" s="31" t="str">
         <f>E8+(A8*F8)+G8</f>
       </c>
     </row>
@@ -1406,7 +1446,7 @@
     </row>
     <row r="13">
       <c r="E13" s="13" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
@@ -1416,62 +1456,62 @@
       <c r="A14">
         <v>2</v>
       </c>
-      <c r="E14" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="29" t="str">
+      <c r="E14" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="31" t="str">
         <f>H2</f>
       </c>
     </row>
     <row r="15">
-      <c r="E15" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="29" t="str">
+      <c r="E15" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="31" t="str">
         <f>H8</f>
       </c>
     </row>
     <row r="16">
-      <c r="E16" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="29" t="str">
+      <c r="E16" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="str">
         <f>H14+H15</f>
       </c>
     </row>
     <row r="17">
-      <c r="E17" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="29" t="str">
+      <c r="E17" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="31" t="str">
         <f>H16/A14</f>
       </c>
     </row>
     <row r="18">
       <c r="E18" s="13" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
-      <c r="H18" s="30">
+      <c r="H18" s="33">
         <v>0.375</v>
       </c>
     </row>
     <row r="19">
       <c r="E19" s="13" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
-      <c r="H19" s="30" t="str">
+      <c r="H19" s="33" t="str">
         <f>H18+H17</f>
       </c>
     </row>
@@ -1598,14 +1638,15 @@
     <col customWidth="true" max="4" min="4" width="3"/>
     <col customWidth="true" max="6" min="5" width="5"/>
     <col customWidth="true" max="7" min="7" width="30"/>
-    <col customWidth="true" max="8" min="8" width="2"/>
+    <col customWidth="true" max="8" min="8" width="5"/>
     <col customWidth="true" max="9" min="9" width="30"/>
     <col customWidth="true" max="11" min="10" width="5"/>
     <col customWidth="true" max="12" min="12" width="3"/>
     <col customWidth="true" max="14" min="13" width="5"/>
     <col customWidth="true" max="15" min="15" width="30"/>
-    <col customWidth="true" max="16" min="16" width="2"/>
-    <col customWidth="true" max="20" min="17" width="10.83"/>
+    <col customWidth="true" max="18" min="16" width="5"/>
+    <col customWidth="true" max="19" min="19" width="30"/>
+    <col customWidth="true" max="20" min="20" width="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1680,444 +1721,536 @@
       <c r="A4" s="14" t="str">
         <f>data!$B$4</f>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="B4" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C4" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F4" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-",""))))*1)</f>
+      </c>
       <c r="G4" s="14" t="str">
         <f>data!$B$3</f>
       </c>
       <c r="I4" s="14" t="str">
         <f>data!$B$11</f>
       </c>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
+      <c r="J4" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(L5:L9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="K4" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="N4" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(L5:L9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-",""))))*1)</f>
+      </c>
       <c r="O4" s="14" t="str">
         <f>data!$B$10</f>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14">
+      <c r="A5" s="18">
         <v>1</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14">
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18">
         <v>1</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="18">
         <v>1</v>
       </c>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14">
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="18"/>
+      <c r="O5" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14">
+      <c r="A6" s="18">
         <v>2</v>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18">
         <v>2</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="18">
         <v>2</v>
       </c>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14">
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18">
         <v>2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14">
+      <c r="A7" s="18">
         <v>3</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18">
         <v>3</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="18">
         <v>3</v>
       </c>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14">
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="18">
         <v>3</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14">
+      <c r="A8" s="18">
         <v>4</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14">
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18">
         <v>4</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="18">
         <v>4</v>
       </c>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14">
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18">
         <v>4</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14">
+      <c r="A9" s="18">
         <v>5</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18">
         <v>5</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="18">
         <v>5</v>
       </c>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14">
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18">
         <v>5</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="str">
+      <c r="A11" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="str">
         <f>data!$B$4</f>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="14" t="str">
-        <f>data!$B$3</f>
-      </c>
-      <c r="I11" s="14" t="str">
-        <f>data!$B$11</f>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="N11" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="O11" s="14" t="str">
+      <c r="B12" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D13:D17)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13:B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13:C17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13:E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13:F17," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C12" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13:B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13:C17," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13:E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13:F17," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F12" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D13:D17)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13:E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13:F17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13:B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13:C17," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="G12" s="14" t="str">
+        <f>data!$B$5</f>
+      </c>
+      <c r="I12" s="14" t="str">
+        <f>data!$B$12</f>
+      </c>
+      <c r="J12" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(L13:L17)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13:J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13:K17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13:M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13:N17," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="K12" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13:J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13:K17," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13:M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13:N17," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="N12" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(L13:L17)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13:M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13:N17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13:J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13:K17," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="O12" s="14" t="str">
         <f>data!$B$10</f>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="I12" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14" t="s">
-        <v>40</v>
+    <row r="13">
+      <c r="A13" s="18">
+        <v>1</v>
+      </c>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18">
+        <v>1</v>
+      </c>
+      <c r="I13" s="18">
+        <v>1</v>
+      </c>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18">
+        <v>2</v>
+      </c>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18">
+        <v>2</v>
+      </c>
+      <c r="I14" s="18">
+        <v>2</v>
+      </c>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="18">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18">
+        <v>3</v>
+      </c>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18">
+        <v>3</v>
+      </c>
+      <c r="I15" s="18">
+        <v>3</v>
+      </c>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18">
+        <v>4</v>
+      </c>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18">
+        <v>4</v>
+      </c>
+      <c r="I16" s="18">
+        <v>4</v>
+      </c>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18">
+        <v>5</v>
+      </c>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18">
+        <v>5</v>
+      </c>
+      <c r="I17" s="18">
+        <v>5</v>
+      </c>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="s">
         <v>35</v>
-      </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="I15" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="str">
-        <f>data!$B$4</f>
-      </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14" t="str">
-        <f>data!$B$5</f>
-      </c>
-      <c r="I16" s="14" t="str">
-        <f>data!$B$12</f>
-      </c>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14" t="str">
-        <f>data!$B$10</f>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14">
-        <v>1</v>
-      </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14">
-        <v>1</v>
-      </c>
-      <c r="I17" s="14">
-        <v>1</v>
-      </c>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14">
-        <v>2</v>
-      </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14">
-        <v>2</v>
-      </c>
-      <c r="I18" s="14">
-        <v>2</v>
-      </c>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14">
-        <v>3</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
+      <c r="D19" s="14" t="s">
+        <v>36</v>
+      </c>
       <c r="E19" s="14"/>
       <c r="F19" s="14"/>
-      <c r="G19" s="14">
-        <v>3</v>
-      </c>
-      <c r="I19" s="14">
-        <v>3</v>
+      <c r="G19" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>35</v>
       </c>
       <c r="J19" s="14"/>
       <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
+      <c r="L19" s="14" t="s">
+        <v>36</v>
+      </c>
       <c r="M19" s="14"/>
       <c r="N19" s="14"/>
-      <c r="O19" s="14">
+      <c r="O19" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="str">
+        <f>data!$B$6</f>
+      </c>
+      <c r="B20" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D21:D25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C20" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F20" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D21:D25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="G20" s="14" t="str">
+        <f>data!$B$5</f>
+      </c>
+      <c r="I20" s="14" t="str">
+        <f>data!$B$12</f>
+      </c>
+      <c r="J20" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(L21:L25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21:J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21:K25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21:M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21:N25," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="K20" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21:J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21:K25," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21:M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21:N25," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="N20" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(L21:L25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21:M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21:N25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21:J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21:K25," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="O20" s="14" t="str">
+        <f>data!$B$11</f>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18">
+        <v>1</v>
+      </c>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18">
+        <v>1</v>
+      </c>
+      <c r="I21" s="18">
+        <v>1</v>
+      </c>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18">
+        <v>2</v>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18">
+        <v>2</v>
+      </c>
+      <c r="I22" s="18">
+        <v>2</v>
+      </c>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18">
         <v>3</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14">
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18">
+        <v>3</v>
+      </c>
+      <c r="I23" s="18">
+        <v>3</v>
+      </c>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18">
         <v>4</v>
       </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14">
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18">
         <v>4</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I24" s="18">
         <v>4</v>
       </c>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14">
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18">
         <v>4</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="14">
+    <row r="25">
+      <c r="A25" s="18">
         <v>5</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14">
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18">
         <v>5</v>
       </c>
-      <c r="I21" s="14">
+      <c r="I25" s="18">
         <v>5</v>
       </c>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="14">
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18">
         <v>5</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="str">
-        <f>data!$B$4</f>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="G23" s="14" t="str">
-        <f>data!$B$5</f>
-      </c>
-      <c r="I23" s="14" t="str">
-        <f>data!$B$12</f>
-      </c>
-      <c r="J23" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K23" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="N23" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="O23" s="14" t="str">
-        <f>data!$B$10</f>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="27">
@@ -2134,1069 +2267,1104 @@
       <c r="G27" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="I27" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
-      <c r="O27" s="16" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="str">
         <f>data!$B$6</f>
       </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
+      <c r="B28" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D29:D33)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29:B33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29:C33," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29:E33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29:F33," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C28" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29:B33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29:C33," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29:E33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29:F33," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F28" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D29:D33)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29:E33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29:F33," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29:B33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29:C33," ",""),"0",""),"-",""))))*1)</f>
+      </c>
       <c r="G28" s="14" t="str">
+        <f>data!$B$3</f>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18">
+        <v>1</v>
+      </c>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18">
+        <v>2</v>
+      </c>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18">
+        <v>3</v>
+      </c>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18">
+        <v>4</v>
+      </c>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="18">
+        <v>5</v>
+      </c>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="str">
         <f>data!$B$5</f>
       </c>
-      <c r="I28" s="14" t="str">
-        <f>data!$B$12</f>
-      </c>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
-      <c r="O28" s="14" t="str">
-        <f>data!$B$11</f>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="14">
+      <c r="B36" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D37:D41)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37:B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37:C41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37:E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37:F41," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C36" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37:B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37:C41," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37:E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37:F41," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F36" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D37:D41)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37:E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37:F41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37:B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37:C41," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="G36" s="14" t="str">
+        <f>data!$B$3</f>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18">
         <v>1</v>
       </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14">
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18">
         <v>1</v>
       </c>
-      <c r="I29" s="14">
-        <v>1</v>
-      </c>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
-      <c r="O29" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14">
+    </row>
+    <row r="38">
+      <c r="A38" s="18">
         <v>2</v>
       </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14">
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18">
         <v>2</v>
       </c>
-      <c r="I30" s="14">
-        <v>2</v>
-      </c>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="14">
+    </row>
+    <row r="39">
+      <c r="A39" s="18">
         <v>3</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14">
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18">
         <v>3</v>
       </c>
-      <c r="I31" s="14">
-        <v>3</v>
-      </c>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
-      <c r="N31" s="14"/>
-      <c r="O31" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="14">
+    </row>
+    <row r="40">
+      <c r="A40" s="18">
         <v>4</v>
       </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14">
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18">
         <v>4</v>
       </c>
-      <c r="I32" s="14">
-        <v>4</v>
-      </c>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="14">
+    </row>
+    <row r="41">
+      <c r="A41" s="18">
         <v>5</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14">
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18">
         <v>5</v>
       </c>
-      <c r="I33" s="14">
-        <v>5</v>
-      </c>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="14" t="str">
-        <f>data!$B$6</f>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F35" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="G35" s="14" t="str">
-        <f>data!$B$5</f>
-      </c>
-      <c r="I35" s="14" t="str">
-        <f>data!$B$12</f>
-      </c>
-      <c r="J35" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K35" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L35" s="14"/>
-      <c r="M35" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="N35" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="O35" s="14" t="str">
-        <f>data!$B$11</f>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="I36" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="17" t="s">
+    </row>
+    <row r="43">
+      <c r="A43" s="17" t="s">
         <v>35</v>
-      </c>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="14" t="str">
-        <f>data!$B$6</f>
-      </c>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14" t="str">
-        <f>data!$B$3</f>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="14">
-        <v>1</v>
-      </c>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="14">
-        <v>2</v>
-      </c>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="14">
-        <v>3</v>
       </c>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
+      <c r="D43" s="14" t="s">
+        <v>36</v>
+      </c>
       <c r="E43" s="14"/>
       <c r="F43" s="14"/>
-      <c r="G43" s="14">
+      <c r="G43" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="str">
+        <f>data!$B$6</f>
+      </c>
+      <c r="B44" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D45:D49)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45:B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45:C49," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45:E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45:F49," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C44" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45:B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45:C49," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45:E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45:F49," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F44" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D45:D49)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45:E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45:F49," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45:B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45:C49," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="G44" s="14" t="str">
+        <f>data!$B$4</f>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="18">
+        <v>1</v>
+      </c>
+      <c r="B45" s="18"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="18">
+        <v>2</v>
+      </c>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="18">
         <v>3</v>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="14">
+      <c r="B47" s="18"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="18">
         <v>4</v>
       </c>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14">
+      <c r="B48" s="18"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18">
         <v>4</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="14">
+    <row r="49">
+      <c r="A49" s="18">
         <v>5</v>
       </c>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14">
+      <c r="B49" s="18"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="18">
         <v>5</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="14" t="str">
+    <row r="52">
+      <c r="A52" s="13"/>
+      <c r="B52" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="I52" s="13"/>
+      <c r="J52" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K52" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="L52" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <f>data!$B$3</f>
+      </c>
+      <c r="B53" s="14" t="str">
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,IF(OR(F4&gt;B4,AND(F4=B4,E4&gt;C4)),1,0)),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),IF(OR(D28="X",D28="x"),0,IF(OR(F28&gt;B28,AND(F28=B28,E28&gt;C28)),1,0)),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,IF(OR(F36&gt;B36,AND(F36=B36,E36&gt;C36)),1,0)),0)</f>
+      </c>
+      <c r="C53" s="14" t="str">
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,IF(OR(F4&lt;B4,AND(F4=B4,E4&lt;C4)),1,0)),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),IF(OR(D28="X",D28="x"),0,IF(OR(F28&lt;B28,AND(F28=B28,E28&lt;C28)),1,0)),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,IF(OR(F36&lt;B36,AND(F36=B36,E36&lt;C36)),1,0)),0)</f>
+      </c>
+      <c r="D53" s="14" t="str">
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),1,0),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),IF(OR(D28="X",D28="x"),1,0),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),1,0),0)</f>
+      </c>
+      <c r="I53" t="str">
+        <f>data!$B$10</f>
+      </c>
+      <c r="J53" s="14" t="str">
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,IF(OR(N4&gt;J4,AND(N4=J4,M4&gt;K4)),1,0)),0)+IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),IF(OR(L12="X",L12="x"),0,IF(OR(N12&gt;J12,AND(N12=J12,M12&gt;K12)),1,0)),0)</f>
+      </c>
+      <c r="K53" s="14" t="str">
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,IF(OR(N4&lt;J4,AND(N4=J4,M4&lt;K4)),1,0)),0)+IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),IF(OR(L12="X",L12="x"),0,IF(OR(N12&lt;J12,AND(N12=J12,M12&lt;K12)),1,0)),0)</f>
+      </c>
+      <c r="L53" s="14" t="str">
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),1,0),0)+IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),IF(OR(L12="X",L12="x"),1,0),0)</f>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <f>data!$B$4</f>
+      </c>
+      <c r="B54" s="14" t="str">
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,IF(OR(B4&gt;F4,AND(B4=F4,C4&gt;E4)),1,0)),0)+IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),IF(OR(D12="X",D12="x"),0,IF(OR(B12&gt;F12,AND(B12=F12,C12&gt;E12)),1,0)),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),IF(OR(D44="X",D44="x"),0,IF(OR(F44&gt;B44,AND(F44=B44,E44&gt;C44)),1,0)),0)</f>
+      </c>
+      <c r="C54" s="14" t="str">
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,IF(OR(B4&lt;F4,AND(B4=F4,C4&lt;E4)),1,0)),0)+IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),IF(OR(D12="X",D12="x"),0,IF(OR(B12&lt;F12,AND(B12=F12,C12&lt;E12)),1,0)),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),IF(OR(D44="X",D44="x"),0,IF(OR(F44&lt;B44,AND(F44=B44,E44&lt;C44)),1,0)),0)</f>
+      </c>
+      <c r="D54" s="14" t="str">
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),1,0),0)+IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),IF(OR(D12="X",D12="x"),1,0),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),IF(OR(D44="X",D44="x"),1,0),0)</f>
+      </c>
+      <c r="I54" t="str">
+        <f>data!$B$11</f>
+      </c>
+      <c r="J54" s="14" t="str">
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,IF(OR(J4&gt;N4,AND(J4=N4,K4&gt;M4)),1,0)),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,IF(OR(N20&gt;J20,AND(N20=J20,M20&gt;K20)),1,0)),0)</f>
+      </c>
+      <c r="K54" s="14" t="str">
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,IF(OR(J4&lt;N4,AND(J4=N4,K4&lt;M4)),1,0)),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,IF(OR(N20&lt;J20,AND(N20=J20,M20&lt;K20)),1,0)),0)</f>
+      </c>
+      <c r="L54" s="14" t="str">
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),1,0),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),1,0),0)</f>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <f>data!$B$5</f>
+      </c>
+      <c r="B55" s="14" t="str">
+        <f>IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),IF(OR(D12="X",D12="x"),0,IF(OR(F12&gt;B12,AND(F12=B12,E12&gt;C12)),1,0)),0)+IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,IF(OR(F20&gt;B20,AND(F20=B20,E20&gt;C20)),1,0)),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,IF(OR(B36&gt;F36,AND(B36=F36,C36&gt;E36)),1,0)),0)</f>
+      </c>
+      <c r="C55" s="14" t="str">
+        <f>IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),IF(OR(D12="X",D12="x"),0,IF(OR(F12&lt;B12,AND(F12=B12,E12&lt;C12)),1,0)),0)+IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,IF(OR(F20&lt;B20,AND(F20=B20,E20&lt;C20)),1,0)),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,IF(OR(B36&lt;F36,AND(B36=F36,C36&lt;E36)),1,0)),0)</f>
+      </c>
+      <c r="D55" s="14" t="str">
+        <f>IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),IF(OR(D12="X",D12="x"),1,0),0)+IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),1,0),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),1,0),0)</f>
+      </c>
+      <c r="I55" t="str">
+        <f>data!$B$12</f>
+      </c>
+      <c r="J55" s="14" t="str">
+        <f>IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),IF(OR(L12="X",L12="x"),0,IF(OR(J12&gt;N12,AND(J12=N12,K12&gt;M12)),1,0)),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,IF(OR(J20&gt;N20,AND(J20=N20,K20&gt;M20)),1,0)),0)</f>
+      </c>
+      <c r="K55" s="14" t="str">
+        <f>IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),IF(OR(L12="X",L12="x"),0,IF(OR(J12&lt;N12,AND(J12=N12,K12&lt;M12)),1,0)),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,IF(OR(J20&lt;N20,AND(J20=N20,K20&lt;M20)),1,0)),0)</f>
+      </c>
+      <c r="L55" s="14" t="str">
+        <f>IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),IF(OR(L12="X",L12="x"),1,0),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),1,0),0)</f>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
         <f>data!$B$6</f>
       </c>
-      <c r="B47" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F47" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="G47" s="14" t="str">
+      <c r="B56" s="14" t="str">
+        <f>IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,IF(OR(B20&gt;F20,AND(B20=F20,C20&gt;E20)),1,0)),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),IF(OR(D28="X",D28="x"),0,IF(OR(B28&gt;F28,AND(B28=F28,C28&gt;E28)),1,0)),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),IF(OR(D44="X",D44="x"),0,IF(OR(B44&gt;F44,AND(B44=F44,C44&gt;E44)),1,0)),0)</f>
+      </c>
+      <c r="C56" s="14" t="str">
+        <f>IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,IF(OR(B20&lt;F20,AND(B20=F20,C20&lt;E20)),1,0)),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),IF(OR(D28="X",D28="x"),0,IF(OR(B28&lt;F28,AND(B28=F28,C28&lt;E28)),1,0)),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),IF(OR(D44="X",D44="x"),0,IF(OR(B44&lt;F44,AND(B44=F44,C44&lt;E44)),1,0)),0)</f>
+      </c>
+      <c r="D56" s="14" t="str">
+        <f>IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),1,0),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),IF(OR(D28="X",D28="x"),1,0),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),IF(OR(D44="X",D44="x"),1,0),0)</f>
+      </c>
+    </row>
+    <row r="57">
+      <c r="I57" s="13"/>
+      <c r="J57" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="K57" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="L57" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="M57" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="N57" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13"/>
+      <c r="B58" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="F58" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I58" t="str">
+        <f>data!$B$10</f>
+      </c>
+      <c r="J58" s="14" t="str">
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),N4,0)+IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),N12,0)</f>
+      </c>
+      <c r="K58" s="14" t="str">
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),J4,0)+IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),J12,0)</f>
+      </c>
+      <c r="L58" s="14" t="str">
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),(IF(OR(L5="X",L5="x"),1,0)+IF(OR(L6="X",L6="x"),1,0)+IF(OR(L7="X",L7="x"),1,0)+IF(OR(L8="X",L8="x"),1,0)+IF(OR(L9="X",L9="x"),1,0)),0)+IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),(IF(OR(L13="X",L13="x"),1,0)+IF(OR(L14="X",L14="x"),1,0)+IF(OR(L15="X",L15="x"),1,0)+IF(OR(L16="X",L16="x"),1,0)+IF(OR(L17="X",L17="x"),1,0)),0)</f>
+      </c>
+      <c r="M58" s="14" t="str">
+        <f>M4+M12</f>
+      </c>
+      <c r="N58" s="14" t="str">
+        <f>K4+K12</f>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
         <f>data!$B$3</f>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="17" t="s">
+      <c r="B59" s="14" t="str">
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),F4,0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),F28,0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),F36,0)</f>
+      </c>
+      <c r="C59" s="14" t="str">
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),B4,0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),B28,0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),B36,0)</f>
+      </c>
+      <c r="D59" s="14" t="str">
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),(IF(OR(D5="X",D5="x"),1,0)+IF(OR(D6="X",D6="x"),1,0)+IF(OR(D7="X",D7="x"),1,0)+IF(OR(D8="X",D8="x"),1,0)+IF(OR(D9="X",D9="x"),1,0)),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),(IF(OR(D29="X",D29="x"),1,0)+IF(OR(D30="X",D30="x"),1,0)+IF(OR(D31="X",D31="x"),1,0)+IF(OR(D32="X",D32="x"),1,0)+IF(OR(D33="X",D33="x"),1,0)),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),(IF(OR(D37="X",D37="x"),1,0)+IF(OR(D38="X",D38="x"),1,0)+IF(OR(D39="X",D39="x"),1,0)+IF(OR(D40="X",D40="x"),1,0)+IF(OR(D41="X",D41="x"),1,0)),0)</f>
+      </c>
+      <c r="E59" s="14" t="str">
+        <f>E4+E28+E36</f>
+      </c>
+      <c r="F59" s="14" t="str">
+        <f>C4+C28+C36</f>
+      </c>
+      <c r="I59" t="str">
+        <f>data!$B$11</f>
+      </c>
+      <c r="J59" s="14" t="str">
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),J4,0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),N20,0)</f>
+      </c>
+      <c r="K59" s="14" t="str">
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),N4,0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),J20,0)</f>
+      </c>
+      <c r="L59" s="14" t="str">
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),(IF(OR(L5="X",L5="x"),1,0)+IF(OR(L6="X",L6="x"),1,0)+IF(OR(L7="X",L7="x"),1,0)+IF(OR(L8="X",L8="x"),1,0)+IF(OR(L9="X",L9="x"),1,0)),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),(IF(OR(L21="X",L21="x"),1,0)+IF(OR(L22="X",L22="x"),1,0)+IF(OR(L23="X",L23="x"),1,0)+IF(OR(L24="X",L24="x"),1,0)+IF(OR(L25="X",L25="x"),1,0)),0)</f>
+      </c>
+      <c r="M59" s="14" t="str">
+        <f>K4+M20</f>
+      </c>
+      <c r="N59" s="14" t="str">
+        <f>M4+K20</f>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <f>data!$B$4</f>
+      </c>
+      <c r="B60" s="14" t="str">
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),B4,0)+IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),B12,0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),F44,0)</f>
+      </c>
+      <c r="C60" s="14" t="str">
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),F4,0)+IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),F12,0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),B44,0)</f>
+      </c>
+      <c r="D60" s="14" t="str">
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),(IF(OR(D5="X",D5="x"),1,0)+IF(OR(D6="X",D6="x"),1,0)+IF(OR(D7="X",D7="x"),1,0)+IF(OR(D8="X",D8="x"),1,0)+IF(OR(D9="X",D9="x"),1,0)),0)+IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),(IF(OR(D13="X",D13="x"),1,0)+IF(OR(D14="X",D14="x"),1,0)+IF(OR(D15="X",D15="x"),1,0)+IF(OR(D16="X",D16="x"),1,0)+IF(OR(D17="X",D17="x"),1,0)),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),(IF(OR(D45="X",D45="x"),1,0)+IF(OR(D46="X",D46="x"),1,0)+IF(OR(D47="X",D47="x"),1,0)+IF(OR(D48="X",D48="x"),1,0)+IF(OR(D49="X",D49="x"),1,0)),0)</f>
+      </c>
+      <c r="E60" s="14" t="str">
+        <f>C4+C12+E44</f>
+      </c>
+      <c r="F60" s="14" t="str">
+        <f>E4+E12+C44</f>
+      </c>
+      <c r="I60" t="str">
+        <f>data!$B$12</f>
+      </c>
+      <c r="J60" s="14" t="str">
+        <f>IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),J12,0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),J20,0)</f>
+      </c>
+      <c r="K60" s="14" t="str">
+        <f>IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),N12,0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),N20,0)</f>
+      </c>
+      <c r="L60" s="14" t="str">
+        <f>IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),(IF(OR(L13="X",L13="x"),1,0)+IF(OR(L14="X",L14="x"),1,0)+IF(OR(L15="X",L15="x"),1,0)+IF(OR(L16="X",L16="x"),1,0)+IF(OR(L17="X",L17="x"),1,0)),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),(IF(OR(L21="X",L21="x"),1,0)+IF(OR(L22="X",L22="x"),1,0)+IF(OR(L23="X",L23="x"),1,0)+IF(OR(L24="X",L24="x"),1,0)+IF(OR(L25="X",L25="x"),1,0)),0)</f>
+      </c>
+      <c r="M60" s="14" t="str">
+        <f>K12+K20</f>
+      </c>
+      <c r="N60" s="14" t="str">
+        <f>M12+M20</f>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <f>data!$B$5</f>
+      </c>
+      <c r="B61" s="14" t="str">
+        <f>IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),F12,0)+IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),F20,0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),B36,0)</f>
+      </c>
+      <c r="C61" s="14" t="str">
+        <f>IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),B12,0)+IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),B20,0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),F36,0)</f>
+      </c>
+      <c r="D61" s="14" t="str">
+        <f>IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),(IF(OR(D13="X",D13="x"),1,0)+IF(OR(D14="X",D14="x"),1,0)+IF(OR(D15="X",D15="x"),1,0)+IF(OR(D16="X",D16="x"),1,0)+IF(OR(D17="X",D17="x"),1,0)),0)+IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),(IF(OR(D21="X",D21="x"),1,0)+IF(OR(D22="X",D22="x"),1,0)+IF(OR(D23="X",D23="x"),1,0)+IF(OR(D24="X",D24="x"),1,0)+IF(OR(D25="X",D25="x"),1,0)),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),(IF(OR(D37="X",D37="x"),1,0)+IF(OR(D38="X",D38="x"),1,0)+IF(OR(D39="X",D39="x"),1,0)+IF(OR(D40="X",D40="x"),1,0)+IF(OR(D41="X",D41="x"),1,0)),0)</f>
+      </c>
+      <c r="E61" s="14" t="str">
+        <f>E12+E20+C36</f>
+      </c>
+      <c r="F61" s="14" t="str">
+        <f>C12+C20+E36</f>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <f>data!$B$6</f>
+      </c>
+      <c r="B62" s="14" t="str">
+        <f>IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),B20,0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),B28,0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),B44,0)</f>
+      </c>
+      <c r="C62" s="14" t="str">
+        <f>IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),F20,0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),F28,0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),F44,0)</f>
+      </c>
+      <c r="D62" s="14" t="str">
+        <f>IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),(IF(OR(D21="X",D21="x"),1,0)+IF(OR(D22="X",D22="x"),1,0)+IF(OR(D23="X",D23="x"),1,0)+IF(OR(D24="X",D24="x"),1,0)+IF(OR(D25="X",D25="x"),1,0)),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),(IF(OR(D29="X",D29="x"),1,0)+IF(OR(D30="X",D30="x"),1,0)+IF(OR(D31="X",D31="x"),1,0)+IF(OR(D32="X",D32="x"),1,0)+IF(OR(D33="X",D33="x"),1,0)),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),(IF(OR(D45="X",D45="x"),1,0)+IF(OR(D46="X",D46="x"),1,0)+IF(OR(D47="X",D47="x"),1,0)+IF(OR(D48="X",D48="x"),1,0)+IF(OR(D49="X",D49="x"),1,0)),0)</f>
+      </c>
+      <c r="E62" s="14" t="str">
+        <f>C20+C28+C44</f>
+      </c>
+      <c r="F62" s="14" t="str">
+        <f>E20+E28+E44</f>
+      </c>
+    </row>
+    <row r="63">
+      <c r="N63" s="13"/>
+      <c r="O63" s="13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="N64" t="s">
+        <v>47</v>
+      </c>
+      <c r="O64" s="19"/>
+    </row>
+    <row r="65">
+      <c r="F65" s="13"/>
+      <c r="G65" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="N65" t="s">
+        <v>48</v>
+      </c>
+      <c r="O65" s="19"/>
+    </row>
+    <row r="66">
+      <c r="F66" t="s">
+        <v>47</v>
+      </c>
+      <c r="G66" s="19"/>
+      <c r="N66" t="s">
+        <v>49</v>
+      </c>
+      <c r="O66" s="19"/>
+    </row>
+    <row r="67">
+      <c r="F67" t="s">
+        <v>48</v>
+      </c>
+      <c r="G67" s="19"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="str">
+        <f>data!$A$9</f>
+      </c>
+      <c r="B68" s="13"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="13"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="17" t="s">
         <v>35</v>
-      </c>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="14" t="str">
-        <f>data!$B$5</f>
-      </c>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14" t="str">
-        <f>data!$B$3</f>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="14">
-        <v>1</v>
-      </c>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="14">
-        <v>2</v>
-      </c>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="14">
-        <v>3</v>
-      </c>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="14">
-        <v>4</v>
-      </c>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="14">
-        <v>5</v>
-      </c>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="14" t="str">
-        <f>data!$B$5</f>
-      </c>
-      <c r="B59" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C59" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F59" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="G59" s="14" t="str">
-        <f>data!$B$3</f>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="14" t="str">
-        <f>data!$B$6</f>
-      </c>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14" t="str">
-        <f>data!$B$4</f>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="14">
-        <v>1</v>
-      </c>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="14">
-        <v>2</v>
-      </c>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="14">
-        <v>3</v>
-      </c>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="14">
-        <v>4</v>
-      </c>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="14">
-        <v>5</v>
       </c>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
+      <c r="D69" s="14" t="s">
+        <v>36</v>
+      </c>
       <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14">
+      <c r="F69" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G69" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="14" t="str">
+        <f>data!$B$8</f>
+      </c>
+      <c r="B70" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D71:D75)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71:B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71:C75," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71:E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71:F75," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C70" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71:B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71:C75," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="D70" s="18"/>
+      <c r="E70" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71:E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71:F75," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F70" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D71:D75)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71:E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71:F75," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71:B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71:C75," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="G70" s="14" t="str">
+        <f>data!$B$7</f>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="18">
+        <v>1</v>
+      </c>
+      <c r="B71" s="18"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="18"/>
+      <c r="E71" s="18"/>
+      <c r="F71" s="18"/>
+      <c r="G71" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="18">
+        <v>2</v>
+      </c>
+      <c r="B72" s="18"/>
+      <c r="C72" s="18"/>
+      <c r="D72" s="18"/>
+      <c r="E72" s="18"/>
+      <c r="F72" s="18"/>
+      <c r="G72" s="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="18">
+        <v>3</v>
+      </c>
+      <c r="B73" s="18"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="18">
+        <v>4</v>
+      </c>
+      <c r="B74" s="18"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="18"/>
+      <c r="E74" s="18"/>
+      <c r="F74" s="18"/>
+      <c r="G74" s="18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="18">
         <v>5</v>
       </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="14" t="str">
-        <f>data!$B$6</f>
-      </c>
-      <c r="B71" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C71" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F71" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="G71" s="14" t="str">
-        <f>data!$B$4</f>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="F73" t="s">
-        <v>41</v>
-      </c>
-      <c r="G73" s="15"/>
-      <c r="N73" t="s">
-        <v>41</v>
-      </c>
-      <c r="O73" s="15"/>
-    </row>
-    <row r="74">
-      <c r="F74" t="s">
-        <v>42</v>
-      </c>
-      <c r="G74" s="15"/>
-      <c r="N74" t="s">
-        <v>42</v>
-      </c>
-      <c r="O74" s="15"/>
-    </row>
-    <row r="75">
-      <c r="F75" t="s">
-        <v>43</v>
-      </c>
-      <c r="G75" s="15"/>
-      <c r="N75" t="s">
-        <v>43</v>
-      </c>
-      <c r="O75" s="15"/>
-    </row>
-    <row r="76">
-      <c r="F76" t="s">
-        <v>44</v>
-      </c>
-      <c r="G76" s="15"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="18"/>
+      <c r="E75" s="18"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B77" s="14"/>
+      <c r="C77" s="14"/>
+      <c r="D77" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E77" s="14"/>
+      <c r="F77" s="14"/>
+      <c r="G77" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="14" t="str">
+        <f>data!$B$9</f>
+      </c>
+      <c r="B78" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D79:D83)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B79:B83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C79:C83," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E79:E83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F79:F83," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C78" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B79:B83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C79:C83," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="D78" s="18"/>
+      <c r="E78" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E79:E83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F79:F83," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F78" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D79:D83)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E79:E83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F79:F83," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B79:B83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C79:C83," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="G78" s="14" t="str">
+        <f>data!$B$7</f>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="13" t="str">
-        <f>data!$A$9</f>
-      </c>
-      <c r="B79" s="13"/>
-      <c r="C79" s="13"/>
-      <c r="D79" s="13"/>
-      <c r="E79" s="13"/>
-      <c r="F79" s="13"/>
-      <c r="G79" s="13"/>
+      <c r="A79" s="18">
+        <v>1</v>
+      </c>
+      <c r="B79" s="18"/>
+      <c r="C79" s="18"/>
+      <c r="D79" s="18"/>
+      <c r="E79" s="18"/>
+      <c r="F79" s="18"/>
+      <c r="G79" s="18">
+        <v>1</v>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="17" t="s">
+      <c r="A80" s="18">
+        <v>2</v>
+      </c>
+      <c r="B80" s="18"/>
+      <c r="C80" s="18"/>
+      <c r="D80" s="18"/>
+      <c r="E80" s="18"/>
+      <c r="F80" s="18"/>
+      <c r="G80" s="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="18">
+        <v>3</v>
+      </c>
+      <c r="B81" s="18"/>
+      <c r="C81" s="18"/>
+      <c r="D81" s="18"/>
+      <c r="E81" s="18"/>
+      <c r="F81" s="18"/>
+      <c r="G81" s="18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="18">
+        <v>4</v>
+      </c>
+      <c r="B82" s="18"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="18"/>
+      <c r="E82" s="18"/>
+      <c r="F82" s="18"/>
+      <c r="G82" s="18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="18">
+        <v>5</v>
+      </c>
+      <c r="B83" s="18"/>
+      <c r="C83" s="18"/>
+      <c r="D83" s="18"/>
+      <c r="E83" s="18"/>
+      <c r="F83" s="18"/>
+      <c r="G83" s="18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="17" t="s">
         <v>35</v>
-      </c>
-      <c r="B80" s="14"/>
-      <c r="C80" s="14"/>
-      <c r="D80" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E80" s="14"/>
-      <c r="F80" s="14"/>
-      <c r="G80" s="16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="14" t="str">
-        <f>data!$B$8</f>
-      </c>
-      <c r="B81" s="14"/>
-      <c r="C81" s="14"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14" t="str">
-        <f>data!$B$7</f>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="14">
-        <v>1</v>
-      </c>
-      <c r="B82" s="14"/>
-      <c r="C82" s="14"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="14">
-        <v>2</v>
-      </c>
-      <c r="B83" s="14"/>
-      <c r="C83" s="14"/>
-      <c r="D83" s="14"/>
-      <c r="E83" s="14"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="14">
-        <v>3</v>
-      </c>
-      <c r="B84" s="14"/>
-      <c r="C84" s="14"/>
-      <c r="D84" s="14"/>
-      <c r="E84" s="14"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="14">
-        <v>4</v>
       </c>
       <c r="B85" s="14"/>
       <c r="C85" s="14"/>
-      <c r="D85" s="14"/>
+      <c r="D85" s="14" t="s">
+        <v>36</v>
+      </c>
       <c r="E85" s="14"/>
       <c r="F85" s="14"/>
-      <c r="G85" s="14">
+      <c r="G85" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="14" t="str">
+        <f>data!$B$9</f>
+      </c>
+      <c r="B86" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D87:D91)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87:B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87:C91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87:E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87:F91," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C86" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87:B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87:C91," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="D86" s="18"/>
+      <c r="E86" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87:E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87:F91," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F86" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D87:D91)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87:E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87:F91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87:B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87:C91," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="G86" s="14" t="str">
+        <f>data!$B$8</f>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="18">
+        <v>1</v>
+      </c>
+      <c r="B87" s="18"/>
+      <c r="C87" s="18"/>
+      <c r="D87" s="18"/>
+      <c r="E87" s="18"/>
+      <c r="F87" s="18"/>
+      <c r="G87" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="18">
+        <v>2</v>
+      </c>
+      <c r="B88" s="18"/>
+      <c r="C88" s="18"/>
+      <c r="D88" s="18"/>
+      <c r="E88" s="18"/>
+      <c r="F88" s="18"/>
+      <c r="G88" s="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="18">
+        <v>3</v>
+      </c>
+      <c r="B89" s="18"/>
+      <c r="C89" s="18"/>
+      <c r="D89" s="18"/>
+      <c r="E89" s="18"/>
+      <c r="F89" s="18"/>
+      <c r="G89" s="18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="18">
         <v>4</v>
       </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="14">
+      <c r="B90" s="18"/>
+      <c r="C90" s="18"/>
+      <c r="D90" s="18"/>
+      <c r="E90" s="18"/>
+      <c r="F90" s="18"/>
+      <c r="G90" s="18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="18">
         <v>5</v>
       </c>
-      <c r="B86" s="14"/>
-      <c r="C86" s="14"/>
-      <c r="D86" s="14"/>
-      <c r="E86" s="14"/>
-      <c r="F86" s="14"/>
-      <c r="G86" s="14">
+      <c r="B91" s="18"/>
+      <c r="C91" s="18"/>
+      <c r="D91" s="18"/>
+      <c r="E91" s="18"/>
+      <c r="F91" s="18"/>
+      <c r="G91" s="18">
         <v>5</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="14" t="str">
+    <row r="94">
+      <c r="A94" s="13"/>
+      <c r="B94" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <f>data!$B$7</f>
+      </c>
+      <c r="B95" s="14" t="str">
+        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),IF(OR(D70="X",D70="x"),0,IF(OR(F70&gt;B70,AND(F70=B70,E70&gt;C70)),1,0)),0)+IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),IF(OR(D78="X",D78="x"),0,IF(OR(F78&gt;B78,AND(F78=B78,E78&gt;C78)),1,0)),0)</f>
+      </c>
+      <c r="C95" s="14" t="str">
+        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),IF(OR(D70="X",D70="x"),0,IF(OR(F70&lt;B70,AND(F70=B70,E70&lt;C70)),1,0)),0)+IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),IF(OR(D78="X",D78="x"),0,IF(OR(F78&lt;B78,AND(F78=B78,E78&lt;C78)),1,0)),0)</f>
+      </c>
+      <c r="D95" s="14" t="str">
+        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),IF(OR(D70="X",D70="x"),1,0),0)+IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),IF(OR(D78="X",D78="x"),1,0),0)</f>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
         <f>data!$B$8</f>
       </c>
-      <c r="B88" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C88" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F88" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="G88" s="14" t="str">
+      <c r="B96" s="14" t="str">
+        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),IF(OR(D70="X",D70="x"),0,IF(OR(B70&gt;F70,AND(B70=F70,C70&gt;E70)),1,0)),0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),IF(OR(D86="X",D86="x"),0,IF(OR(F86&gt;B86,AND(F86=B86,E86&gt;C86)),1,0)),0)</f>
+      </c>
+      <c r="C96" s="14" t="str">
+        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),IF(OR(D70="X",D70="x"),0,IF(OR(B70&lt;F70,AND(B70=F70,C70&lt;E70)),1,0)),0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),IF(OR(D86="X",D86="x"),0,IF(OR(F86&lt;B86,AND(F86=B86,E86&lt;C86)),1,0)),0)</f>
+      </c>
+      <c r="D96" s="14" t="str">
+        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),IF(OR(D70="X",D70="x"),1,0),0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),IF(OR(D86="X",D86="x"),1,0),0)</f>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <f>data!$B$9</f>
+      </c>
+      <c r="B97" s="14" t="str">
+        <f>IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),IF(OR(D78="X",D78="x"),0,IF(OR(B78&gt;F78,AND(B78=F78,C78&gt;E78)),1,0)),0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),IF(OR(D86="X",D86="x"),0,IF(OR(B86&gt;F86,AND(B86=F86,C86&gt;E86)),1,0)),0)</f>
+      </c>
+      <c r="C97" s="14" t="str">
+        <f>IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),IF(OR(D78="X",D78="x"),0,IF(OR(B78&lt;F78,AND(B78=F78,C78&lt;E78)),1,0)),0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),IF(OR(D86="X",D86="x"),0,IF(OR(B86&lt;F86,AND(B86=F86,C86&lt;E86)),1,0)),0)</f>
+      </c>
+      <c r="D97" s="14" t="str">
+        <f>IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),IF(OR(D78="X",D78="x"),1,0),0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),IF(OR(D86="X",D86="x"),1,0),0)</f>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="13"/>
+      <c r="B99" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C99" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D99" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E99" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="F99" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
         <f>data!$B$7</f>
       </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B89" s="14"/>
-      <c r="C89" s="14"/>
-      <c r="D89" s="14"/>
-      <c r="E89" s="14"/>
-      <c r="F89" s="14"/>
-      <c r="G89" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B92" s="14"/>
-      <c r="C92" s="14"/>
-      <c r="D92" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E92" s="14"/>
-      <c r="F92" s="14"/>
-      <c r="G92" s="16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="14" t="str">
+      <c r="B100" s="14" t="str">
+        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),F70,0)+IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),F78,0)</f>
+      </c>
+      <c r="C100" s="14" t="str">
+        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),B70,0)+IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),B78,0)</f>
+      </c>
+      <c r="D100" s="14" t="str">
+        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),(IF(OR(D71="X",D71="x"),1,0)+IF(OR(D72="X",D72="x"),1,0)+IF(OR(D73="X",D73="x"),1,0)+IF(OR(D74="X",D74="x"),1,0)+IF(OR(D75="X",D75="x"),1,0)),0)+IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),(IF(OR(D79="X",D79="x"),1,0)+IF(OR(D80="X",D80="x"),1,0)+IF(OR(D81="X",D81="x"),1,0)+IF(OR(D82="X",D82="x"),1,0)+IF(OR(D83="X",D83="x"),1,0)),0)</f>
+      </c>
+      <c r="E100" s="14" t="str">
+        <f>E70+E78</f>
+      </c>
+      <c r="F100" s="14" t="str">
+        <f>C70+C78</f>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <f>data!$B$8</f>
+      </c>
+      <c r="B101" s="14" t="str">
+        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),B70,0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),F86,0)</f>
+      </c>
+      <c r="C101" s="14" t="str">
+        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),F70,0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),B86,0)</f>
+      </c>
+      <c r="D101" s="14" t="str">
+        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),(IF(OR(D71="X",D71="x"),1,0)+IF(OR(D72="X",D72="x"),1,0)+IF(OR(D73="X",D73="x"),1,0)+IF(OR(D74="X",D74="x"),1,0)+IF(OR(D75="X",D75="x"),1,0)),0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),(IF(OR(D87="X",D87="x"),1,0)+IF(OR(D88="X",D88="x"),1,0)+IF(OR(D89="X",D89="x"),1,0)+IF(OR(D90="X",D90="x"),1,0)+IF(OR(D91="X",D91="x"),1,0)),0)</f>
+      </c>
+      <c r="E101" s="14" t="str">
+        <f>C70+E86</f>
+      </c>
+      <c r="F101" s="14" t="str">
+        <f>E70+C86</f>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
         <f>data!$B$9</f>
       </c>
-      <c r="B93" s="14"/>
-      <c r="C93" s="14"/>
-      <c r="D93" s="14"/>
-      <c r="E93" s="14"/>
-      <c r="F93" s="14"/>
-      <c r="G93" s="14" t="str">
-        <f>data!$B$7</f>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="14">
-        <v>1</v>
-      </c>
-      <c r="B94" s="14"/>
-      <c r="C94" s="14"/>
-      <c r="D94" s="14"/>
-      <c r="E94" s="14"/>
-      <c r="F94" s="14"/>
-      <c r="G94" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="14">
-        <v>2</v>
-      </c>
-      <c r="B95" s="14"/>
-      <c r="C95" s="14"/>
-      <c r="D95" s="14"/>
-      <c r="E95" s="14"/>
-      <c r="F95" s="14"/>
-      <c r="G95" s="14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="14">
-        <v>3</v>
-      </c>
-      <c r="B96" s="14"/>
-      <c r="C96" s="14"/>
-      <c r="D96" s="14"/>
-      <c r="E96" s="14"/>
-      <c r="F96" s="14"/>
-      <c r="G96" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="14">
-        <v>4</v>
-      </c>
-      <c r="B97" s="14"/>
-      <c r="C97" s="14"/>
-      <c r="D97" s="14"/>
-      <c r="E97" s="14"/>
-      <c r="F97" s="14"/>
-      <c r="G97" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="14">
-        <v>5</v>
-      </c>
-      <c r="B98" s="14"/>
-      <c r="C98" s="14"/>
-      <c r="D98" s="14"/>
-      <c r="E98" s="14"/>
-      <c r="F98" s="14"/>
-      <c r="G98" s="14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="14" t="str">
-        <f>data!$B$9</f>
-      </c>
-      <c r="B100" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C100" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D100" s="14"/>
-      <c r="E100" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F100" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="G100" s="14" t="str">
-        <f>data!$B$7</f>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B101" s="14"/>
-      <c r="C101" s="14"/>
-      <c r="D101" s="14"/>
-      <c r="E101" s="14"/>
-      <c r="F101" s="14"/>
-      <c r="G101" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B104" s="14"/>
-      <c r="C104" s="14"/>
-      <c r="D104" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E104" s="14"/>
-      <c r="F104" s="14"/>
-      <c r="G104" s="16" t="s">
-        <v>37</v>
+      <c r="B102" s="14" t="str">
+        <f>IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),B78,0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),B86,0)</f>
+      </c>
+      <c r="C102" s="14" t="str">
+        <f>IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),F78,0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),F86,0)</f>
+      </c>
+      <c r="D102" s="14" t="str">
+        <f>IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),(IF(OR(D79="X",D79="x"),1,0)+IF(OR(D80="X",D80="x"),1,0)+IF(OR(D81="X",D81="x"),1,0)+IF(OR(D82="X",D82="x"),1,0)+IF(OR(D83="X",D83="x"),1,0)),0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),(IF(OR(D87="X",D87="x"),1,0)+IF(OR(D88="X",D88="x"),1,0)+IF(OR(D89="X",D89="x"),1,0)+IF(OR(D90="X",D90="x"),1,0)+IF(OR(D91="X",D91="x"),1,0)),0)</f>
+      </c>
+      <c r="E102" s="14" t="str">
+        <f>C78+C86</f>
+      </c>
+      <c r="F102" s="14" t="str">
+        <f>E78+E86</f>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="14" t="str">
-        <f>data!$B$9</f>
-      </c>
-      <c r="B105" s="14"/>
-      <c r="C105" s="14"/>
-      <c r="D105" s="14"/>
-      <c r="E105" s="14"/>
-      <c r="F105" s="14"/>
-      <c r="G105" s="14" t="str">
-        <f>data!$B$8</f>
+      <c r="F105" s="13"/>
+      <c r="G105" s="13" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="14">
-        <v>1</v>
-      </c>
-      <c r="B106" s="14"/>
-      <c r="C106" s="14"/>
-      <c r="D106" s="14"/>
-      <c r="E106" s="14"/>
-      <c r="F106" s="14"/>
-      <c r="G106" s="14">
-        <v>1</v>
-      </c>
+      <c r="F106" t="s">
+        <v>47</v>
+      </c>
+      <c r="G106" s="19"/>
     </row>
     <row r="107">
-      <c r="A107" s="14">
-        <v>2</v>
-      </c>
-      <c r="B107" s="14"/>
-      <c r="C107" s="14"/>
-      <c r="D107" s="14"/>
-      <c r="E107" s="14"/>
-      <c r="F107" s="14"/>
-      <c r="G107" s="14">
-        <v>2</v>
-      </c>
+      <c r="F107" t="s">
+        <v>48</v>
+      </c>
+      <c r="G107" s="19"/>
     </row>
     <row r="108">
-      <c r="A108" s="14">
-        <v>3</v>
-      </c>
-      <c r="B108" s="14"/>
-      <c r="C108" s="14"/>
-      <c r="D108" s="14"/>
-      <c r="E108" s="14"/>
-      <c r="F108" s="14"/>
-      <c r="G108" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="14">
-        <v>4</v>
-      </c>
-      <c r="B109" s="14"/>
-      <c r="C109" s="14"/>
-      <c r="D109" s="14"/>
-      <c r="E109" s="14"/>
-      <c r="F109" s="14"/>
-      <c r="G109" s="14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="14">
-        <v>5</v>
-      </c>
-      <c r="B110" s="14"/>
-      <c r="C110" s="14"/>
-      <c r="D110" s="14"/>
-      <c r="E110" s="14"/>
-      <c r="F110" s="14"/>
-      <c r="G110" s="14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="14" t="str">
-        <f>data!$B$9</f>
-      </c>
-      <c r="B112" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C112" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D112" s="14"/>
-      <c r="E112" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F112" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="G112" s="14" t="str">
-        <f>data!$B$8</f>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B113" s="14"/>
-      <c r="C113" s="14"/>
-      <c r="D113" s="14"/>
-      <c r="E113" s="14"/>
-      <c r="F113" s="14"/>
-      <c r="G113" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="F114" t="s">
-        <v>41</v>
-      </c>
-      <c r="G114" s="15"/>
-    </row>
-    <row r="115">
-      <c r="F115" t="s">
-        <v>42</v>
-      </c>
-      <c r="G115" s="15"/>
-    </row>
-    <row r="116">
-      <c r="F116" t="s">
-        <v>43</v>
-      </c>
-      <c r="G116" s="15"/>
+      <c r="F108" t="s">
+        <v>49</v>
+      </c>
+      <c r="G108" s="19"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="5">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I1:O1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="I2:O2"/>
-    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="A68:G68"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageSetup fitToHeight="0" fitToWidth="2" orientation="portrait" pageOrder="downThenOver" paperSize="9"/>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="1" max="16383" man="true"/>
-    <brk id="38" max="16383" man="true"/>
-    <brk id="78" max="16383" man="true"/>
+    <brk id="44" max="16383" man="true"/>
+    <brk id="67" max="16383" man="true"/>
   </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="8" max="1048575" man="true"/>
@@ -3217,14 +3385,15 @@
     <col customWidth="true" max="4" min="4" width="3"/>
     <col customWidth="true" max="6" min="5" width="5"/>
     <col customWidth="true" max="7" min="7" width="30"/>
-    <col customWidth="true" max="8" min="8" width="2"/>
+    <col customWidth="true" max="8" min="8" width="5"/>
     <col customWidth="true" max="9" min="9" width="30"/>
     <col customWidth="true" max="11" min="10" width="5"/>
     <col customWidth="true" max="12" min="12" width="3"/>
     <col customWidth="true" max="14" min="13" width="5"/>
     <col customWidth="true" max="15" min="15" width="30"/>
-    <col customWidth="true" max="16" min="16" width="2"/>
-    <col customWidth="true" max="20" min="17" width="10.83"/>
+    <col customWidth="true" max="18" min="16" width="5"/>
+    <col customWidth="true" max="19" min="19" width="30"/>
+    <col customWidth="true" max="20" min="20" width="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3249,7 +3418,7 @@
     </row>
     <row r="2">
       <c r="A2" s="13" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -3257,15 +3426,15 @@
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
-      <c r="I2" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
+      <c r="M2" s="13" t="s">
+        <v>65</v>
+      </c>
       <c r="N2" s="13"/>
       <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
     </row>
     <row r="3">
       <c r="A3" s="17" t="s">
@@ -3277,61 +3446,61 @@
       <c r="G3" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="M3" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="L3" s="14" t="s">
+      <c r="P3" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="O3" s="16" t="s">
+      <c r="S3" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G115)</f>
-      </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G107)</f>
+      </c>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O73)</f>
-      </c>
-      <c r="I4" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O74)</f>
-      </c>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G74)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O64)</f>
+      </c>
+      <c r="M4" s="14" t="str">
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O65)</f>
+      </c>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="18"/>
+      <c r="R4" s="18"/>
+      <c r="S4" s="14" t="str">
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G67)</f>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14">
         <v>1</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
       <c r="G5" s="14">
         <v>1</v>
       </c>
-      <c r="I5" s="14">
+      <c r="M5" s="14">
         <v>1</v>
       </c>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14">
+      <c r="N5" s="18"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="18"/>
+      <c r="Q5" s="18"/>
+      <c r="R5" s="18"/>
+      <c r="S5" s="14">
         <v>1</v>
       </c>
     </row>
@@ -3339,23 +3508,23 @@
       <c r="A6" s="14">
         <v>2</v>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
       <c r="G6" s="14">
         <v>2</v>
       </c>
-      <c r="I6" s="14">
+      <c r="M6" s="14">
         <v>2</v>
       </c>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14">
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="14">
         <v>2</v>
       </c>
     </row>
@@ -3363,23 +3532,23 @@
       <c r="A7" s="14">
         <v>3</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
       <c r="G7" s="14">
         <v>3</v>
       </c>
-      <c r="I7" s="14">
+      <c r="M7" s="14">
         <v>3</v>
       </c>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14">
+      <c r="N7" s="18"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="18"/>
+      <c r="Q7" s="18"/>
+      <c r="R7" s="18"/>
+      <c r="S7" s="14">
         <v>3</v>
       </c>
     </row>
@@ -3387,23 +3556,23 @@
       <c r="A8" s="14">
         <v>4</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
       <c r="G8" s="14">
         <v>4</v>
       </c>
-      <c r="I8" s="14">
+      <c r="M8" s="14">
         <v>4</v>
       </c>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14">
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="18"/>
+      <c r="R8" s="18"/>
+      <c r="S8" s="14">
         <v>4</v>
       </c>
     </row>
@@ -3411,69 +3580,69 @@
       <c r="A9" s="14">
         <v>5</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
       <c r="G9" s="14">
         <v>5</v>
       </c>
-      <c r="I9" s="14">
+      <c r="M9" s="14">
         <v>5</v>
       </c>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14">
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="18"/>
+      <c r="R9" s="18"/>
+      <c r="S9" s="14">
         <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G115)</f>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>39</v>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G107)</f>
+      </c>
+      <c r="B11" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C11" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))</f>
       </c>
       <c r="D11" s="14"/>
-      <c r="E11" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>38</v>
+      <c r="E11" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F11" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-",""))))*1)</f>
       </c>
       <c r="G11" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O73)</f>
-      </c>
-      <c r="I11" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O74)</f>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="N11" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="O11" s="14" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G74)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O64)</f>
+      </c>
+      <c r="M11" s="14" t="str">
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O65)</f>
+      </c>
+      <c r="N11" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(P5:P9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(O5:O9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Q5:Q9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(R5:R9," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="O11" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(O5:O9," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Q5:Q9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(R5:R9," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="R11" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(P5:P9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Q5:Q9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(R5:R9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(O5:O9," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="S11" s="14" t="str">
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G67)</f>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
@@ -3481,43 +3650,43 @@
       <c r="E12" s="14"/>
       <c r="F12" s="14"/>
       <c r="G12" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="I12" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
+        <v>62</v>
+      </c>
+      <c r="M12" s="14" t="s">
+        <v>62</v>
+      </c>
       <c r="N12" s="14"/>
-      <c r="O12" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="F14" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14" s="15"/>
-      <c r="N14" t="s">
-        <v>56</v>
-      </c>
-      <c r="O14" s="15"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="14"/>
+      <c r="R12" s="14"/>
+      <c r="S12" s="14" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="15">
       <c r="F15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15" s="15"/>
-      <c r="N15" t="s">
-        <v>57</v>
-      </c>
-      <c r="O15" s="15"/>
+        <v>63</v>
+      </c>
+      <c r="G15" s="19"/>
+      <c r="R15" t="s">
+        <v>63</v>
+      </c>
+      <c r="S15" s="19"/>
+    </row>
+    <row r="16">
+      <c r="F16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16" s="19"/>
+      <c r="R16" t="s">
+        <v>64</v>
+      </c>
+      <c r="S16" s="19"/>
     </row>
     <row r="23">
       <c r="A23" s="13" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -3525,15 +3694,15 @@
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
       <c r="G23" s="13"/>
-      <c r="I23" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13"/>
+      <c r="M23" s="13" t="s">
+        <v>67</v>
+      </c>
       <c r="N23" s="13"/>
       <c r="O23" s="13"/>
+      <c r="P23" s="13"/>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="13"/>
+      <c r="S23" s="13"/>
     </row>
     <row r="24">
       <c r="A24" s="17" t="s">
@@ -3545,61 +3714,61 @@
       <c r="G24" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="I24" s="17" t="s">
+      <c r="M24" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="L24" s="14" t="s">
+      <c r="P24" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="O24" s="16" t="s">
+      <c r="S24" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="str">
-        <f>CONCATENATE("M 1 ",G14)</f>
-      </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
+        <f>CONCATENATE("M 1 ",G15)</f>
+      </c>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
       <c r="G25" s="14" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G73)</f>
-      </c>
-      <c r="I25" s="14" t="str">
-        <f>CONCATENATE("M 2 ",O14)</f>
-      </c>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G114)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G66)</f>
+      </c>
+      <c r="M25" s="14" t="str">
+        <f>CONCATENATE("M 2 ",S15)</f>
+      </c>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="18"/>
+      <c r="Q25" s="18"/>
+      <c r="R25" s="18"/>
+      <c r="S25" s="14" t="str">
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G106)</f>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14">
         <v>1</v>
       </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="14">
         <v>1</v>
       </c>
-      <c r="I26" s="14">
+      <c r="M26" s="14">
         <v>1</v>
       </c>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="14">
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
+      <c r="P26" s="18"/>
+      <c r="Q26" s="18"/>
+      <c r="R26" s="18"/>
+      <c r="S26" s="14">
         <v>1</v>
       </c>
     </row>
@@ -3607,23 +3776,23 @@
       <c r="A27" s="14">
         <v>2</v>
       </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
       <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="I27" s="14">
+      <c r="M27" s="14">
         <v>2</v>
       </c>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
-      <c r="O27" s="14">
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="18"/>
+      <c r="R27" s="18"/>
+      <c r="S27" s="14">
         <v>2</v>
       </c>
     </row>
@@ -3631,23 +3800,23 @@
       <c r="A28" s="14">
         <v>3</v>
       </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="14">
         <v>3</v>
       </c>
-      <c r="I28" s="14">
+      <c r="M28" s="14">
         <v>3</v>
       </c>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
-      <c r="O28" s="14">
+      <c r="N28" s="18"/>
+      <c r="O28" s="18"/>
+      <c r="P28" s="18"/>
+      <c r="Q28" s="18"/>
+      <c r="R28" s="18"/>
+      <c r="S28" s="14">
         <v>3</v>
       </c>
     </row>
@@ -3655,23 +3824,23 @@
       <c r="A29" s="14">
         <v>4</v>
       </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
       <c r="G29" s="14">
         <v>4</v>
       </c>
-      <c r="I29" s="14">
+      <c r="M29" s="14">
         <v>4</v>
       </c>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
-      <c r="O29" s="14">
+      <c r="N29" s="18"/>
+      <c r="O29" s="18"/>
+      <c r="P29" s="18"/>
+      <c r="Q29" s="18"/>
+      <c r="R29" s="18"/>
+      <c r="S29" s="14">
         <v>4</v>
       </c>
     </row>
@@ -3679,69 +3848,69 @@
       <c r="A30" s="14">
         <v>5</v>
       </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
       <c r="G30" s="14">
         <v>5</v>
       </c>
-      <c r="I30" s="14">
+      <c r="M30" s="14">
         <v>5</v>
       </c>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="14">
+      <c r="N30" s="18"/>
+      <c r="O30" s="18"/>
+      <c r="P30" s="18"/>
+      <c r="Q30" s="18"/>
+      <c r="R30" s="18"/>
+      <c r="S30" s="14">
         <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="str">
-        <f>CONCATENATE("M 1 ",G14)</f>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>39</v>
+        <f>CONCATENATE("M 1 ",G15)</f>
+      </c>
+      <c r="B32" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D26:D30)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26:B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C26:C30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E26:E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F26:F30," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C32" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26:B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C26:C30," ",""),"0",""),"-","")))</f>
       </c>
       <c r="D32" s="14"/>
-      <c r="E32" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>38</v>
+      <c r="E32" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E26:E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F26:F30," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F32" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D26:D30)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E26:E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F26:F30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26:B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C26:C30," ",""),"0",""),"-",""))))*1)</f>
       </c>
       <c r="G32" s="14" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G73)</f>
-      </c>
-      <c r="I32" s="14" t="str">
-        <f>CONCATENATE("M 2 ",O14)</f>
-      </c>
-      <c r="J32" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="K32" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="N32" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="O32" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G114)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G66)</f>
+      </c>
+      <c r="M32" s="14" t="str">
+        <f>CONCATENATE("M 2 ",S15)</f>
+      </c>
+      <c r="N32" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(P26:P30)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N26:N30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(O26:O30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Q26:Q30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(R26:R30," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="O32" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N26:N30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(O26:O30," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="P32" s="14"/>
+      <c r="Q32" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Q26:Q30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(R26:R30," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="R32" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(P26:P30)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Q26:Q30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(R26:R30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N26:N30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(O26:O30," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="S32" s="14" t="str">
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G106)</f>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -3749,43 +3918,43 @@
       <c r="E33" s="14"/>
       <c r="F33" s="14"/>
       <c r="G33" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="I33" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
+        <v>62</v>
+      </c>
+      <c r="M33" s="14" t="s">
+        <v>62</v>
+      </c>
       <c r="N33" s="14"/>
-      <c r="O33" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="F35" t="s">
-        <v>56</v>
-      </c>
-      <c r="G35" s="15"/>
-      <c r="N35" t="s">
-        <v>56</v>
-      </c>
-      <c r="O35" s="15"/>
+      <c r="O33" s="14"/>
+      <c r="P33" s="14"/>
+      <c r="Q33" s="14"/>
+      <c r="R33" s="14"/>
+      <c r="S33" s="14" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="36">
       <c r="F36" t="s">
-        <v>57</v>
-      </c>
-      <c r="G36" s="15"/>
-      <c r="N36" t="s">
-        <v>57</v>
-      </c>
-      <c r="O36" s="15"/>
+        <v>63</v>
+      </c>
+      <c r="G36" s="19"/>
+      <c r="R36" t="s">
+        <v>63</v>
+      </c>
+      <c r="S36" s="19"/>
+    </row>
+    <row r="37">
+      <c r="F37" t="s">
+        <v>64</v>
+      </c>
+      <c r="G37" s="19"/>
+      <c r="R37" t="s">
+        <v>64</v>
+      </c>
+      <c r="S37" s="19"/>
     </row>
     <row r="44">
       <c r="A44" s="13" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
@@ -3807,26 +3976,26 @@
     </row>
     <row r="46">
       <c r="A46" s="14" t="str">
-        <f>CONCATENATE("M 4 ",O35)</f>
-      </c>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
+        <f>CONCATENATE("M 4 ",S36)</f>
+      </c>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18"/>
       <c r="G46" s="14" t="str">
-        <f>CONCATENATE("M 3 ",G35)</f>
+        <f>CONCATENATE("M 3 ",G36)</f>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="14">
         <v>1</v>
       </c>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="18"/>
       <c r="G47" s="14">
         <v>1</v>
       </c>
@@ -3835,11 +4004,11 @@
       <c r="A48" s="14">
         <v>2</v>
       </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="18"/>
       <c r="G48" s="14">
         <v>2</v>
       </c>
@@ -3848,11 +4017,11 @@
       <c r="A49" s="14">
         <v>3</v>
       </c>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18"/>
       <c r="G49" s="14">
         <v>3</v>
       </c>
@@ -3861,11 +4030,11 @@
       <c r="A50" s="14">
         <v>4</v>
       </c>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
       <c r="G50" s="14">
         <v>4</v>
       </c>
@@ -3874,39 +4043,39 @@
       <c r="A51" s="14">
         <v>5</v>
       </c>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="18"/>
       <c r="G51" s="14">
         <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="str">
-        <f>CONCATENATE("M 4 ",O35)</f>
-      </c>
-      <c r="B53" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C53" s="14" t="s">
-        <v>39</v>
+        <f>CONCATENATE("M 4 ",S36)</f>
+      </c>
+      <c r="B53" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D47:D51)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47:B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47:C51," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47:E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47:F51," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C53" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47:B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47:C51," ",""),"0",""),"-","")))</f>
       </c>
       <c r="D53" s="14"/>
-      <c r="E53" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F53" s="14" t="s">
-        <v>38</v>
+      <c r="E53" s="18" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47:E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47:F51," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F53" s="18" t="str">
+        <f>SUMPRODUCT((UPPER(D47:D51)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47:E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47:F51," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47:B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47:C51," ",""),"0",""),"-",""))))*1)</f>
       </c>
       <c r="G53" s="14" t="str">
-        <f>CONCATENATE("M 3 ",G35)</f>
+        <f>CONCATENATE("M 3 ",G36)</f>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="14" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
@@ -3914,29 +4083,30 @@
       <c r="E54" s="14"/>
       <c r="F54" s="14"/>
       <c r="G54" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="F56" t="s">
-        <v>56</v>
-      </c>
-      <c r="G56" s="15"/>
+        <v>62</v>
+      </c>
     </row>
     <row r="57">
       <c r="F57" t="s">
-        <v>57</v>
-      </c>
-      <c r="G57" s="15"/>
+        <v>63</v>
+      </c>
+      <c r="G57" s="19"/>
+    </row>
+    <row r="58">
+      <c r="F58" t="s">
+        <v>64</v>
+      </c>
+      <c r="G58" s="19"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="7">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I1:O1"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="I2:O2"/>
+    <mergeCell ref="M2:S2"/>
     <mergeCell ref="A23:G23"/>
-    <mergeCell ref="I23:O23"/>
+    <mergeCell ref="M23:S23"/>
     <mergeCell ref="A44:G44"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
@@ -3980,80 +4150,81 @@
       <c r="P1" s="13"/>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="str">
+      <c r="A4" s="24" t="str">
         <f>data!$A$6</f>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="str">
+      <c r="A5" s="25" t="str">
         <f>"1. " &amp; data!$B$3</f>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="str">
+      <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$4</f>
       </c>
-      <c r="E6" s="21" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G73)</f>
+      <c r="E6" s="23" t="str">
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G66)</f>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="str">
+      <c r="A7" s="26" t="str">
         <f>"3. " &amp; data!$B$5</f>
       </c>
-      <c r="F7" s="20"/>
-      <c r="G7" s="18"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="20"/>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="str">
+      <c r="A8" s="27" t="str">
         <f>"4. " &amp; data!$B$6</f>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="21">
         <v>3</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20"/>
-      <c r="C9" s="21" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O73)</f>
-      </c>
-      <c r="G9" s="18"/>
+      <c r="A9" s="22"/>
+      <c r="C9" s="23" t="str">
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O64)</f>
+      </c>
+      <c r="G9" s="20"/>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="str">
+      <c r="A10" s="24" t="str">
         <f>data!$A$9</f>
       </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="19">
+      <c r="D10" s="22"/>
+      <c r="E10" s="21">
         <v>1</v>
       </c>
       <c r="F10" s="15"/>
-      <c r="G10" s="18"/>
+      <c r="G10" s="20"/>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="str">
+      <c r="A11" s="25" t="str">
         <f>"1. " &amp; data!$B$7</f>
       </c>
-      <c r="C11" s="21" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G115)</f>
+      <c r="C11" s="23" t="str">
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G107)</f>
       </c>
       <c r="D11" s="15"/>
-      <c r="E11" s="18"/>
+      <c r="E11" s="20"/>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="str">
+      <c r="A12" s="26" t="str">
         <f>"2. " &amp; data!$B$8</f>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="str">
+      <c r="A13" s="27" t="str">
         <f>"3. " &amp; data!$B$9</f>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20"/>
+      <c r="A14" s="22"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -4092,58 +4263,59 @@
       <c r="P1" s="13"/>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="str">
+      <c r="A4" s="24" t="str">
         <f>data!$A$12</f>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="str">
+      <c r="A5" s="25" t="str">
         <f>"1. " &amp; data!$B$10</f>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="str">
+      <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$11</f>
       </c>
-      <c r="E6" s="21" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G114)</f>
+      <c r="E6" s="23" t="str">
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G106)</f>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="str">
+      <c r="A7" s="27" t="str">
         <f>"3. " &amp; data!$B$12</f>
       </c>
-      <c r="F7" s="20"/>
-      <c r="G7" s="18"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="20"/>
     </row>
     <row r="8">
-      <c r="A8" s="20"/>
-      <c r="G8" s="19">
+      <c r="A8" s="22"/>
+      <c r="G8" s="21">
         <v>4</v>
       </c>
     </row>
     <row r="9">
-      <c r="C9" s="21" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G74)</f>
-      </c>
-      <c r="G9" s="18"/>
+      <c r="C9" s="23" t="str">
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G67)</f>
+      </c>
+      <c r="G9" s="20"/>
     </row>
     <row r="10">
-      <c r="D10" s="20"/>
-      <c r="E10" s="19">
+      <c r="D10" s="22"/>
+      <c r="E10" s="21">
         <v>2</v>
       </c>
       <c r="F10" s="15"/>
-      <c r="G10" s="18"/>
+      <c r="G10" s="20"/>
     </row>
     <row r="11">
-      <c r="C11" s="21" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O74)</f>
+      <c r="C11" s="23" t="str">
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O65)</f>
       </c>
       <c r="D11" s="15"/>
-      <c r="E11" s="18"/>
+      <c r="E11" s="20"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -20,10 +20,10 @@
   </sheets>
   <definedNames>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$12</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$O$109</definedName>
+    <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$P$111</definedName>
     <definedName localSheetId="7" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$7</definedName>
     <definedName localSheetId="8" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$3</definedName>
-    <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$O$64</definedName>
+    <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$P$64</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
@@ -146,6 +146,9 @@
     <t>Red</t>
   </si>
   <si>
+    <t>Team Results</t>
+  </si>
+  <si>
     <t>W</t>
   </si>
   <si>
@@ -155,6 +158,9 @@
     <t>T</t>
   </si>
   <si>
+    <t>Rank</t>
+  </si>
+  <si>
     <t>IV</t>
   </si>
   <si>
@@ -173,16 +179,16 @@
     <t>Ranking</t>
   </si>
   <si>
-    <t xml:space="preserve">1. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. </t>
+    <t>1.</t>
+  </si>
+  <si>
+    <t>2.</t>
+  </si>
+  <si>
+    <t>3.</t>
+  </si>
+  <si>
+    <t>4.</t>
   </si>
   <si>
     <t>A1</t>
@@ -219,12 +225,6 @@
   </si>
   <si>
     <t>Victories / Points</t>
-  </si>
-  <si>
-    <t>1.</t>
-  </si>
-  <si>
-    <t>2.</t>
   </si>
   <si>
     <t>Round 1 - Match 2</t>
@@ -1010,58 +1010,58 @@
   <sheetData>
     <row r="1" ht="270" customHeight="true">
       <c r="A1" s="28" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B1" s="29" t="str">
-        <f>data!$B$3</f>
+        <f>'data'!$B$3</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
       <c r="A2" s="28" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B2" s="29" t="str">
-        <f>data!$B$4</f>
+        <f>'data'!$B$4</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
       <c r="A3" s="28" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B3" s="29" t="str">
-        <f>data!$B$5</f>
+        <f>'data'!$B$5</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
       <c r="A4" s="28" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" s="29" t="str">
-        <f>data!$B$6</f>
+        <f>'data'!$B$6</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
       <c r="A5" s="28" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B5" s="29" t="str">
-        <f>data!$B$7</f>
+        <f>'data'!$B$7</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
       <c r="A6" s="28" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6" s="29" t="str">
-        <f>data!$B$8</f>
+        <f>'data'!$B$8</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
       <c r="A7" s="28" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B7" s="29" t="str">
-        <f>data!$B$9</f>
+        <f>'data'!$B$9</f>
       </c>
     </row>
   </sheetData>
@@ -1086,26 +1086,26 @@
   <sheetData>
     <row r="1" ht="270" customHeight="true">
       <c r="A1" s="28" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B1" s="29" t="str">
-        <f>data!$B$10</f>
+        <f>'data'!$B$10</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
       <c r="A2" s="28" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B2" s="29" t="str">
-        <f>data!$B$11</f>
+        <f>'data'!$B$11</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
       <c r="A3" s="28" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B3" s="29" t="str">
-        <f>data!$B$12</f>
+        <f>'data'!$B$12</f>
       </c>
     </row>
   </sheetData>
@@ -1128,102 +1128,102 @@
   <sheetData>
     <row r="1" ht="390" customHeight="true">
       <c r="A1" s="30" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" ht="390" customHeight="true">
       <c r="A2" s="30" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" ht="390" customHeight="true">
       <c r="A3" s="30" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" ht="390" customHeight="true">
       <c r="A4" s="30" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" ht="390" customHeight="true">
       <c r="A5" s="30" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" ht="390" customHeight="true">
       <c r="A6" s="30" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" ht="390" customHeight="true">
       <c r="A7" s="30" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" ht="390" customHeight="true">
       <c r="A8" s="30" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" ht="390" customHeight="true">
       <c r="A9" s="30" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" ht="390" customHeight="true">
       <c r="A10" s="30" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" ht="390" customHeight="true">
       <c r="A11" s="30" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" ht="390" customHeight="true">
       <c r="A12" s="30" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" ht="390" customHeight="true">
       <c r="A13" s="30" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" ht="390" customHeight="true">
       <c r="A14" s="30" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" ht="390" customHeight="true">
       <c r="A15" s="30" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" ht="390" customHeight="true">
       <c r="A16" s="30" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" ht="390" customHeight="true">
       <c r="A17" s="30" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" ht="390" customHeight="true">
       <c r="A18" s="30" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" ht="390" customHeight="true">
       <c r="A19" s="30" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" ht="390" customHeight="true">
       <c r="A20" s="30" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1569,13 +1569,13 @@
     </row>
     <row r="5" ht="17" customHeight="true">
       <c r="B5" s="11" t="str">
-        <f>data!$A$6</f>
+        <f>'data'!$A$6</f>
       </c>
       <c r="D5" s="11" t="str">
-        <f>data!$A$9</f>
+        <f>'data'!$A$9</f>
       </c>
       <c r="F5" s="11" t="str">
-        <f>data!$A$12</f>
+        <f>'data'!$A$12</f>
       </c>
     </row>
     <row r="6" ht="17" customHeight="true">
@@ -1634,19 +1634,16 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="3" min="2" width="5"/>
-    <col customWidth="true" max="4" min="4" width="3"/>
-    <col customWidth="true" max="6" min="5" width="5"/>
+    <col customWidth="true" max="6" min="2" width="5"/>
     <col customWidth="true" max="7" min="7" width="30"/>
     <col customWidth="true" max="8" min="8" width="5"/>
     <col customWidth="true" max="9" min="9" width="30"/>
-    <col customWidth="true" max="11" min="10" width="5"/>
-    <col customWidth="true" max="12" min="12" width="3"/>
-    <col customWidth="true" max="14" min="13" width="5"/>
+    <col customWidth="true" max="14" min="10" width="5"/>
     <col customWidth="true" max="15" min="15" width="30"/>
-    <col customWidth="true" max="18" min="16" width="5"/>
-    <col customWidth="true" max="19" min="19" width="30"/>
-    <col customWidth="true" max="20" min="20" width="2"/>
+    <col customWidth="true" max="16" min="16" width="5"/>
+    <col customWidth="true" max="20" min="17" width="10.83"/>
+    <col customWidth="true" hidden="true" max="21" min="21" width="9.140625"/>
+    <col customWidth="true" hidden="true" max="29" min="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1671,7 +1668,7 @@
     </row>
     <row r="2">
       <c r="A2" s="13" t="str">
-        <f>data!$A$6</f>
+        <f>'data'!$A$6</f>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -1680,7 +1677,7 @@
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
       <c r="I2" s="13" t="str">
-        <f>data!$A$12</f>
+        <f>'data'!$A$12</f>
       </c>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
@@ -1719,46 +1716,46 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>data!$B$4</f>
-      </c>
-      <c r="B4" s="18" t="str">
+        <f>'data'!$B$4</f>
+      </c>
+      <c r="B4" s="14" t="str">
         <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-",""))))*1)</f>
       </c>
-      <c r="C4" s="18" t="str">
+      <c r="C4" s="14" t="str">
         <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))</f>
       </c>
       <c r="D4" s="18"/>
-      <c r="E4" s="18" t="str">
+      <c r="E4" s="14" t="str">
         <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))</f>
       </c>
-      <c r="F4" s="18" t="str">
+      <c r="F4" s="14" t="str">
         <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-",""))))*1)</f>
       </c>
       <c r="G4" s="14" t="str">
-        <f>data!$B$3</f>
+        <f>'data'!$B$3</f>
       </c>
       <c r="I4" s="14" t="str">
-        <f>data!$B$11</f>
-      </c>
-      <c r="J4" s="18" t="str">
+        <f>'data'!$B$11</f>
+      </c>
+      <c r="J4" s="14" t="str">
         <f>SUMPRODUCT((UPPER(L5:L9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-",""))))*1)</f>
       </c>
-      <c r="K4" s="18" t="str">
+      <c r="K4" s="14" t="str">
         <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-","")))</f>
       </c>
       <c r="L4" s="18"/>
-      <c r="M4" s="18" t="str">
+      <c r="M4" s="14" t="str">
         <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-","")))</f>
       </c>
-      <c r="N4" s="18" t="str">
+      <c r="N4" s="14" t="str">
         <f>SUMPRODUCT((UPPER(L5:L9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-",""))))*1)</f>
       </c>
       <c r="O4" s="14" t="str">
-        <f>data!$B$10</f>
+        <f>'data'!$B$10</f>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18">
+      <c r="A5" s="14">
         <v>1</v>
       </c>
       <c r="B5" s="18"/>
@@ -1766,10 +1763,10 @@
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
       <c r="F5" s="18"/>
-      <c r="G5" s="18">
+      <c r="G5" s="14">
         <v>1</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="14">
         <v>1</v>
       </c>
       <c r="J5" s="18"/>
@@ -1777,12 +1774,12 @@
       <c r="L5" s="18"/>
       <c r="M5" s="18"/>
       <c r="N5" s="18"/>
-      <c r="O5" s="18">
+      <c r="O5" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18">
+      <c r="A6" s="14">
         <v>2</v>
       </c>
       <c r="B6" s="18"/>
@@ -1790,10 +1787,10 @@
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
-      <c r="G6" s="18">
+      <c r="G6" s="14">
         <v>2</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="14">
         <v>2</v>
       </c>
       <c r="J6" s="18"/>
@@ -1801,12 +1798,12 @@
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
       <c r="N6" s="18"/>
-      <c r="O6" s="18">
+      <c r="O6" s="14">
         <v>2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18">
+      <c r="A7" s="14">
         <v>3</v>
       </c>
       <c r="B7" s="18"/>
@@ -1814,10 +1811,10 @@
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
       <c r="F7" s="18"/>
-      <c r="G7" s="18">
+      <c r="G7" s="14">
         <v>3</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="14">
         <v>3</v>
       </c>
       <c r="J7" s="18"/>
@@ -1825,12 +1822,12 @@
       <c r="L7" s="18"/>
       <c r="M7" s="18"/>
       <c r="N7" s="18"/>
-      <c r="O7" s="18">
+      <c r="O7" s="14">
         <v>3</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18">
+      <c r="A8" s="14">
         <v>4</v>
       </c>
       <c r="B8" s="18"/>
@@ -1838,10 +1835,10 @@
       <c r="D8" s="18"/>
       <c r="E8" s="18"/>
       <c r="F8" s="18"/>
-      <c r="G8" s="18">
+      <c r="G8" s="14">
         <v>4</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="14">
         <v>4</v>
       </c>
       <c r="J8" s="18"/>
@@ -1849,12 +1846,12 @@
       <c r="L8" s="18"/>
       <c r="M8" s="18"/>
       <c r="N8" s="18"/>
-      <c r="O8" s="18">
+      <c r="O8" s="14">
         <v>4</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18">
+      <c r="A9" s="14">
         <v>5</v>
       </c>
       <c r="B9" s="18"/>
@@ -1862,10 +1859,10 @@
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
-      <c r="G9" s="18">
+      <c r="G9" s="14">
         <v>5</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="14">
         <v>5</v>
       </c>
       <c r="J9" s="18"/>
@@ -1873,7 +1870,7 @@
       <c r="L9" s="18"/>
       <c r="M9" s="18"/>
       <c r="N9" s="18"/>
-      <c r="O9" s="18">
+      <c r="O9" s="14">
         <v>5</v>
       </c>
     </row>
@@ -1907,46 +1904,46 @@
     </row>
     <row r="12">
       <c r="A12" s="14" t="str">
-        <f>data!$B$4</f>
-      </c>
-      <c r="B12" s="18" t="str">
+        <f>'data'!$B$4</f>
+      </c>
+      <c r="B12" s="14" t="str">
         <f>SUMPRODUCT((UPPER(D13:D17)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13:B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13:C17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13:E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13:F17," ",""),"0",""),"-",""))))*1)</f>
       </c>
-      <c r="C12" s="18" t="str">
+      <c r="C12" s="14" t="str">
         <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13:B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13:C17," ",""),"0",""),"-","")))</f>
       </c>
       <c r="D12" s="18"/>
-      <c r="E12" s="18" t="str">
+      <c r="E12" s="14" t="str">
         <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13:E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13:F17," ",""),"0",""),"-","")))</f>
       </c>
-      <c r="F12" s="18" t="str">
+      <c r="F12" s="14" t="str">
         <f>SUMPRODUCT((UPPER(D13:D17)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13:E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13:F17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13:B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13:C17," ",""),"0",""),"-",""))))*1)</f>
       </c>
       <c r="G12" s="14" t="str">
-        <f>data!$B$5</f>
+        <f>'data'!$B$5</f>
       </c>
       <c r="I12" s="14" t="str">
-        <f>data!$B$12</f>
-      </c>
-      <c r="J12" s="18" t="str">
+        <f>'data'!$B$12</f>
+      </c>
+      <c r="J12" s="14" t="str">
         <f>SUMPRODUCT((UPPER(L13:L17)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13:J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13:K17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13:M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13:N17," ",""),"0",""),"-",""))))*1)</f>
       </c>
-      <c r="K12" s="18" t="str">
+      <c r="K12" s="14" t="str">
         <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13:J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13:K17," ",""),"0",""),"-","")))</f>
       </c>
       <c r="L12" s="18"/>
-      <c r="M12" s="18" t="str">
+      <c r="M12" s="14" t="str">
         <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13:M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13:N17," ",""),"0",""),"-","")))</f>
       </c>
-      <c r="N12" s="18" t="str">
+      <c r="N12" s="14" t="str">
         <f>SUMPRODUCT((UPPER(L13:L17)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13:M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13:N17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13:J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13:K17," ",""),"0",""),"-",""))))*1)</f>
       </c>
       <c r="O12" s="14" t="str">
-        <f>data!$B$10</f>
+        <f>'data'!$B$10</f>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18">
+      <c r="A13" s="14">
         <v>1</v>
       </c>
       <c r="B13" s="18"/>
@@ -1954,10 +1951,10 @@
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
-      <c r="G13" s="18">
+      <c r="G13" s="14">
         <v>1</v>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="14">
         <v>1</v>
       </c>
       <c r="J13" s="18"/>
@@ -1965,12 +1962,12 @@
       <c r="L13" s="18"/>
       <c r="M13" s="18"/>
       <c r="N13" s="18"/>
-      <c r="O13" s="18">
+      <c r="O13" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18">
+      <c r="A14" s="14">
         <v>2</v>
       </c>
       <c r="B14" s="18"/>
@@ -1978,10 +1975,10 @@
       <c r="D14" s="18"/>
       <c r="E14" s="18"/>
       <c r="F14" s="18"/>
-      <c r="G14" s="18">
+      <c r="G14" s="14">
         <v>2</v>
       </c>
-      <c r="I14" s="18">
+      <c r="I14" s="14">
         <v>2</v>
       </c>
       <c r="J14" s="18"/>
@@ -1989,12 +1986,12 @@
       <c r="L14" s="18"/>
       <c r="M14" s="18"/>
       <c r="N14" s="18"/>
-      <c r="O14" s="18">
+      <c r="O14" s="14">
         <v>2</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18">
+      <c r="A15" s="14">
         <v>3</v>
       </c>
       <c r="B15" s="18"/>
@@ -2002,10 +1999,10 @@
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
       <c r="F15" s="18"/>
-      <c r="G15" s="18">
+      <c r="G15" s="14">
         <v>3</v>
       </c>
-      <c r="I15" s="18">
+      <c r="I15" s="14">
         <v>3</v>
       </c>
       <c r="J15" s="18"/>
@@ -2013,12 +2010,12 @@
       <c r="L15" s="18"/>
       <c r="M15" s="18"/>
       <c r="N15" s="18"/>
-      <c r="O15" s="18">
+      <c r="O15" s="14">
         <v>3</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18">
+      <c r="A16" s="14">
         <v>4</v>
       </c>
       <c r="B16" s="18"/>
@@ -2026,10 +2023,10 @@
       <c r="D16" s="18"/>
       <c r="E16" s="18"/>
       <c r="F16" s="18"/>
-      <c r="G16" s="18">
+      <c r="G16" s="14">
         <v>4</v>
       </c>
-      <c r="I16" s="18">
+      <c r="I16" s="14">
         <v>4</v>
       </c>
       <c r="J16" s="18"/>
@@ -2037,12 +2034,12 @@
       <c r="L16" s="18"/>
       <c r="M16" s="18"/>
       <c r="N16" s="18"/>
-      <c r="O16" s="18">
+      <c r="O16" s="14">
         <v>4</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18">
+      <c r="A17" s="14">
         <v>5</v>
       </c>
       <c r="B17" s="18"/>
@@ -2050,10 +2047,10 @@
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
       <c r="F17" s="18"/>
-      <c r="G17" s="18">
+      <c r="G17" s="14">
         <v>5</v>
       </c>
-      <c r="I17" s="18">
+      <c r="I17" s="14">
         <v>5</v>
       </c>
       <c r="J17" s="18"/>
@@ -2061,7 +2058,7 @@
       <c r="L17" s="18"/>
       <c r="M17" s="18"/>
       <c r="N17" s="18"/>
-      <c r="O17" s="18">
+      <c r="O17" s="14">
         <v>5</v>
       </c>
     </row>
@@ -2095,46 +2092,46 @@
     </row>
     <row r="20">
       <c r="A20" s="14" t="str">
-        <f>data!$B$6</f>
-      </c>
-      <c r="B20" s="18" t="str">
+        <f>'data'!$B$6</f>
+      </c>
+      <c r="B20" s="14" t="str">
         <f>SUMPRODUCT((UPPER(D21:D25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-",""))))*1)</f>
       </c>
-      <c r="C20" s="18" t="str">
+      <c r="C20" s="14" t="str">
         <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-","")))</f>
       </c>
       <c r="D20" s="18"/>
-      <c r="E20" s="18" t="str">
+      <c r="E20" s="14" t="str">
         <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-","")))</f>
       </c>
-      <c r="F20" s="18" t="str">
+      <c r="F20" s="14" t="str">
         <f>SUMPRODUCT((UPPER(D21:D25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-",""))))*1)</f>
       </c>
       <c r="G20" s="14" t="str">
-        <f>data!$B$5</f>
+        <f>'data'!$B$5</f>
       </c>
       <c r="I20" s="14" t="str">
-        <f>data!$B$12</f>
-      </c>
-      <c r="J20" s="18" t="str">
+        <f>'data'!$B$12</f>
+      </c>
+      <c r="J20" s="14" t="str">
         <f>SUMPRODUCT((UPPER(L21:L25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21:J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21:K25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21:M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21:N25," ",""),"0",""),"-",""))))*1)</f>
       </c>
-      <c r="K20" s="18" t="str">
+      <c r="K20" s="14" t="str">
         <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21:J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21:K25," ",""),"0",""),"-","")))</f>
       </c>
       <c r="L20" s="18"/>
-      <c r="M20" s="18" t="str">
+      <c r="M20" s="14" t="str">
         <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21:M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21:N25," ",""),"0",""),"-","")))</f>
       </c>
-      <c r="N20" s="18" t="str">
+      <c r="N20" s="14" t="str">
         <f>SUMPRODUCT((UPPER(L21:L25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21:M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21:N25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21:J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21:K25," ",""),"0",""),"-",""))))*1)</f>
       </c>
       <c r="O20" s="14" t="str">
-        <f>data!$B$11</f>
+        <f>'data'!$B$11</f>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18">
+      <c r="A21" s="14">
         <v>1</v>
       </c>
       <c r="B21" s="18"/>
@@ -2142,10 +2139,10 @@
       <c r="D21" s="18"/>
       <c r="E21" s="18"/>
       <c r="F21" s="18"/>
-      <c r="G21" s="18">
+      <c r="G21" s="14">
         <v>1</v>
       </c>
-      <c r="I21" s="18">
+      <c r="I21" s="14">
         <v>1</v>
       </c>
       <c r="J21" s="18"/>
@@ -2153,12 +2150,12 @@
       <c r="L21" s="18"/>
       <c r="M21" s="18"/>
       <c r="N21" s="18"/>
-      <c r="O21" s="18">
+      <c r="O21" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18">
+      <c r="A22" s="14">
         <v>2</v>
       </c>
       <c r="B22" s="18"/>
@@ -2166,10 +2163,10 @@
       <c r="D22" s="18"/>
       <c r="E22" s="18"/>
       <c r="F22" s="18"/>
-      <c r="G22" s="18">
+      <c r="G22" s="14">
         <v>2</v>
       </c>
-      <c r="I22" s="18">
+      <c r="I22" s="14">
         <v>2</v>
       </c>
       <c r="J22" s="18"/>
@@ -2177,12 +2174,12 @@
       <c r="L22" s="18"/>
       <c r="M22" s="18"/>
       <c r="N22" s="18"/>
-      <c r="O22" s="18">
+      <c r="O22" s="14">
         <v>2</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18">
+      <c r="A23" s="14">
         <v>3</v>
       </c>
       <c r="B23" s="18"/>
@@ -2190,10 +2187,10 @@
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="18"/>
-      <c r="G23" s="18">
+      <c r="G23" s="14">
         <v>3</v>
       </c>
-      <c r="I23" s="18">
+      <c r="I23" s="14">
         <v>3</v>
       </c>
       <c r="J23" s="18"/>
@@ -2201,12 +2198,12 @@
       <c r="L23" s="18"/>
       <c r="M23" s="18"/>
       <c r="N23" s="18"/>
-      <c r="O23" s="18">
+      <c r="O23" s="14">
         <v>3</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18">
+      <c r="A24" s="14">
         <v>4</v>
       </c>
       <c r="B24" s="18"/>
@@ -2214,10 +2211,10 @@
       <c r="D24" s="18"/>
       <c r="E24" s="18"/>
       <c r="F24" s="18"/>
-      <c r="G24" s="18">
+      <c r="G24" s="14">
         <v>4</v>
       </c>
-      <c r="I24" s="18">
+      <c r="I24" s="14">
         <v>4</v>
       </c>
       <c r="J24" s="18"/>
@@ -2225,12 +2222,12 @@
       <c r="L24" s="18"/>
       <c r="M24" s="18"/>
       <c r="N24" s="18"/>
-      <c r="O24" s="18">
+      <c r="O24" s="14">
         <v>4</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18">
+      <c r="A25" s="14">
         <v>5</v>
       </c>
       <c r="B25" s="18"/>
@@ -2238,10 +2235,10 @@
       <c r="D25" s="18"/>
       <c r="E25" s="18"/>
       <c r="F25" s="18"/>
-      <c r="G25" s="18">
+      <c r="G25" s="14">
         <v>5</v>
       </c>
-      <c r="I25" s="18">
+      <c r="I25" s="14">
         <v>5</v>
       </c>
       <c r="J25" s="18"/>
@@ -2249,7 +2246,7 @@
       <c r="L25" s="18"/>
       <c r="M25" s="18"/>
       <c r="N25" s="18"/>
-      <c r="O25" s="18">
+      <c r="O25" s="14">
         <v>5</v>
       </c>
     </row>
@@ -2270,27 +2267,27 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="str">
-        <f>data!$B$6</f>
-      </c>
-      <c r="B28" s="18" t="str">
+        <f>'data'!$B$6</f>
+      </c>
+      <c r="B28" s="14" t="str">
         <f>SUMPRODUCT((UPPER(D29:D33)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29:B33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29:C33," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29:E33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29:F33," ",""),"0",""),"-",""))))*1)</f>
       </c>
-      <c r="C28" s="18" t="str">
+      <c r="C28" s="14" t="str">
         <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29:B33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29:C33," ",""),"0",""),"-","")))</f>
       </c>
       <c r="D28" s="18"/>
-      <c r="E28" s="18" t="str">
+      <c r="E28" s="14" t="str">
         <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29:E33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29:F33," ",""),"0",""),"-","")))</f>
       </c>
-      <c r="F28" s="18" t="str">
+      <c r="F28" s="14" t="str">
         <f>SUMPRODUCT((UPPER(D29:D33)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29:E33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29:F33," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29:B33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29:C33," ",""),"0",""),"-",""))))*1)</f>
       </c>
       <c r="G28" s="14" t="str">
-        <f>data!$B$3</f>
+        <f>'data'!$B$3</f>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18">
+      <c r="A29" s="14">
         <v>1</v>
       </c>
       <c r="B29" s="18"/>
@@ -2298,12 +2295,12 @@
       <c r="D29" s="18"/>
       <c r="E29" s="18"/>
       <c r="F29" s="18"/>
-      <c r="G29" s="18">
+      <c r="G29" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18">
+      <c r="A30" s="14">
         <v>2</v>
       </c>
       <c r="B30" s="18"/>
@@ -2311,12 +2308,12 @@
       <c r="D30" s="18"/>
       <c r="E30" s="18"/>
       <c r="F30" s="18"/>
-      <c r="G30" s="18">
+      <c r="G30" s="14">
         <v>2</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18">
+      <c r="A31" s="14">
         <v>3</v>
       </c>
       <c r="B31" s="18"/>
@@ -2324,12 +2321,12 @@
       <c r="D31" s="18"/>
       <c r="E31" s="18"/>
       <c r="F31" s="18"/>
-      <c r="G31" s="18">
+      <c r="G31" s="14">
         <v>3</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18">
+      <c r="A32" s="14">
         <v>4</v>
       </c>
       <c r="B32" s="18"/>
@@ -2337,12 +2334,12 @@
       <c r="D32" s="18"/>
       <c r="E32" s="18"/>
       <c r="F32" s="18"/>
-      <c r="G32" s="18">
+      <c r="G32" s="14">
         <v>4</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18">
+      <c r="A33" s="14">
         <v>5</v>
       </c>
       <c r="B33" s="18"/>
@@ -2350,7 +2347,7 @@
       <c r="D33" s="18"/>
       <c r="E33" s="18"/>
       <c r="F33" s="18"/>
-      <c r="G33" s="18">
+      <c r="G33" s="14">
         <v>5</v>
       </c>
     </row>
@@ -2371,27 +2368,27 @@
     </row>
     <row r="36">
       <c r="A36" s="14" t="str">
-        <f>data!$B$5</f>
-      </c>
-      <c r="B36" s="18" t="str">
+        <f>'data'!$B$5</f>
+      </c>
+      <c r="B36" s="14" t="str">
         <f>SUMPRODUCT((UPPER(D37:D41)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37:B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37:C41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37:E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37:F41," ",""),"0",""),"-",""))))*1)</f>
       </c>
-      <c r="C36" s="18" t="str">
+      <c r="C36" s="14" t="str">
         <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37:B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37:C41," ",""),"0",""),"-","")))</f>
       </c>
       <c r="D36" s="18"/>
-      <c r="E36" s="18" t="str">
+      <c r="E36" s="14" t="str">
         <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37:E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37:F41," ",""),"0",""),"-","")))</f>
       </c>
-      <c r="F36" s="18" t="str">
+      <c r="F36" s="14" t="str">
         <f>SUMPRODUCT((UPPER(D37:D41)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37:E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37:F41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37:B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37:C41," ",""),"0",""),"-",""))))*1)</f>
       </c>
       <c r="G36" s="14" t="str">
-        <f>data!$B$3</f>
+        <f>'data'!$B$3</f>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18">
+      <c r="A37" s="14">
         <v>1</v>
       </c>
       <c r="B37" s="18"/>
@@ -2399,12 +2396,12 @@
       <c r="D37" s="18"/>
       <c r="E37" s="18"/>
       <c r="F37" s="18"/>
-      <c r="G37" s="18">
+      <c r="G37" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18">
+      <c r="A38" s="14">
         <v>2</v>
       </c>
       <c r="B38" s="18"/>
@@ -2412,12 +2409,12 @@
       <c r="D38" s="18"/>
       <c r="E38" s="18"/>
       <c r="F38" s="18"/>
-      <c r="G38" s="18">
+      <c r="G38" s="14">
         <v>2</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18">
+      <c r="A39" s="14">
         <v>3</v>
       </c>
       <c r="B39" s="18"/>
@@ -2425,12 +2422,12 @@
       <c r="D39" s="18"/>
       <c r="E39" s="18"/>
       <c r="F39" s="18"/>
-      <c r="G39" s="18">
+      <c r="G39" s="14">
         <v>3</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18">
+      <c r="A40" s="14">
         <v>4</v>
       </c>
       <c r="B40" s="18"/>
@@ -2438,12 +2435,12 @@
       <c r="D40" s="18"/>
       <c r="E40" s="18"/>
       <c r="F40" s="18"/>
-      <c r="G40" s="18">
+      <c r="G40" s="14">
         <v>4</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18">
+      <c r="A41" s="14">
         <v>5</v>
       </c>
       <c r="B41" s="18"/>
@@ -2451,7 +2448,7 @@
       <c r="D41" s="18"/>
       <c r="E41" s="18"/>
       <c r="F41" s="18"/>
-      <c r="G41" s="18">
+      <c r="G41" s="14">
         <v>5</v>
       </c>
     </row>
@@ -2472,27 +2469,27 @@
     </row>
     <row r="44">
       <c r="A44" s="14" t="str">
-        <f>data!$B$6</f>
-      </c>
-      <c r="B44" s="18" t="str">
+        <f>'data'!$B$6</f>
+      </c>
+      <c r="B44" s="14" t="str">
         <f>SUMPRODUCT((UPPER(D45:D49)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45:B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45:C49," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45:E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45:F49," ",""),"0",""),"-",""))))*1)</f>
       </c>
-      <c r="C44" s="18" t="str">
+      <c r="C44" s="14" t="str">
         <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45:B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45:C49," ",""),"0",""),"-","")))</f>
       </c>
       <c r="D44" s="18"/>
-      <c r="E44" s="18" t="str">
+      <c r="E44" s="14" t="str">
         <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45:E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45:F49," ",""),"0",""),"-","")))</f>
       </c>
-      <c r="F44" s="18" t="str">
+      <c r="F44" s="14" t="str">
         <f>SUMPRODUCT((UPPER(D45:D49)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45:E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45:F49," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45:B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45:C49," ",""),"0",""),"-",""))))*1)</f>
       </c>
       <c r="G44" s="14" t="str">
-        <f>data!$B$4</f>
+        <f>'data'!$B$4</f>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18">
+      <c r="A45" s="14">
         <v>1</v>
       </c>
       <c r="B45" s="18"/>
@@ -2500,12 +2497,12 @@
       <c r="D45" s="18"/>
       <c r="E45" s="18"/>
       <c r="F45" s="18"/>
-      <c r="G45" s="18">
+      <c r="G45" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18">
+      <c r="A46" s="14">
         <v>2</v>
       </c>
       <c r="B46" s="18"/>
@@ -2513,12 +2510,12 @@
       <c r="D46" s="18"/>
       <c r="E46" s="18"/>
       <c r="F46" s="18"/>
-      <c r="G46" s="18">
+      <c r="G46" s="14">
         <v>2</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18">
+      <c r="A47" s="14">
         <v>3</v>
       </c>
       <c r="B47" s="18"/>
@@ -2526,12 +2523,12 @@
       <c r="D47" s="18"/>
       <c r="E47" s="18"/>
       <c r="F47" s="18"/>
-      <c r="G47" s="18">
+      <c r="G47" s="14">
         <v>3</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18">
+      <c r="A48" s="14">
         <v>4</v>
       </c>
       <c r="B48" s="18"/>
@@ -2539,12 +2536,12 @@
       <c r="D48" s="18"/>
       <c r="E48" s="18"/>
       <c r="F48" s="18"/>
-      <c r="G48" s="18">
+      <c r="G48" s="14">
         <v>4</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18">
+      <c r="A49" s="14">
         <v>5</v>
       </c>
       <c r="B49" s="18"/>
@@ -2552,170 +2549,226 @@
       <c r="D49" s="18"/>
       <c r="E49" s="18"/>
       <c r="F49" s="18"/>
-      <c r="G49" s="18">
+      <c r="G49" s="14">
         <v>5</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="13"/>
+      <c r="A52" s="13" t="s">
+        <v>38</v>
+      </c>
       <c r="B52" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I52" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="J52" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="K52" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I52" s="13"/>
-      <c r="J52" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="K52" s="13" t="s">
-        <v>39</v>
-      </c>
       <c r="L52" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="M52" s="13"/>
+      <c r="N52" s="13"/>
+      <c r="O52" s="13" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="str">
-        <f>data!$B$3</f>
+      <c r="A53" s="14" t="str">
+        <f>'data'!$B$3</f>
       </c>
       <c r="B53" s="14" t="str">
-        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,IF(OR(F4&gt;B4,AND(F4=B4,E4&gt;C4)),1,0)),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),IF(OR(D28="X",D28="x"),0,IF(OR(F28&gt;B28,AND(F28=B28,E28&gt;C28)),1,0)),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,IF(OR(F36&gt;B36,AND(F36=B36,E36&gt;C36)),1,0)),0)</f>
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,D5="X",D5="x",D6="X",D6="x",D7="X",D7="x",D8="X",D8="x",D9="X",D9="x",OR(D4="X",D4="x")),IF(OR(OR(D4="X",D4="x"),AND(B4=F4,C4=E4)),0,IF(OR(F4&gt;B4,AND(F4=B4,E4&gt;C4)),1,0)),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,D29="X",D29="x",D30="X",D30="x",D31="X",D31="x",D32="X",D32="x",D33="X",D33="x",OR(D28="X",D28="x")),IF(OR(OR(D28="X",D28="x"),AND(B28=F28,C28=E28)),0,IF(OR(F28&gt;B28,AND(F28=B28,E28&gt;C28)),1,0)),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,D37="X",D37="x",D38="X",D38="x",D39="X",D39="x",D40="X",D40="x",D41="X",D41="x",OR(D36="X",D36="x")),IF(OR(OR(D36="X",D36="x"),AND(B36=F36,C36=E36)),0,IF(OR(F36&gt;B36,AND(F36=B36,E36&gt;C36)),1,0)),0)</f>
       </c>
       <c r="C53" s="14" t="str">
-        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,IF(OR(F4&lt;B4,AND(F4=B4,E4&lt;C4)),1,0)),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),IF(OR(D28="X",D28="x"),0,IF(OR(F28&lt;B28,AND(F28=B28,E28&lt;C28)),1,0)),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,IF(OR(F36&lt;B36,AND(F36=B36,E36&lt;C36)),1,0)),0)</f>
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,D5="X",D5="x",D6="X",D6="x",D7="X",D7="x",D8="X",D8="x",D9="X",D9="x",OR(D4="X",D4="x")),IF(OR(OR(D4="X",D4="x"),AND(B4=F4,C4=E4)),0,IF(OR(F4&lt;B4,AND(F4=B4,E4&lt;C4)),1,0)),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,D29="X",D29="x",D30="X",D30="x",D31="X",D31="x",D32="X",D32="x",D33="X",D33="x",OR(D28="X",D28="x")),IF(OR(OR(D28="X",D28="x"),AND(B28=F28,C28=E28)),0,IF(OR(F28&lt;B28,AND(F28=B28,E28&lt;C28)),1,0)),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,D37="X",D37="x",D38="X",D38="x",D39="X",D39="x",D40="X",D40="x",D41="X",D41="x",OR(D36="X",D36="x")),IF(OR(OR(D36="X",D36="x"),AND(B36=F36,C36=E36)),0,IF(OR(F36&lt;B36,AND(F36=B36,E36&lt;C36)),1,0)),0)</f>
       </c>
       <c r="D53" s="14" t="str">
-        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),1,0),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),IF(OR(D28="X",D28="x"),1,0),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),1,0),0)</f>
-      </c>
-      <c r="I53" t="str">
-        <f>data!$B$10</f>
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,D5="X",D5="x",D6="X",D6="x",D7="X",D7="x",D8="X",D8="x",D9="X",D9="x",OR(D4="X",D4="x")),IF(OR(OR(D4="X",D4="x"),AND(B4=F4,C4=E4)),1,0),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,D29="X",D29="x",D30="X",D30="x",D31="X",D31="x",D32="X",D32="x",D33="X",D33="x",OR(D28="X",D28="x")),IF(OR(OR(D28="X",D28="x"),AND(B28=F28,C28=E28)),1,0),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,D37="X",D37="x",D38="X",D38="x",D39="X",D39="x",D40="X",D40="x",D41="X",D41="x",OR(D36="X",D36="x")),IF(OR(OR(D36="X",D36="x"),AND(B36=F36,C36=E36)),1,0),0)</f>
+      </c>
+      <c r="G53" s="18" t="str">
+        <f>RANK(U53,$U$53:$U$56)+COUNTIF($U$52:U52,U53)</f>
+      </c>
+      <c r="I53" s="14" t="str">
+        <f>'data'!$B$10</f>
       </c>
       <c r="J53" s="14" t="str">
-        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,IF(OR(N4&gt;J4,AND(N4=J4,M4&gt;K4)),1,0)),0)+IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),IF(OR(L12="X",L12="x"),0,IF(OR(N12&gt;J12,AND(N12=J12,M12&gt;K12)),1,0)),0)</f>
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,L5="X",L5="x",L6="X",L6="x",L7="X",L7="x",L8="X",L8="x",L9="X",L9="x",OR(L4="X",L4="x")),IF(OR(OR(L4="X",L4="x"),AND(J4=N4,K4=M4)),0,IF(OR(N4&gt;J4,AND(N4=J4,M4&gt;K4)),1,0)),0)+IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,L13="X",L13="x",L14="X",L14="x",L15="X",L15="x",L16="X",L16="x",L17="X",L17="x",OR(L12="X",L12="x")),IF(OR(OR(L12="X",L12="x"),AND(J12=N12,K12=M12)),0,IF(OR(N12&gt;J12,AND(N12=J12,M12&gt;K12)),1,0)),0)</f>
       </c>
       <c r="K53" s="14" t="str">
-        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,IF(OR(N4&lt;J4,AND(N4=J4,M4&lt;K4)),1,0)),0)+IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),IF(OR(L12="X",L12="x"),0,IF(OR(N12&lt;J12,AND(N12=J12,M12&lt;K12)),1,0)),0)</f>
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,L5="X",L5="x",L6="X",L6="x",L7="X",L7="x",L8="X",L8="x",L9="X",L9="x",OR(L4="X",L4="x")),IF(OR(OR(L4="X",L4="x"),AND(J4=N4,K4=M4)),0,IF(OR(N4&lt;J4,AND(N4=J4,M4&lt;K4)),1,0)),0)+IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,L13="X",L13="x",L14="X",L14="x",L15="X",L15="x",L16="X",L16="x",L17="X",L17="x",OR(L12="X",L12="x")),IF(OR(OR(L12="X",L12="x"),AND(J12=N12,K12=M12)),0,IF(OR(N12&lt;J12,AND(N12=J12,M12&lt;K12)),1,0)),0)</f>
       </c>
       <c r="L53" s="14" t="str">
-        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),1,0),0)+IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),IF(OR(L12="X",L12="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,L5="X",L5="x",L6="X",L6="x",L7="X",L7="x",L8="X",L8="x",L9="X",L9="x",OR(L4="X",L4="x")),IF(OR(OR(L4="X",L4="x"),AND(J4=N4,K4=M4)),1,0),0)+IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,L13="X",L13="x",L14="X",L14="x",L15="X",L15="x",L16="X",L16="x",L17="X",L17="x",OR(L12="X",L12="x")),IF(OR(OR(L12="X",L12="x"),AND(J12=N12,K12=M12)),1,0),0)</f>
+      </c>
+      <c r="O53" s="18" t="str">
+        <f>RANK(AC53,$AC$53:$AC$55)+COUNTIF($AC$52:AC52,AC53)</f>
+      </c>
+      <c r="U53" t="str">
+        <f>=(B53*1000000000)-(C53*10000000)+(D53*100000)+(B59*1000)-(C59*100)+(D59*10)+(E59*1)-(F59*0.01)</f>
+      </c>
+      <c r="AC53" t="str">
+        <f>=(J53*1000000000)-(K53*10000000)+(L53*100000)+(J58*1000)-(K58*100)+(L58*10)+(M58*1)-(N58*0.01)</f>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="str">
-        <f>data!$B$4</f>
+      <c r="A54" s="14" t="str">
+        <f>'data'!$B$4</f>
       </c>
       <c r="B54" s="14" t="str">
-        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,IF(OR(B4&gt;F4,AND(B4=F4,C4&gt;E4)),1,0)),0)+IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),IF(OR(D12="X",D12="x"),0,IF(OR(B12&gt;F12,AND(B12=F12,C12&gt;E12)),1,0)),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),IF(OR(D44="X",D44="x"),0,IF(OR(F44&gt;B44,AND(F44=B44,E44&gt;C44)),1,0)),0)</f>
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,D5="X",D5="x",D6="X",D6="x",D7="X",D7="x",D8="X",D8="x",D9="X",D9="x",OR(D4="X",D4="x")),IF(OR(OR(D4="X",D4="x"),AND(B4=F4,C4=E4)),0,IF(OR(B4&gt;F4,AND(B4=F4,C4&gt;E4)),1,0)),0)+IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,D13="X",D13="x",D14="X",D14="x",D15="X",D15="x",D16="X",D16="x",D17="X",D17="x",OR(D12="X",D12="x")),IF(OR(OR(D12="X",D12="x"),AND(B12=F12,C12=E12)),0,IF(OR(B12&gt;F12,AND(B12=F12,C12&gt;E12)),1,0)),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,D45="X",D45="x",D46="X",D46="x",D47="X",D47="x",D48="X",D48="x",D49="X",D49="x",OR(D44="X",D44="x")),IF(OR(OR(D44="X",D44="x"),AND(B44=F44,C44=E44)),0,IF(OR(F44&gt;B44,AND(F44=B44,E44&gt;C44)),1,0)),0)</f>
       </c>
       <c r="C54" s="14" t="str">
-        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,IF(OR(B4&lt;F4,AND(B4=F4,C4&lt;E4)),1,0)),0)+IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),IF(OR(D12="X",D12="x"),0,IF(OR(B12&lt;F12,AND(B12=F12,C12&lt;E12)),1,0)),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),IF(OR(D44="X",D44="x"),0,IF(OR(F44&lt;B44,AND(F44=B44,E44&lt;C44)),1,0)),0)</f>
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,D5="X",D5="x",D6="X",D6="x",D7="X",D7="x",D8="X",D8="x",D9="X",D9="x",OR(D4="X",D4="x")),IF(OR(OR(D4="X",D4="x"),AND(B4=F4,C4=E4)),0,IF(OR(B4&lt;F4,AND(B4=F4,C4&lt;E4)),1,0)),0)+IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,D13="X",D13="x",D14="X",D14="x",D15="X",D15="x",D16="X",D16="x",D17="X",D17="x",OR(D12="X",D12="x")),IF(OR(OR(D12="X",D12="x"),AND(B12=F12,C12=E12)),0,IF(OR(B12&lt;F12,AND(B12=F12,C12&lt;E12)),1,0)),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,D45="X",D45="x",D46="X",D46="x",D47="X",D47="x",D48="X",D48="x",D49="X",D49="x",OR(D44="X",D44="x")),IF(OR(OR(D44="X",D44="x"),AND(B44=F44,C44=E44)),0,IF(OR(F44&lt;B44,AND(F44=B44,E44&lt;C44)),1,0)),0)</f>
       </c>
       <c r="D54" s="14" t="str">
-        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),1,0),0)+IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),IF(OR(D12="X",D12="x"),1,0),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),IF(OR(D44="X",D44="x"),1,0),0)</f>
-      </c>
-      <c r="I54" t="str">
-        <f>data!$B$11</f>
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,D5="X",D5="x",D6="X",D6="x",D7="X",D7="x",D8="X",D8="x",D9="X",D9="x",OR(D4="X",D4="x")),IF(OR(OR(D4="X",D4="x"),AND(B4=F4,C4=E4)),1,0),0)+IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,D13="X",D13="x",D14="X",D14="x",D15="X",D15="x",D16="X",D16="x",D17="X",D17="x",OR(D12="X",D12="x")),IF(OR(OR(D12="X",D12="x"),AND(B12=F12,C12=E12)),1,0),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,D45="X",D45="x",D46="X",D46="x",D47="X",D47="x",D48="X",D48="x",D49="X",D49="x",OR(D44="X",D44="x")),IF(OR(OR(D44="X",D44="x"),AND(B44=F44,C44=E44)),1,0),0)</f>
+      </c>
+      <c r="G54" s="18" t="str">
+        <f>RANK(U54,$U$53:$U$56)+COUNTIF($U$52:U53,U54)</f>
+      </c>
+      <c r="I54" s="14" t="str">
+        <f>'data'!$B$11</f>
       </c>
       <c r="J54" s="14" t="str">
-        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,IF(OR(J4&gt;N4,AND(J4=N4,K4&gt;M4)),1,0)),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,IF(OR(N20&gt;J20,AND(N20=J20,M20&gt;K20)),1,0)),0)</f>
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,L5="X",L5="x",L6="X",L6="x",L7="X",L7="x",L8="X",L8="x",L9="X",L9="x",OR(L4="X",L4="x")),IF(OR(OR(L4="X",L4="x"),AND(J4=N4,K4=M4)),0,IF(OR(J4&gt;N4,AND(J4=N4,K4&gt;M4)),1,0)),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,L21="X",L21="x",L22="X",L22="x",L23="X",L23="x",L24="X",L24="x",L25="X",L25="x",OR(L20="X",L20="x")),IF(OR(OR(L20="X",L20="x"),AND(J20=N20,K20=M20)),0,IF(OR(N20&gt;J20,AND(N20=J20,M20&gt;K20)),1,0)),0)</f>
       </c>
       <c r="K54" s="14" t="str">
-        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,IF(OR(J4&lt;N4,AND(J4=N4,K4&lt;M4)),1,0)),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,IF(OR(N20&lt;J20,AND(N20=J20,M20&lt;K20)),1,0)),0)</f>
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,L5="X",L5="x",L6="X",L6="x",L7="X",L7="x",L8="X",L8="x",L9="X",L9="x",OR(L4="X",L4="x")),IF(OR(OR(L4="X",L4="x"),AND(J4=N4,K4=M4)),0,IF(OR(J4&lt;N4,AND(J4=N4,K4&lt;M4)),1,0)),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,L21="X",L21="x",L22="X",L22="x",L23="X",L23="x",L24="X",L24="x",L25="X",L25="x",OR(L20="X",L20="x")),IF(OR(OR(L20="X",L20="x"),AND(J20=N20,K20=M20)),0,IF(OR(N20&lt;J20,AND(N20=J20,M20&lt;K20)),1,0)),0)</f>
       </c>
       <c r="L54" s="14" t="str">
-        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),1,0),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,L5="X",L5="x",L6="X",L6="x",L7="X",L7="x",L8="X",L8="x",L9="X",L9="x",OR(L4="X",L4="x")),IF(OR(OR(L4="X",L4="x"),AND(J4=N4,K4=M4)),1,0),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,L21="X",L21="x",L22="X",L22="x",L23="X",L23="x",L24="X",L24="x",L25="X",L25="x",OR(L20="X",L20="x")),IF(OR(OR(L20="X",L20="x"),AND(J20=N20,K20=M20)),1,0),0)</f>
+      </c>
+      <c r="O54" s="18" t="str">
+        <f>RANK(AC54,$AC$53:$AC$55)+COUNTIF($AC$52:AC53,AC54)</f>
+      </c>
+      <c r="U54" t="str">
+        <f>=(B54*1000000000)-(C54*10000000)+(D54*100000)+(B60*1000)-(C60*100)+(D60*10)+(E60*1)-(F60*0.01)</f>
+      </c>
+      <c r="AC54" t="str">
+        <f>=(J54*1000000000)-(K54*10000000)+(L54*100000)+(J59*1000)-(K59*100)+(L59*10)+(M59*1)-(N59*0.01)</f>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="str">
-        <f>data!$B$5</f>
+      <c r="A55" s="14" t="str">
+        <f>'data'!$B$5</f>
       </c>
       <c r="B55" s="14" t="str">
-        <f>IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),IF(OR(D12="X",D12="x"),0,IF(OR(F12&gt;B12,AND(F12=B12,E12&gt;C12)),1,0)),0)+IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,IF(OR(F20&gt;B20,AND(F20=B20,E20&gt;C20)),1,0)),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,IF(OR(B36&gt;F36,AND(B36=F36,C36&gt;E36)),1,0)),0)</f>
+        <f>IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,D13="X",D13="x",D14="X",D14="x",D15="X",D15="x",D16="X",D16="x",D17="X",D17="x",OR(D12="X",D12="x")),IF(OR(OR(D12="X",D12="x"),AND(B12=F12,C12=E12)),0,IF(OR(F12&gt;B12,AND(F12=B12,E12&gt;C12)),1,0)),0)+IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,D21="X",D21="x",D22="X",D22="x",D23="X",D23="x",D24="X",D24="x",D25="X",D25="x",OR(D20="X",D20="x")),IF(OR(OR(D20="X",D20="x"),AND(B20=F20,C20=E20)),0,IF(OR(F20&gt;B20,AND(F20=B20,E20&gt;C20)),1,0)),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,D37="X",D37="x",D38="X",D38="x",D39="X",D39="x",D40="X",D40="x",D41="X",D41="x",OR(D36="X",D36="x")),IF(OR(OR(D36="X",D36="x"),AND(B36=F36,C36=E36)),0,IF(OR(B36&gt;F36,AND(B36=F36,C36&gt;E36)),1,0)),0)</f>
       </c>
       <c r="C55" s="14" t="str">
-        <f>IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),IF(OR(D12="X",D12="x"),0,IF(OR(F12&lt;B12,AND(F12=B12,E12&lt;C12)),1,0)),0)+IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,IF(OR(F20&lt;B20,AND(F20=B20,E20&lt;C20)),1,0)),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,IF(OR(B36&lt;F36,AND(B36=F36,C36&lt;E36)),1,0)),0)</f>
+        <f>IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,D13="X",D13="x",D14="X",D14="x",D15="X",D15="x",D16="X",D16="x",D17="X",D17="x",OR(D12="X",D12="x")),IF(OR(OR(D12="X",D12="x"),AND(B12=F12,C12=E12)),0,IF(OR(F12&lt;B12,AND(F12=B12,E12&lt;C12)),1,0)),0)+IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,D21="X",D21="x",D22="X",D22="x",D23="X",D23="x",D24="X",D24="x",D25="X",D25="x",OR(D20="X",D20="x")),IF(OR(OR(D20="X",D20="x"),AND(B20=F20,C20=E20)),0,IF(OR(F20&lt;B20,AND(F20=B20,E20&lt;C20)),1,0)),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,D37="X",D37="x",D38="X",D38="x",D39="X",D39="x",D40="X",D40="x",D41="X",D41="x",OR(D36="X",D36="x")),IF(OR(OR(D36="X",D36="x"),AND(B36=F36,C36=E36)),0,IF(OR(B36&lt;F36,AND(B36=F36,C36&lt;E36)),1,0)),0)</f>
       </c>
       <c r="D55" s="14" t="str">
-        <f>IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),IF(OR(D12="X",D12="x"),1,0),0)+IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),1,0),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),1,0),0)</f>
-      </c>
-      <c r="I55" t="str">
-        <f>data!$B$12</f>
+        <f>IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,D13="X",D13="x",D14="X",D14="x",D15="X",D15="x",D16="X",D16="x",D17="X",D17="x",OR(D12="X",D12="x")),IF(OR(OR(D12="X",D12="x"),AND(B12=F12,C12=E12)),1,0),0)+IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,D21="X",D21="x",D22="X",D22="x",D23="X",D23="x",D24="X",D24="x",D25="X",D25="x",OR(D20="X",D20="x")),IF(OR(OR(D20="X",D20="x"),AND(B20=F20,C20=E20)),1,0),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,D37="X",D37="x",D38="X",D38="x",D39="X",D39="x",D40="X",D40="x",D41="X",D41="x",OR(D36="X",D36="x")),IF(OR(OR(D36="X",D36="x"),AND(B36=F36,C36=E36)),1,0),0)</f>
+      </c>
+      <c r="G55" s="18" t="str">
+        <f>RANK(U55,$U$53:$U$56)+COUNTIF($U$52:U54,U55)</f>
+      </c>
+      <c r="I55" s="14" t="str">
+        <f>'data'!$B$12</f>
       </c>
       <c r="J55" s="14" t="str">
-        <f>IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),IF(OR(L12="X",L12="x"),0,IF(OR(J12&gt;N12,AND(J12=N12,K12&gt;M12)),1,0)),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,IF(OR(J20&gt;N20,AND(J20=N20,K20&gt;M20)),1,0)),0)</f>
+        <f>IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,L13="X",L13="x",L14="X",L14="x",L15="X",L15="x",L16="X",L16="x",L17="X",L17="x",OR(L12="X",L12="x")),IF(OR(OR(L12="X",L12="x"),AND(J12=N12,K12=M12)),0,IF(OR(J12&gt;N12,AND(J12=N12,K12&gt;M12)),1,0)),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,L21="X",L21="x",L22="X",L22="x",L23="X",L23="x",L24="X",L24="x",L25="X",L25="x",OR(L20="X",L20="x")),IF(OR(OR(L20="X",L20="x"),AND(J20=N20,K20=M20)),0,IF(OR(J20&gt;N20,AND(J20=N20,K20&gt;M20)),1,0)),0)</f>
       </c>
       <c r="K55" s="14" t="str">
-        <f>IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),IF(OR(L12="X",L12="x"),0,IF(OR(J12&lt;N12,AND(J12=N12,K12&lt;M12)),1,0)),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,IF(OR(J20&lt;N20,AND(J20=N20,K20&lt;M20)),1,0)),0)</f>
+        <f>IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,L13="X",L13="x",L14="X",L14="x",L15="X",L15="x",L16="X",L16="x",L17="X",L17="x",OR(L12="X",L12="x")),IF(OR(OR(L12="X",L12="x"),AND(J12=N12,K12=M12)),0,IF(OR(J12&lt;N12,AND(J12=N12,K12&lt;M12)),1,0)),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,L21="X",L21="x",L22="X",L22="x",L23="X",L23="x",L24="X",L24="x",L25="X",L25="x",OR(L20="X",L20="x")),IF(OR(OR(L20="X",L20="x"),AND(J20=N20,K20=M20)),0,IF(OR(J20&lt;N20,AND(J20=N20,K20&lt;M20)),1,0)),0)</f>
       </c>
       <c r="L55" s="14" t="str">
-        <f>IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),IF(OR(L12="X",L12="x"),1,0),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,L13="X",L13="x",L14="X",L14="x",L15="X",L15="x",L16="X",L16="x",L17="X",L17="x",OR(L12="X",L12="x")),IF(OR(OR(L12="X",L12="x"),AND(J12=N12,K12=M12)),1,0),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,L21="X",L21="x",L22="X",L22="x",L23="X",L23="x",L24="X",L24="x",L25="X",L25="x",OR(L20="X",L20="x")),IF(OR(OR(L20="X",L20="x"),AND(J20=N20,K20=M20)),1,0),0)</f>
+      </c>
+      <c r="O55" s="18" t="str">
+        <f>RANK(AC55,$AC$53:$AC$55)+COUNTIF($AC$52:AC54,AC55)</f>
+      </c>
+      <c r="U55" t="str">
+        <f>=(B55*1000000000)-(C55*10000000)+(D55*100000)+(B61*1000)-(C61*100)+(D61*10)+(E61*1)-(F61*0.01)</f>
+      </c>
+      <c r="AC55" t="str">
+        <f>=(J55*1000000000)-(K55*10000000)+(L55*100000)+(J60*1000)-(K60*100)+(L60*10)+(M60*1)-(N60*0.01)</f>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="str">
-        <f>data!$B$6</f>
+      <c r="A56" s="14" t="str">
+        <f>'data'!$B$6</f>
       </c>
       <c r="B56" s="14" t="str">
-        <f>IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,IF(OR(B20&gt;F20,AND(B20=F20,C20&gt;E20)),1,0)),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),IF(OR(D28="X",D28="x"),0,IF(OR(B28&gt;F28,AND(B28=F28,C28&gt;E28)),1,0)),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),IF(OR(D44="X",D44="x"),0,IF(OR(B44&gt;F44,AND(B44=F44,C44&gt;E44)),1,0)),0)</f>
+        <f>IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,D21="X",D21="x",D22="X",D22="x",D23="X",D23="x",D24="X",D24="x",D25="X",D25="x",OR(D20="X",D20="x")),IF(OR(OR(D20="X",D20="x"),AND(B20=F20,C20=E20)),0,IF(OR(B20&gt;F20,AND(B20=F20,C20&gt;E20)),1,0)),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,D29="X",D29="x",D30="X",D30="x",D31="X",D31="x",D32="X",D32="x",D33="X",D33="x",OR(D28="X",D28="x")),IF(OR(OR(D28="X",D28="x"),AND(B28=F28,C28=E28)),0,IF(OR(B28&gt;F28,AND(B28=F28,C28&gt;E28)),1,0)),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,D45="X",D45="x",D46="X",D46="x",D47="X",D47="x",D48="X",D48="x",D49="X",D49="x",OR(D44="X",D44="x")),IF(OR(OR(D44="X",D44="x"),AND(B44=F44,C44=E44)),0,IF(OR(B44&gt;F44,AND(B44=F44,C44&gt;E44)),1,0)),0)</f>
       </c>
       <c r="C56" s="14" t="str">
-        <f>IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,IF(OR(B20&lt;F20,AND(B20=F20,C20&lt;E20)),1,0)),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),IF(OR(D28="X",D28="x"),0,IF(OR(B28&lt;F28,AND(B28=F28,C28&lt;E28)),1,0)),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),IF(OR(D44="X",D44="x"),0,IF(OR(B44&lt;F44,AND(B44=F44,C44&lt;E44)),1,0)),0)</f>
+        <f>IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,D21="X",D21="x",D22="X",D22="x",D23="X",D23="x",D24="X",D24="x",D25="X",D25="x",OR(D20="X",D20="x")),IF(OR(OR(D20="X",D20="x"),AND(B20=F20,C20=E20)),0,IF(OR(B20&lt;F20,AND(B20=F20,C20&lt;E20)),1,0)),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,D29="X",D29="x",D30="X",D30="x",D31="X",D31="x",D32="X",D32="x",D33="X",D33="x",OR(D28="X",D28="x")),IF(OR(OR(D28="X",D28="x"),AND(B28=F28,C28=E28)),0,IF(OR(B28&lt;F28,AND(B28=F28,C28&lt;E28)),1,0)),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,D45="X",D45="x",D46="X",D46="x",D47="X",D47="x",D48="X",D48="x",D49="X",D49="x",OR(D44="X",D44="x")),IF(OR(OR(D44="X",D44="x"),AND(B44=F44,C44=E44)),0,IF(OR(B44&lt;F44,AND(B44=F44,C44&lt;E44)),1,0)),0)</f>
       </c>
       <c r="D56" s="14" t="str">
-        <f>IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),1,0),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),IF(OR(D28="X",D28="x"),1,0),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),IF(OR(D44="X",D44="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,D21="X",D21="x",D22="X",D22="x",D23="X",D23="x",D24="X",D24="x",D25="X",D25="x",OR(D20="X",D20="x")),IF(OR(OR(D20="X",D20="x"),AND(B20=F20,C20=E20)),1,0),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,D29="X",D29="x",D30="X",D30="x",D31="X",D31="x",D32="X",D32="x",D33="X",D33="x",OR(D28="X",D28="x")),IF(OR(OR(D28="X",D28="x"),AND(B28=F28,C28=E28)),1,0),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,D45="X",D45="x",D46="X",D46="x",D47="X",D47="x",D48="X",D48="x",D49="X",D49="x",OR(D44="X",D44="x")),IF(OR(OR(D44="X",D44="x"),AND(B44=F44,C44=E44)),1,0),0)</f>
+      </c>
+      <c r="G56" s="18" t="str">
+        <f>RANK(U56,$U$53:$U$56)+COUNTIF($U$52:U55,U56)</f>
+      </c>
+      <c r="U56" t="str">
+        <f>=(B56*1000000000)-(C56*10000000)+(D56*100000)+(B62*1000)-(C62*100)+(D62*10)+(E62*1)-(F62*0.01)</f>
       </c>
     </row>
     <row r="57">
       <c r="I57" s="13"/>
       <c r="J57" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K57" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L57" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M57" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N57" s="13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="13"/>
       <c r="B58" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="I58" t="str">
-        <f>data!$B$10</f>
+        <v>47</v>
+      </c>
+      <c r="I58" s="14" t="str">
+        <f>'data'!$B$10</f>
       </c>
       <c r="J58" s="14" t="str">
-        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),N4,0)+IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),N12,0)</f>
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x"),UPPER(L5)="X",UPPER(L6)="X",UPPER(L7)="X",UPPER(L8)="X",UPPER(L9)="X"),N4,0)+IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x"),UPPER(L13)="X",UPPER(L14)="X",UPPER(L15)="X",UPPER(L16)="X",UPPER(L17)="X"),N12,0)</f>
       </c>
       <c r="K58" s="14" t="str">
-        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),J4,0)+IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),J12,0)</f>
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x"),UPPER(L5)="X",UPPER(L6)="X",UPPER(L7)="X",UPPER(L8)="X",UPPER(L9)="X"),J4,0)+IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x"),UPPER(L13)="X",UPPER(L14)="X",UPPER(L15)="X",UPPER(L16)="X",UPPER(L17)="X"),J12,0)</f>
       </c>
       <c r="L58" s="14" t="str">
-        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),(IF(OR(L5="X",L5="x"),1,0)+IF(OR(L6="X",L6="x"),1,0)+IF(OR(L7="X",L7="x"),1,0)+IF(OR(L8="X",L8="x"),1,0)+IF(OR(L9="X",L9="x"),1,0)),0)+IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),(IF(OR(L13="X",L13="x"),1,0)+IF(OR(L14="X",L14="x"),1,0)+IF(OR(L15="X",L15="x"),1,0)+IF(OR(L16="X",L16="x"),1,0)+IF(OR(L17="X",L17="x"),1,0)),0)</f>
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x"),UPPER(L5)="X",UPPER(L6)="X",UPPER(L7)="X",UPPER(L8)="X",UPPER(L9)="X"),(IF(OR(L5="X",L5="x",AND(COUNTA(J5,K5,M5,N5)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))))),1,0)+IF(OR(L6="X",L6="x",AND(COUNTA(J6,K6,M6,N6)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))))),1,0)+IF(OR(L7="X",L7="x",AND(COUNTA(J7,K7,M7,N7)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-",""))))),1,0)+IF(OR(L8="X",L8="x",AND(COUNTA(J8,K8,M8,N8)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-",""))))),1,0)+IF(OR(L9="X",L9="x",AND(COUNTA(J9,K9,M9,N9)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-",""))))),1,0)),0)+IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x"),UPPER(L13)="X",UPPER(L14)="X",UPPER(L15)="X",UPPER(L16)="X",UPPER(L17)="X"),(IF(OR(L13="X",L13="x",AND(COUNTA(J13,K13,M13,N13)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-",""))))),1,0)+IF(OR(L14="X",L14="x",AND(COUNTA(J14,K14,M14,N14)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-",""))))),1,0)+IF(OR(L15="X",L15="x",AND(COUNTA(J15,K15,M15,N15)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-",""))))),1,0)+IF(OR(L16="X",L16="x",AND(COUNTA(J16,K16,M16,N16)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-",""))))),1,0)+IF(OR(L17="X",L17="x",AND(COUNTA(J17,K17,M17,N17)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-",""))))),1,0)),0)</f>
       </c>
       <c r="M58" s="14" t="str">
         <f>M4+M12</f>
@@ -2725,17 +2778,17 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="str">
-        <f>data!$B$3</f>
+      <c r="A59" s="14" t="str">
+        <f>'data'!$B$3</f>
       </c>
       <c r="B59" s="14" t="str">
-        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),F4,0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),F28,0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),F36,0)</f>
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x"),UPPER(D5)="X",UPPER(D6)="X",UPPER(D7)="X",UPPER(D8)="X",UPPER(D9)="X"),F4,0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x"),UPPER(D29)="X",UPPER(D30)="X",UPPER(D31)="X",UPPER(D32)="X",UPPER(D33)="X"),F28,0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x"),UPPER(D37)="X",UPPER(D38)="X",UPPER(D39)="X",UPPER(D40)="X",UPPER(D41)="X"),F36,0)</f>
       </c>
       <c r="C59" s="14" t="str">
-        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),B4,0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),B28,0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),B36,0)</f>
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x"),UPPER(D5)="X",UPPER(D6)="X",UPPER(D7)="X",UPPER(D8)="X",UPPER(D9)="X"),B4,0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x"),UPPER(D29)="X",UPPER(D30)="X",UPPER(D31)="X",UPPER(D32)="X",UPPER(D33)="X"),B28,0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x"),UPPER(D37)="X",UPPER(D38)="X",UPPER(D39)="X",UPPER(D40)="X",UPPER(D41)="X"),B36,0)</f>
       </c>
       <c r="D59" s="14" t="str">
-        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),(IF(OR(D5="X",D5="x"),1,0)+IF(OR(D6="X",D6="x"),1,0)+IF(OR(D7="X",D7="x"),1,0)+IF(OR(D8="X",D8="x"),1,0)+IF(OR(D9="X",D9="x"),1,0)),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),(IF(OR(D29="X",D29="x"),1,0)+IF(OR(D30="X",D30="x"),1,0)+IF(OR(D31="X",D31="x"),1,0)+IF(OR(D32="X",D32="x"),1,0)+IF(OR(D33="X",D33="x"),1,0)),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),(IF(OR(D37="X",D37="x"),1,0)+IF(OR(D38="X",D38="x"),1,0)+IF(OR(D39="X",D39="x"),1,0)+IF(OR(D40="X",D40="x"),1,0)+IF(OR(D41="X",D41="x"),1,0)),0)</f>
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x"),UPPER(D5)="X",UPPER(D6)="X",UPPER(D7)="X",UPPER(D8)="X",UPPER(D9)="X"),(IF(OR(D5="X",D5="x",AND(COUNTA(B5,C5,E5,F5)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))))),1,0)+IF(OR(D6="X",D6="x",AND(COUNTA(B6,C6,E6,F6)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))))),1,0)+IF(OR(D7="X",D7="x",AND(COUNTA(B7,C7,E7,F7)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))))),1,0)+IF(OR(D8="X",D8="x",AND(COUNTA(B8,C8,E8,F8)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-",""))))),1,0)+IF(OR(D9="X",D9="x",AND(COUNTA(B9,C9,E9,F9)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-",""))))),1,0)),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x"),UPPER(D29)="X",UPPER(D30)="X",UPPER(D31)="X",UPPER(D32)="X",UPPER(D33)="X"),(IF(OR(D29="X",D29="x",AND(COUNTA(B29,C29,E29,F29)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-",""))))),1,0)+IF(OR(D30="X",D30="x",AND(COUNTA(B30,C30,E30,F30)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-",""))))),1,0)+IF(OR(D31="X",D31="x",AND(COUNTA(B31,C31,E31,F31)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-",""))))),1,0)+IF(OR(D32="X",D32="x",AND(COUNTA(B32,C32,E32,F32)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C32," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F32," ",""),"0",""),"-",""))))),1,0)+IF(OR(D33="X",D33="x",AND(COUNTA(B33,C33,E33,F33)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C33," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F33," ",""),"0",""),"-",""))))),1,0)),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x"),UPPER(D37)="X",UPPER(D38)="X",UPPER(D39)="X",UPPER(D40)="X",UPPER(D41)="X"),(IF(OR(D37="X",D37="x",AND(COUNTA(B37,C37,E37,F37)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))))),1,0)+IF(OR(D38="X",D38="x",AND(COUNTA(B38,C38,E38,F38)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))))),1,0)+IF(OR(D39="X",D39="x",AND(COUNTA(B39,C39,E39,F39)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))))),1,0)+IF(OR(D40="X",D40="x",AND(COUNTA(B40,C40,E40,F40)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))))),1,0)+IF(OR(D41="X",D41="x",AND(COUNTA(B41,C41,E41,F41)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-",""))))),1,0)),0)</f>
       </c>
       <c r="E59" s="14" t="str">
         <f>E4+E28+E36</f>
@@ -2743,17 +2796,17 @@
       <c r="F59" s="14" t="str">
         <f>C4+C28+C36</f>
       </c>
-      <c r="I59" t="str">
-        <f>data!$B$11</f>
+      <c r="I59" s="14" t="str">
+        <f>'data'!$B$11</f>
       </c>
       <c r="J59" s="14" t="str">
-        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),J4,0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),N20,0)</f>
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x"),UPPER(L5)="X",UPPER(L6)="X",UPPER(L7)="X",UPPER(L8)="X",UPPER(L9)="X"),J4,0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x"),UPPER(L21)="X",UPPER(L22)="X",UPPER(L23)="X",UPPER(L24)="X",UPPER(L25)="X"),N20,0)</f>
       </c>
       <c r="K59" s="14" t="str">
-        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),N4,0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),J20,0)</f>
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x"),UPPER(L5)="X",UPPER(L6)="X",UPPER(L7)="X",UPPER(L8)="X",UPPER(L9)="X"),N4,0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x"),UPPER(L21)="X",UPPER(L22)="X",UPPER(L23)="X",UPPER(L24)="X",UPPER(L25)="X"),J20,0)</f>
       </c>
       <c r="L59" s="14" t="str">
-        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x")),(IF(OR(L5="X",L5="x"),1,0)+IF(OR(L6="X",L6="x"),1,0)+IF(OR(L7="X",L7="x"),1,0)+IF(OR(L8="X",L8="x"),1,0)+IF(OR(L9="X",L9="x"),1,0)),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),(IF(OR(L21="X",L21="x"),1,0)+IF(OR(L22="X",L22="x"),1,0)+IF(OR(L23="X",L23="x"),1,0)+IF(OR(L24="X",L24="x"),1,0)+IF(OR(L25="X",L25="x"),1,0)),0)</f>
+        <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x"),UPPER(L5)="X",UPPER(L6)="X",UPPER(L7)="X",UPPER(L8)="X",UPPER(L9)="X"),(IF(OR(L5="X",L5="x",AND(COUNTA(J5,K5,M5,N5)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))))),1,0)+IF(OR(L6="X",L6="x",AND(COUNTA(J6,K6,M6,N6)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))))),1,0)+IF(OR(L7="X",L7="x",AND(COUNTA(J7,K7,M7,N7)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-",""))))),1,0)+IF(OR(L8="X",L8="x",AND(COUNTA(J8,K8,M8,N8)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-",""))))),1,0)+IF(OR(L9="X",L9="x",AND(COUNTA(J9,K9,M9,N9)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-",""))))),1,0)),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x"),UPPER(L21)="X",UPPER(L22)="X",UPPER(L23)="X",UPPER(L24)="X",UPPER(L25)="X"),(IF(OR(L21="X",L21="x",AND(COUNTA(J21,K21,M21,N21)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))))),1,0)+IF(OR(L22="X",L22="x",AND(COUNTA(J22,K22,M22,N22)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))))),1,0)+IF(OR(L23="X",L23="x",AND(COUNTA(J23,K23,M23,N23)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))))),1,0)+IF(OR(L24="X",L24="x",AND(COUNTA(J24,K24,M24,N24)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-",""))))),1,0)+IF(OR(L25="X",L25="x",AND(COUNTA(J25,K25,M25,N25)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-",""))))),1,0)),0)</f>
       </c>
       <c r="M59" s="14" t="str">
         <f>K4+M20</f>
@@ -2763,17 +2816,17 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="str">
-        <f>data!$B$4</f>
+      <c r="A60" s="14" t="str">
+        <f>'data'!$B$4</f>
       </c>
       <c r="B60" s="14" t="str">
-        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),B4,0)+IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),B12,0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),F44,0)</f>
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x"),UPPER(D5)="X",UPPER(D6)="X",UPPER(D7)="X",UPPER(D8)="X",UPPER(D9)="X"),B4,0)+IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x"),UPPER(D13)="X",UPPER(D14)="X",UPPER(D15)="X",UPPER(D16)="X",UPPER(D17)="X"),B12,0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x"),UPPER(D45)="X",UPPER(D46)="X",UPPER(D47)="X",UPPER(D48)="X",UPPER(D49)="X"),F44,0)</f>
       </c>
       <c r="C60" s="14" t="str">
-        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),F4,0)+IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),F12,0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),B44,0)</f>
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x"),UPPER(D5)="X",UPPER(D6)="X",UPPER(D7)="X",UPPER(D8)="X",UPPER(D9)="X"),F4,0)+IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x"),UPPER(D13)="X",UPPER(D14)="X",UPPER(D15)="X",UPPER(D16)="X",UPPER(D17)="X"),F12,0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x"),UPPER(D45)="X",UPPER(D46)="X",UPPER(D47)="X",UPPER(D48)="X",UPPER(D49)="X"),B44,0)</f>
       </c>
       <c r="D60" s="14" t="str">
-        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x")),(IF(OR(D5="X",D5="x"),1,0)+IF(OR(D6="X",D6="x"),1,0)+IF(OR(D7="X",D7="x"),1,0)+IF(OR(D8="X",D8="x"),1,0)+IF(OR(D9="X",D9="x"),1,0)),0)+IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),(IF(OR(D13="X",D13="x"),1,0)+IF(OR(D14="X",D14="x"),1,0)+IF(OR(D15="X",D15="x"),1,0)+IF(OR(D16="X",D16="x"),1,0)+IF(OR(D17="X",D17="x"),1,0)),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),(IF(OR(D45="X",D45="x"),1,0)+IF(OR(D46="X",D46="x"),1,0)+IF(OR(D47="X",D47="x"),1,0)+IF(OR(D48="X",D48="x"),1,0)+IF(OR(D49="X",D49="x"),1,0)),0)</f>
+        <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x"),UPPER(D5)="X",UPPER(D6)="X",UPPER(D7)="X",UPPER(D8)="X",UPPER(D9)="X"),(IF(OR(D5="X",D5="x",AND(COUNTA(B5,C5,E5,F5)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))))),1,0)+IF(OR(D6="X",D6="x",AND(COUNTA(B6,C6,E6,F6)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))))),1,0)+IF(OR(D7="X",D7="x",AND(COUNTA(B7,C7,E7,F7)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))))),1,0)+IF(OR(D8="X",D8="x",AND(COUNTA(B8,C8,E8,F8)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-",""))))),1,0)+IF(OR(D9="X",D9="x",AND(COUNTA(B9,C9,E9,F9)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-",""))))),1,0)),0)+IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x"),UPPER(D13)="X",UPPER(D14)="X",UPPER(D15)="X",UPPER(D16)="X",UPPER(D17)="X"),(IF(OR(D13="X",D13="x",AND(COUNTA(B13,C13,E13,F13)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-",""))))),1,0)+IF(OR(D14="X",D14="x",AND(COUNTA(B14,C14,E14,F14)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-",""))))),1,0)+IF(OR(D15="X",D15="x",AND(COUNTA(B15,C15,E15,F15)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-",""))))),1,0)+IF(OR(D16="X",D16="x",AND(COUNTA(B16,C16,E16,F16)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-",""))))),1,0)+IF(OR(D17="X",D17="x",AND(COUNTA(B17,C17,E17,F17)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-",""))))),1,0)),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x"),UPPER(D45)="X",UPPER(D46)="X",UPPER(D47)="X",UPPER(D48)="X",UPPER(D49)="X"),(IF(OR(D45="X",D45="x",AND(COUNTA(B45,C45,E45,F45)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-",""))))),1,0)+IF(OR(D46="X",D46="x",AND(COUNTA(B46,C46,E46,F46)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-",""))))),1,0)+IF(OR(D47="X",D47="x",AND(COUNTA(B47,C47,E47,F47)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-",""))))),1,0)+IF(OR(D48="X",D48="x",AND(COUNTA(B48,C48,E48,F48)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-",""))))),1,0)+IF(OR(D49="X",D49="x",AND(COUNTA(B49,C49,E49,F49)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-",""))))),1,0)),0)</f>
       </c>
       <c r="E60" s="14" t="str">
         <f>C4+C12+E44</f>
@@ -2781,17 +2834,17 @@
       <c r="F60" s="14" t="str">
         <f>E4+E12+C44</f>
       </c>
-      <c r="I60" t="str">
-        <f>data!$B$12</f>
+      <c r="I60" s="14" t="str">
+        <f>'data'!$B$12</f>
       </c>
       <c r="J60" s="14" t="str">
-        <f>IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),J12,0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),J20,0)</f>
+        <f>IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x"),UPPER(L13)="X",UPPER(L14)="X",UPPER(L15)="X",UPPER(L16)="X",UPPER(L17)="X"),J12,0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x"),UPPER(L21)="X",UPPER(L22)="X",UPPER(L23)="X",UPPER(L24)="X",UPPER(L25)="X"),J20,0)</f>
       </c>
       <c r="K60" s="14" t="str">
-        <f>IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),N12,0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),N20,0)</f>
+        <f>IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x"),UPPER(L13)="X",UPPER(L14)="X",UPPER(L15)="X",UPPER(L16)="X",UPPER(L17)="X"),N12,0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x"),UPPER(L21)="X",UPPER(L22)="X",UPPER(L23)="X",UPPER(L24)="X",UPPER(L25)="X"),N20,0)</f>
       </c>
       <c r="L60" s="14" t="str">
-        <f>IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x")),(IF(OR(L13="X",L13="x"),1,0)+IF(OR(L14="X",L14="x"),1,0)+IF(OR(L15="X",L15="x"),1,0)+IF(OR(L16="X",L16="x"),1,0)+IF(OR(L17="X",L17="x"),1,0)),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x")),(IF(OR(L21="X",L21="x"),1,0)+IF(OR(L22="X",L22="x"),1,0)+IF(OR(L23="X",L23="x"),1,0)+IF(OR(L24="X",L24="x"),1,0)+IF(OR(L25="X",L25="x"),1,0)),0)</f>
+        <f>IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x"),UPPER(L13)="X",UPPER(L14)="X",UPPER(L15)="X",UPPER(L16)="X",UPPER(L17)="X"),(IF(OR(L13="X",L13="x",AND(COUNTA(J13,K13,M13,N13)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-",""))))),1,0)+IF(OR(L14="X",L14="x",AND(COUNTA(J14,K14,M14,N14)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-",""))))),1,0)+IF(OR(L15="X",L15="x",AND(COUNTA(J15,K15,M15,N15)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-",""))))),1,0)+IF(OR(L16="X",L16="x",AND(COUNTA(J16,K16,M16,N16)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-",""))))),1,0)+IF(OR(L17="X",L17="x",AND(COUNTA(J17,K17,M17,N17)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-",""))))),1,0)),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x"),UPPER(L21)="X",UPPER(L22)="X",UPPER(L23)="X",UPPER(L24)="X",UPPER(L25)="X"),(IF(OR(L21="X",L21="x",AND(COUNTA(J21,K21,M21,N21)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))))),1,0)+IF(OR(L22="X",L22="x",AND(COUNTA(J22,K22,M22,N22)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))))),1,0)+IF(OR(L23="X",L23="x",AND(COUNTA(J23,K23,M23,N23)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))))),1,0)+IF(OR(L24="X",L24="x",AND(COUNTA(J24,K24,M24,N24)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-",""))))),1,0)+IF(OR(L25="X",L25="x",AND(COUNTA(J25,K25,M25,N25)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-",""))))),1,0)),0)</f>
       </c>
       <c r="M60" s="14" t="str">
         <f>K12+K20</f>
@@ -2801,17 +2854,17 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="str">
-        <f>data!$B$5</f>
+      <c r="A61" s="14" t="str">
+        <f>'data'!$B$5</f>
       </c>
       <c r="B61" s="14" t="str">
-        <f>IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),F12,0)+IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),F20,0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),B36,0)</f>
+        <f>IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x"),UPPER(D13)="X",UPPER(D14)="X",UPPER(D15)="X",UPPER(D16)="X",UPPER(D17)="X"),F12,0)+IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x"),UPPER(D21)="X",UPPER(D22)="X",UPPER(D23)="X",UPPER(D24)="X",UPPER(D25)="X"),F20,0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x"),UPPER(D37)="X",UPPER(D38)="X",UPPER(D39)="X",UPPER(D40)="X",UPPER(D41)="X"),B36,0)</f>
       </c>
       <c r="C61" s="14" t="str">
-        <f>IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),B12,0)+IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),B20,0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),F36,0)</f>
+        <f>IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x"),UPPER(D13)="X",UPPER(D14)="X",UPPER(D15)="X",UPPER(D16)="X",UPPER(D17)="X"),B12,0)+IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x"),UPPER(D21)="X",UPPER(D22)="X",UPPER(D23)="X",UPPER(D24)="X",UPPER(D25)="X"),B20,0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x"),UPPER(D37)="X",UPPER(D38)="X",UPPER(D39)="X",UPPER(D40)="X",UPPER(D41)="X"),F36,0)</f>
       </c>
       <c r="D61" s="14" t="str">
-        <f>IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x")),(IF(OR(D13="X",D13="x"),1,0)+IF(OR(D14="X",D14="x"),1,0)+IF(OR(D15="X",D15="x"),1,0)+IF(OR(D16="X",D16="x"),1,0)+IF(OR(D17="X",D17="x"),1,0)),0)+IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),(IF(OR(D21="X",D21="x"),1,0)+IF(OR(D22="X",D22="x"),1,0)+IF(OR(D23="X",D23="x"),1,0)+IF(OR(D24="X",D24="x"),1,0)+IF(OR(D25="X",D25="x"),1,0)),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x")),(IF(OR(D37="X",D37="x"),1,0)+IF(OR(D38="X",D38="x"),1,0)+IF(OR(D39="X",D39="x"),1,0)+IF(OR(D40="X",D40="x"),1,0)+IF(OR(D41="X",D41="x"),1,0)),0)</f>
+        <f>IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x"),UPPER(D13)="X",UPPER(D14)="X",UPPER(D15)="X",UPPER(D16)="X",UPPER(D17)="X"),(IF(OR(D13="X",D13="x",AND(COUNTA(B13,C13,E13,F13)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-",""))))),1,0)+IF(OR(D14="X",D14="x",AND(COUNTA(B14,C14,E14,F14)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-",""))))),1,0)+IF(OR(D15="X",D15="x",AND(COUNTA(B15,C15,E15,F15)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-",""))))),1,0)+IF(OR(D16="X",D16="x",AND(COUNTA(B16,C16,E16,F16)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-",""))))),1,0)+IF(OR(D17="X",D17="x",AND(COUNTA(B17,C17,E17,F17)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-",""))))),1,0)),0)+IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x"),UPPER(D21)="X",UPPER(D22)="X",UPPER(D23)="X",UPPER(D24)="X",UPPER(D25)="X"),(IF(OR(D21="X",D21="x",AND(COUNTA(B21,C21,E21,F21)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))))),1,0)+IF(OR(D22="X",D22="x",AND(COUNTA(B22,C22,E22,F22)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))))),1,0)+IF(OR(D23="X",D23="x",AND(COUNTA(B23,C23,E23,F23)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))))),1,0)+IF(OR(D24="X",D24="x",AND(COUNTA(B24,C24,E24,F24)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-",""))))),1,0)+IF(OR(D25="X",D25="x",AND(COUNTA(B25,C25,E25,F25)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-",""))))),1,0)),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x"),UPPER(D37)="X",UPPER(D38)="X",UPPER(D39)="X",UPPER(D40)="X",UPPER(D41)="X"),(IF(OR(D37="X",D37="x",AND(COUNTA(B37,C37,E37,F37)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))))),1,0)+IF(OR(D38="X",D38="x",AND(COUNTA(B38,C38,E38,F38)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))))),1,0)+IF(OR(D39="X",D39="x",AND(COUNTA(B39,C39,E39,F39)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))))),1,0)+IF(OR(D40="X",D40="x",AND(COUNTA(B40,C40,E40,F40)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))))),1,0)+IF(OR(D41="X",D41="x",AND(COUNTA(B41,C41,E41,F41)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-",""))))),1,0)),0)</f>
       </c>
       <c r="E61" s="14" t="str">
         <f>E12+E20+C36</f>
@@ -2821,17 +2874,17 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="str">
-        <f>data!$B$6</f>
+      <c r="A62" s="14" t="str">
+        <f>'data'!$B$6</f>
       </c>
       <c r="B62" s="14" t="str">
-        <f>IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),B20,0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),B28,0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),B44,0)</f>
+        <f>IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x"),UPPER(D21)="X",UPPER(D22)="X",UPPER(D23)="X",UPPER(D24)="X",UPPER(D25)="X"),B20,0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x"),UPPER(D29)="X",UPPER(D30)="X",UPPER(D31)="X",UPPER(D32)="X",UPPER(D33)="X"),B28,0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x"),UPPER(D45)="X",UPPER(D46)="X",UPPER(D47)="X",UPPER(D48)="X",UPPER(D49)="X"),B44,0)</f>
       </c>
       <c r="C62" s="14" t="str">
-        <f>IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),F20,0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),F28,0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),F44,0)</f>
+        <f>IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x"),UPPER(D21)="X",UPPER(D22)="X",UPPER(D23)="X",UPPER(D24)="X",UPPER(D25)="X"),F20,0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x"),UPPER(D29)="X",UPPER(D30)="X",UPPER(D31)="X",UPPER(D32)="X",UPPER(D33)="X"),F28,0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x"),UPPER(D45)="X",UPPER(D46)="X",UPPER(D47)="X",UPPER(D48)="X",UPPER(D49)="X"),F44,0)</f>
       </c>
       <c r="D62" s="14" t="str">
-        <f>IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x")),(IF(OR(D21="X",D21="x"),1,0)+IF(OR(D22="X",D22="x"),1,0)+IF(OR(D23="X",D23="x"),1,0)+IF(OR(D24="X",D24="x"),1,0)+IF(OR(D25="X",D25="x"),1,0)),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x")),(IF(OR(D29="X",D29="x"),1,0)+IF(OR(D30="X",D30="x"),1,0)+IF(OR(D31="X",D31="x"),1,0)+IF(OR(D32="X",D32="x"),1,0)+IF(OR(D33="X",D33="x"),1,0)),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x")),(IF(OR(D45="X",D45="x"),1,0)+IF(OR(D46="X",D46="x"),1,0)+IF(OR(D47="X",D47="x"),1,0)+IF(OR(D48="X",D48="x"),1,0)+IF(OR(D49="X",D49="x"),1,0)),0)</f>
+        <f>IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x"),UPPER(D21)="X",UPPER(D22)="X",UPPER(D23)="X",UPPER(D24)="X",UPPER(D25)="X"),(IF(OR(D21="X",D21="x",AND(COUNTA(B21,C21,E21,F21)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))))),1,0)+IF(OR(D22="X",D22="x",AND(COUNTA(B22,C22,E22,F22)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))))),1,0)+IF(OR(D23="X",D23="x",AND(COUNTA(B23,C23,E23,F23)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))))),1,0)+IF(OR(D24="X",D24="x",AND(COUNTA(B24,C24,E24,F24)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-",""))))),1,0)+IF(OR(D25="X",D25="x",AND(COUNTA(B25,C25,E25,F25)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-",""))))),1,0)),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x"),UPPER(D29)="X",UPPER(D30)="X",UPPER(D31)="X",UPPER(D32)="X",UPPER(D33)="X"),(IF(OR(D29="X",D29="x",AND(COUNTA(B29,C29,E29,F29)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-",""))))),1,0)+IF(OR(D30="X",D30="x",AND(COUNTA(B30,C30,E30,F30)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-",""))))),1,0)+IF(OR(D31="X",D31="x",AND(COUNTA(B31,C31,E31,F31)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-",""))))),1,0)+IF(OR(D32="X",D32="x",AND(COUNTA(B32,C32,E32,F32)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C32," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F32," ",""),"0",""),"-",""))))),1,0)+IF(OR(D33="X",D33="x",AND(COUNTA(B33,C33,E33,F33)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C33," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F33," ",""),"0",""),"-",""))))),1,0)),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x"),UPPER(D45)="X",UPPER(D46)="X",UPPER(D47)="X",UPPER(D48)="X",UPPER(D49)="X"),(IF(OR(D45="X",D45="x",AND(COUNTA(B45,C45,E45,F45)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-",""))))),1,0)+IF(OR(D46="X",D46="x",AND(COUNTA(B46,C46,E46,F46)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-",""))))),1,0)+IF(OR(D47="X",D47="x",AND(COUNTA(B47,C47,E47,F47)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-",""))))),1,0)+IF(OR(D48="X",D48="x",AND(COUNTA(B48,C48,E48,F48)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-",""))))),1,0)+IF(OR(D49="X",D49="x",AND(COUNTA(B49,C49,E49,F49)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-",""))))),1,0)),0)</f>
       </c>
       <c r="E62" s="14" t="str">
         <f>C20+C28+C44</f>
@@ -2843,512 +2896,559 @@
     <row r="63">
       <c r="N63" s="13"/>
       <c r="O63" s="13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64">
       <c r="N64" t="s">
-        <v>47</v>
-      </c>
-      <c r="O64" s="19"/>
+        <v>49</v>
+      </c>
+      <c r="O64" s="19" t="str">
+        <f>IFERROR(INDEX($I$53:$I$60, MATCH(1, $O$53:$O$60, 0)), "-")</f>
+      </c>
     </row>
     <row r="65">
       <c r="F65" s="13"/>
       <c r="G65" s="13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N65" t="s">
-        <v>48</v>
-      </c>
-      <c r="O65" s="19"/>
+        <v>50</v>
+      </c>
+      <c r="O65" s="19" t="str">
+        <f>IFERROR(INDEX($I$53:$I$60, MATCH(2, $O$53:$O$60, 0)), "-")</f>
+      </c>
     </row>
     <row r="66">
       <c r="F66" t="s">
-        <v>47</v>
-      </c>
-      <c r="G66" s="19"/>
+        <v>49</v>
+      </c>
+      <c r="G66" s="19" t="str">
+        <f>IFERROR(INDEX($A$53:$A$62, MATCH(1, $G$53:$G$62, 0)), "-")</f>
+      </c>
       <c r="N66" t="s">
-        <v>49</v>
-      </c>
-      <c r="O66" s="19"/>
+        <v>51</v>
+      </c>
+      <c r="O66" s="19" t="str">
+        <f>IFERROR(INDEX($I$53:$I$60, MATCH(3, $O$53:$O$60, 0)), "-")</f>
+      </c>
     </row>
     <row r="67">
       <c r="F67" t="s">
-        <v>48</v>
-      </c>
-      <c r="G67" s="19"/>
+        <v>50</v>
+      </c>
+      <c r="G67" s="19" t="str">
+        <f>IFERROR(INDEX($A$53:$A$62, MATCH(2, $G$53:$G$62, 0)), "-")</f>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="13" t="str">
-        <f>data!$A$9</f>
-      </c>
-      <c r="B68" s="13"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
+      <c r="F68" t="s">
+        <v>51</v>
+      </c>
+      <c r="G68" s="19" t="str">
+        <f>IFERROR(INDEX($A$53:$A$62, MATCH(3, $G$53:$G$62, 0)), "-")</f>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="17" t="s">
+      <c r="A69" s="13" t="str">
+        <f>'data'!$A$9</f>
+      </c>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="13"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14" t="s">
+      <c r="B70" s="14"/>
+      <c r="C70" s="14"/>
+      <c r="D70" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G69" s="16" t="s">
+      <c r="E70" s="14"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="14" t="str">
-        <f>data!$B$8</f>
-      </c>
-      <c r="B70" s="18" t="str">
-        <f>SUMPRODUCT((UPPER(D71:D75)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71:B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71:C75," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71:E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71:F75," ",""),"0",""),"-",""))))*1)</f>
-      </c>
-      <c r="C70" s="18" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71:B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71:C75," ",""),"0",""),"-","")))</f>
-      </c>
-      <c r="D70" s="18"/>
-      <c r="E70" s="18" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71:E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71:F75," ",""),"0",""),"-","")))</f>
-      </c>
-      <c r="F70" s="18" t="str">
-        <f>SUMPRODUCT((UPPER(D71:D75)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71:E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71:F75," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71:B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71:C75," ",""),"0",""),"-",""))))*1)</f>
-      </c>
-      <c r="G70" s="14" t="str">
-        <f>data!$B$7</f>
-      </c>
-    </row>
     <row r="71">
-      <c r="A71" s="18">
+      <c r="A71" s="14" t="str">
+        <f>'data'!$B$8</f>
+      </c>
+      <c r="B71" s="14" t="str">
+        <f>SUMPRODUCT((UPPER(D72:D76)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72:B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72:C76," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72:E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72:F76," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C71" s="14" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72:B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72:C76," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="D71" s="18"/>
+      <c r="E71" s="14" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72:E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72:F76," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F71" s="14" t="str">
+        <f>SUMPRODUCT((UPPER(D72:D76)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72:E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72:F76," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72:B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72:C76," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="G71" s="14" t="str">
+        <f>'data'!$B$7</f>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="14">
         <v>1</v>
-      </c>
-      <c r="B71" s="18"/>
-      <c r="C71" s="18"/>
-      <c r="D71" s="18"/>
-      <c r="E71" s="18"/>
-      <c r="F71" s="18"/>
-      <c r="G71" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="18">
-        <v>2</v>
       </c>
       <c r="B72" s="18"/>
       <c r="C72" s="18"/>
       <c r="D72" s="18"/>
       <c r="E72" s="18"/>
       <c r="F72" s="18"/>
-      <c r="G72" s="18">
+      <c r="G72" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="14">
         <v>2</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="18">
-        <v>3</v>
       </c>
       <c r="B73" s="18"/>
       <c r="C73" s="18"/>
       <c r="D73" s="18"/>
       <c r="E73" s="18"/>
       <c r="F73" s="18"/>
-      <c r="G73" s="18">
+      <c r="G73" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="14">
         <v>3</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="18">
-        <v>4</v>
       </c>
       <c r="B74" s="18"/>
       <c r="C74" s="18"/>
       <c r="D74" s="18"/>
       <c r="E74" s="18"/>
       <c r="F74" s="18"/>
-      <c r="G74" s="18">
+      <c r="G74" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="14">
         <v>4</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="18">
-        <v>5</v>
       </c>
       <c r="B75" s="18"/>
       <c r="C75" s="18"/>
       <c r="D75" s="18"/>
       <c r="E75" s="18"/>
       <c r="F75" s="18"/>
-      <c r="G75" s="18">
+      <c r="G75" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="14">
         <v>5</v>
       </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="17" t="s">
+      <c r="B76" s="18"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="18"/>
+      <c r="E76" s="18"/>
+      <c r="F76" s="18"/>
+      <c r="G76" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="14" t="s">
+      <c r="B78" s="14"/>
+      <c r="C78" s="14"/>
+      <c r="D78" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="16" t="s">
+      <c r="E78" s="14"/>
+      <c r="F78" s="14"/>
+      <c r="G78" s="16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="14" t="str">
-        <f>data!$B$9</f>
-      </c>
-      <c r="B78" s="18" t="str">
-        <f>SUMPRODUCT((UPPER(D79:D83)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B79:B83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C79:C83," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E79:E83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F79:F83," ",""),"0",""),"-",""))))*1)</f>
-      </c>
-      <c r="C78" s="18" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B79:B83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C79:C83," ",""),"0",""),"-","")))</f>
-      </c>
-      <c r="D78" s="18"/>
-      <c r="E78" s="18" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E79:E83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F79:F83," ",""),"0",""),"-","")))</f>
-      </c>
-      <c r="F78" s="18" t="str">
-        <f>SUMPRODUCT((UPPER(D79:D83)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E79:E83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F79:F83," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B79:B83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C79:C83," ",""),"0",""),"-",""))))*1)</f>
-      </c>
-      <c r="G78" s="14" t="str">
-        <f>data!$B$7</f>
-      </c>
-    </row>
     <row r="79">
-      <c r="A79" s="18">
+      <c r="A79" s="14" t="str">
+        <f>'data'!$B$9</f>
+      </c>
+      <c r="B79" s="14" t="str">
+        <f>SUMPRODUCT((UPPER(D80:D84)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80:B84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80:C84," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80:E84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80:F84," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C79" s="14" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80:B84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80:C84," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="D79" s="18"/>
+      <c r="E79" s="14" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80:E84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80:F84," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F79" s="14" t="str">
+        <f>SUMPRODUCT((UPPER(D80:D84)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80:E84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80:F84," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80:B84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80:C84," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="G79" s="14" t="str">
+        <f>'data'!$B$7</f>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="14">
         <v>1</v>
-      </c>
-      <c r="B79" s="18"/>
-      <c r="C79" s="18"/>
-      <c r="D79" s="18"/>
-      <c r="E79" s="18"/>
-      <c r="F79" s="18"/>
-      <c r="G79" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="18">
-        <v>2</v>
       </c>
       <c r="B80" s="18"/>
       <c r="C80" s="18"/>
       <c r="D80" s="18"/>
       <c r="E80" s="18"/>
       <c r="F80" s="18"/>
-      <c r="G80" s="18">
+      <c r="G80" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="14">
         <v>2</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="18">
-        <v>3</v>
       </c>
       <c r="B81" s="18"/>
       <c r="C81" s="18"/>
       <c r="D81" s="18"/>
       <c r="E81" s="18"/>
       <c r="F81" s="18"/>
-      <c r="G81" s="18">
+      <c r="G81" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="14">
         <v>3</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="18">
-        <v>4</v>
       </c>
       <c r="B82" s="18"/>
       <c r="C82" s="18"/>
       <c r="D82" s="18"/>
       <c r="E82" s="18"/>
       <c r="F82" s="18"/>
-      <c r="G82" s="18">
+      <c r="G82" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="14">
         <v>4</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="18">
-        <v>5</v>
       </c>
       <c r="B83" s="18"/>
       <c r="C83" s="18"/>
       <c r="D83" s="18"/>
       <c r="E83" s="18"/>
       <c r="F83" s="18"/>
-      <c r="G83" s="18">
+      <c r="G83" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="14">
         <v>5</v>
       </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="17" t="s">
+      <c r="B84" s="18"/>
+      <c r="C84" s="18"/>
+      <c r="D84" s="18"/>
+      <c r="E84" s="18"/>
+      <c r="F84" s="18"/>
+      <c r="G84" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B85" s="14"/>
-      <c r="C85" s="14"/>
-      <c r="D85" s="14" t="s">
+      <c r="B86" s="14"/>
+      <c r="C86" s="14"/>
+      <c r="D86" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E85" s="14"/>
-      <c r="F85" s="14"/>
-      <c r="G85" s="16" t="s">
+      <c r="E86" s="14"/>
+      <c r="F86" s="14"/>
+      <c r="G86" s="16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="14" t="str">
-        <f>data!$B$9</f>
-      </c>
-      <c r="B86" s="18" t="str">
-        <f>SUMPRODUCT((UPPER(D87:D91)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87:B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87:C91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87:E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87:F91," ",""),"0",""),"-",""))))*1)</f>
-      </c>
-      <c r="C86" s="18" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87:B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87:C91," ",""),"0",""),"-","")))</f>
-      </c>
-      <c r="D86" s="18"/>
-      <c r="E86" s="18" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87:E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87:F91," ",""),"0",""),"-","")))</f>
-      </c>
-      <c r="F86" s="18" t="str">
-        <f>SUMPRODUCT((UPPER(D87:D91)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87:E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87:F91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87:B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87:C91," ",""),"0",""),"-",""))))*1)</f>
-      </c>
-      <c r="G86" s="14" t="str">
-        <f>data!$B$8</f>
-      </c>
-    </row>
     <row r="87">
-      <c r="A87" s="18">
+      <c r="A87" s="14" t="str">
+        <f>'data'!$B$9</f>
+      </c>
+      <c r="B87" s="14" t="str">
+        <f>SUMPRODUCT((UPPER(D88:D92)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88:B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88:C92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88:E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88:F92," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C87" s="14" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88:B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88:C92," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="D87" s="18"/>
+      <c r="E87" s="14" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88:E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88:F92," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F87" s="14" t="str">
+        <f>SUMPRODUCT((UPPER(D88:D92)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88:E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88:F92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88:B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88:C92," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="G87" s="14" t="str">
+        <f>'data'!$B$8</f>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="14">
         <v>1</v>
-      </c>
-      <c r="B87" s="18"/>
-      <c r="C87" s="18"/>
-      <c r="D87" s="18"/>
-      <c r="E87" s="18"/>
-      <c r="F87" s="18"/>
-      <c r="G87" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="18">
-        <v>2</v>
       </c>
       <c r="B88" s="18"/>
       <c r="C88" s="18"/>
       <c r="D88" s="18"/>
       <c r="E88" s="18"/>
       <c r="F88" s="18"/>
-      <c r="G88" s="18">
+      <c r="G88" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="14">
         <v>2</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="18">
-        <v>3</v>
       </c>
       <c r="B89" s="18"/>
       <c r="C89" s="18"/>
       <c r="D89" s="18"/>
       <c r="E89" s="18"/>
       <c r="F89" s="18"/>
-      <c r="G89" s="18">
+      <c r="G89" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="14">
         <v>3</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="18">
-        <v>4</v>
       </c>
       <c r="B90" s="18"/>
       <c r="C90" s="18"/>
       <c r="D90" s="18"/>
       <c r="E90" s="18"/>
       <c r="F90" s="18"/>
-      <c r="G90" s="18">
+      <c r="G90" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="14">
         <v>4</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="18">
-        <v>5</v>
       </c>
       <c r="B91" s="18"/>
       <c r="C91" s="18"/>
       <c r="D91" s="18"/>
       <c r="E91" s="18"/>
       <c r="F91" s="18"/>
-      <c r="G91" s="18">
+      <c r="G91" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="14">
         <v>5</v>
       </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="13"/>
-      <c r="B94" s="13" t="s">
+      <c r="B92" s="18"/>
+      <c r="C92" s="18"/>
+      <c r="D92" s="18"/>
+      <c r="E92" s="18"/>
+      <c r="F92" s="18"/>
+      <c r="G92" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C94" s="13" t="s">
+      <c r="B95" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D94" s="13" t="s">
+      <c r="C95" s="13" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <f>data!$B$7</f>
-      </c>
-      <c r="B95" s="14" t="str">
-        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),IF(OR(D70="X",D70="x"),0,IF(OR(F70&gt;B70,AND(F70=B70,E70&gt;C70)),1,0)),0)+IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),IF(OR(D78="X",D78="x"),0,IF(OR(F78&gt;B78,AND(F78=B78,E78&gt;C78)),1,0)),0)</f>
-      </c>
-      <c r="C95" s="14" t="str">
-        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),IF(OR(D70="X",D70="x"),0,IF(OR(F70&lt;B70,AND(F70=B70,E70&lt;C70)),1,0)),0)+IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),IF(OR(D78="X",D78="x"),0,IF(OR(F78&lt;B78,AND(F78=B78,E78&lt;C78)),1,0)),0)</f>
-      </c>
-      <c r="D95" s="14" t="str">
-        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),IF(OR(D70="X",D70="x"),1,0),0)+IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),IF(OR(D78="X",D78="x"),1,0),0)</f>
+      <c r="D95" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E95" s="13"/>
+      <c r="F95" s="13"/>
+      <c r="G95" s="13" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="str">
-        <f>data!$B$8</f>
+      <c r="A96" s="14" t="str">
+        <f>'data'!$B$7</f>
       </c>
       <c r="B96" s="14" t="str">
-        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),IF(OR(D70="X",D70="x"),0,IF(OR(B70&gt;F70,AND(B70=F70,C70&gt;E70)),1,0)),0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),IF(OR(D86="X",D86="x"),0,IF(OR(F86&gt;B86,AND(F86=B86,E86&gt;C86)),1,0)),0)</f>
+        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,D72="X",D72="x",D73="X",D73="x",D74="X",D74="x",D75="X",D75="x",D76="X",D76="x",OR(D71="X",D71="x")),IF(OR(OR(D71="X",D71="x"),AND(B71=F71,C71=E71)),0,IF(OR(F71&gt;B71,AND(F71=B71,E71&gt;C71)),1,0)),0)+IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,D80="X",D80="x",D81="X",D81="x",D82="X",D82="x",D83="X",D83="x",D84="X",D84="x",OR(D79="X",D79="x")),IF(OR(OR(D79="X",D79="x"),AND(B79=F79,C79=E79)),0,IF(OR(F79&gt;B79,AND(F79=B79,E79&gt;C79)),1,0)),0)</f>
       </c>
       <c r="C96" s="14" t="str">
-        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),IF(OR(D70="X",D70="x"),0,IF(OR(B70&lt;F70,AND(B70=F70,C70&lt;E70)),1,0)),0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),IF(OR(D86="X",D86="x"),0,IF(OR(F86&lt;B86,AND(F86=B86,E86&lt;C86)),1,0)),0)</f>
+        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,D72="X",D72="x",D73="X",D73="x",D74="X",D74="x",D75="X",D75="x",D76="X",D76="x",OR(D71="X",D71="x")),IF(OR(OR(D71="X",D71="x"),AND(B71=F71,C71=E71)),0,IF(OR(F71&lt;B71,AND(F71=B71,E71&lt;C71)),1,0)),0)+IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,D80="X",D80="x",D81="X",D81="x",D82="X",D82="x",D83="X",D83="x",D84="X",D84="x",OR(D79="X",D79="x")),IF(OR(OR(D79="X",D79="x"),AND(B79=F79,C79=E79)),0,IF(OR(F79&lt;B79,AND(F79=B79,E79&lt;C79)),1,0)),0)</f>
       </c>
       <c r="D96" s="14" t="str">
-        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),IF(OR(D70="X",D70="x"),1,0),0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),IF(OR(D86="X",D86="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,D72="X",D72="x",D73="X",D73="x",D74="X",D74="x",D75="X",D75="x",D76="X",D76="x",OR(D71="X",D71="x")),IF(OR(OR(D71="X",D71="x"),AND(B71=F71,C71=E71)),1,0),0)+IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,D80="X",D80="x",D81="X",D81="x",D82="X",D82="x",D83="X",D83="x",D84="X",D84="x",OR(D79="X",D79="x")),IF(OR(OR(D79="X",D79="x"),AND(B79=F79,C79=E79)),1,0),0)</f>
+      </c>
+      <c r="G96" s="18" t="str">
+        <f>RANK(U96,$U$96:$U$98)+COUNTIF($U$95:U95,U96)</f>
+      </c>
+      <c r="U96" t="str">
+        <f>=(B96*1000000000)-(C96*10000000)+(D96*100000)+(B101*1000)-(C101*100)+(D101*10)+(E101*1)-(F101*0.01)</f>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="str">
-        <f>data!$B$9</f>
+      <c r="A97" s="14" t="str">
+        <f>'data'!$B$8</f>
       </c>
       <c r="B97" s="14" t="str">
-        <f>IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),IF(OR(D78="X",D78="x"),0,IF(OR(B78&gt;F78,AND(B78=F78,C78&gt;E78)),1,0)),0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),IF(OR(D86="X",D86="x"),0,IF(OR(B86&gt;F86,AND(B86=F86,C86&gt;E86)),1,0)),0)</f>
+        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,D72="X",D72="x",D73="X",D73="x",D74="X",D74="x",D75="X",D75="x",D76="X",D76="x",OR(D71="X",D71="x")),IF(OR(OR(D71="X",D71="x"),AND(B71=F71,C71=E71)),0,IF(OR(B71&gt;F71,AND(B71=F71,C71&gt;E71)),1,0)),0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,D88="X",D88="x",D89="X",D89="x",D90="X",D90="x",D91="X",D91="x",D92="X",D92="x",OR(D87="X",D87="x")),IF(OR(OR(D87="X",D87="x"),AND(B87=F87,C87=E87)),0,IF(OR(F87&gt;B87,AND(F87=B87,E87&gt;C87)),1,0)),0)</f>
       </c>
       <c r="C97" s="14" t="str">
-        <f>IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),IF(OR(D78="X",D78="x"),0,IF(OR(B78&lt;F78,AND(B78=F78,C78&lt;E78)),1,0)),0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),IF(OR(D86="X",D86="x"),0,IF(OR(B86&lt;F86,AND(B86=F86,C86&lt;E86)),1,0)),0)</f>
+        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,D72="X",D72="x",D73="X",D73="x",D74="X",D74="x",D75="X",D75="x",D76="X",D76="x",OR(D71="X",D71="x")),IF(OR(OR(D71="X",D71="x"),AND(B71=F71,C71=E71)),0,IF(OR(B71&lt;F71,AND(B71=F71,C71&lt;E71)),1,0)),0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,D88="X",D88="x",D89="X",D89="x",D90="X",D90="x",D91="X",D91="x",D92="X",D92="x",OR(D87="X",D87="x")),IF(OR(OR(D87="X",D87="x"),AND(B87=F87,C87=E87)),0,IF(OR(F87&lt;B87,AND(F87=B87,E87&lt;C87)),1,0)),0)</f>
       </c>
       <c r="D97" s="14" t="str">
-        <f>IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),IF(OR(D78="X",D78="x"),1,0),0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),IF(OR(D86="X",D86="x"),1,0),0)</f>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="13"/>
-      <c r="B99" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C99" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D99" s="13" t="s">
+        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,D72="X",D72="x",D73="X",D73="x",D74="X",D74="x",D75="X",D75="x",D76="X",D76="x",OR(D71="X",D71="x")),IF(OR(OR(D71="X",D71="x"),AND(B71=F71,C71=E71)),1,0),0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,D88="X",D88="x",D89="X",D89="x",D90="X",D90="x",D91="X",D91="x",D92="X",D92="x",OR(D87="X",D87="x")),IF(OR(OR(D87="X",D87="x"),AND(B87=F87,C87=E87)),1,0),0)</f>
+      </c>
+      <c r="G97" s="18" t="str">
+        <f>RANK(U97,$U$96:$U$98)+COUNTIF($U$95:U96,U97)</f>
+      </c>
+      <c r="U97" t="str">
+        <f>=(B97*1000000000)-(C97*10000000)+(D97*100000)+(B102*1000)-(C102*100)+(D102*10)+(E102*1)-(F102*0.01)</f>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="14" t="str">
+        <f>'data'!$B$9</f>
+      </c>
+      <c r="B98" s="14" t="str">
+        <f>IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,D80="X",D80="x",D81="X",D81="x",D82="X",D82="x",D83="X",D83="x",D84="X",D84="x",OR(D79="X",D79="x")),IF(OR(OR(D79="X",D79="x"),AND(B79=F79,C79=E79)),0,IF(OR(B79&gt;F79,AND(B79=F79,C79&gt;E79)),1,0)),0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,D88="X",D88="x",D89="X",D89="x",D90="X",D90="x",D91="X",D91="x",D92="X",D92="x",OR(D87="X",D87="x")),IF(OR(OR(D87="X",D87="x"),AND(B87=F87,C87=E87)),0,IF(OR(B87&gt;F87,AND(B87=F87,C87&gt;E87)),1,0)),0)</f>
+      </c>
+      <c r="C98" s="14" t="str">
+        <f>IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,D80="X",D80="x",D81="X",D81="x",D82="X",D82="x",D83="X",D83="x",D84="X",D84="x",OR(D79="X",D79="x")),IF(OR(OR(D79="X",D79="x"),AND(B79=F79,C79=E79)),0,IF(OR(B79&lt;F79,AND(B79=F79,C79&lt;E79)),1,0)),0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,D88="X",D88="x",D89="X",D89="x",D90="X",D90="x",D91="X",D91="x",D92="X",D92="x",OR(D87="X",D87="x")),IF(OR(OR(D87="X",D87="x"),AND(B87=F87,C87=E87)),0,IF(OR(B87&lt;F87,AND(B87=F87,C87&lt;E87)),1,0)),0)</f>
+      </c>
+      <c r="D98" s="14" t="str">
+        <f>IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,D80="X",D80="x",D81="X",D81="x",D82="X",D82="x",D83="X",D83="x",D84="X",D84="x",OR(D79="X",D79="x")),IF(OR(OR(D79="X",D79="x"),AND(B79=F79,C79=E79)),1,0),0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,D88="X",D88="x",D89="X",D89="x",D90="X",D90="x",D91="X",D91="x",D92="X",D92="x",OR(D87="X",D87="x")),IF(OR(OR(D87="X",D87="x"),AND(B87=F87,C87=E87)),1,0),0)</f>
+      </c>
+      <c r="G98" s="18" t="str">
+        <f>RANK(U98,$U$96:$U$98)+COUNTIF($U$95:U97,U98)</f>
+      </c>
+      <c r="U98" t="str">
+        <f>=(B98*1000000000)-(C98*10000000)+(D98*100000)+(B103*1000)-(C103*100)+(D103*10)+(E103*1)-(F103*0.01)</f>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="13"/>
+      <c r="B100" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E99" s="13" t="s">
+      <c r="C100" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F99" s="13" t="s">
+      <c r="D100" s="13" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <f>data!$B$7</f>
-      </c>
-      <c r="B100" s="14" t="str">
-        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),F70,0)+IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),F78,0)</f>
-      </c>
-      <c r="C100" s="14" t="str">
-        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),B70,0)+IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),B78,0)</f>
-      </c>
-      <c r="D100" s="14" t="str">
-        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),(IF(OR(D71="X",D71="x"),1,0)+IF(OR(D72="X",D72="x"),1,0)+IF(OR(D73="X",D73="x"),1,0)+IF(OR(D74="X",D74="x"),1,0)+IF(OR(D75="X",D75="x"),1,0)),0)+IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),(IF(OR(D79="X",D79="x"),1,0)+IF(OR(D80="X",D80="x"),1,0)+IF(OR(D81="X",D81="x"),1,0)+IF(OR(D82="X",D82="x"),1,0)+IF(OR(D83="X",D83="x"),1,0)),0)</f>
-      </c>
-      <c r="E100" s="14" t="str">
-        <f>E70+E78</f>
-      </c>
-      <c r="F100" s="14" t="str">
-        <f>C70+C78</f>
+      <c r="E100" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F100" s="13" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="str">
-        <f>data!$B$8</f>
+      <c r="A101" s="14" t="str">
+        <f>'data'!$B$7</f>
       </c>
       <c r="B101" s="14" t="str">
-        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),B70,0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),F86,0)</f>
+        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,OR(D71="X",D71="x"),UPPER(D72)="X",UPPER(D73)="X",UPPER(D74)="X",UPPER(D75)="X",UPPER(D76)="X"),F71,0)+IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,OR(D79="X",D79="x"),UPPER(D80)="X",UPPER(D81)="X",UPPER(D82)="X",UPPER(D83)="X",UPPER(D84)="X"),F79,0)</f>
       </c>
       <c r="C101" s="14" t="str">
-        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),F70,0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),B86,0)</f>
+        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,OR(D71="X",D71="x"),UPPER(D72)="X",UPPER(D73)="X",UPPER(D74)="X",UPPER(D75)="X",UPPER(D76)="X"),B71,0)+IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,OR(D79="X",D79="x"),UPPER(D80)="X",UPPER(D81)="X",UPPER(D82)="X",UPPER(D83)="X",UPPER(D84)="X"),B79,0)</f>
       </c>
       <c r="D101" s="14" t="str">
-        <f>IF(OR(COUNTA(B71:C75,E71:F75)&gt;0,OR(D70="X",D70="x")),(IF(OR(D71="X",D71="x"),1,0)+IF(OR(D72="X",D72="x"),1,0)+IF(OR(D73="X",D73="x"),1,0)+IF(OR(D74="X",D74="x"),1,0)+IF(OR(D75="X",D75="x"),1,0)),0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),(IF(OR(D87="X",D87="x"),1,0)+IF(OR(D88="X",D88="x"),1,0)+IF(OR(D89="X",D89="x"),1,0)+IF(OR(D90="X",D90="x"),1,0)+IF(OR(D91="X",D91="x"),1,0)),0)</f>
+        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,OR(D71="X",D71="x"),UPPER(D72)="X",UPPER(D73)="X",UPPER(D74)="X",UPPER(D75)="X",UPPER(D76)="X"),(IF(OR(D72="X",D72="x",AND(COUNTA(B72,C72,E72,F72)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-",""))))),1,0)+IF(OR(D73="X",D73="x",AND(COUNTA(B73,C73,E73,F73)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-",""))))),1,0)+IF(OR(D74="X",D74="x",AND(COUNTA(B74,C74,E74,F74)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-",""))))),1,0)+IF(OR(D75="X",D75="x",AND(COUNTA(B75,C75,E75,F75)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-",""))))),1,0)+IF(OR(D76="X",D76="x",AND(COUNTA(B76,C76,E76,F76)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-",""))))),1,0)),0)+IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,OR(D79="X",D79="x"),UPPER(D80)="X",UPPER(D81)="X",UPPER(D82)="X",UPPER(D83)="X",UPPER(D84)="X"),(IF(OR(D80="X",D80="x",AND(COUNTA(B80,C80,E80,F80)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-",""))))),1,0)+IF(OR(D81="X",D81="x",AND(COUNTA(B81,C81,E81,F81)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-",""))))),1,0)+IF(OR(D82="X",D82="x",AND(COUNTA(B82,C82,E82,F82)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C82," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F82," ",""),"0",""),"-",""))))),1,0)+IF(OR(D83="X",D83="x",AND(COUNTA(B83,C83,E83,F83)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C83," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F83," ",""),"0",""),"-",""))))),1,0)+IF(OR(D84="X",D84="x",AND(COUNTA(B84,C84,E84,F84)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C84," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F84," ",""),"0",""),"-",""))))),1,0)),0)</f>
       </c>
       <c r="E101" s="14" t="str">
-        <f>C70+E86</f>
+        <f>E71+E79</f>
       </c>
       <c r="F101" s="14" t="str">
-        <f>E70+C86</f>
+        <f>C71+C79</f>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="str">
-        <f>data!$B$9</f>
+      <c r="A102" s="14" t="str">
+        <f>'data'!$B$8</f>
       </c>
       <c r="B102" s="14" t="str">
-        <f>IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),B78,0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),B86,0)</f>
+        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,OR(D71="X",D71="x"),UPPER(D72)="X",UPPER(D73)="X",UPPER(D74)="X",UPPER(D75)="X",UPPER(D76)="X"),B71,0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,OR(D87="X",D87="x"),UPPER(D88)="X",UPPER(D89)="X",UPPER(D90)="X",UPPER(D91)="X",UPPER(D92)="X"),F87,0)</f>
       </c>
       <c r="C102" s="14" t="str">
-        <f>IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),F78,0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),F86,0)</f>
+        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,OR(D71="X",D71="x"),UPPER(D72)="X",UPPER(D73)="X",UPPER(D74)="X",UPPER(D75)="X",UPPER(D76)="X"),F71,0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,OR(D87="X",D87="x"),UPPER(D88)="X",UPPER(D89)="X",UPPER(D90)="X",UPPER(D91)="X",UPPER(D92)="X"),B87,0)</f>
       </c>
       <c r="D102" s="14" t="str">
-        <f>IF(OR(COUNTA(B79:C83,E79:F83)&gt;0,OR(D78="X",D78="x")),(IF(OR(D79="X",D79="x"),1,0)+IF(OR(D80="X",D80="x"),1,0)+IF(OR(D81="X",D81="x"),1,0)+IF(OR(D82="X",D82="x"),1,0)+IF(OR(D83="X",D83="x"),1,0)),0)+IF(OR(COUNTA(B87:C91,E87:F91)&gt;0,OR(D86="X",D86="x")),(IF(OR(D87="X",D87="x"),1,0)+IF(OR(D88="X",D88="x"),1,0)+IF(OR(D89="X",D89="x"),1,0)+IF(OR(D90="X",D90="x"),1,0)+IF(OR(D91="X",D91="x"),1,0)),0)</f>
+        <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,OR(D71="X",D71="x"),UPPER(D72)="X",UPPER(D73)="X",UPPER(D74)="X",UPPER(D75)="X",UPPER(D76)="X"),(IF(OR(D72="X",D72="x",AND(COUNTA(B72,C72,E72,F72)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-",""))))),1,0)+IF(OR(D73="X",D73="x",AND(COUNTA(B73,C73,E73,F73)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-",""))))),1,0)+IF(OR(D74="X",D74="x",AND(COUNTA(B74,C74,E74,F74)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-",""))))),1,0)+IF(OR(D75="X",D75="x",AND(COUNTA(B75,C75,E75,F75)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-",""))))),1,0)+IF(OR(D76="X",D76="x",AND(COUNTA(B76,C76,E76,F76)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-",""))))),1,0)),0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,OR(D87="X",D87="x"),UPPER(D88)="X",UPPER(D89)="X",UPPER(D90)="X",UPPER(D91)="X",UPPER(D92)="X"),(IF(OR(D88="X",D88="x",AND(COUNTA(B88,C88,E88,F88)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-",""))))),1,0)+IF(OR(D89="X",D89="x",AND(COUNTA(B89,C89,E89,F89)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-",""))))),1,0)+IF(OR(D90="X",D90="x",AND(COUNTA(B90,C90,E90,F90)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-",""))))),1,0)+IF(OR(D91="X",D91="x",AND(COUNTA(B91,C91,E91,F91)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))))),1,0)+IF(OR(D92="X",D92="x",AND(COUNTA(B92,C92,E92,F92)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))))),1,0)),0)</f>
       </c>
       <c r="E102" s="14" t="str">
-        <f>C78+C86</f>
+        <f>C71+E87</f>
       </c>
       <c r="F102" s="14" t="str">
-        <f>E78+E86</f>
-      </c>
-    </row>
-    <row r="105">
-      <c r="F105" s="13"/>
-      <c r="G105" s="13" t="s">
-        <v>46</v>
+        <f>E71+C87</f>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="14" t="str">
+        <f>'data'!$B$9</f>
+      </c>
+      <c r="B103" s="14" t="str">
+        <f>IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,OR(D79="X",D79="x"),UPPER(D80)="X",UPPER(D81)="X",UPPER(D82)="X",UPPER(D83)="X",UPPER(D84)="X"),B79,0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,OR(D87="X",D87="x"),UPPER(D88)="X",UPPER(D89)="X",UPPER(D90)="X",UPPER(D91)="X",UPPER(D92)="X"),B87,0)</f>
+      </c>
+      <c r="C103" s="14" t="str">
+        <f>IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,OR(D79="X",D79="x"),UPPER(D80)="X",UPPER(D81)="X",UPPER(D82)="X",UPPER(D83)="X",UPPER(D84)="X"),F79,0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,OR(D87="X",D87="x"),UPPER(D88)="X",UPPER(D89)="X",UPPER(D90)="X",UPPER(D91)="X",UPPER(D92)="X"),F87,0)</f>
+      </c>
+      <c r="D103" s="14" t="str">
+        <f>IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,OR(D79="X",D79="x"),UPPER(D80)="X",UPPER(D81)="X",UPPER(D82)="X",UPPER(D83)="X",UPPER(D84)="X"),(IF(OR(D80="X",D80="x",AND(COUNTA(B80,C80,E80,F80)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-",""))))),1,0)+IF(OR(D81="X",D81="x",AND(COUNTA(B81,C81,E81,F81)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-",""))))),1,0)+IF(OR(D82="X",D82="x",AND(COUNTA(B82,C82,E82,F82)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C82," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F82," ",""),"0",""),"-",""))))),1,0)+IF(OR(D83="X",D83="x",AND(COUNTA(B83,C83,E83,F83)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C83," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F83," ",""),"0",""),"-",""))))),1,0)+IF(OR(D84="X",D84="x",AND(COUNTA(B84,C84,E84,F84)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C84," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F84," ",""),"0",""),"-",""))))),1,0)),0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,OR(D87="X",D87="x"),UPPER(D88)="X",UPPER(D89)="X",UPPER(D90)="X",UPPER(D91)="X",UPPER(D92)="X"),(IF(OR(D88="X",D88="x",AND(COUNTA(B88,C88,E88,F88)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-",""))))),1,0)+IF(OR(D89="X",D89="x",AND(COUNTA(B89,C89,E89,F89)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-",""))))),1,0)+IF(OR(D90="X",D90="x",AND(COUNTA(B90,C90,E90,F90)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-",""))))),1,0)+IF(OR(D91="X",D91="x",AND(COUNTA(B91,C91,E91,F91)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))))),1,0)+IF(OR(D92="X",D92="x",AND(COUNTA(B92,C92,E92,F92)&gt;0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))))),1,0)),0)</f>
+      </c>
+      <c r="E103" s="14" t="str">
+        <f>C79+C87</f>
+      </c>
+      <c r="F103" s="14" t="str">
+        <f>E79+E87</f>
       </c>
     </row>
     <row r="106">
-      <c r="F106" t="s">
-        <v>47</v>
-      </c>
-      <c r="G106" s="19"/>
+      <c r="F106" s="13"/>
+      <c r="G106" s="13" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="107">
       <c r="F107" t="s">
-        <v>48</v>
-      </c>
-      <c r="G107" s="19"/>
+        <v>49</v>
+      </c>
+      <c r="G107" s="19" t="str">
+        <f>IFERROR(INDEX($A$96:$A$103, MATCH(1, $G$96:$G$103, 0)), "-")</f>
+      </c>
     </row>
     <row r="108">
       <c r="F108" t="s">
-        <v>49</v>
-      </c>
-      <c r="G108" s="19"/>
+        <v>50</v>
+      </c>
+      <c r="G108" s="19" t="str">
+        <f>IFERROR(INDEX($A$96:$A$103, MATCH(2, $G$96:$G$103, 0)), "-")</f>
+      </c>
+    </row>
+    <row r="109">
+      <c r="F109" t="s">
+        <v>51</v>
+      </c>
+      <c r="G109" s="19" t="str">
+        <f>IFERROR(INDEX($A$96:$A$103, MATCH(3, $G$96:$G$103, 0)), "-")</f>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
@@ -3357,14 +3457,14 @@
     <mergeCell ref="I1:O1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="I2:O2"/>
-    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A69:G69"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageSetup fitToHeight="0" fitToWidth="2" orientation="portrait" pageOrder="downThenOver" paperSize="9"/>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="1" max="16383" man="true"/>
     <brk id="44" max="16383" man="true"/>
-    <brk id="67" max="16383" man="true"/>
+    <brk id="68" max="16383" man="true"/>
   </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="8" max="1048575" man="true"/>
@@ -3381,19 +3481,14 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="3" min="2" width="5"/>
-    <col customWidth="true" max="4" min="4" width="3"/>
-    <col customWidth="true" max="6" min="5" width="5"/>
+    <col customWidth="true" max="6" min="2" width="5"/>
     <col customWidth="true" max="7" min="7" width="30"/>
     <col customWidth="true" max="8" min="8" width="5"/>
     <col customWidth="true" max="9" min="9" width="30"/>
-    <col customWidth="true" max="11" min="10" width="5"/>
-    <col customWidth="true" max="12" min="12" width="3"/>
-    <col customWidth="true" max="14" min="13" width="5"/>
+    <col customWidth="true" max="14" min="10" width="5"/>
     <col customWidth="true" max="15" min="15" width="30"/>
-    <col customWidth="true" max="18" min="16" width="5"/>
-    <col customWidth="true" max="19" min="19" width="30"/>
-    <col customWidth="true" max="20" min="20" width="2"/>
+    <col customWidth="true" max="16" min="16" width="5"/>
+    <col customWidth="true" max="20" min="17" width="10.83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3418,7 +3513,7 @@
     </row>
     <row r="2">
       <c r="A2" s="13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -3426,15 +3521,15 @@
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
-      <c r="M2" s="13" t="s">
+      <c r="I2" s="13" t="s">
         <v>65</v>
       </c>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
       <c r="N2" s="13"/>
       <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13"/>
     </row>
     <row r="3">
       <c r="A3" s="17" t="s">
@@ -3446,38 +3541,38 @@
       <c r="G3" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="M3" s="17" t="s">
+      <c r="I3" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="P3" s="14" t="s">
+      <c r="L3" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="O3" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G107)</f>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G111)</f>
+      </c>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
       <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
       <c r="G4" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O64)</f>
-      </c>
-      <c r="M4" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O65)</f>
-      </c>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18"/>
-      <c r="P4" s="18"/>
-      <c r="Q4" s="18"/>
-      <c r="R4" s="18"/>
-      <c r="S4" s="14" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G67)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O67)</f>
+      </c>
+      <c r="I4" s="14" t="str">
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O68)</f>
+      </c>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14" t="str">
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G71)</f>
       </c>
     </row>
     <row r="5">
@@ -3492,15 +3587,15 @@
       <c r="G5" s="14">
         <v>1</v>
       </c>
-      <c r="M5" s="14">
+      <c r="I5" s="14">
         <v>1</v>
       </c>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
       <c r="N5" s="18"/>
-      <c r="O5" s="18"/>
-      <c r="P5" s="18"/>
-      <c r="Q5" s="18"/>
-      <c r="R5" s="18"/>
-      <c r="S5" s="14">
+      <c r="O5" s="14">
         <v>1</v>
       </c>
     </row>
@@ -3516,15 +3611,15 @@
       <c r="G6" s="14">
         <v>2</v>
       </c>
-      <c r="M6" s="14">
+      <c r="I6" s="14">
         <v>2</v>
       </c>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
       <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="18"/>
-      <c r="S6" s="14">
+      <c r="O6" s="14">
         <v>2</v>
       </c>
     </row>
@@ -3540,15 +3635,15 @@
       <c r="G7" s="14">
         <v>3</v>
       </c>
-      <c r="M7" s="14">
+      <c r="I7" s="14">
         <v>3</v>
       </c>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="18"/>
       <c r="N7" s="18"/>
-      <c r="O7" s="18"/>
-      <c r="P7" s="18"/>
-      <c r="Q7" s="18"/>
-      <c r="R7" s="18"/>
-      <c r="S7" s="14">
+      <c r="O7" s="14">
         <v>3</v>
       </c>
     </row>
@@ -3564,15 +3659,15 @@
       <c r="G8" s="14">
         <v>4</v>
       </c>
-      <c r="M8" s="14">
+      <c r="I8" s="14">
         <v>4</v>
       </c>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
       <c r="N8" s="18"/>
-      <c r="O8" s="18"/>
-      <c r="P8" s="18"/>
-      <c r="Q8" s="18"/>
-      <c r="R8" s="18"/>
-      <c r="S8" s="14">
+      <c r="O8" s="14">
         <v>4</v>
       </c>
     </row>
@@ -3588,101 +3683,117 @@
       <c r="G9" s="14">
         <v>5</v>
       </c>
-      <c r="M9" s="14">
+      <c r="I9" s="14">
         <v>5</v>
       </c>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
       <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="18"/>
-      <c r="R9" s="18"/>
-      <c r="S9" s="14">
+      <c r="O9" s="14">
         <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G107)</f>
-      </c>
-      <c r="B11" s="18" t="str">
-        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-",""))))*1)</f>
-      </c>
-      <c r="C11" s="18" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G111)</f>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>46</v>
       </c>
       <c r="D11" s="14"/>
-      <c r="E11" s="18" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))</f>
-      </c>
-      <c r="F11" s="18" t="str">
-        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-",""))))*1)</f>
+      <c r="E11" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>43</v>
       </c>
       <c r="G11" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O64)</f>
-      </c>
-      <c r="M11" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O65)</f>
-      </c>
-      <c r="N11" s="18" t="str">
-        <f>SUMPRODUCT((UPPER(P5:P9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(O5:O9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Q5:Q9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(R5:R9," ",""),"0",""),"-",""))))*1)</f>
-      </c>
-      <c r="O11" s="18" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(O5:O9," ",""),"0",""),"-","")))</f>
-      </c>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="18" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Q5:Q9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(R5:R9," ",""),"0",""),"-","")))</f>
-      </c>
-      <c r="R11" s="18" t="str">
-        <f>SUMPRODUCT((UPPER(P5:P9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Q5:Q9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(R5:R9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(O5:O9," ",""),"0",""),"-",""))))*1)</f>
-      </c>
-      <c r="S11" s="14" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G67)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O67)</f>
+      </c>
+      <c r="I11" s="14" t="str">
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O68)</f>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="N11" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="O11" s="14" t="str">
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G71)</f>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
+        <v>64</v>
+      </c>
+      <c r="B12" s="14" t="str">
+        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C12" s="14" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))</f>
+      </c>
       <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
+      <c r="E12" s="14" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F12" s="14" t="str">
+        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-",""))))*1)</f>
+      </c>
       <c r="G12" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="M12" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="14"/>
-      <c r="S12" s="14" t="s">
-        <v>62</v>
+        <v>64</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="J12" s="14" t="str">
+        <f>SUMPRODUCT((UPPER(L5:L9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="K12" s="14" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="N12" s="14" t="str">
+        <f>SUMPRODUCT((UPPER(L5:L9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="O12" s="14" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="15">
       <c r="F15" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="G15" s="19"/>
-      <c r="R15" t="s">
-        <v>63</v>
-      </c>
-      <c r="S15" s="19"/>
+      <c r="N15" t="s">
+        <v>49</v>
+      </c>
+      <c r="O15" s="19"/>
     </row>
     <row r="16">
       <c r="F16" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G16" s="19"/>
-      <c r="R16" t="s">
-        <v>64</v>
-      </c>
-      <c r="S16" s="19"/>
+      <c r="N16" t="s">
+        <v>50</v>
+      </c>
+      <c r="O16" s="19"/>
     </row>
     <row r="23">
       <c r="A23" s="13" t="s">
@@ -3694,15 +3805,15 @@
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
       <c r="G23" s="13"/>
-      <c r="M23" s="13" t="s">
+      <c r="I23" s="13" t="s">
         <v>67</v>
       </c>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
       <c r="N23" s="13"/>
       <c r="O23" s="13"/>
-      <c r="P23" s="13"/>
-      <c r="Q23" s="13"/>
-      <c r="R23" s="13"/>
-      <c r="S23" s="13"/>
     </row>
     <row r="24">
       <c r="A24" s="17" t="s">
@@ -3714,13 +3825,13 @@
       <c r="G24" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="M24" s="17" t="s">
+      <c r="I24" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="P24" s="14" t="s">
+      <c r="L24" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="S24" s="16" t="s">
+      <c r="O24" s="16" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3728,24 +3839,24 @@
       <c r="A25" s="14" t="str">
         <f>CONCATENATE("M 1 ",G15)</f>
       </c>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
       <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
       <c r="G25" s="14" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G66)</f>
-      </c>
-      <c r="M25" s="14" t="str">
-        <f>CONCATENATE("M 2 ",S15)</f>
-      </c>
-      <c r="N25" s="18"/>
-      <c r="O25" s="18"/>
-      <c r="P25" s="18"/>
-      <c r="Q25" s="18"/>
-      <c r="R25" s="18"/>
-      <c r="S25" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G106)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G70)</f>
+      </c>
+      <c r="I25" s="14" t="str">
+        <f>CONCATENATE("M 2 ",O15)</f>
+      </c>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="14"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="14" t="str">
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G110)</f>
       </c>
     </row>
     <row r="26">
@@ -3760,15 +3871,15 @@
       <c r="G26" s="14">
         <v>1</v>
       </c>
-      <c r="M26" s="14">
+      <c r="I26" s="14">
         <v>1</v>
       </c>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
       <c r="N26" s="18"/>
-      <c r="O26" s="18"/>
-      <c r="P26" s="18"/>
-      <c r="Q26" s="18"/>
-      <c r="R26" s="18"/>
-      <c r="S26" s="14">
+      <c r="O26" s="14">
         <v>1</v>
       </c>
     </row>
@@ -3784,15 +3895,15 @@
       <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="M27" s="14">
+      <c r="I27" s="14">
         <v>2</v>
       </c>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18"/>
       <c r="N27" s="18"/>
-      <c r="O27" s="18"/>
-      <c r="P27" s="18"/>
-      <c r="Q27" s="18"/>
-      <c r="R27" s="18"/>
-      <c r="S27" s="14">
+      <c r="O27" s="14">
         <v>2</v>
       </c>
     </row>
@@ -3808,15 +3919,15 @@
       <c r="G28" s="14">
         <v>3</v>
       </c>
-      <c r="M28" s="14">
+      <c r="I28" s="14">
         <v>3</v>
       </c>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
       <c r="N28" s="18"/>
-      <c r="O28" s="18"/>
-      <c r="P28" s="18"/>
-      <c r="Q28" s="18"/>
-      <c r="R28" s="18"/>
-      <c r="S28" s="14">
+      <c r="O28" s="14">
         <v>3</v>
       </c>
     </row>
@@ -3832,15 +3943,15 @@
       <c r="G29" s="14">
         <v>4</v>
       </c>
-      <c r="M29" s="14">
+      <c r="I29" s="14">
         <v>4</v>
       </c>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
+      <c r="M29" s="18"/>
       <c r="N29" s="18"/>
-      <c r="O29" s="18"/>
-      <c r="P29" s="18"/>
-      <c r="Q29" s="18"/>
-      <c r="R29" s="18"/>
-      <c r="S29" s="14">
+      <c r="O29" s="14">
         <v>4</v>
       </c>
     </row>
@@ -3856,15 +3967,15 @@
       <c r="G30" s="14">
         <v>5</v>
       </c>
-      <c r="M30" s="14">
+      <c r="I30" s="14">
         <v>5</v>
       </c>
+      <c r="J30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
+      <c r="M30" s="18"/>
       <c r="N30" s="18"/>
-      <c r="O30" s="18"/>
-      <c r="P30" s="18"/>
-      <c r="Q30" s="18"/>
-      <c r="R30" s="18"/>
-      <c r="S30" s="14">
+      <c r="O30" s="14">
         <v>5</v>
       </c>
     </row>
@@ -3872,85 +3983,101 @@
       <c r="A32" s="14" t="str">
         <f>CONCATENATE("M 1 ",G15)</f>
       </c>
-      <c r="B32" s="18" t="str">
-        <f>SUMPRODUCT((UPPER(D26:D30)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26:B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C26:C30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E26:E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F26:F30," ",""),"0",""),"-",""))))*1)</f>
-      </c>
-      <c r="C32" s="18" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26:B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C26:C30," ",""),"0",""),"-","")))</f>
+      <c r="B32" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>46</v>
       </c>
       <c r="D32" s="14"/>
-      <c r="E32" s="18" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E26:E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F26:F30," ",""),"0",""),"-","")))</f>
-      </c>
-      <c r="F32" s="18" t="str">
-        <f>SUMPRODUCT((UPPER(D26:D30)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E26:E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F26:F30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26:B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C26:C30," ",""),"0",""),"-",""))))*1)</f>
+      <c r="E32" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>43</v>
       </c>
       <c r="G32" s="14" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G66)</f>
-      </c>
-      <c r="M32" s="14" t="str">
-        <f>CONCATENATE("M 2 ",S15)</f>
-      </c>
-      <c r="N32" s="18" t="str">
-        <f>SUMPRODUCT((UPPER(P26:P30)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N26:N30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(O26:O30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Q26:Q30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(R26:R30," ",""),"0",""),"-",""))))*1)</f>
-      </c>
-      <c r="O32" s="18" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N26:N30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(O26:O30," ",""),"0",""),"-","")))</f>
-      </c>
-      <c r="P32" s="14"/>
-      <c r="Q32" s="18" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Q26:Q30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(R26:R30," ",""),"0",""),"-","")))</f>
-      </c>
-      <c r="R32" s="18" t="str">
-        <f>SUMPRODUCT((UPPER(P26:P30)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(Q26:Q30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(R26:R30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N26:N30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(O26:O30," ",""),"0",""),"-",""))))*1)</f>
-      </c>
-      <c r="S32" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G106)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G70)</f>
+      </c>
+      <c r="I32" s="14" t="str">
+        <f>CONCATENATE("M 2 ",O15)</f>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="N32" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="O32" s="14" t="str">
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G110)</f>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
+        <v>64</v>
+      </c>
+      <c r="B33" s="14" t="str">
+        <f>SUMPRODUCT((UPPER(D26:D30)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26:B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C26:C30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E26:E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F26:F30," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C33" s="14" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26:B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C26:C30," ",""),"0",""),"-","")))</f>
+      </c>
       <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
+      <c r="E33" s="14" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E26:E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F26:F30," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F33" s="14" t="str">
+        <f>SUMPRODUCT((UPPER(D26:D30)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E26:E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F26:F30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26:B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C26:C30," ",""),"0",""),"-",""))))*1)</f>
+      </c>
       <c r="G33" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="M33" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="N33" s="14"/>
-      <c r="O33" s="14"/>
-      <c r="P33" s="14"/>
-      <c r="Q33" s="14"/>
-      <c r="R33" s="14"/>
-      <c r="S33" s="14" t="s">
-        <v>62</v>
+        <v>64</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="J33" s="14" t="str">
+        <f>SUMPRODUCT((UPPER(L26:L30)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J26:J30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K26:K30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M26:M30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N26:N30," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="K33" s="14" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J26:J30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K26:K30," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M26:M30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N26:N30," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="N33" s="14" t="str">
+        <f>SUMPRODUCT((UPPER(L26:L30)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M26:M30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N26:N30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J26:J30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K26:K30," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="O33" s="14" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="36">
       <c r="F36" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="G36" s="19"/>
-      <c r="R36" t="s">
-        <v>63</v>
-      </c>
-      <c r="S36" s="19"/>
+      <c r="N36" t="s">
+        <v>49</v>
+      </c>
+      <c r="O36" s="19"/>
     </row>
     <row r="37">
       <c r="F37" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G37" s="19"/>
-      <c r="R37" t="s">
-        <v>64</v>
-      </c>
-      <c r="S37" s="19"/>
+      <c r="N37" t="s">
+        <v>50</v>
+      </c>
+      <c r="O37" s="19"/>
     </row>
     <row r="44">
       <c r="A44" s="13" t="s">
@@ -3976,13 +4103,13 @@
     </row>
     <row r="46">
       <c r="A46" s="14" t="str">
-        <f>CONCATENATE("M 4 ",S36)</f>
-      </c>
-      <c r="B46" s="18"/>
-      <c r="C46" s="18"/>
+        <f>CONCATENATE("M 4 ",O36)</f>
+      </c>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
       <c r="D46" s="18"/>
-      <c r="E46" s="18"/>
-      <c r="F46" s="18"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
       <c r="G46" s="14" t="str">
         <f>CONCATENATE("M 3 ",G36)</f>
       </c>
@@ -4054,20 +4181,20 @@
     </row>
     <row r="53">
       <c r="A53" s="14" t="str">
-        <f>CONCATENATE("M 4 ",S36)</f>
-      </c>
-      <c r="B53" s="18" t="str">
-        <f>SUMPRODUCT((UPPER(D47:D51)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47:B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47:C51," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47:E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47:F51," ",""),"0",""),"-",""))))*1)</f>
-      </c>
-      <c r="C53" s="18" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47:B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47:C51," ",""),"0",""),"-","")))</f>
+        <f>CONCATENATE("M 4 ",O36)</f>
+      </c>
+      <c r="B53" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>46</v>
       </c>
       <c r="D53" s="14"/>
-      <c r="E53" s="18" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47:E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47:F51," ",""),"0",""),"-","")))</f>
-      </c>
-      <c r="F53" s="18" t="str">
-        <f>SUMPRODUCT((UPPER(D47:D51)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47:E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47:F51," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47:B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47:C51," ",""),"0",""),"-",""))))*1)</f>
+      <c r="E53" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F53" s="14" t="s">
+        <v>43</v>
       </c>
       <c r="G53" s="14" t="str">
         <f>CONCATENATE("M 3 ",G36)</f>
@@ -4075,26 +4202,34 @@
     </row>
     <row r="54">
       <c r="A54" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
+        <v>64</v>
+      </c>
+      <c r="B54" s="14" t="str">
+        <f>SUMPRODUCT((UPPER(D47:D51)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47:B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47:C51," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47:E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47:F51," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C54" s="14" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47:B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47:C51," ",""),"0",""),"-","")))</f>
+      </c>
       <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
+      <c r="E54" s="14" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47:E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47:F51," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F54" s="14" t="str">
+        <f>SUMPRODUCT((UPPER(D47:D51)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47:E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47:F51," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47:B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47:C51," ",""),"0",""),"-",""))))*1)</f>
+      </c>
       <c r="G54" s="14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="57">
       <c r="F57" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="G57" s="19"/>
     </row>
     <row r="58">
       <c r="F58" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G58" s="19"/>
     </row>
@@ -4104,9 +4239,9 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I1:O1"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="M2:S2"/>
+    <mergeCell ref="I2:O2"/>
     <mergeCell ref="A23:G23"/>
-    <mergeCell ref="M23:S23"/>
+    <mergeCell ref="I23:O23"/>
     <mergeCell ref="A44:G44"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
@@ -4151,7 +4286,7 @@
     </row>
     <row r="4">
       <c r="A4" s="24" t="str">
-        <f>data!$A$6</f>
+        <f>'data'!$A$6</f>
       </c>
     </row>
     <row r="5">
@@ -4164,7 +4299,7 @@
         <f>"2. " &amp; data!$B$4</f>
       </c>
       <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G66)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G70)</f>
       </c>
     </row>
     <row r="7">
@@ -4185,13 +4320,13 @@
     <row r="9">
       <c r="A9" s="22"/>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O64)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O67)</f>
       </c>
       <c r="G9" s="20"/>
     </row>
     <row r="10">
       <c r="A10" s="24" t="str">
-        <f>data!$A$9</f>
+        <f>'data'!$A$9</f>
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="21">
@@ -4205,7 +4340,7 @@
         <f>"1. " &amp; data!$B$7</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G107)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G111)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -4264,7 +4399,7 @@
     </row>
     <row r="4">
       <c r="A4" s="24" t="str">
-        <f>data!$A$12</f>
+        <f>'data'!$A$12</f>
       </c>
     </row>
     <row r="5">
@@ -4277,7 +4412,7 @@
         <f>"2. " &amp; data!$B$11</f>
       </c>
       <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G106)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G110)</f>
       </c>
     </row>
     <row r="7">
@@ -4295,7 +4430,7 @@
     </row>
     <row r="9">
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G67)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G71)</f>
       </c>
       <c r="G9" s="20"/>
     </row>
@@ -4309,7 +4444,7 @@
     </row>
     <row r="11">
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O65)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O68)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -3553,7 +3553,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G111)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G108)</f>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -3561,10 +3561,10 @@
       <c r="E4" s="14"/>
       <c r="F4" s="14"/>
       <c r="G4" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O67)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O64)</f>
       </c>
       <c r="I4" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O68)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O65)</f>
       </c>
       <c r="J4" s="14"/>
       <c r="K4" s="14"/>
@@ -3572,7 +3572,7 @@
       <c r="M4" s="14"/>
       <c r="N4" s="14"/>
       <c r="O4" s="14" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G71)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G67)</f>
       </c>
     </row>
     <row r="5">
@@ -3697,7 +3697,7 @@
     </row>
     <row r="11">
       <c r="A11" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G111)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G108)</f>
       </c>
       <c r="B11" s="14" t="s">
         <v>43</v>
@@ -3713,10 +3713,10 @@
         <v>43</v>
       </c>
       <c r="G11" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O67)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O64)</f>
       </c>
       <c r="I11" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O68)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O65)</f>
       </c>
       <c r="J11" s="14" t="s">
         <v>43</v>
@@ -3732,7 +3732,7 @@
         <v>43</v>
       </c>
       <c r="O11" s="14" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G71)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G67)</f>
       </c>
     </row>
     <row r="12">
@@ -3845,7 +3845,7 @@
       <c r="E25" s="14"/>
       <c r="F25" s="14"/>
       <c r="G25" s="14" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G70)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G66)</f>
       </c>
       <c r="I25" s="14" t="str">
         <f>CONCATENATE("M 2 ",O15)</f>
@@ -3856,7 +3856,7 @@
       <c r="M25" s="14"/>
       <c r="N25" s="14"/>
       <c r="O25" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G110)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G107)</f>
       </c>
     </row>
     <row r="26">
@@ -3997,7 +3997,7 @@
         <v>43</v>
       </c>
       <c r="G32" s="14" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G70)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G66)</f>
       </c>
       <c r="I32" s="14" t="str">
         <f>CONCATENATE("M 2 ",O15)</f>
@@ -4016,7 +4016,7 @@
         <v>43</v>
       </c>
       <c r="O32" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G110)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G107)</f>
       </c>
     </row>
     <row r="33">
@@ -4299,7 +4299,7 @@
         <f>"2. " &amp; data!$B$4</f>
       </c>
       <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G70)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G66)</f>
       </c>
     </row>
     <row r="7">
@@ -4320,7 +4320,7 @@
     <row r="9">
       <c r="A9" s="22"/>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O67)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O64)</f>
       </c>
       <c r="G9" s="20"/>
     </row>
@@ -4340,7 +4340,7 @@
         <f>"1. " &amp; data!$B$7</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G111)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G108)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -4412,7 +4412,7 @@
         <f>"2. " &amp; data!$B$11</f>
       </c>
       <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G110)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G107)</f>
       </c>
     </row>
     <row r="7">
@@ -4430,7 +4430,7 @@
     </row>
     <row r="9">
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G71)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G67)</f>
       </c>
       <c r="G9" s="20"/>
     </row>
@@ -4444,7 +4444,7 @@
     </row>
     <row r="11">
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O68)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O65)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -2621,10 +2621,10 @@
         <f>RANK(AC53,$AC$53:$AC$55)+COUNTIF($AC$52:AC52,AC53)</f>
       </c>
       <c r="U53" t="str">
-        <f>=(B53*1000000000)-(C53*10000000)+(D53*100000)+(B59*1000)-(C59*100)+(D59*10)+(E59*1)-(F59*0.01)</f>
+        <f>(B53*1000000000)-(C53*10000000)+(D53*100000)+(B59*1000)-(C59*100)+(D59*10)+(E59*1)-(F59*0.01)</f>
       </c>
       <c r="AC53" t="str">
-        <f>=(J53*1000000000)-(K53*10000000)+(L53*100000)+(J58*1000)-(K58*100)+(L58*10)+(M58*1)-(N58*0.01)</f>
+        <f>(J53*1000000000)-(K53*10000000)+(L53*100000)+(J58*1000)-(K58*100)+(L58*10)+(M58*1)-(N58*0.01)</f>
       </c>
     </row>
     <row r="54">
@@ -2659,10 +2659,10 @@
         <f>RANK(AC54,$AC$53:$AC$55)+COUNTIF($AC$52:AC53,AC54)</f>
       </c>
       <c r="U54" t="str">
-        <f>=(B54*1000000000)-(C54*10000000)+(D54*100000)+(B60*1000)-(C60*100)+(D60*10)+(E60*1)-(F60*0.01)</f>
+        <f>(B54*1000000000)-(C54*10000000)+(D54*100000)+(B60*1000)-(C60*100)+(D60*10)+(E60*1)-(F60*0.01)</f>
       </c>
       <c r="AC54" t="str">
-        <f>=(J54*1000000000)-(K54*10000000)+(L54*100000)+(J59*1000)-(K59*100)+(L59*10)+(M59*1)-(N59*0.01)</f>
+        <f>(J54*1000000000)-(K54*10000000)+(L54*100000)+(J59*1000)-(K59*100)+(L59*10)+(M59*1)-(N59*0.01)</f>
       </c>
     </row>
     <row r="55">
@@ -2697,10 +2697,10 @@
         <f>RANK(AC55,$AC$53:$AC$55)+COUNTIF($AC$52:AC54,AC55)</f>
       </c>
       <c r="U55" t="str">
-        <f>=(B55*1000000000)-(C55*10000000)+(D55*100000)+(B61*1000)-(C61*100)+(D61*10)+(E61*1)-(F61*0.01)</f>
+        <f>(B55*1000000000)-(C55*10000000)+(D55*100000)+(B61*1000)-(C61*100)+(D61*10)+(E61*1)-(F61*0.01)</f>
       </c>
       <c r="AC55" t="str">
-        <f>=(J55*1000000000)-(K55*10000000)+(L55*100000)+(J60*1000)-(K60*100)+(L60*10)+(M60*1)-(N60*0.01)</f>
+        <f>(J55*1000000000)-(K55*10000000)+(L55*100000)+(J60*1000)-(K60*100)+(L60*10)+(M60*1)-(N60*0.01)</f>
       </c>
     </row>
     <row r="56">
@@ -2720,7 +2720,7 @@
         <f>RANK(U56,$U$53:$U$56)+COUNTIF($U$52:U55,U56)</f>
       </c>
       <c r="U56" t="str">
-        <f>=(B56*1000000000)-(C56*10000000)+(D56*100000)+(B62*1000)-(C62*100)+(D62*10)+(E62*1)-(F62*0.01)</f>
+        <f>(B56*1000000000)-(C56*10000000)+(D56*100000)+(B62*1000)-(C62*100)+(D62*10)+(E62*1)-(F62*0.01)</f>
       </c>
     </row>
     <row r="57">
@@ -3299,7 +3299,7 @@
         <f>RANK(U96,$U$96:$U$98)+COUNTIF($U$95:U95,U96)</f>
       </c>
       <c r="U96" t="str">
-        <f>=(B96*1000000000)-(C96*10000000)+(D96*100000)+(B101*1000)-(C101*100)+(D101*10)+(E101*1)-(F101*0.01)</f>
+        <f>(B96*1000000000)-(C96*10000000)+(D96*100000)+(B101*1000)-(C101*100)+(D101*10)+(E101*1)-(F101*0.01)</f>
       </c>
     </row>
     <row r="97">
@@ -3319,7 +3319,7 @@
         <f>RANK(U97,$U$96:$U$98)+COUNTIF($U$95:U96,U97)</f>
       </c>
       <c r="U97" t="str">
-        <f>=(B97*1000000000)-(C97*10000000)+(D97*100000)+(B102*1000)-(C102*100)+(D102*10)+(E102*1)-(F102*0.01)</f>
+        <f>(B97*1000000000)-(C97*10000000)+(D97*100000)+(B102*1000)-(C102*100)+(D102*10)+(E102*1)-(F102*0.01)</f>
       </c>
     </row>
     <row r="98">
@@ -3339,7 +3339,7 @@
         <f>RANK(U98,$U$96:$U$98)+COUNTIF($U$95:U97,U98)</f>
       </c>
       <c r="U98" t="str">
-        <f>=(B98*1000000000)-(C98*10000000)+(D98*100000)+(B103*1000)-(C103*100)+(D103*10)+(E103*1)-(F103*0.01)</f>
+        <f>(B98*1000000000)-(C98*10000000)+(D98*100000)+(B103*1000)-(C103*100)+(D103*10)+(E103*1)-(F103*0.01)</f>
       </c>
     </row>
     <row r="100">

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -1719,17 +1719,17 @@
         <f>'data'!$B$4</f>
       </c>
       <c r="B4" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C4" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F4" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G4" s="14" t="str">
         <f>'data'!$B$3</f>
@@ -1738,17 +1738,17 @@
         <f>'data'!$B$11</f>
       </c>
       <c r="J4" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L5:L9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K4" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L4" s="18"/>
       <c r="M4" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N4" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L5:L9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O4" s="14" t="str">
         <f>'data'!$B$10</f>
@@ -1907,17 +1907,17 @@
         <f>'data'!$B$4</f>
       </c>
       <c r="B12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D13:D17)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13:B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13:C17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13:E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13:F17," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13:B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13:C17," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D12" s="18"/>
       <c r="E12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13:E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13:F17," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D13:D17)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13:E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13:F17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13:B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13:C17," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G12" s="14" t="str">
         <f>'data'!$B$5</f>
@@ -1926,17 +1926,17 @@
         <f>'data'!$B$12</f>
       </c>
       <c r="J12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L13:L17)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13:J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13:K17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13:M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13:N17," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13:J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13:K17," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L12" s="18"/>
       <c r="M12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13:M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13:N17," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L13:L17)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13:M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13:N17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13:J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13:K17," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O12" s="14" t="str">
         <f>'data'!$B$10</f>
@@ -2095,17 +2095,17 @@
         <f>'data'!$B$6</f>
       </c>
       <c r="B20" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D21:D25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C20" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D20" s="18"/>
       <c r="E20" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F20" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D21:D25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G20" s="14" t="str">
         <f>'data'!$B$5</f>
@@ -2114,17 +2114,17 @@
         <f>'data'!$B$12</f>
       </c>
       <c r="J20" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L21:L25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21:J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21:K25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21:M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21:N25," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K20" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21:J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21:K25," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L20" s="18"/>
       <c r="M20" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21:M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21:N25," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N20" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L21:L25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21:M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21:N25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21:J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21:K25," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O20" s="14" t="str">
         <f>'data'!$B$11</f>
@@ -2270,17 +2270,17 @@
         <f>'data'!$B$6</f>
       </c>
       <c r="B28" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D29:D33)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29:B33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29:C33," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29:E33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29:F33," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D31)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D32)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C32," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F32," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D33)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C33," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F33," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C28" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29:B33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29:C33," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C33," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D28" s="18"/>
       <c r="E28" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29:E33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29:F33," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F33," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F28" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D29:D33)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29:E33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29:F33," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29:B33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29:C33," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D31)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D32)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F32," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C32," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D33)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F33," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C33," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G28" s="14" t="str">
         <f>'data'!$B$3</f>
@@ -2371,17 +2371,17 @@
         <f>'data'!$B$5</f>
       </c>
       <c r="B36" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D37:D41)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37:B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37:C41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37:E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37:F41," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C36" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37:B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37:C41," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D36" s="18"/>
       <c r="E36" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37:E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37:F41," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F36" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D37:D41)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37:E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37:F41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37:B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37:C41," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G36" s="14" t="str">
         <f>'data'!$B$3</f>
@@ -2472,17 +2472,17 @@
         <f>'data'!$B$6</f>
       </c>
       <c r="B44" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D45:D49)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45:B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45:C49," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45:E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45:F49," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D45)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D46)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D47)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C44" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45:B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45:C49," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D44" s="18"/>
       <c r="E44" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45:E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45:F49," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F44" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D45:D49)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45:E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45:F49," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45:B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45:C49," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D45)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D46)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D47)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G44" s="14" t="str">
         <f>'data'!$B$4</f>
@@ -2980,17 +2980,17 @@
         <f>'data'!$B$8</f>
       </c>
       <c r="B71" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D72:D76)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72:B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72:C76," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72:E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72:F76," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C71" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72:B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72:C76," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D71" s="18"/>
       <c r="E71" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72:E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72:F76," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F71" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D72:D76)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72:E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72:F76," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72:B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72:C76," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G71" s="14" t="str">
         <f>'data'!$B$7</f>
@@ -3081,17 +3081,17 @@
         <f>'data'!$B$9</f>
       </c>
       <c r="B79" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D80:D84)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80:B84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80:C84," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80:E84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80:F84," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D80)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D81)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D82)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B82," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C82," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E82," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F82," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D83)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B83," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C83," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E83," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F83," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D84)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B84," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C84," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E84," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F84," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C79" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80:B84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80:C84," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B82," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C82," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B83," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C83," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B84," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C84," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D79" s="18"/>
       <c r="E79" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80:E84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80:F84," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E82," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F82," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E83," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F83," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E84," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F84," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F79" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D80:D84)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80:E84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80:F84," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80:B84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80:C84," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D80)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D81)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D82)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E82," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F82," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B82," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C82," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D83)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E83," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F83," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B83," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C83," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D84)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E84," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F84," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B84," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C84," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G79" s="14" t="str">
         <f>'data'!$B$7</f>
@@ -3182,17 +3182,17 @@
         <f>'data'!$B$9</f>
       </c>
       <c r="B87" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D88:D92)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88:B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88:C92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88:E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88:F92," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D90)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C87" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88:B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88:C92," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D87" s="18"/>
       <c r="E87" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88:E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88:F92," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F87" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D88:D92)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88:E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88:F92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88:B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88:C92," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D90)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G87" s="14" t="str">
         <f>'data'!$B$8</f>
@@ -3740,17 +3740,17 @@
         <v>64</v>
       </c>
       <c r="B12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G12" s="14" t="s">
         <v>64</v>
@@ -3759,17 +3759,17 @@
         <v>64</v>
       </c>
       <c r="J12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L5:L9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L12" s="14"/>
       <c r="M12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L5:L9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O12" s="14" t="s">
         <v>64</v>
@@ -4024,17 +4024,17 @@
         <v>64</v>
       </c>
       <c r="B33" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D26:D30)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26:B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C26:C30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E26:E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F26:F30," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D26)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C26," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F26," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D27)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C27," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D28)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C28," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C33" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26:B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C26:C30," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D33" s="14"/>
       <c r="E33" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E26:E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F26:F30," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F33" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D26:D30)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E26:E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F26:F30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26:B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C26:C30," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D26)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F26," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C26," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D27)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C27," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D28)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C28," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G33" s="14" t="s">
         <v>64</v>
@@ -4043,17 +4043,17 @@
         <v>64</v>
       </c>
       <c r="J33" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L26:L30)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J26:J30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K26:K30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M26:M30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N26:N30," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L26)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K26," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N26," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L27)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K27," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N27," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L28)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K28," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N28," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K29," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N29," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K30," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N30," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K33" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J26:J30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K26:K30," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K30," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L33" s="14"/>
       <c r="M33" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M26:M30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N26:N30," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N30," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N33" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L26:L30)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M26:M30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N26:N30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J26:J30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K26:K30," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L26)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N26," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K26," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L27)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N27," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K27," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L28)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N28," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K28," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N29," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K29," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N30," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K30," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O33" s="14" t="s">
         <v>64</v>
@@ -4205,17 +4205,17 @@
         <v>64</v>
       </c>
       <c r="B54" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D47:D51)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47:B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47:C51," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47:E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47:F51," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D47)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D51)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C54" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47:B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47:C51," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D54" s="14"/>
       <c r="E54" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47:E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47:F51," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F54" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D47:D51)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47:E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47:F51," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47:B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47:C51," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D47)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D51)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G54" s="14" t="s">
         <v>64</v>

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -1719,17 +1719,17 @@
         <f>'data'!$B$4</f>
       </c>
       <c r="B4" s="14" t="str">
-        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C4" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F4" s="14" t="str">
-        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G4" s="14" t="str">
         <f>'data'!$B$3</f>
@@ -1738,17 +1738,17 @@
         <f>'data'!$B$11</f>
       </c>
       <c r="J4" s="14" t="str">
-        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K4" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L4" s="18"/>
       <c r="M4" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N4" s="14" t="str">
-        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O4" s="14" t="str">
         <f>'data'!$B$10</f>
@@ -1907,17 +1907,17 @@
         <f>'data'!$B$4</f>
       </c>
       <c r="B12" s="14" t="str">
-        <f>IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C12" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D12" s="18"/>
       <c r="E12" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F12" s="14" t="str">
-        <f>IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G12" s="14" t="str">
         <f>'data'!$B$5</f>
@@ -1926,17 +1926,17 @@
         <f>'data'!$B$12</f>
       </c>
       <c r="J12" s="14" t="str">
-        <f>IF(UPPER(L13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K12" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L12" s="18"/>
       <c r="M12" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N12" s="14" t="str">
-        <f>IF(UPPER(L13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O12" s="14" t="str">
         <f>'data'!$B$10</f>
@@ -2095,17 +2095,17 @@
         <f>'data'!$B$6</f>
       </c>
       <c r="B20" s="14" t="str">
-        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C20" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D20" s="18"/>
       <c r="E20" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F20" s="14" t="str">
-        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G20" s="14" t="str">
         <f>'data'!$B$5</f>
@@ -2114,17 +2114,17 @@
         <f>'data'!$B$12</f>
       </c>
       <c r="J20" s="14" t="str">
-        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K20" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L20" s="18"/>
       <c r="M20" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N20" s="14" t="str">
-        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O20" s="14" t="str">
         <f>'data'!$B$11</f>
@@ -2270,17 +2270,17 @@
         <f>'data'!$B$6</f>
       </c>
       <c r="B28" s="14" t="str">
-        <f>IF(UPPER(D29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D31)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D32)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C32," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F32," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D33)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C33," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F33," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D31)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D32)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C32," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F32," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D33)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C33," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F33," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C28" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C33," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C33," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D28" s="18"/>
       <c r="E28" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F33," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F33," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F28" s="14" t="str">
-        <f>IF(UPPER(D29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D31)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D32)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F32," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B32," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C32," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D33)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F33," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B33," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C33," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D31)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D32)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F32," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C32," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D33)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F33," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C33," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G28" s="14" t="str">
         <f>'data'!$B$3</f>
@@ -2371,17 +2371,17 @@
         <f>'data'!$B$5</f>
       </c>
       <c r="B36" s="14" t="str">
-        <f>IF(UPPER(D37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C36" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D36" s="18"/>
       <c r="E36" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F36" s="14" t="str">
-        <f>IF(UPPER(D37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G36" s="14" t="str">
         <f>'data'!$B$3</f>
@@ -2472,17 +2472,17 @@
         <f>'data'!$B$6</f>
       </c>
       <c r="B44" s="14" t="str">
-        <f>IF(UPPER(D45)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D46)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D47)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D45)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D46)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D47)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C44" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D44" s="18"/>
       <c r="E44" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F44" s="14" t="str">
-        <f>IF(UPPER(D45)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D46)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D47)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D45)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D46)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D47)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G44" s="14" t="str">
         <f>'data'!$B$4</f>
@@ -2980,17 +2980,17 @@
         <f>'data'!$B$8</f>
       </c>
       <c r="B71" s="14" t="str">
-        <f>IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C71" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D71" s="18"/>
       <c r="E71" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F71" s="14" t="str">
-        <f>IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G71" s="14" t="str">
         <f>'data'!$B$7</f>
@@ -3081,17 +3081,17 @@
         <f>'data'!$B$9</f>
       </c>
       <c r="B79" s="14" t="str">
-        <f>IF(UPPER(D80)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D81)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D82)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B82," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C82," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E82," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F82," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D83)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B83," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C83," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E83," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F83," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D84)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B84," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C84," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E84," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F84," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D80)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D81)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D82)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C82," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F82," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D83)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C83," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F83," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D84)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C84," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F84," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C79" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B82," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C82," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B83," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C83," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B84," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C84," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C84," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D79" s="18"/>
       <c r="E79" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E82," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F82," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E83," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F83," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E84," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F84," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F84," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F79" s="14" t="str">
-        <f>IF(UPPER(D80)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D81)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D82)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E82," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F82," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B82," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C82," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D83)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E83," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F83," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B83," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C83," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D84)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E84," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F84," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B84," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C84," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D80)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D81)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D82)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F82," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C82," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D83)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F83," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C83," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D84)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F84," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C84," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G79" s="14" t="str">
         <f>'data'!$B$7</f>
@@ -3182,17 +3182,17 @@
         <f>'data'!$B$9</f>
       </c>
       <c r="B87" s="14" t="str">
-        <f>IF(UPPER(D88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D90)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D90)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C87" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D87" s="18"/>
       <c r="E87" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F87" s="14" t="str">
-        <f>IF(UPPER(D88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D90)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D90)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G87" s="14" t="str">
         <f>'data'!$B$8</f>
@@ -3740,17 +3740,17 @@
         <v>64</v>
       </c>
       <c r="B12" s="14" t="str">
-        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C12" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F12" s="14" t="str">
-        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G12" s="14" t="s">
         <v>64</v>
@@ -3759,17 +3759,17 @@
         <v>64</v>
       </c>
       <c r="J12" s="14" t="str">
-        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K12" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L12" s="14"/>
       <c r="M12" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N12" s="14" t="str">
-        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O12" s="14" t="s">
         <v>64</v>
@@ -4024,17 +4024,17 @@
         <v>64</v>
       </c>
       <c r="B33" s="14" t="str">
-        <f>IF(UPPER(D26)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C26," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F26," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D27)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C27," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D28)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C28," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D26)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C26," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F26," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D27)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C27," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D28)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C28," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C33" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D33" s="14"/>
       <c r="E33" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F33" s="14" t="str">
-        <f>IF(UPPER(D26)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F26," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C26," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D27)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C27," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D28)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C28," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D26)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F26," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C26," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D27)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C27," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D28)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C28," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G33" s="14" t="s">
         <v>64</v>
@@ -4043,17 +4043,17 @@
         <v>64</v>
       </c>
       <c r="J33" s="14" t="str">
-        <f>IF(UPPER(L26)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K26," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N26," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L27)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K27," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N27," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L28)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K28," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N28," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K29," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N29," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K30," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N30," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L26)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K26," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N26," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L27)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K27," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N27," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L28)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K28," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N28," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K29," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N29," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N30," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K33" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K30," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K30," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L33" s="14"/>
       <c r="M33" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N30," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N30," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N33" s="14" t="str">
-        <f>IF(UPPER(L26)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N26," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J26," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K26," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L27)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N27," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J27," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K27," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L28)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N28," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J28," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K28," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N29," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J29," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K29," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N30," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J30," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K30," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L26)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N26," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K26," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L27)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N27," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K27," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L28)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N28," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K28," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N29," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K29," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K30," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O33" s="14" t="s">
         <v>64</v>
@@ -4205,17 +4205,17 @@
         <v>64</v>
       </c>
       <c r="B54" s="14" t="str">
-        <f>IF(UPPER(D47)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D51)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D47)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D51)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C54" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D54" s="14"/>
       <c r="E54" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F54" s="14" t="str">
-        <f>IF(UPPER(D47)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D51)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D47)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D51)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G54" s="14" t="s">
         <v>64</v>

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -357,7 +357,7 @@
       <family val="2"/>
       <b val="1"/>
       <color/>
-      <sz val="150"/>
+      <sz val="200"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1126,102 +1126,102 @@
     <col customWidth="true" max="1" min="1" width="90"/>
   </cols>
   <sheetData>
-    <row r="1" ht="390" customHeight="true">
+    <row r="1" ht="409" customHeight="true">
       <c r="A1" s="30" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="2" ht="390" customHeight="true">
+    <row r="2" ht="409" customHeight="true">
       <c r="A2" s="30" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" ht="390" customHeight="true">
+    <row r="3" ht="409" customHeight="true">
       <c r="A3" s="30" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" ht="390" customHeight="true">
+    <row r="4" ht="409" customHeight="true">
       <c r="A4" s="30" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" ht="390" customHeight="true">
+    <row r="5" ht="409" customHeight="true">
       <c r="A5" s="30" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="6" ht="390" customHeight="true">
+    <row r="6" ht="409" customHeight="true">
       <c r="A6" s="30" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="7" ht="390" customHeight="true">
+    <row r="7" ht="409" customHeight="true">
       <c r="A7" s="30" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="8" ht="390" customHeight="true">
+    <row r="8" ht="409" customHeight="true">
       <c r="A8" s="30" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="9" ht="390" customHeight="true">
+    <row r="9" ht="409" customHeight="true">
       <c r="A9" s="30" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="10" ht="390" customHeight="true">
+    <row r="10" ht="409" customHeight="true">
       <c r="A10" s="30" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="11" ht="390" customHeight="true">
+    <row r="11" ht="409" customHeight="true">
       <c r="A11" s="30" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" ht="390" customHeight="true">
+    <row r="12" ht="409" customHeight="true">
       <c r="A12" s="30" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="13" ht="390" customHeight="true">
+    <row r="13" ht="409" customHeight="true">
       <c r="A13" s="30" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="14" ht="390" customHeight="true">
+    <row r="14" ht="409" customHeight="true">
       <c r="A14" s="30" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="15" ht="390" customHeight="true">
+    <row r="15" ht="409" customHeight="true">
       <c r="A15" s="30" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="16" ht="390" customHeight="true">
+    <row r="16" ht="409" customHeight="true">
       <c r="A16" s="30" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="17" ht="390" customHeight="true">
+    <row r="17" ht="409" customHeight="true">
       <c r="A17" s="30" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="18" ht="390" customHeight="true">
+    <row r="18" ht="409" customHeight="true">
       <c r="A18" s="30" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="19" ht="390" customHeight="true">
+    <row r="19" ht="409" customHeight="true">
       <c r="A19" s="30" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="20" ht="390" customHeight="true">
+    <row r="20" ht="409" customHeight="true">
       <c r="A20" s="30" t="s">
         <v>62</v>
       </c>

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -357,7 +357,7 @@
       <family val="2"/>
       <b val="1"/>
       <color/>
-      <sz val="200"/>
+      <sz val="250"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1123,7 +1123,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="90"/>
+    <col customWidth="true" max="1" min="1" width="110"/>
   </cols>
   <sheetData>
     <row r="1" ht="409" customHeight="true">

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -21,6 +21,8 @@
   <definedNames>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$12</definedName>
     <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$P$111</definedName>
+    <definedName localSheetId="5" name="_xlnm.Print_Area">'Tree 1'!$A$1:$G$14</definedName>
+    <definedName localSheetId="6" name="_xlnm.Print_Area">'Tree 2'!$A$1:$G$11</definedName>
     <definedName localSheetId="7" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$7</definedName>
     <definedName localSheetId="8" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$3</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$P$64</definedName>
@@ -4256,12 +4258,17 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4274,15 +4281,6 @@
       <c r="E1" s="13"/>
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
     </row>
     <row r="4">
       <c r="A4" s="24" t="str">
@@ -4361,20 +4359,25 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4387,15 +4390,6 @@
       <c r="E1" s="13"/>
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
     </row>
     <row r="4">
       <c r="A4" s="24" t="str">
@@ -4452,9 +4446,9 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -553,7 +553,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
@@ -4296,6 +4296,8 @@
       <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$4</f>
       </c>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="23" t="str">
         <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G66)</f>
       </c>
@@ -4405,6 +4407,8 @@
       <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$11</f>
       </c>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="23" t="str">
         <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G107)</f>
       </c>

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -3555,7 +3555,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G108)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O65)</f>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -3563,10 +3563,10 @@
       <c r="E4" s="14"/>
       <c r="F4" s="14"/>
       <c r="G4" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O64)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G107)</f>
       </c>
       <c r="I4" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O65)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G108)</f>
       </c>
       <c r="J4" s="14"/>
       <c r="K4" s="14"/>
@@ -3699,7 +3699,7 @@
     </row>
     <row r="11">
       <c r="A11" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G108)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O65)</f>
       </c>
       <c r="B11" s="14" t="s">
         <v>43</v>
@@ -3715,10 +3715,10 @@
         <v>43</v>
       </c>
       <c r="G11" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O64)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G107)</f>
       </c>
       <c r="I11" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O65)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G108)</f>
       </c>
       <c r="J11" s="14" t="s">
         <v>43</v>
@@ -3858,7 +3858,7 @@
       <c r="M25" s="14"/>
       <c r="N25" s="14"/>
       <c r="O25" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G107)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O64)</f>
       </c>
     </row>
     <row r="26">
@@ -4018,7 +4018,7 @@
         <v>43</v>
       </c>
       <c r="O32" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G107)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O64)</f>
       </c>
     </row>
     <row r="33">
@@ -4320,7 +4320,7 @@
     <row r="9">
       <c r="A9" s="22"/>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O64)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G107)</f>
       </c>
       <c r="G9" s="20"/>
     </row>
@@ -4340,7 +4340,7 @@
         <f>"1. " &amp; data!$B$7</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G108)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O65)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -4410,7 +4410,7 @@
       <c r="C6" s="23"/>
       <c r="D6" s="23"/>
       <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G107)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O64)</f>
       </c>
     </row>
     <row r="7">
@@ -4442,7 +4442,7 @@
     </row>
     <row r="11">
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O65)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G108)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -94,28 +94,28 @@
     <t>Team Beta</t>
   </si>
   <si>
+    <t>Steven Hernandez</t>
+  </si>
+  <si>
+    <t>Team Delta</t>
+  </si>
+  <si>
+    <t>Robert Young</t>
+  </si>
+  <si>
+    <t>Team Gamma</t>
+  </si>
+  <si>
+    <t>Pool B</t>
+  </si>
+  <si>
+    <t>Luke Rodriguez</t>
+  </si>
+  <si>
     <t>Oliver Walker</t>
   </si>
   <si>
     <t>Team Epsilon</t>
-  </si>
-  <si>
-    <t>Robert Young</t>
-  </si>
-  <si>
-    <t>Team Gamma</t>
-  </si>
-  <si>
-    <t>Pool B</t>
-  </si>
-  <si>
-    <t>Luke Rodriguez</t>
-  </si>
-  <si>
-    <t>Steven Hernandez</t>
-  </si>
-  <si>
-    <t>Team Delta</t>
   </si>
   <si>
     <t>Michael Lewis</t>
@@ -982,7 +982,7 @@
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -993,7 +993,7 @@
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -88,25 +88,40 @@
     <t>Team Alpha</t>
   </si>
   <si>
+    <t>Nathan Lee</t>
+  </si>
+  <si>
+    <t>Team Delta</t>
+  </si>
+  <si>
     <t>Quentin Allen</t>
   </si>
   <si>
     <t>Team Beta</t>
   </si>
   <si>
+    <t>Robert Young</t>
+  </si>
+  <si>
+    <t>Team Gamma</t>
+  </si>
+  <si>
+    <t>Pool B</t>
+  </si>
+  <si>
+    <t>Michael Lewis</t>
+  </si>
+  <si>
     <t>Steven Hernandez</t>
   </si>
   <si>
-    <t>Team Delta</t>
-  </si>
-  <si>
-    <t>Robert Young</t>
-  </si>
-  <si>
-    <t>Team Gamma</t>
-  </si>
-  <si>
-    <t>Pool B</t>
+    <t>Thomas King</t>
+  </si>
+  <si>
+    <t>Team Epsilon</t>
+  </si>
+  <si>
+    <t>Pool C</t>
   </si>
   <si>
     <t>Luke Rodriguez</t>
@@ -115,22 +130,7 @@
     <t>Oliver Walker</t>
   </si>
   <si>
-    <t>Team Epsilon</t>
-  </si>
-  <si>
-    <t>Michael Lewis</t>
-  </si>
-  <si>
-    <t>Pool C</t>
-  </si>
-  <si>
     <t>Paul Hall</t>
-  </si>
-  <si>
-    <t>Nathan Lee</t>
-  </si>
-  <si>
-    <t>Thomas King</t>
   </si>
   <si>
     <t>Shiaijo A</t>
@@ -938,7 +938,7 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -949,7 +949,7 @@
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -957,10 +957,10 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
         <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -971,7 +971,7 @@
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -982,7 +982,7 @@
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -993,7 +993,7 @@
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t>Number of pools</t>
   </si>
@@ -76,6 +76,9 @@
     <t>Player Dojo</t>
   </si>
   <si>
+    <t>Player Number</t>
+  </si>
+  <si>
     <t>Metadata</t>
   </si>
   <si>
@@ -88,51 +91,81 @@
     <t>Team Alpha</t>
   </si>
   <si>
+    <t>K1</t>
+  </si>
+  <si>
     <t>Nathan Lee</t>
   </si>
   <si>
     <t>Team Delta</t>
   </si>
   <si>
+    <t>K2</t>
+  </si>
+  <si>
     <t>Quentin Allen</t>
   </si>
   <si>
     <t>Team Beta</t>
   </si>
   <si>
+    <t>K3</t>
+  </si>
+  <si>
     <t>Robert Young</t>
   </si>
   <si>
     <t>Team Gamma</t>
   </si>
   <si>
+    <t>K4</t>
+  </si>
+  <si>
     <t>Pool B</t>
   </si>
   <si>
     <t>Michael Lewis</t>
   </si>
   <si>
+    <t>K5</t>
+  </si>
+  <si>
     <t>Steven Hernandez</t>
   </si>
   <si>
+    <t>K6</t>
+  </si>
+  <si>
     <t>Thomas King</t>
   </si>
   <si>
     <t>Team Epsilon</t>
   </si>
   <si>
+    <t>K7</t>
+  </si>
+  <si>
     <t>Pool C</t>
   </si>
   <si>
     <t>Luke Rodriguez</t>
   </si>
   <si>
+    <t>K8</t>
+  </si>
+  <si>
     <t>Oliver Walker</t>
   </si>
   <si>
+    <t>K9</t>
+  </si>
+  <si>
     <t>Paul Hall</t>
   </si>
   <si>
+    <t>K10</t>
+  </si>
+  <si>
     <t>Shiaijo A</t>
   </si>
   <si>
@@ -191,36 +224,6 @@
   </si>
   <si>
     <t>4.</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>A2</t>
-  </si>
-  <si>
-    <t>A3</t>
-  </si>
-  <si>
-    <t>A4</t>
-  </si>
-  <si>
-    <t>B1</t>
-  </si>
-  <si>
-    <t>B2</t>
-  </si>
-  <si>
-    <t>B3</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>C3</t>
   </si>
   <si>
     <t>Round 1 - Match 1</t>
@@ -882,118 +885,151 @@
       <c r="C2" t="s">
         <v>13</v>
       </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1011,56 +1047,56 @@
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="28" t="s">
-        <v>53</v>
+      <c r="A1" s="28" t="str">
+        <f>'data'!$D$3</f>
       </c>
       <c r="B1" s="29" t="str">
         <f>'data'!$B$3</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="28" t="s">
-        <v>54</v>
+      <c r="A2" s="28" t="str">
+        <f>'data'!$D$4</f>
       </c>
       <c r="B2" s="29" t="str">
         <f>'data'!$B$4</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="28" t="s">
-        <v>55</v>
+      <c r="A3" s="28" t="str">
+        <f>'data'!$D$5</f>
       </c>
       <c r="B3" s="29" t="str">
         <f>'data'!$B$5</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="28" t="s">
-        <v>56</v>
+      <c r="A4" s="28" t="str">
+        <f>'data'!$D$6</f>
       </c>
       <c r="B4" s="29" t="str">
         <f>'data'!$B$6</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="28" t="s">
-        <v>57</v>
+      <c r="A5" s="28" t="str">
+        <f>'data'!$D$7</f>
       </c>
       <c r="B5" s="29" t="str">
         <f>'data'!$B$7</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="28" t="s">
-        <v>58</v>
+      <c r="A6" s="28" t="str">
+        <f>'data'!$D$8</f>
       </c>
       <c r="B6" s="29" t="str">
         <f>'data'!$B$8</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="28" t="s">
-        <v>59</v>
+      <c r="A7" s="28" t="str">
+        <f>'data'!$D$9</f>
       </c>
       <c r="B7" s="29" t="str">
         <f>'data'!$B$9</f>
@@ -1087,24 +1123,24 @@
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="28" t="s">
-        <v>60</v>
+      <c r="A1" s="28" t="str">
+        <f>'data'!$D$10</f>
       </c>
       <c r="B1" s="29" t="str">
         <f>'data'!$B$10</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="28" t="s">
-        <v>61</v>
+      <c r="A2" s="28" t="str">
+        <f>'data'!$D$11</f>
       </c>
       <c r="B2" s="29" t="str">
         <f>'data'!$B$11</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="28" t="s">
-        <v>62</v>
+      <c r="A3" s="28" t="str">
+        <f>'data'!$D$12</f>
       </c>
       <c r="B3" s="29" t="str">
         <f>'data'!$B$12</f>
@@ -1130,102 +1166,102 @@
   <sheetData>
     <row r="1" ht="409" customHeight="true">
       <c r="A1" s="30" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" ht="409" customHeight="true">
       <c r="A2" s="30" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" ht="409" customHeight="true">
       <c r="A3" s="30" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="409" customHeight="true">
       <c r="A4" s="30" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" ht="409" customHeight="true">
       <c r="A5" s="30" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" ht="409" customHeight="true">
       <c r="A6" s="30" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" ht="409" customHeight="true">
       <c r="A7" s="30" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" ht="409" customHeight="true">
       <c r="A8" s="30" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" ht="409" customHeight="true">
       <c r="A9" s="30" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" ht="409" customHeight="true">
       <c r="A10" s="30" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" ht="409" customHeight="true">
       <c r="A11" s="30" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" ht="409" customHeight="true">
       <c r="A12" s="30" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" ht="409" customHeight="true">
       <c r="A13" s="30" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" ht="409" customHeight="true">
       <c r="A14" s="30" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" ht="409" customHeight="true">
       <c r="A15" s="30" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" ht="409" customHeight="true">
       <c r="A16" s="30" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" ht="409" customHeight="true">
       <c r="A17" s="30" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" ht="409" customHeight="true">
       <c r="A18" s="30" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" ht="409" customHeight="true">
       <c r="A19" s="30" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" ht="409" customHeight="true">
       <c r="A20" s="30" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1448,7 +1484,7 @@
     </row>
     <row r="13">
       <c r="E13" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
@@ -1459,7 +1495,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -1469,7 +1505,7 @@
     </row>
     <row r="15">
       <c r="E15" s="32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -1479,7 +1515,7 @@
     </row>
     <row r="16">
       <c r="E16" s="32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -1489,7 +1525,7 @@
     </row>
     <row r="17">
       <c r="E17" s="32" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
@@ -1499,7 +1535,7 @@
     </row>
     <row r="18">
       <c r="E18" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
@@ -1509,7 +1545,7 @@
     </row>
     <row r="19">
       <c r="E19" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
@@ -1582,40 +1618,40 @@
     </row>
     <row r="6" ht="17" customHeight="true">
       <c r="B6" s="12" t="str">
-        <f>"1. " &amp; data!$B$3</f>
+        <f>data!$D$3&amp;" "&amp;data!$B$3</f>
       </c>
       <c r="D6" s="12" t="str">
-        <f>"1. " &amp; data!$B$7</f>
+        <f>data!$D$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="F6" s="12" t="str">
-        <f>"1. " &amp; data!$B$10</f>
+        <f>data!$D$10&amp;" "&amp;data!$B$10</f>
       </c>
     </row>
     <row r="7" ht="17" customHeight="true">
       <c r="B7" s="12" t="str">
-        <f>"2. " &amp; data!$B$4</f>
+        <f>data!$D$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="D7" s="12" t="str">
-        <f>"2. " &amp; data!$B$8</f>
+        <f>data!$D$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="F7" s="12" t="str">
-        <f>"2. " &amp; data!$B$11</f>
+        <f>data!$D$11&amp;" "&amp;data!$B$11</f>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="12" t="str">
-        <f>"3. " &amp; data!$B$5</f>
+        <f>data!$D$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="D8" s="12" t="str">
-        <f>"3. " &amp; data!$B$9</f>
+        <f>data!$D$9&amp;" "&amp;data!$B$9</f>
       </c>
       <c r="F8" s="12" t="str">
-        <f>"3. " &amp; data!$B$12</f>
+        <f>data!$D$12&amp;" "&amp;data!$B$12</f>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="12" t="str">
-        <f>"4. " &amp; data!$B$6</f>
+        <f>data!$D$6&amp;" "&amp;data!$B$6</f>
       </c>
     </row>
   </sheetData>
@@ -1650,7 +1686,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -1659,7 +1695,7 @@
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
       <c r="I1" s="13" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
@@ -1690,35 +1726,35 @@
     </row>
     <row r="3">
       <c r="A3" s="17" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B3" s="14"/>
       <c r="C3" s="14"/>
       <c r="D3" s="14" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E3" s="14"/>
       <c r="F3" s="14"/>
       <c r="G3" s="16" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J3" s="14"/>
       <c r="K3" s="14"/>
       <c r="L3" s="14" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="M3" s="14"/>
       <c r="N3" s="14"/>
       <c r="O3" s="16" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>'data'!$B$4</f>
+        <f>data!$D$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="B4" s="14" t="str">
         <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-",""))),1,0))</f>
@@ -1734,10 +1770,10 @@
         <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G4" s="14" t="str">
-        <f>'data'!$B$3</f>
+        <f>data!$D$3&amp;" "&amp;data!$B$3</f>
       </c>
       <c r="I4" s="14" t="str">
-        <f>'data'!$B$11</f>
+        <f>data!$D$11&amp;" "&amp;data!$B$11</f>
       </c>
       <c r="J4" s="14" t="str">
         <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-",""))),1,0))</f>
@@ -1753,7 +1789,7 @@
         <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O4" s="14" t="str">
-        <f>'data'!$B$10</f>
+        <f>data!$D$10&amp;" "&amp;data!$B$10</f>
       </c>
     </row>
     <row r="5">
@@ -1878,35 +1914,35 @@
     </row>
     <row r="11">
       <c r="A11" s="17" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
       <c r="D11" s="14" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E11" s="14"/>
       <c r="F11" s="14"/>
       <c r="G11" s="16" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I11" s="17" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
       <c r="L11" s="14" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="M11" s="14"/>
       <c r="N11" s="14"/>
       <c r="O11" s="16" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="str">
-        <f>'data'!$B$4</f>
+        <f>data!$D$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="B12" s="14" t="str">
         <f>IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-",""))),1,0))</f>
@@ -1922,10 +1958,10 @@
         <f>IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G12" s="14" t="str">
-        <f>'data'!$B$5</f>
+        <f>data!$D$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="I12" s="14" t="str">
-        <f>'data'!$B$12</f>
+        <f>data!$D$12&amp;" "&amp;data!$B$12</f>
       </c>
       <c r="J12" s="14" t="str">
         <f>IF(UPPER(L13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-",""))),1,0))</f>
@@ -1941,7 +1977,7 @@
         <f>IF(UPPER(L13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O12" s="14" t="str">
-        <f>'data'!$B$10</f>
+        <f>data!$D$10&amp;" "&amp;data!$B$10</f>
       </c>
     </row>
     <row r="13">
@@ -2066,35 +2102,35 @@
     </row>
     <row r="19">
       <c r="A19" s="17" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
       <c r="D19" s="14" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E19" s="14"/>
       <c r="F19" s="14"/>
       <c r="G19" s="16" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I19" s="17" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J19" s="14"/>
       <c r="K19" s="14"/>
       <c r="L19" s="14" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="M19" s="14"/>
       <c r="N19" s="14"/>
       <c r="O19" s="16" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="str">
-        <f>'data'!$B$6</f>
+        <f>data!$D$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="B20" s="14" t="str">
         <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-",""))),1,0))</f>
@@ -2110,10 +2146,10 @@
         <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G20" s="14" t="str">
-        <f>'data'!$B$5</f>
+        <f>data!$D$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="I20" s="14" t="str">
-        <f>'data'!$B$12</f>
+        <f>data!$D$12&amp;" "&amp;data!$B$12</f>
       </c>
       <c r="J20" s="14" t="str">
         <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-",""))),1,0))</f>
@@ -2129,7 +2165,7 @@
         <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O20" s="14" t="str">
-        <f>'data'!$B$11</f>
+        <f>data!$D$11&amp;" "&amp;data!$B$11</f>
       </c>
     </row>
     <row r="21">
@@ -2254,22 +2290,22 @@
     </row>
     <row r="27">
       <c r="A27" s="17" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
       <c r="D27" s="14" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E27" s="14"/>
       <c r="F27" s="14"/>
       <c r="G27" s="16" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="str">
-        <f>'data'!$B$6</f>
+        <f>data!$D$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="B28" s="14" t="str">
         <f>IF(UPPER(D29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D31)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D32)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C32," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F32," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D33)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C33," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F33," ",""),"0",""),"-",""))),1,0))</f>
@@ -2285,7 +2321,7 @@
         <f>IF(UPPER(D29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D31)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D32)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F32," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B32," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C32," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D33)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F33," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B33," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C33," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G28" s="14" t="str">
-        <f>'data'!$B$3</f>
+        <f>data!$D$3&amp;" "&amp;data!$B$3</f>
       </c>
     </row>
     <row r="29">
@@ -2355,22 +2391,22 @@
     </row>
     <row r="35">
       <c r="A35" s="17" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
       <c r="D35" s="14" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E35" s="14"/>
       <c r="F35" s="14"/>
       <c r="G35" s="16" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="str">
-        <f>'data'!$B$5</f>
+        <f>data!$D$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="B36" s="14" t="str">
         <f>IF(UPPER(D37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-",""))),1,0))</f>
@@ -2386,7 +2422,7 @@
         <f>IF(UPPER(D37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G36" s="14" t="str">
-        <f>'data'!$B$3</f>
+        <f>data!$D$3&amp;" "&amp;data!$B$3</f>
       </c>
     </row>
     <row r="37">
@@ -2456,22 +2492,22 @@
     </row>
     <row r="43">
       <c r="A43" s="17" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
       <c r="D43" s="14" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E43" s="14"/>
       <c r="F43" s="14"/>
       <c r="G43" s="16" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="14" t="str">
-        <f>'data'!$B$6</f>
+        <f>data!$D$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="B44" s="14" t="str">
         <f>IF(UPPER(D45)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D46)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D47)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-",""))),1,0))</f>
@@ -2487,7 +2523,7 @@
         <f>IF(UPPER(D45)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D46)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D47)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G44" s="14" t="str">
-        <f>'data'!$B$4</f>
+        <f>data!$D$4&amp;" "&amp;data!$B$4</f>
       </c>
     </row>
     <row r="45">
@@ -2557,43 +2593,43 @@
     </row>
     <row r="52">
       <c r="A52" s="13" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="E52" s="13"/>
       <c r="F52" s="13"/>
       <c r="G52" s="13" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="J52" s="13" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="K52" s="13" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="L52" s="13" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="M52" s="13"/>
       <c r="N52" s="13"/>
       <c r="O52" s="13" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="str">
-        <f>'data'!$B$3</f>
+        <f>data!$D$3&amp;" "&amp;data!$B$3</f>
       </c>
       <c r="B53" s="14" t="str">
         <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,D5="X",D5="x",D6="X",D6="x",D7="X",D7="x",D8="X",D8="x",D9="X",D9="x",OR(D4="X",D4="x")),IF(OR(OR(D4="X",D4="x"),AND(B4=F4,C4=E4)),0,IF(OR(F4&gt;B4,AND(F4=B4,E4&gt;C4)),1,0)),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,D29="X",D29="x",D30="X",D30="x",D31="X",D31="x",D32="X",D32="x",D33="X",D33="x",OR(D28="X",D28="x")),IF(OR(OR(D28="X",D28="x"),AND(B28=F28,C28=E28)),0,IF(OR(F28&gt;B28,AND(F28=B28,E28&gt;C28)),1,0)),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,D37="X",D37="x",D38="X",D38="x",D39="X",D39="x",D40="X",D40="x",D41="X",D41="x",OR(D36="X",D36="x")),IF(OR(OR(D36="X",D36="x"),AND(B36=F36,C36=E36)),0,IF(OR(F36&gt;B36,AND(F36=B36,E36&gt;C36)),1,0)),0)</f>
@@ -2608,7 +2644,7 @@
         <f>RANK(U53,$U$53:$U$56)+COUNTIF($U$52:U52,U53)</f>
       </c>
       <c r="I53" s="14" t="str">
-        <f>'data'!$B$10</f>
+        <f>data!$D$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="J53" s="14" t="str">
         <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,L5="X",L5="x",L6="X",L6="x",L7="X",L7="x",L8="X",L8="x",L9="X",L9="x",OR(L4="X",L4="x")),IF(OR(OR(L4="X",L4="x"),AND(J4=N4,K4=M4)),0,IF(OR(N4&gt;J4,AND(N4=J4,M4&gt;K4)),1,0)),0)+IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,L13="X",L13="x",L14="X",L14="x",L15="X",L15="x",L16="X",L16="x",L17="X",L17="x",OR(L12="X",L12="x")),IF(OR(OR(L12="X",L12="x"),AND(J12=N12,K12=M12)),0,IF(OR(N12&gt;J12,AND(N12=J12,M12&gt;K12)),1,0)),0)</f>
@@ -2631,7 +2667,7 @@
     </row>
     <row r="54">
       <c r="A54" s="14" t="str">
-        <f>'data'!$B$4</f>
+        <f>data!$D$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="B54" s="14" t="str">
         <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,D5="X",D5="x",D6="X",D6="x",D7="X",D7="x",D8="X",D8="x",D9="X",D9="x",OR(D4="X",D4="x")),IF(OR(OR(D4="X",D4="x"),AND(B4=F4,C4=E4)),0,IF(OR(B4&gt;F4,AND(B4=F4,C4&gt;E4)),1,0)),0)+IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,D13="X",D13="x",D14="X",D14="x",D15="X",D15="x",D16="X",D16="x",D17="X",D17="x",OR(D12="X",D12="x")),IF(OR(OR(D12="X",D12="x"),AND(B12=F12,C12=E12)),0,IF(OR(B12&gt;F12,AND(B12=F12,C12&gt;E12)),1,0)),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,D45="X",D45="x",D46="X",D46="x",D47="X",D47="x",D48="X",D48="x",D49="X",D49="x",OR(D44="X",D44="x")),IF(OR(OR(D44="X",D44="x"),AND(B44=F44,C44=E44)),0,IF(OR(F44&gt;B44,AND(F44=B44,E44&gt;C44)),1,0)),0)</f>
@@ -2646,7 +2682,7 @@
         <f>RANK(U54,$U$53:$U$56)+COUNTIF($U$52:U53,U54)</f>
       </c>
       <c r="I54" s="14" t="str">
-        <f>'data'!$B$11</f>
+        <f>data!$D$11&amp;" "&amp;data!$B$11</f>
       </c>
       <c r="J54" s="14" t="str">
         <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,L5="X",L5="x",L6="X",L6="x",L7="X",L7="x",L8="X",L8="x",L9="X",L9="x",OR(L4="X",L4="x")),IF(OR(OR(L4="X",L4="x"),AND(J4=N4,K4=M4)),0,IF(OR(J4&gt;N4,AND(J4=N4,K4&gt;M4)),1,0)),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,L21="X",L21="x",L22="X",L22="x",L23="X",L23="x",L24="X",L24="x",L25="X",L25="x",OR(L20="X",L20="x")),IF(OR(OR(L20="X",L20="x"),AND(J20=N20,K20=M20)),0,IF(OR(N20&gt;J20,AND(N20=J20,M20&gt;K20)),1,0)),0)</f>
@@ -2669,7 +2705,7 @@
     </row>
     <row r="55">
       <c r="A55" s="14" t="str">
-        <f>'data'!$B$5</f>
+        <f>data!$D$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="B55" s="14" t="str">
         <f>IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,D13="X",D13="x",D14="X",D14="x",D15="X",D15="x",D16="X",D16="x",D17="X",D17="x",OR(D12="X",D12="x")),IF(OR(OR(D12="X",D12="x"),AND(B12=F12,C12=E12)),0,IF(OR(F12&gt;B12,AND(F12=B12,E12&gt;C12)),1,0)),0)+IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,D21="X",D21="x",D22="X",D22="x",D23="X",D23="x",D24="X",D24="x",D25="X",D25="x",OR(D20="X",D20="x")),IF(OR(OR(D20="X",D20="x"),AND(B20=F20,C20=E20)),0,IF(OR(F20&gt;B20,AND(F20=B20,E20&gt;C20)),1,0)),0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,D37="X",D37="x",D38="X",D38="x",D39="X",D39="x",D40="X",D40="x",D41="X",D41="x",OR(D36="X",D36="x")),IF(OR(OR(D36="X",D36="x"),AND(B36=F36,C36=E36)),0,IF(OR(B36&gt;F36,AND(B36=F36,C36&gt;E36)),1,0)),0)</f>
@@ -2684,7 +2720,7 @@
         <f>RANK(U55,$U$53:$U$56)+COUNTIF($U$52:U54,U55)</f>
       </c>
       <c r="I55" s="14" t="str">
-        <f>'data'!$B$12</f>
+        <f>data!$D$12&amp;" "&amp;data!$B$12</f>
       </c>
       <c r="J55" s="14" t="str">
         <f>IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,L13="X",L13="x",L14="X",L14="x",L15="X",L15="x",L16="X",L16="x",L17="X",L17="x",OR(L12="X",L12="x")),IF(OR(OR(L12="X",L12="x"),AND(J12=N12,K12=M12)),0,IF(OR(J12&gt;N12,AND(J12=N12,K12&gt;M12)),1,0)),0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,L21="X",L21="x",L22="X",L22="x",L23="X",L23="x",L24="X",L24="x",L25="X",L25="x",OR(L20="X",L20="x")),IF(OR(OR(L20="X",L20="x"),AND(J20=N20,K20=M20)),0,IF(OR(J20&gt;N20,AND(J20=N20,K20&gt;M20)),1,0)),0)</f>
@@ -2707,7 +2743,7 @@
     </row>
     <row r="56">
       <c r="A56" s="14" t="str">
-        <f>'data'!$B$6</f>
+        <f>data!$D$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="B56" s="14" t="str">
         <f>IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,D21="X",D21="x",D22="X",D22="x",D23="X",D23="x",D24="X",D24="x",D25="X",D25="x",OR(D20="X",D20="x")),IF(OR(OR(D20="X",D20="x"),AND(B20=F20,C20=E20)),0,IF(OR(B20&gt;F20,AND(B20=F20,C20&gt;E20)),1,0)),0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,D29="X",D29="x",D30="X",D30="x",D31="X",D31="x",D32="X",D32="x",D33="X",D33="x",OR(D28="X",D28="x")),IF(OR(OR(D28="X",D28="x"),AND(B28=F28,C28=E28)),0,IF(OR(B28&gt;F28,AND(B28=F28,C28&gt;E28)),1,0)),0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,D45="X",D45="x",D46="X",D46="x",D47="X",D47="x",D48="X",D48="x",D49="X",D49="x",OR(D44="X",D44="x")),IF(OR(OR(D44="X",D44="x"),AND(B44=F44,C44=E44)),0,IF(OR(B44&gt;F44,AND(B44=F44,C44&gt;E44)),1,0)),0)</f>
@@ -2728,40 +2764,40 @@
     <row r="57">
       <c r="I57" s="13"/>
       <c r="J57" s="13" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="K57" s="13" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="L57" s="13" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="M57" s="13" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="N57" s="13" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="13"/>
       <c r="B58" s="13" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="I58" s="14" t="str">
-        <f>'data'!$B$10</f>
+        <f>data!$D$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="J58" s="14" t="str">
         <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x"),UPPER(L5)="X",UPPER(L6)="X",UPPER(L7)="X",UPPER(L8)="X",UPPER(L9)="X"),N4,0)+IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x"),UPPER(L13)="X",UPPER(L14)="X",UPPER(L15)="X",UPPER(L16)="X",UPPER(L17)="X"),N12,0)</f>
@@ -2781,7 +2817,7 @@
     </row>
     <row r="59">
       <c r="A59" s="14" t="str">
-        <f>'data'!$B$3</f>
+        <f>data!$D$3&amp;" "&amp;data!$B$3</f>
       </c>
       <c r="B59" s="14" t="str">
         <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x"),UPPER(D5)="X",UPPER(D6)="X",UPPER(D7)="X",UPPER(D8)="X",UPPER(D9)="X"),F4,0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x"),UPPER(D29)="X",UPPER(D30)="X",UPPER(D31)="X",UPPER(D32)="X",UPPER(D33)="X"),F28,0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x"),UPPER(D37)="X",UPPER(D38)="X",UPPER(D39)="X",UPPER(D40)="X",UPPER(D41)="X"),F36,0)</f>
@@ -2799,7 +2835,7 @@
         <f>C4+C28+C36</f>
       </c>
       <c r="I59" s="14" t="str">
-        <f>'data'!$B$11</f>
+        <f>data!$D$11&amp;" "&amp;data!$B$11</f>
       </c>
       <c r="J59" s="14" t="str">
         <f>IF(OR(COUNTA(J5:K9,M5:N9)&gt;0,OR(L4="X",L4="x"),UPPER(L5)="X",UPPER(L6)="X",UPPER(L7)="X",UPPER(L8)="X",UPPER(L9)="X"),J4,0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x"),UPPER(L21)="X",UPPER(L22)="X",UPPER(L23)="X",UPPER(L24)="X",UPPER(L25)="X"),N20,0)</f>
@@ -2819,7 +2855,7 @@
     </row>
     <row r="60">
       <c r="A60" s="14" t="str">
-        <f>'data'!$B$4</f>
+        <f>data!$D$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="B60" s="14" t="str">
         <f>IF(OR(COUNTA(B5:C9,E5:F9)&gt;0,OR(D4="X",D4="x"),UPPER(D5)="X",UPPER(D6)="X",UPPER(D7)="X",UPPER(D8)="X",UPPER(D9)="X"),B4,0)+IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x"),UPPER(D13)="X",UPPER(D14)="X",UPPER(D15)="X",UPPER(D16)="X",UPPER(D17)="X"),B12,0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x"),UPPER(D45)="X",UPPER(D46)="X",UPPER(D47)="X",UPPER(D48)="X",UPPER(D49)="X"),F44,0)</f>
@@ -2837,7 +2873,7 @@
         <f>E4+E12+C44</f>
       </c>
       <c r="I60" s="14" t="str">
-        <f>'data'!$B$12</f>
+        <f>data!$D$12&amp;" "&amp;data!$B$12</f>
       </c>
       <c r="J60" s="14" t="str">
         <f>IF(OR(COUNTA(J13:K17,M13:N17)&gt;0,OR(L12="X",L12="x"),UPPER(L13)="X",UPPER(L14)="X",UPPER(L15)="X",UPPER(L16)="X",UPPER(L17)="X"),J12,0)+IF(OR(COUNTA(J21:K25,M21:N25)&gt;0,OR(L20="X",L20="x"),UPPER(L21)="X",UPPER(L22)="X",UPPER(L23)="X",UPPER(L24)="X",UPPER(L25)="X"),J20,0)</f>
@@ -2857,7 +2893,7 @@
     </row>
     <row r="61">
       <c r="A61" s="14" t="str">
-        <f>'data'!$B$5</f>
+        <f>data!$D$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="B61" s="14" t="str">
         <f>IF(OR(COUNTA(B13:C17,E13:F17)&gt;0,OR(D12="X",D12="x"),UPPER(D13)="X",UPPER(D14)="X",UPPER(D15)="X",UPPER(D16)="X",UPPER(D17)="X"),F12,0)+IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x"),UPPER(D21)="X",UPPER(D22)="X",UPPER(D23)="X",UPPER(D24)="X",UPPER(D25)="X"),F20,0)+IF(OR(COUNTA(B37:C41,E37:F41)&gt;0,OR(D36="X",D36="x"),UPPER(D37)="X",UPPER(D38)="X",UPPER(D39)="X",UPPER(D40)="X",UPPER(D41)="X"),B36,0)</f>
@@ -2877,7 +2913,7 @@
     </row>
     <row r="62">
       <c r="A62" s="14" t="str">
-        <f>'data'!$B$6</f>
+        <f>data!$D$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="B62" s="14" t="str">
         <f>IF(OR(COUNTA(B21:C25,E21:F25)&gt;0,OR(D20="X",D20="x"),UPPER(D21)="X",UPPER(D22)="X",UPPER(D23)="X",UPPER(D24)="X",UPPER(D25)="X"),B20,0)+IF(OR(COUNTA(B29:C33,E29:F33)&gt;0,OR(D28="X",D28="x"),UPPER(D29)="X",UPPER(D30)="X",UPPER(D31)="X",UPPER(D32)="X",UPPER(D33)="X"),B28,0)+IF(OR(COUNTA(B45:C49,E45:F49)&gt;0,OR(D44="X",D44="x"),UPPER(D45)="X",UPPER(D46)="X",UPPER(D47)="X",UPPER(D48)="X",UPPER(D49)="X"),B44,0)</f>
@@ -2898,12 +2934,12 @@
     <row r="63">
       <c r="N63" s="13"/>
       <c r="O63" s="13" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="64">
       <c r="N64" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="O64" s="19" t="str">
         <f>IFERROR(INDEX($I$53:$I$60, MATCH(1, $O$53:$O$60, 0)), "-")</f>
@@ -2912,10 +2948,10 @@
     <row r="65">
       <c r="F65" s="13"/>
       <c r="G65" s="13" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="N65" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="O65" s="19" t="str">
         <f>IFERROR(INDEX($I$53:$I$60, MATCH(2, $O$53:$O$60, 0)), "-")</f>
@@ -2923,13 +2959,13 @@
     </row>
     <row r="66">
       <c r="F66" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="G66" s="19" t="str">
         <f>IFERROR(INDEX($A$53:$A$62, MATCH(1, $G$53:$G$62, 0)), "-")</f>
       </c>
       <c r="N66" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="O66" s="19" t="str">
         <f>IFERROR(INDEX($I$53:$I$60, MATCH(3, $O$53:$O$60, 0)), "-")</f>
@@ -2937,7 +2973,7 @@
     </row>
     <row r="67">
       <c r="F67" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G67" s="19" t="str">
         <f>IFERROR(INDEX($A$53:$A$62, MATCH(2, $G$53:$G$62, 0)), "-")</f>
@@ -2945,7 +2981,7 @@
     </row>
     <row r="68">
       <c r="F68" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="G68" s="19" t="str">
         <f>IFERROR(INDEX($A$53:$A$62, MATCH(3, $G$53:$G$62, 0)), "-")</f>
@@ -2964,22 +3000,22 @@
     </row>
     <row r="70">
       <c r="A70" s="17" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
       <c r="D70" s="14" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E70" s="14"/>
       <c r="F70" s="14"/>
       <c r="G70" s="16" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="14" t="str">
-        <f>'data'!$B$8</f>
+        <f>data!$D$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="B71" s="14" t="str">
         <f>IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-",""))),1,0))</f>
@@ -2995,7 +3031,7 @@
         <f>IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G71" s="14" t="str">
-        <f>'data'!$B$7</f>
+        <f>data!$D$7&amp;" "&amp;data!$B$7</f>
       </c>
     </row>
     <row r="72">
@@ -3065,22 +3101,22 @@
     </row>
     <row r="78">
       <c r="A78" s="17" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
       <c r="D78" s="14" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E78" s="14"/>
       <c r="F78" s="14"/>
       <c r="G78" s="16" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="14" t="str">
-        <f>'data'!$B$9</f>
+        <f>data!$D$9&amp;" "&amp;data!$B$9</f>
       </c>
       <c r="B79" s="14" t="str">
         <f>IF(UPPER(D80)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D81)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D82)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C82," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F82," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D83)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C83," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F83," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D84)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C84," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F84," ",""),"0",""),"-",""))),1,0))</f>
@@ -3096,7 +3132,7 @@
         <f>IF(UPPER(D80)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F80," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B80," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C80," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D81)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F81," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B81," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C81," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D82)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F82," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B82," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C82," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D83)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F83," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B83," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C83," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D84)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F84," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B84," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C84," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G79" s="14" t="str">
-        <f>'data'!$B$7</f>
+        <f>data!$D$7&amp;" "&amp;data!$B$7</f>
       </c>
     </row>
     <row r="80">
@@ -3166,22 +3202,22 @@
     </row>
     <row r="86">
       <c r="A86" s="17" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
       <c r="D86" s="14" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E86" s="14"/>
       <c r="F86" s="14"/>
       <c r="G86" s="16" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="14" t="str">
-        <f>'data'!$B$9</f>
+        <f>data!$D$9&amp;" "&amp;data!$B$9</f>
       </c>
       <c r="B87" s="14" t="str">
         <f>IF(UPPER(D88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D90)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))),1,0))</f>
@@ -3197,7 +3233,7 @@
         <f>IF(UPPER(D88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D90)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G87" s="14" t="str">
-        <f>'data'!$B$8</f>
+        <f>data!$D$8&amp;" "&amp;data!$B$8</f>
       </c>
     </row>
     <row r="88">
@@ -3267,26 +3303,26 @@
     </row>
     <row r="95">
       <c r="A95" s="13" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D95" s="13" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="E95" s="13"/>
       <c r="F95" s="13"/>
       <c r="G95" s="13" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="str">
-        <f>'data'!$B$7</f>
+        <f>data!$D$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="B96" s="14" t="str">
         <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,D72="X",D72="x",D73="X",D73="x",D74="X",D74="x",D75="X",D75="x",D76="X",D76="x",OR(D71="X",D71="x")),IF(OR(OR(D71="X",D71="x"),AND(B71=F71,C71=E71)),0,IF(OR(F71&gt;B71,AND(F71=B71,E71&gt;C71)),1,0)),0)+IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,D80="X",D80="x",D81="X",D81="x",D82="X",D82="x",D83="X",D83="x",D84="X",D84="x",OR(D79="X",D79="x")),IF(OR(OR(D79="X",D79="x"),AND(B79=F79,C79=E79)),0,IF(OR(F79&gt;B79,AND(F79=B79,E79&gt;C79)),1,0)),0)</f>
@@ -3306,7 +3342,7 @@
     </row>
     <row r="97">
       <c r="A97" s="14" t="str">
-        <f>'data'!$B$8</f>
+        <f>data!$D$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="B97" s="14" t="str">
         <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,D72="X",D72="x",D73="X",D73="x",D74="X",D74="x",D75="X",D75="x",D76="X",D76="x",OR(D71="X",D71="x")),IF(OR(OR(D71="X",D71="x"),AND(B71=F71,C71=E71)),0,IF(OR(B71&gt;F71,AND(B71=F71,C71&gt;E71)),1,0)),0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,D88="X",D88="x",D89="X",D89="x",D90="X",D90="x",D91="X",D91="x",D92="X",D92="x",OR(D87="X",D87="x")),IF(OR(OR(D87="X",D87="x"),AND(B87=F87,C87=E87)),0,IF(OR(F87&gt;B87,AND(F87=B87,E87&gt;C87)),1,0)),0)</f>
@@ -3326,7 +3362,7 @@
     </row>
     <row r="98">
       <c r="A98" s="14" t="str">
-        <f>'data'!$B$9</f>
+        <f>data!$D$9&amp;" "&amp;data!$B$9</f>
       </c>
       <c r="B98" s="14" t="str">
         <f>IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,D80="X",D80="x",D81="X",D81="x",D82="X",D82="x",D83="X",D83="x",D84="X",D84="x",OR(D79="X",D79="x")),IF(OR(OR(D79="X",D79="x"),AND(B79=F79,C79=E79)),0,IF(OR(B79&gt;F79,AND(B79=F79,C79&gt;E79)),1,0)),0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,D88="X",D88="x",D89="X",D89="x",D90="X",D90="x",D91="X",D91="x",D92="X",D92="x",OR(D87="X",D87="x")),IF(OR(OR(D87="X",D87="x"),AND(B87=F87,C87=E87)),0,IF(OR(B87&gt;F87,AND(B87=F87,C87&gt;E87)),1,0)),0)</f>
@@ -3347,24 +3383,24 @@
     <row r="100">
       <c r="A100" s="13"/>
       <c r="B100" s="13" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D100" s="13" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F100" s="13" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="14" t="str">
-        <f>'data'!$B$7</f>
+        <f>data!$D$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="B101" s="14" t="str">
         <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,OR(D71="X",D71="x"),UPPER(D72)="X",UPPER(D73)="X",UPPER(D74)="X",UPPER(D75)="X",UPPER(D76)="X"),F71,0)+IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,OR(D79="X",D79="x"),UPPER(D80)="X",UPPER(D81)="X",UPPER(D82)="X",UPPER(D83)="X",UPPER(D84)="X"),F79,0)</f>
@@ -3384,7 +3420,7 @@
     </row>
     <row r="102">
       <c r="A102" s="14" t="str">
-        <f>'data'!$B$8</f>
+        <f>data!$D$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="B102" s="14" t="str">
         <f>IF(OR(COUNTA(B72:C76,E72:F76)&gt;0,OR(D71="X",D71="x"),UPPER(D72)="X",UPPER(D73)="X",UPPER(D74)="X",UPPER(D75)="X",UPPER(D76)="X"),B71,0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,OR(D87="X",D87="x"),UPPER(D88)="X",UPPER(D89)="X",UPPER(D90)="X",UPPER(D91)="X",UPPER(D92)="X"),F87,0)</f>
@@ -3404,7 +3440,7 @@
     </row>
     <row r="103">
       <c r="A103" s="14" t="str">
-        <f>'data'!$B$9</f>
+        <f>data!$D$9&amp;" "&amp;data!$B$9</f>
       </c>
       <c r="B103" s="14" t="str">
         <f>IF(OR(COUNTA(B80:C84,E80:F84)&gt;0,OR(D79="X",D79="x"),UPPER(D80)="X",UPPER(D81)="X",UPPER(D82)="X",UPPER(D83)="X",UPPER(D84)="X"),B79,0)+IF(OR(COUNTA(B88:C92,E88:F92)&gt;0,OR(D87="X",D87="x"),UPPER(D88)="X",UPPER(D89)="X",UPPER(D90)="X",UPPER(D91)="X",UPPER(D92)="X"),B87,0)</f>
@@ -3425,12 +3461,12 @@
     <row r="106">
       <c r="F106" s="13"/>
       <c r="G106" s="13" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="107">
       <c r="F107" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="G107" s="19" t="str">
         <f>IFERROR(INDEX($A$96:$A$103, MATCH(1, $G$96:$G$103, 0)), "-")</f>
@@ -3438,7 +3474,7 @@
     </row>
     <row r="108">
       <c r="F108" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G108" s="19" t="str">
         <f>IFERROR(INDEX($A$96:$A$103, MATCH(2, $G$96:$G$103, 0)), "-")</f>
@@ -3446,7 +3482,7 @@
     </row>
     <row r="109">
       <c r="F109" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="G109" s="19" t="str">
         <f>IFERROR(INDEX($A$96:$A$103, MATCH(3, $G$96:$G$103, 0)), "-")</f>
@@ -3495,7 +3531,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -3504,7 +3540,7 @@
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
       <c r="I1" s="13" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
@@ -3515,7 +3551,7 @@
     </row>
     <row r="2">
       <c r="A2" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -3524,7 +3560,7 @@
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
       <c r="I2" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
@@ -3535,22 +3571,22 @@
     </row>
     <row r="3">
       <c r="A3" s="17" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
@@ -3702,17 +3738,17 @@
         <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O65)</f>
       </c>
       <c r="B11" s="14" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D11" s="14"/>
       <c r="E11" s="14" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="G11" s="14" t="str">
         <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G107)</f>
@@ -3721,17 +3757,17 @@
         <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G108)</f>
       </c>
       <c r="J11" s="14" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="L11" s="14"/>
       <c r="M11" s="14" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="N11" s="14" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="O11" s="14" t="str">
         <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G67)</f>
@@ -3739,7 +3775,7 @@
     </row>
     <row r="12">
       <c r="A12" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B12" s="14" t="str">
         <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-",""))),1,0))</f>
@@ -3755,10 +3791,10 @@
         <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G12" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J12" s="14" t="str">
         <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-",""))),1,0))</f>
@@ -3774,32 +3810,32 @@
         <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O12" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
       <c r="F15" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="G15" s="19"/>
       <c r="N15" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="O15" s="19"/>
     </row>
     <row r="16">
       <c r="F16" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G16" s="19"/>
       <c r="N16" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="O16" s="19"/>
     </row>
     <row r="23">
       <c r="A23" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -3808,7 +3844,7 @@
       <c r="F23" s="13"/>
       <c r="G23" s="13"/>
       <c r="I23" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J23" s="13"/>
       <c r="K23" s="13"/>
@@ -3819,22 +3855,22 @@
     </row>
     <row r="24">
       <c r="A24" s="17" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="L24" s="14" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="O24" s="16" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25">
@@ -3986,17 +4022,17 @@
         <f>CONCATENATE("M 1 ",G15)</f>
       </c>
       <c r="B32" s="14" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="G32" s="14" t="str">
         <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G66)</f>
@@ -4005,17 +4041,17 @@
         <f>CONCATENATE("M 2 ",O15)</f>
       </c>
       <c r="J32" s="14" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="L32" s="14"/>
       <c r="M32" s="14" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="N32" s="14" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="O32" s="14" t="str">
         <f>CONCATENATE("Pool C-1st ",'Pool Matches'!O64)</f>
@@ -4023,7 +4059,7 @@
     </row>
     <row r="33">
       <c r="A33" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B33" s="14" t="str">
         <f>IF(UPPER(D26)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C26," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F26," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D27)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C27," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D28)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C28," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-",""))),1,0))</f>
@@ -4039,10 +4075,10 @@
         <f>IF(UPPER(D26)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F26," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C26," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D27)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C27," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D28)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C28," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G33" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J33" s="14" t="str">
         <f>IF(UPPER(L26)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K26," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N26," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L27)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K27," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N27," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L28)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K28," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N28," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K29," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N29," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N30," ",""),"0",""),"-",""))),1,0))</f>
@@ -4058,32 +4094,32 @@
         <f>IF(UPPER(L26)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N26," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J26," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K26," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L27)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N27," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K27," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L28)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N28," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K28," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L29)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N29," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K29," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L30)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N30," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K30," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O33" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36">
       <c r="F36" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="G36" s="19"/>
       <c r="N36" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="O36" s="19"/>
     </row>
     <row r="37">
       <c r="F37" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G37" s="19"/>
       <c r="N37" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="O37" s="19"/>
     </row>
     <row r="44">
       <c r="A44" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
@@ -4094,13 +4130,13 @@
     </row>
     <row r="45">
       <c r="A45" s="17" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46">
@@ -4186,17 +4222,17 @@
         <f>CONCATENATE("M 4 ",O36)</f>
       </c>
       <c r="B53" s="14" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D53" s="14"/>
       <c r="E53" s="14" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="G53" s="14" t="str">
         <f>CONCATENATE("M 3 ",G36)</f>
@@ -4204,7 +4240,7 @@
     </row>
     <row r="54">
       <c r="A54" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B54" s="14" t="str">
         <f>IF(UPPER(D47)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D51)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-",""))),1,0))</f>
@@ -4220,18 +4256,18 @@
         <f>IF(UPPER(D47)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F47," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B47," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C47," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D51)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G54" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="57">
       <c r="F57" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="G57" s="19"/>
     </row>
     <row r="58">
       <c r="F58" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G58" s="19"/>
     </row>
@@ -4289,12 +4325,12 @@
     </row>
     <row r="5">
       <c r="A5" s="25" t="str">
-        <f>"1. " &amp; data!$B$3</f>
+        <f>data!$D$3&amp;" "&amp;data!$B$3</f>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="str">
-        <f>"2. " &amp; data!$B$4</f>
+        <f>data!$D$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="C6" s="23"/>
       <c r="D6" s="23"/>
@@ -4304,14 +4340,14 @@
     </row>
     <row r="7">
       <c r="A7" s="26" t="str">
-        <f>"3. " &amp; data!$B$5</f>
+        <f>data!$D$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="F7" s="22"/>
       <c r="G7" s="20"/>
     </row>
     <row r="8">
       <c r="A8" s="27" t="str">
-        <f>"4. " &amp; data!$B$6</f>
+        <f>data!$D$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="G8" s="21">
         <v>3</v>
@@ -4337,7 +4373,7 @@
     </row>
     <row r="11">
       <c r="A11" s="25" t="str">
-        <f>"1. " &amp; data!$B$7</f>
+        <f>data!$D$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="C11" s="23" t="str">
         <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!O65)</f>
@@ -4347,12 +4383,12 @@
     </row>
     <row r="12">
       <c r="A12" s="26" t="str">
-        <f>"2. " &amp; data!$B$8</f>
+        <f>data!$D$8&amp;" "&amp;data!$B$8</f>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="27" t="str">
-        <f>"3. " &amp; data!$B$9</f>
+        <f>data!$D$9&amp;" "&amp;data!$B$9</f>
       </c>
     </row>
     <row r="14">
@@ -4400,12 +4436,12 @@
     </row>
     <row r="5">
       <c r="A5" s="25" t="str">
-        <f>"1. " &amp; data!$B$10</f>
+        <f>data!$D$10&amp;" "&amp;data!$B$10</f>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="str">
-        <f>"2. " &amp; data!$B$11</f>
+        <f>data!$D$11&amp;" "&amp;data!$B$11</f>
       </c>
       <c r="C6" s="23"/>
       <c r="D6" s="23"/>
@@ -4415,7 +4451,7 @@
     </row>
     <row r="7">
       <c r="A7" s="27" t="str">
-        <f>"3. " &amp; data!$B$12</f>
+        <f>data!$D$12&amp;" "&amp;data!$B$12</f>
       </c>
       <c r="F7" s="22"/>
       <c r="G7" s="20"/>

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -25,6 +25,7 @@
     <definedName localSheetId="6" name="_xlnm.Print_Area">'Tree 2'!$A$1:$G$11</definedName>
     <definedName localSheetId="7" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$7</definedName>
     <definedName localSheetId="8" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$3</definedName>
+    <definedName localSheetId="9" name="_xlnm.Print_Area">'Tags'!$A$1:$A$20</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$P$64</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
@@ -572,13 +573,13 @@
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
@@ -1161,7 +1162,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="110"/>
+    <col customWidth="true" max="1" min="1" width="88"/>
   </cols>
   <sheetData>
     <row r="1" ht="409" customHeight="true">

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -576,7 +576,7 @@
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
@@ -1043,8 +1043,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="2" min="2" width="160"/>
+    <col customWidth="true" max="1" min="1" width="40"/>
+    <col customWidth="true" max="2" min="2" width="140"/>
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
@@ -1119,8 +1119,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="2" min="2" width="160"/>
+    <col customWidth="true" max="1" min="1" width="40"/>
+    <col customWidth="true" max="2" min="2" width="140"/>
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">

--- a/pools-example-small.xlsx
+++ b/pools-example-small.xlsx
@@ -579,7 +579,7 @@
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
